--- a/docs/bongi-calculator-data.xlsx
+++ b/docs/bongi-calculator-data.xlsx
@@ -24,8 +24,9 @@
     <sheet name="15_LGU_Together" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="30_CALC_Formula" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="31_CALC_Example_SKT" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="32_CALC_Example_KT_Premium" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="20_Schema" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="31b_CALC_Example_KT_Total" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="32_CALC_Example_KT_Premium" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="20_Schema" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -35,7 +36,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -130,6 +131,12 @@
       <sz val="10"/>
     </font>
     <font>
+      <name val="Noto Sans KR"/>
+      <b val="1"/>
+      <color rgb="00dc2626"/>
+      <sz val="13"/>
+    </font>
+    <font>
       <name val="SF Mono"/>
       <sz val="10"/>
     </font>
@@ -219,7 +226,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -257,27 +264,30 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -2475,7 +2485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2653,304 +2663,354 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="25" t="inlineStr">
+        <is>
+          <t>⚠️ 핵심 주의사항 — 3사 결합할인 적용 방식 다름</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="26" t="inlineStr">
+        <is>
+          <t>• SKT 요즘가족결합: 단독가 **REPLACE** (요즘우리집 대체) → tvInternetNoWifi 무시</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="26" t="inlineStr">
+        <is>
+          <t>• KT 총액/정액: 기본 TV결합할인 + 총액할인 **STACK** (중복 적용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="26" t="inlineStr">
+        <is>
+          <t>• KT 프리미엄: 총액대상(대표자+77K미만) + 프리미엄대상(77K↑) 독립 계산</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="26" t="inlineStr">
+        <is>
+          <t>• LG U+ 참쉬운: 단독가 **REPLACE** (SKT와 유사)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="26" t="inlineStr">
+        <is>
+          <t>• LG U+ 투게더: 단독가 **REPLACE** (85K↑ 고가요금제 한정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>🏷️ 결합할인 계산 — 통신사별 분기</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>통신사</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>결합 종류</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>계산 공식</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="25" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="27" t="inlineStr">
         <is>
           <t>SKT</t>
         </is>
       </c>
-      <c r="B23" s="25" t="inlineStr">
+      <c r="B31" s="27" t="inlineStr">
         <is>
           <t>요즘가족결합</t>
         </is>
       </c>
-      <c r="C23" s="26" t="inlineStr">
+      <c r="C31" s="28" t="inlineStr">
         <is>
           <t>inetDc = D.skt.bundle.family.internet[sp]</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="24" t="inlineStr"/>
-      <c r="B24" s="24" t="inlineStr"/>
-      <c r="C24" s="27" t="inlineStr">
-        <is>
-          <t>iptvDc = hasTv ? D.skt.bundle.family.iptv : 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="24" t="inlineStr"/>
-      <c r="B25" s="24" t="inlineStr"/>
-      <c r="C25" s="27" t="inlineStr">
-        <is>
-          <t>mobPer = D.skt.bundle.family.mobilePerBySpeed[sp][lines]</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="24" t="inlineStr"/>
-      <c r="B26" s="24" t="inlineStr"/>
-      <c r="C26" s="27" t="inlineStr">
-        <is>
-          <t>mobTotal = mobPer × lines  ← 인당 × 인원</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="24" t="inlineStr"/>
-      <c r="B27" s="24" t="inlineStr"/>
-      <c r="C27" s="27" t="inlineStr">
-        <is>
-          <t>bundleDc = inetDc + iptvDc (인터넷/TV 할인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="24" t="inlineStr"/>
-      <c r="B28" s="24" t="inlineStr"/>
-      <c r="C28" s="27" t="inlineStr">
-        <is>
-          <t>mobileSideDiscount = mobTotal (휴대폰 고지서에서 별도 차감)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="28" t="inlineStr">
-        <is>
-          <t>KT</t>
-        </is>
-      </c>
-      <c r="B29" s="28" t="inlineStr">
-        <is>
-          <t>총액결합 (total)</t>
-        </is>
-      </c>
-      <c r="C29" s="29" t="inlineStr">
-        <is>
-          <t>rngIdx = 합산_요금_구간 (6단계)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="24" t="inlineStr"/>
-      <c r="B30" s="24" t="inlineStr"/>
-      <c r="C30" s="27" t="inlineStr">
-        <is>
-          <t>inetDc = D.kt.bundle.total.internet[sp][rngIdx]</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="24" t="inlineStr"/>
-      <c r="B31" s="24" t="inlineStr"/>
-      <c r="C31" s="27" t="inlineStr">
-        <is>
-          <t>mobDc = D.kt.bundle.total.mobile[sp][rngIdx]</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="24" t="inlineStr"/>
       <c r="B32" s="24" t="inlineStr"/>
-      <c r="C32" s="27" t="inlineStr">
-        <is>
-          <t>bundleDc = inetDc (인터넷 할인 · 기본 TV결합할인과 중복 적용)</t>
+      <c r="C32" s="29" t="inlineStr">
+        <is>
+          <t>iptvDc = hasTv ? D.skt.bundle.family.iptv : 0</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="24" t="inlineStr"/>
       <c r="B33" s="24" t="inlineStr"/>
-      <c r="C33" s="27" t="inlineStr">
-        <is>
-          <t>mobileSideDiscount = mobDc</t>
+      <c r="C33" s="29" t="inlineStr">
+        <is>
+          <t>mobPer = D.skt.bundle.family.mobilePerBySpeed[sp][lines]</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="28" t="inlineStr">
-        <is>
-          <t>KT</t>
-        </is>
-      </c>
-      <c r="B34" s="28" t="inlineStr">
-        <is>
-          <t>정액결합 (fixed)</t>
-        </is>
-      </c>
+      <c r="A34" s="24" t="inlineStr"/>
+      <c r="B34" s="24" t="inlineStr"/>
       <c r="C34" s="29" t="inlineStr">
         <is>
-          <t>fxIdx = 요금_구간 (4단계)</t>
+          <t>mobTotal = mobPer × lines  ← 인당 × 인원</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="24" t="inlineStr"/>
       <c r="B35" s="24" t="inlineStr"/>
-      <c r="C35" s="27" t="inlineStr">
-        <is>
-          <t>inetDc = D.kt.bundle.fixed.internet[fxIdx]  (전구간 5,500)</t>
+      <c r="C35" s="29" t="inlineStr">
+        <is>
+          <t>bundleDc = inetDc + iptvDc (인터넷/TV 할인)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="24" t="inlineStr"/>
       <c r="B36" s="24" t="inlineStr"/>
-      <c r="C36" s="27" t="inlineStr">
-        <is>
-          <t>mobDc = D.kt.bundle.fixed.mobile[fxIdx]</t>
+      <c r="C36" s="29" t="inlineStr">
+        <is>
+          <t>mobileSideDiscount = mobTotal (휴대폰 고지서에서 별도 차감)</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="28" t="inlineStr">
+      <c r="A37" s="30" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
       </c>
-      <c r="B37" s="28" t="inlineStr">
-        <is>
-          <t>💎 프리미엄 가족결합</t>
-        </is>
-      </c>
-      <c r="C37" s="29" t="inlineStr">
-        <is>
-          <t>자격: 77K↑ 요금제 2회선 이상</t>
+      <c r="B37" s="30" t="inlineStr">
+        <is>
+          <t>총액결합 (total)</t>
+        </is>
+      </c>
+      <c r="C37" s="31" t="inlineStr">
+        <is>
+          <t>rngIdx = 합산_요금_구간 (6단계)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="24" t="inlineStr"/>
       <c r="B38" s="24" t="inlineStr"/>
-      <c r="C38" s="27" t="inlineStr">
-        <is>
-          <t>대표자 + 77K미만 구성원 → 총액결합 합산 → 구간 mobDc</t>
+      <c r="C38" s="29" t="inlineStr">
+        <is>
+          <t>inetDc = D.kt.bundle.total.internet[sp][rngIdx]</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="24" t="inlineStr"/>
       <c r="B39" s="24" t="inlineStr"/>
-      <c r="C39" s="27" t="inlineStr">
-        <is>
-          <t>77K↑ 구성원(대표자 제외) → 각각 D.kt.bundle.premium.planCatalog[plan].dc 합산</t>
+      <c r="C39" s="29" t="inlineStr">
+        <is>
+          <t>mobDc = D.kt.bundle.total.mobile[sp][rngIdx]</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="24" t="inlineStr"/>
       <c r="B40" s="24" t="inlineStr"/>
-      <c r="C40" s="27" t="inlineStr">
-        <is>
-          <t>totalDc = 5500 (인터넷 고정) + 총액결합mobDc + 프리미엄dc 합</t>
+      <c r="C40" s="29" t="inlineStr">
+        <is>
+          <t>bundleDc = inetDc (인터넷 할인 · 기본 TV결합할인과 중복 적용)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="30" t="inlineStr">
-        <is>
-          <t>LG U+</t>
-        </is>
-      </c>
-      <c r="B41" s="30" t="inlineStr">
-        <is>
-          <t>참쉬운가족결합</t>
-        </is>
-      </c>
-      <c r="C41" s="31" t="inlineStr">
-        <is>
-          <t>inetDc = D.lgu.bundle.chweyswun.internet[sp]</t>
+      <c r="A41" s="24" t="inlineStr"/>
+      <c r="B41" s="24" t="inlineStr"/>
+      <c r="C41" s="29" t="inlineStr">
+        <is>
+          <t>mobileSideDiscount = mobDc</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="24" t="inlineStr"/>
-      <c r="B42" s="24" t="inlineStr"/>
-      <c r="C42" s="27" t="inlineStr">
-        <is>
-          <t>planIdx = 요금제_구간 (3단계: 69K미만/69K↑/88K↑)</t>
+      <c r="A42" s="30" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="B42" s="30" t="inlineStr">
+        <is>
+          <t>정액결합 (fixed)</t>
+        </is>
+      </c>
+      <c r="C42" s="31" t="inlineStr">
+        <is>
+          <t>fxIdx = 요금_구간 (4단계)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="24" t="inlineStr"/>
       <c r="B43" s="24" t="inlineStr"/>
-      <c r="C43" s="27" t="inlineStr">
-        <is>
-          <t>lineIdx = min(lines,4) - 2  ← 2회선:0, 3회선:1, 4+:2</t>
+      <c r="C43" s="29" t="inlineStr">
+        <is>
+          <t>inetDc = D.kt.bundle.fixed.internet[fxIdx]  (전구간 5,500)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="24" t="inlineStr"/>
       <c r="B44" s="24" t="inlineStr"/>
-      <c r="C44" s="27" t="inlineStr">
-        <is>
-          <t>mobDc = D.lgu.bundle.chweyswun.mobile[planIdx][lineIdx]</t>
+      <c r="C44" s="29" t="inlineStr">
+        <is>
+          <t>mobDc = D.kt.bundle.fixed.mobile[fxIdx]</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="30" t="inlineStr">
         <is>
-          <t>LG U+</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="B45" s="30" t="inlineStr">
         <is>
-          <t>투게더 결합</t>
+          <t>💎 프리미엄 가족결합</t>
         </is>
       </c>
       <c r="C45" s="31" t="inlineStr">
         <is>
-          <t>자격: 85K↑ 고가요금제 (100M 결합 불가)</t>
+          <t>자격: 77K↑ 요금제 2회선 이상</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="24" t="inlineStr"/>
       <c r="B46" s="24" t="inlineStr"/>
-      <c r="C46" s="27" t="inlineStr">
-        <is>
-          <t>inetDc = D.lgu.bundle.together.internet[sp]  (100M=0)</t>
+      <c r="C46" s="29" t="inlineStr">
+        <is>
+          <t>대표자 + 77K미만 구성원 → 총액결합 합산 → 구간 mobDc</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="24" t="inlineStr"/>
       <c r="B47" s="24" t="inlineStr"/>
-      <c r="C47" s="27" t="inlineStr">
+      <c r="C47" s="29" t="inlineStr">
+        <is>
+          <t>77K↑ 구성원(대표자 제외) → 각각 D.kt.bundle.premium.planCatalog[plan].dc 합산</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="24" t="inlineStr"/>
+      <c r="B48" s="24" t="inlineStr"/>
+      <c r="C48" s="29" t="inlineStr">
+        <is>
+          <t>totalDc = 5500 (인터넷 고정) + 총액결합mobDc + 프리미엄dc 합</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="32" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="B49" s="32" t="inlineStr">
+        <is>
+          <t>참쉬운가족결합</t>
+        </is>
+      </c>
+      <c r="C49" s="33" t="inlineStr">
+        <is>
+          <t>inetDc = D.lgu.bundle.chweyswun.internet[sp]</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="24" t="inlineStr"/>
+      <c r="B50" s="24" t="inlineStr"/>
+      <c r="C50" s="29" t="inlineStr">
+        <is>
+          <t>planIdx = 요금제_구간 (3단계: 69K미만/69K↑/88K↑)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="24" t="inlineStr"/>
+      <c r="B51" s="24" t="inlineStr"/>
+      <c r="C51" s="29" t="inlineStr">
+        <is>
+          <t>lineIdx = min(lines,4) - 2  ← 2회선:0, 3회선:1, 4+:2</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="24" t="inlineStr"/>
+      <c r="B52" s="24" t="inlineStr"/>
+      <c r="C52" s="29" t="inlineStr">
+        <is>
+          <t>mobDc = D.lgu.bundle.chweyswun.mobile[planIdx][lineIdx]</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="32" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="B53" s="32" t="inlineStr">
+        <is>
+          <t>투게더 결합</t>
+        </is>
+      </c>
+      <c r="C53" s="33" t="inlineStr">
+        <is>
+          <t>자격: 85K↑ 고가요금제 (100M 결합 불가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="24" t="inlineStr"/>
+      <c r="B54" s="24" t="inlineStr"/>
+      <c r="C54" s="29" t="inlineStr">
+        <is>
+          <t>inetDc = D.lgu.bundle.together.internet[sp]  (100M=0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="24" t="inlineStr"/>
+      <c r="B55" s="24" t="inlineStr"/>
+      <c r="C55" s="29" t="inlineStr">
         <is>
           <t>mobDc = D.lgu.bundle.together.mobile[lineIdx]</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A22:B22"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2961,7 +3021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2977,355 +3037,507 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="32" t="inlineStr">
+      <c r="A3" s="34" t="inlineStr">
         <is>
           <t>입력값</t>
         </is>
       </c>
-      <c r="B3" s="27" t="inlineStr"/>
-      <c r="C3" s="33" t="inlineStr"/>
+      <c r="B3" s="29" t="inlineStr"/>
+      <c r="C3" s="35" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="34" t="inlineStr">
+      <c r="A4" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">  통신사</t>
         </is>
       </c>
-      <c r="B4" s="27" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>SKT</t>
         </is>
       </c>
-      <c r="C4" s="33" t="inlineStr">
+      <c r="C4" s="35" t="inlineStr">
         <is>
           <t>D["skt"]</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="34" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">  속도</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="C5" s="33" t="inlineStr"/>
+      <c r="C5" s="35" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">  TV 상품</t>
         </is>
       </c>
-      <c r="B6" s="27" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>B tv 올 (tvIdx=3)</t>
         </is>
       </c>
-      <c r="C6" s="33" t="inlineStr">
+      <c r="C6" s="35" t="inlineStr">
         <is>
           <t>D.skt.tv[3] = {p:18700, dc:2200}</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">  WiFi</t>
         </is>
       </c>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="C7" s="33" t="inlineStr"/>
+      <c r="C7" s="35" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">  결합 종류</t>
         </is>
       </c>
-      <c r="B8" s="27" t="inlineStr">
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>요즘가족결합 (family)</t>
         </is>
       </c>
-      <c r="C8" s="33" t="inlineStr"/>
+      <c r="C8" s="35" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">  결합 인원</t>
         </is>
       </c>
-      <c r="B9" s="27" t="inlineStr">
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>3명</t>
         </is>
       </c>
-      <c r="C9" s="33" t="inlineStr"/>
+      <c r="C9" s="35" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="35" t="inlineStr"/>
-      <c r="B10" s="36" t="inlineStr"/>
-      <c r="C10" s="37" t="inlineStr"/>
+      <c r="A10" s="37" t="inlineStr"/>
+      <c r="B10" s="38" t="inlineStr"/>
+      <c r="C10" s="39" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="32" t="inlineStr">
-        <is>
-          <t>기본가 계산</t>
-        </is>
-      </c>
-      <c r="B11" s="27" t="inlineStr"/>
-      <c r="C11" s="33" t="inlineStr"/>
+      <c r="A11" s="34" t="inlineStr">
+        <is>
+          <t>【경로 A】 휴대폰 결합 X (요즘우리집결합만 적용)</t>
+        </is>
+      </c>
+      <c r="B11" s="29" t="inlineStr"/>
+      <c r="C11" s="35" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1. 인터넷 결합가 (WiFi 미포함)</t>
-        </is>
-      </c>
-      <c r="B12" s="27" t="inlineStr">
+      <c r="A12" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1. 인터넷 결합가 (tvInternetNoWifi)</t>
+        </is>
+      </c>
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>27,500원</t>
         </is>
       </c>
-      <c r="C12" s="33" t="inlineStr">
+      <c r="C12" s="35" t="inlineStr">
         <is>
           <t>D.skt.tvInternetNoWifi["500M"]</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2. TV 최종요금 (결합할인 후)</t>
-        </is>
-      </c>
-      <c r="B13" s="27" t="inlineStr">
+      <c r="A13" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. TV 최종요금 (결합할인 -2,200)</t>
+        </is>
+      </c>
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>16,500원</t>
         </is>
       </c>
-      <c r="C13" s="33" t="inlineStr">
+      <c r="C13" s="35" t="inlineStr">
         <is>
           <t>18,700 - 2,200</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="34" t="inlineStr">
+      <c r="A14" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">  3. 셋톱박스 스마트3</t>
         </is>
       </c>
-      <c r="B14" s="27" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>4,400원</t>
         </is>
       </c>
-      <c r="C14" s="33" t="inlineStr">
-        <is>
-          <t>D.skt.setTopOptions[0].fee</t>
+      <c r="C14" s="35" t="inlineStr">
+        <is>
+          <t>D.skt.setTop</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  = 월 기본요금</t>
-        </is>
-      </c>
-      <c r="B15" s="26" t="inlineStr">
+      <c r="A15" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  = 월 기본요금 (요즘우리집)</t>
+        </is>
+      </c>
+      <c r="B15" s="28" t="inlineStr">
         <is>
           <t>48,400원</t>
         </is>
       </c>
-      <c r="C15" s="39" t="inlineStr">
+      <c r="C15" s="41" t="inlineStr">
         <is>
           <t>27,500 + 16,500 + 4,400</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="35" t="inlineStr"/>
-      <c r="B16" s="36" t="inlineStr"/>
-      <c r="C16" s="37" t="inlineStr"/>
+      <c r="A16" s="37" t="inlineStr"/>
+      <c r="B16" s="38" t="inlineStr"/>
+      <c r="C16" s="39" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="32" t="inlineStr">
-        <is>
-          <t>요즘가족결합 할인</t>
-        </is>
-      </c>
-      <c r="B17" s="27" t="inlineStr"/>
-      <c r="C17" s="33" t="inlineStr"/>
+      <c r="A17" s="34" t="inlineStr">
+        <is>
+          <t>【경로 B】 휴대폰 결합 O (요즘가족결합 적용 · 요즘우리집 REPLACE)</t>
+        </is>
+      </c>
+      <c r="B17" s="29" t="inlineStr"/>
+      <c r="C17" s="35" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  인터넷 할인</t>
-        </is>
-      </c>
-      <c r="B18" s="27" t="inlineStr">
+      <c r="A18" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ※ 주의: 단독가에서 재계산 (tvInternetNoWifi 사용 X)</t>
+        </is>
+      </c>
+      <c r="B18" s="29" t="inlineStr"/>
+      <c r="C18" s="35" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1. 인터넷 단독가 500M</t>
+        </is>
+      </c>
+      <c r="B19" s="29" t="inlineStr">
+        <is>
+          <t>33,000원</t>
+        </is>
+      </c>
+      <c r="C19" s="35" t="inlineStr">
+        <is>
+          <t>D.skt.internet["500M"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. 요즘가족결합 인터넷 할인</t>
+        </is>
+      </c>
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>-11,000원</t>
         </is>
       </c>
-      <c r="C18" s="33" t="inlineStr">
+      <c r="C20" s="35" t="inlineStr">
         <is>
           <t>D.skt.bundle.family.internet["500M"]</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  IPTV 추가 할인 (TV 결합 시)</t>
-        </is>
-      </c>
-      <c r="B19" s="27" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  → 인터넷 실질</t>
+        </is>
+      </c>
+      <c r="B21" s="29" t="inlineStr">
+        <is>
+          <t>22,000원</t>
+        </is>
+      </c>
+      <c r="C21" s="35" t="inlineStr">
+        <is>
+          <t>33,000 - 11,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3. TV 기본 (B tv 올)</t>
+        </is>
+      </c>
+      <c r="B22" s="29" t="inlineStr">
+        <is>
+          <t>18,700원</t>
+        </is>
+      </c>
+      <c r="C22" s="35" t="inlineStr">
+        <is>
+          <t>D.skt.tv[3].p</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4. TV 결합할인</t>
+        </is>
+      </c>
+      <c r="B23" s="29" t="inlineStr">
+        <is>
+          <t>-2,200원</t>
+        </is>
+      </c>
+      <c r="C23" s="35" t="inlineStr">
+        <is>
+          <t>D.skt.tv[3].dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5. IPTV 추가 할인 (요즘가족 전용)</t>
+        </is>
+      </c>
+      <c r="B24" s="29" t="inlineStr">
         <is>
           <t>-1,100원</t>
         </is>
       </c>
-      <c r="C19" s="33" t="inlineStr">
+      <c r="C24" s="35" t="inlineStr">
         <is>
           <t>D.skt.bundle.family.iptv</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  휴대폰 할인 (500M, 3회선 × 6,000)</t>
-        </is>
-      </c>
-      <c r="B20" s="27" t="inlineStr">
-        <is>
-          <t>-18,000원</t>
-        </is>
-      </c>
-      <c r="C20" s="33" t="inlineStr">
-        <is>
-          <t>mobilePerBySpeed["500M"][3] × 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="35" t="inlineStr"/>
-      <c r="B21" s="36" t="inlineStr"/>
-      <c r="C21" s="37" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="32" t="inlineStr">
-        <is>
-          <t>최종 계산</t>
-        </is>
-      </c>
-      <c r="B22" s="27" t="inlineStr"/>
-      <c r="C22" s="33" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  인터넷+TV 실납부</t>
-        </is>
-      </c>
-      <c r="B23" s="27" t="inlineStr">
-        <is>
-          <t>36,300원</t>
-        </is>
-      </c>
-      <c r="C23" s="33" t="inlineStr">
-        <is>
-          <t>48,400 - 11,000 - 1,100</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  휴대폰 고지서 별도 차감</t>
-        </is>
-      </c>
-      <c r="B24" s="27" t="inlineStr">
-        <is>
-          <t>-18,000원</t>
-        </is>
-      </c>
-      <c r="C24" s="33" t="inlineStr">
-        <is>
-          <t>(3회선 합산)</t>
-        </is>
-      </c>
-    </row>
     <row r="25">
-      <c r="A25" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  🎉 혜택가 (최종)</t>
-        </is>
-      </c>
-      <c r="B25" s="26" t="inlineStr">
-        <is>
-          <t>18,300원/월</t>
-        </is>
-      </c>
-      <c r="C25" s="39" t="inlineStr">
-        <is>
-          <t>36,300 - 18,000</t>
+      <c r="A25" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  → TV 실질</t>
+        </is>
+      </c>
+      <c r="B25" s="29" t="inlineStr">
+        <is>
+          <t>15,400원</t>
+        </is>
+      </c>
+      <c r="C25" s="35" t="inlineStr">
+        <is>
+          <t>18,700 - 2,200 - 1,100</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="35" t="inlineStr"/>
-      <c r="B26" s="36" t="inlineStr"/>
-      <c r="C26" s="37" t="inlineStr"/>
+      <c r="A26" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6. 셋톱박스</t>
+        </is>
+      </c>
+      <c r="B26" s="29" t="inlineStr">
+        <is>
+          <t>4,400원</t>
+        </is>
+      </c>
+      <c r="C26" s="35" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="32" t="inlineStr">
-        <is>
-          <t>부가 혜택</t>
-        </is>
-      </c>
-      <c r="B27" s="27" t="inlineStr"/>
-      <c r="C27" s="33" t="inlineStr"/>
+      <c r="A27" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  = 인터넷+TV 월 실납부</t>
+        </is>
+      </c>
+      <c r="B27" s="29" t="inlineStr">
+        <is>
+          <t>41,800원</t>
+        </is>
+      </c>
+      <c r="C27" s="35" t="inlineStr">
+        <is>
+          <t>22,000 + 15,400 + 4,400</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  설치비 (1회성)</t>
-        </is>
-      </c>
-      <c r="B28" s="27" t="inlineStr">
-        <is>
-          <t>56,100원</t>
-        </is>
-      </c>
-      <c r="C28" s="33" t="inlineStr">
-        <is>
-          <t>D.skt.install.combo</t>
-        </is>
-      </c>
+      <c r="A28" s="37" t="inlineStr"/>
+      <c r="B28" s="38" t="inlineStr"/>
+      <c r="C28" s="39" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="34" t="inlineStr">
         <is>
+          <t>휴대폰 고지서 별도 차감</t>
+        </is>
+      </c>
+      <c r="B29" s="29" t="inlineStr"/>
+      <c r="C29" s="35" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  휴대폰 할인 인당 (500M, 3회선)</t>
+        </is>
+      </c>
+      <c r="B30" s="29" t="inlineStr">
+        <is>
+          <t>6,000원</t>
+        </is>
+      </c>
+      <c r="C30" s="35" t="inlineStr">
+        <is>
+          <t>mobilePerBySpeed["500M"][3]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  총 할인 (인당 × 회선수)</t>
+        </is>
+      </c>
+      <c r="B31" s="29" t="inlineStr">
+        <is>
+          <t>-18,000원</t>
+        </is>
+      </c>
+      <c r="C31" s="35" t="inlineStr">
+        <is>
+          <t>6,000 × 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="37" t="inlineStr"/>
+      <c r="B32" s="38" t="inlineStr"/>
+      <c r="C32" s="39" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  🎉 혜택가 (최종)</t>
+        </is>
+      </c>
+      <c r="B33" s="28" t="inlineStr">
+        <is>
+          <t>23,800원/월</t>
+        </is>
+      </c>
+      <c r="C33" s="41" t="inlineStr">
+        <is>
+          <t>41,800 - 18,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="37" t="inlineStr"/>
+      <c r="B34" s="38" t="inlineStr"/>
+      <c r="C34" s="39" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="34" t="inlineStr">
+        <is>
+          <t>경로 A vs B 차이</t>
+        </is>
+      </c>
+      <c r="B35" s="29" t="inlineStr"/>
+      <c r="C35" s="35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  요즘우리집 (A): 48,400원</t>
+        </is>
+      </c>
+      <c r="B36" s="29" t="inlineStr"/>
+      <c r="C36" s="35" t="inlineStr">
+        <is>
+          <t>휴대폰 결합 없을 때</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  요즘가족 (B): 23,800원</t>
+        </is>
+      </c>
+      <c r="B37" s="29" t="inlineStr"/>
+      <c r="C37" s="35" t="inlineStr">
+        <is>
+          <t>휴대폰 3회선 결합 시 (-24,600 절감)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="37" t="inlineStr"/>
+      <c r="B38" s="38" t="inlineStr"/>
+      <c r="C38" s="39" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="34" t="inlineStr">
+        <is>
+          <t>부가 혜택</t>
+        </is>
+      </c>
+      <c r="B39" s="29" t="inlineStr"/>
+      <c r="C39" s="35" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  설치비 (1회성, 결합)</t>
+        </is>
+      </c>
+      <c r="B40" s="29" t="inlineStr">
+        <is>
+          <t>56,100원</t>
+        </is>
+      </c>
+      <c r="C40" s="35" t="inlineStr">
+        <is>
+          <t>D.skt.install.combo</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="36" t="inlineStr">
+        <is>
           <t xml:space="preserve">  사은품 (500M + TV 결합)</t>
         </is>
       </c>
-      <c r="B29" s="27" t="inlineStr">
+      <c r="B41" s="29" t="inlineStr">
         <is>
           <t>430,000원</t>
         </is>
       </c>
-      <c r="C29" s="33" t="inlineStr">
+      <c r="C41" s="35" t="inlineStr">
         <is>
           <t>D.skt.gift.combo["500M"]</t>
         </is>
@@ -3337,6 +3549,425 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>🧮 KT 총액결합 계산 예시 — 500M+지니TV 에센스+WiFi O+총액결합(108,900원↑)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="34" t="inlineStr">
+        <is>
+          <t>입력값</t>
+        </is>
+      </c>
+      <c r="B3" s="29" t="inlineStr"/>
+      <c r="C3" s="35" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  통신사/속도</t>
+        </is>
+      </c>
+      <c r="B4" s="29" t="inlineStr">
+        <is>
+          <t>KT 500M</t>
+        </is>
+      </c>
+      <c r="C4" s="35" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TV 상품</t>
+        </is>
+      </c>
+      <c r="B5" s="29" t="inlineStr">
+        <is>
+          <t>지니TV 에센스 (tvIdx=3)</t>
+        </is>
+      </c>
+      <c r="C5" s="35" t="inlineStr">
+        <is>
+          <t>D.kt.tv[3] = {p:20240, dc:3740}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WiFi</t>
+        </is>
+      </c>
+      <c r="B6" s="29" t="inlineStr">
+        <is>
+          <t>사용 (+1,100원)</t>
+        </is>
+      </c>
+      <c r="C6" s="35" t="inlineStr">
+        <is>
+          <t>D.kt.wifiPrice["500M"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  결합 종류</t>
+        </is>
+      </c>
+      <c r="B7" s="29" t="inlineStr">
+        <is>
+          <t>총액결합 (kt-total)</t>
+        </is>
+      </c>
+      <c r="C7" s="35" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  휴대폰 합산 구간</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>108,900원 이상 (rngIdx=3)</t>
+        </is>
+      </c>
+      <c r="C8" s="35" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="42" t="inlineStr"/>
+      <c r="B9" s="29" t="inlineStr"/>
+      <c r="C9" s="35" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="34" t="inlineStr">
+        <is>
+          <t>【기본 TV 결합 인터넷 할인】 (KT 기본)</t>
+        </is>
+      </c>
+      <c r="B10" s="29" t="inlineStr"/>
+      <c r="C10" s="35" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  인터넷 단독 (500M)</t>
+        </is>
+      </c>
+      <c r="B11" s="29" t="inlineStr">
+        <is>
+          <t>33,000원</t>
+        </is>
+      </c>
+      <c r="C11" s="35" t="inlineStr">
+        <is>
+          <t>D.kt.internet["500M"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WiFi 추가</t>
+        </is>
+      </c>
+      <c r="B12" s="29" t="inlineStr">
+        <is>
+          <t>+1,100원</t>
+        </is>
+      </c>
+      <c r="C12" s="35" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  인터넷 결합가 (tvInternetWithWifi)</t>
+        </is>
+      </c>
+      <c r="B13" s="29" t="inlineStr">
+        <is>
+          <t>28,600원</t>
+        </is>
+      </c>
+      <c r="C13" s="35" t="inlineStr">
+        <is>
+          <t>D.kt.tvInternetWithWifi["500M"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  → 기본 TV결합 인터넷 할인</t>
+        </is>
+      </c>
+      <c r="B14" s="29" t="inlineStr">
+        <is>
+          <t>-5,500원</t>
+        </is>
+      </c>
+      <c r="C14" s="35" t="inlineStr">
+        <is>
+          <t>(33,000+1,100) - 28,600</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="42" t="inlineStr"/>
+      <c r="B15" s="29" t="inlineStr"/>
+      <c r="C15" s="35" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="34" t="inlineStr">
+        <is>
+          <t>【총액결합 추가 할인】 ← 중복 적용</t>
+        </is>
+      </c>
+      <c r="B16" s="29" t="inlineStr"/>
+      <c r="C16" s="35" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  총액결합 인터넷 할인</t>
+        </is>
+      </c>
+      <c r="B17" s="29" t="inlineStr">
+        <is>
+          <t>-5,500원</t>
+        </is>
+      </c>
+      <c r="C17" s="35" t="inlineStr">
+        <is>
+          <t>D.kt.bundle.total.internet["500M"][3]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  → 인터넷 최종</t>
+        </is>
+      </c>
+      <c r="B18" s="29" t="inlineStr">
+        <is>
+          <t>23,100원</t>
+        </is>
+      </c>
+      <c r="C18" s="35" t="inlineStr">
+        <is>
+          <t>28,600 - 5,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="42" t="inlineStr"/>
+      <c r="B19" s="29" t="inlineStr"/>
+      <c r="C19" s="35" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="34" t="inlineStr">
+        <is>
+          <t>【TV + 셋톱】</t>
+        </is>
+      </c>
+      <c r="B20" s="29" t="inlineStr"/>
+      <c r="C20" s="35" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TV 기본</t>
+        </is>
+      </c>
+      <c r="B21" s="29" t="inlineStr">
+        <is>
+          <t>20,240원</t>
+        </is>
+      </c>
+      <c r="C21" s="35" t="inlineStr">
+        <is>
+          <t>D.kt.tv[3].p</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TV 결합할인</t>
+        </is>
+      </c>
+      <c r="B22" s="29" t="inlineStr">
+        <is>
+          <t>-3,740원</t>
+        </is>
+      </c>
+      <c r="C22" s="35" t="inlineStr">
+        <is>
+          <t>D.kt.tv[3].dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  → TV 실질</t>
+        </is>
+      </c>
+      <c r="B23" s="29" t="inlineStr">
+        <is>
+          <t>16,500원</t>
+        </is>
+      </c>
+      <c r="C23" s="35" t="inlineStr">
+        <is>
+          <t>20,240 - 3,740</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  셋톱박스 기가지니3</t>
+        </is>
+      </c>
+      <c r="B24" s="29" t="inlineStr">
+        <is>
+          <t>4,400원</t>
+        </is>
+      </c>
+      <c r="C24" s="35" t="inlineStr">
+        <is>
+          <t>D.kt.setTop</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="42" t="inlineStr"/>
+      <c r="B25" s="29" t="inlineStr"/>
+      <c r="C25" s="35" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="43" t="inlineStr">
+        <is>
+          <t>【월 실납부】</t>
+        </is>
+      </c>
+      <c r="B26" s="31" t="inlineStr"/>
+      <c r="C26" s="44" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  인터넷+TV+셋톱</t>
+        </is>
+      </c>
+      <c r="B27" s="29" t="inlineStr">
+        <is>
+          <t>44,000원</t>
+        </is>
+      </c>
+      <c r="C27" s="35" t="inlineStr">
+        <is>
+          <t>23,100 + 16,500 + 4,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="42" t="inlineStr"/>
+      <c r="B28" s="29" t="inlineStr"/>
+      <c r="C28" s="35" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="34" t="inlineStr">
+        <is>
+          <t>휴대폰 고지서 별도 할인</t>
+        </is>
+      </c>
+      <c r="B29" s="29" t="inlineStr"/>
+      <c r="C29" s="35" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  500M mobile[3]</t>
+        </is>
+      </c>
+      <c r="B30" s="29" t="inlineStr">
+        <is>
+          <t>-16,610원</t>
+        </is>
+      </c>
+      <c r="C30" s="35" t="inlineStr">
+        <is>
+          <t>D.kt.bundle.total.mobile["500M"][3]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="42" t="inlineStr"/>
+      <c r="B31" s="29" t="inlineStr"/>
+      <c r="C31" s="35" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  🎉 총 월 절감액 (vs 단독)</t>
+        </is>
+      </c>
+      <c r="B32" s="31" t="inlineStr">
+        <is>
+          <t>44,000 + (-16,610) 별도</t>
+        </is>
+      </c>
+      <c r="C32" s="44" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="42" t="inlineStr"/>
+      <c r="B33" s="29" t="inlineStr"/>
+      <c r="C33" s="35" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="34" t="inlineStr">
+        <is>
+          <t>※ KT 특성: 기본 TV결합 할인 + 총액결합 할인 **중복 적용** (STACK)</t>
+        </is>
+      </c>
+      <c r="B34" s="29" t="inlineStr"/>
+      <c r="C34" s="35" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   → SKT 요즘가족결합(REPLACE)과 반대 방식</t>
+        </is>
+      </c>
+      <c r="B35" s="29" t="inlineStr"/>
+      <c r="C35" s="35" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3358,597 +3989,227 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="32" t="inlineStr">
+      <c r="A3" s="34" t="inlineStr">
         <is>
           <t>입력값</t>
         </is>
       </c>
-      <c r="B3" s="27" t="inlineStr"/>
-      <c r="C3" s="33" t="inlineStr"/>
+      <c r="B3" s="29" t="inlineStr"/>
+      <c r="C3" s="35" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="40" t="inlineStr">
+      <c r="A4" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">  인터넷</t>
         </is>
       </c>
-      <c r="B4" s="27" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>100M + WiFi 없음 (TV 없음)</t>
         </is>
       </c>
-      <c r="C4" s="33" t="inlineStr"/>
+      <c r="C4" s="35" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="40" t="inlineStr">
+      <c r="A5" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">  회선 구성</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>대표 89K + 구성원 89K(프리미엄) + 구성원 89K(프리미엄)</t>
         </is>
       </c>
-      <c r="C5" s="33" t="inlineStr">
+      <c r="C5" s="35" t="inlineStr">
         <is>
           <t>총 3회선</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="40" t="inlineStr">
+      <c r="A6" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">  총액결합 대상</t>
         </is>
       </c>
-      <c r="B6" s="27" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>대표자 89K만 (프리미엄 2명 제외)</t>
         </is>
       </c>
-      <c r="C6" s="33" t="inlineStr">
+      <c r="C6" s="35" t="inlineStr">
         <is>
           <t>합산 89,000원</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="40" t="inlineStr">
+      <c r="A7" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">  구간 판정</t>
         </is>
       </c>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>64,900원 이상 (index 2)</t>
         </is>
       </c>
-      <c r="C7" s="33" t="inlineStr"/>
+      <c r="C7" s="35" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="40" t="inlineStr"/>
-      <c r="B8" s="27" t="inlineStr"/>
-      <c r="C8" s="33" t="inlineStr"/>
+      <c r="A8" s="42" t="inlineStr"/>
+      <c r="B8" s="29" t="inlineStr"/>
+      <c r="C8" s="35" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="32" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>총액결합 할인 (대표자 몫)</t>
         </is>
       </c>
-      <c r="B9" s="27" t="inlineStr"/>
-      <c r="C9" s="33" t="inlineStr"/>
+      <c r="B9" s="29" t="inlineStr"/>
+      <c r="C9" s="35" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="40" t="inlineStr">
+      <c r="A10" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">  100M mobile[index 2]</t>
         </is>
       </c>
-      <c r="B10" s="27" t="inlineStr">
+      <c r="B10" s="29" t="inlineStr">
         <is>
           <t>-3,300원</t>
         </is>
       </c>
-      <c r="C10" s="33" t="inlineStr">
+      <c r="C10" s="35" t="inlineStr">
         <is>
           <t>D.kt.bundle.total.mobile["100M"][2]</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="40" t="inlineStr"/>
-      <c r="B11" s="27" t="inlineStr"/>
-      <c r="C11" s="33" t="inlineStr"/>
+      <c r="A11" s="42" t="inlineStr"/>
+      <c r="B11" s="29" t="inlineStr"/>
+      <c r="C11" s="35" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="32" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>프리미엄 할인 (구성원 2명)</t>
         </is>
       </c>
-      <c r="B12" s="27" t="inlineStr"/>
-      <c r="C12" s="33" t="inlineStr"/>
+      <c r="B12" s="29" t="inlineStr"/>
+      <c r="C12" s="35" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="40" t="inlineStr">
+      <c r="A13" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">  89,000원 요금제 × 25% (정확)</t>
         </is>
       </c>
-      <c r="B13" s="27" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>-22,250원 × 2 = -44,500원</t>
         </is>
       </c>
-      <c r="C13" s="33" t="inlineStr">
+      <c r="C13" s="35" t="inlineStr">
         <is>
           <t>planCatalog[89000].dc</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="40" t="inlineStr"/>
-      <c r="B14" s="27" t="inlineStr"/>
-      <c r="C14" s="33" t="inlineStr"/>
+      <c r="A14" s="42" t="inlineStr"/>
+      <c r="B14" s="29" t="inlineStr"/>
+      <c r="C14" s="35" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="32" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>인터넷 할인 (고정)</t>
         </is>
       </c>
-      <c r="B15" s="27" t="inlineStr"/>
-      <c r="C15" s="33" t="inlineStr"/>
+      <c r="B15" s="29" t="inlineStr"/>
+      <c r="C15" s="35" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="40" t="inlineStr">
+      <c r="A16" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">  프리미엄 인터넷 할인</t>
         </is>
       </c>
-      <c r="B16" s="27" t="inlineStr">
+      <c r="B16" s="29" t="inlineStr">
         <is>
           <t>-5,500원</t>
         </is>
       </c>
-      <c r="C16" s="33" t="inlineStr">
+      <c r="C16" s="35" t="inlineStr">
         <is>
           <t>D.kt.bundle.premium.internet</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="40" t="inlineStr"/>
-      <c r="B17" s="27" t="inlineStr"/>
-      <c r="C17" s="33" t="inlineStr"/>
+      <c r="A17" s="42" t="inlineStr"/>
+      <c r="B17" s="29" t="inlineStr"/>
+      <c r="C17" s="35" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="32" t="inlineStr">
+      <c r="A18" s="34" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="B18" s="27" t="inlineStr"/>
-      <c r="C18" s="33" t="inlineStr"/>
+      <c r="B18" s="29" t="inlineStr"/>
+      <c r="C18" s="35" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="41" t="inlineStr">
+      <c r="A19" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">  총 할인액</t>
         </is>
       </c>
-      <c r="B19" s="29" t="inlineStr">
+      <c r="B19" s="31" t="inlineStr">
         <is>
           <t>-53,300원</t>
         </is>
       </c>
-      <c r="C19" s="42" t="inlineStr">
+      <c r="C19" s="44" t="inlineStr">
         <is>
           <t>3,300 + 44,500 + 5,500</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="40" t="inlineStr">
+      <c r="A20" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">  총액결합만 했을 때 비교</t>
         </is>
       </c>
-      <c r="B20" s="27" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>-28,600원</t>
         </is>
       </c>
-      <c r="C20" s="33" t="inlineStr">
+      <c r="C20" s="35" t="inlineStr">
         <is>
           <t>(174,900↑ 구간 기준)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  💎 프리미엄 선택 시 추가 이득</t>
-        </is>
-      </c>
-      <c r="B21" s="44" t="inlineStr">
-        <is>
-          <t>+24,700원 더 할인</t>
-        </is>
-      </c>
-      <c r="C21" s="45" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A56"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="80" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>📐 D 객체 JSON 스키마 (TypeScript 인터페이스)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="46" t="inlineStr">
-        <is>
-          <t>interface CarrierData {</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  name: string;          // "SKT (B tv)"</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  prefix: string;        // "SK" | "KT" | "LG"</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  internet: Record&lt;"100M"|"500M"|"1G", number&gt;;</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  wifiCost?: number;     // SKT, LGU+ 사용 (단일값)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  wifiPrice?: Record&lt;"100M"|"500M"|"1G", number&gt;;  // KT 사용 (속도별)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  setTopOptions: SetTop[];</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  wifiOptions: WiFi[];</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  tvInternetNoWifi: Record&lt;"100M"|"500M"|"1G", number&gt;;</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  tvInternetWithWifi: Record&lt;"100M"|"500M"|"1G", number&gt;;</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  tv: TVProduct[];</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  install: { solo: number; combo: number; };</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  gift: { solo: SpeedMap; combo: SpeedMap; };</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  bundle: BundleConfig;  // 통신사별 상이</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="46" t="inlineStr">
-        <is>
-          <t>}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="46" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="46" t="inlineStr">
-        <is>
-          <t>interface SetTop { id: string; name: string; fee: number; isDefault?: boolean; active: boolean; }</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="46" t="inlineStr">
-        <is>
-          <t>interface WiFi { id: string; name: string; fees: Record&lt;"100M"|"500M"|"1G", number&gt;; isDefault?: boolean; active: boolean; }</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="46" t="inlineStr">
         <is>
-          <t>interface TVProduct { n: string; p: number; dc: number; }  // n=이름, p=단독가, dc=결합할인</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="46" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="46" t="inlineStr">
-        <is>
-          <t>type BundleConfig =</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  | { family: SktFamily }                              // SKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  | { ranges_total, total, ranges_fixed, fixed, premium }  // KT</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  | { chweyswun, together };                           // LGU+</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="46" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="46" t="inlineStr">
-        <is>
-          <t>interface SktFamily {</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  internet: SpeedMap;</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  iptv: number;  // 1100</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  mobilePerBySpeed: Record&lt;Speed, Record&lt;1|2|3|4|5, number&gt;&gt;;</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="46" t="inlineStr">
-        <is>
-          <t>}</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="46" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="46" t="inlineStr">
-        <is>
-          <t>interface KTTotal {</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  internet: Record&lt;Speed, number[]&gt;;  // 6구간</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  mobile: Record&lt;Speed, number[]&gt;;    // 6구간</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="46" t="inlineStr">
-        <is>
-          <t>}</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="46" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="46" t="inlineStr">
-        <is>
-          <t>interface KTPremium {</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  internet: 5500;</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  planCatalog: Array&lt;{ v: number; label: string; dc: number; prem: boolean }&gt;;</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="46" t="inlineStr">
-        <is>
-          <t>}</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="46" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="46" t="inlineStr">
-        <is>
-          <t>interface LguChweyswun {</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  internet: SpeedMap;</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  planLabels: string[];  // 3개</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  mobile: number[][];    // 3 (요금구간) × 3 (회선수)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="46" t="inlineStr">
-        <is>
-          <t>}</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="46" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="46" t="inlineStr">
-        <is>
-          <t>interface LguTogether {</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  internet: SpeedMap;  // 100M=0 (불가)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  mobile: [number, number, number];  // 2/3/4+회선</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="46" t="inlineStr">
-        <is>
-          <t>}</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="46" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="46" t="inlineStr">
-        <is>
-          <t>type Speed = "100M" | "500M" | "1G";</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="46" t="inlineStr">
-        <is>
-          <t>type SpeedMap = Record&lt;Speed, number&gt;;</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  💎 프리미엄 선택 시 추가 이득</t>
+        </is>
+      </c>
+      <c r="B21" s="47" t="inlineStr">
+        <is>
+          <t>+24,700원 더 할인</t>
+        </is>
+      </c>
+      <c r="C21" s="48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4072,6 +4333,376 @@
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>※ 3사 모두 3년 약정 기준 · 부가세 포함 · WiFi/셋톱 별도</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A56"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="80" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>📐 D 객체 JSON 스키마 (TypeScript 인터페이스)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="49" t="inlineStr">
+        <is>
+          <t>interface CarrierData {</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  name: string;          // "SKT (B tv)"</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  prefix: string;        // "SK" | "KT" | "LG"</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  internet: Record&lt;"100M"|"500M"|"1G", number&gt;;</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  wifiCost?: number;     // SKT, LGU+ 사용 (단일값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  wifiPrice?: Record&lt;"100M"|"500M"|"1G", number&gt;;  // KT 사용 (속도별)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  setTopOptions: SetTop[];</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  wifiOptions: WiFi[];</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  tvInternetNoWifi: Record&lt;"100M"|"500M"|"1G", number&gt;;</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  tvInternetWithWifi: Record&lt;"100M"|"500M"|"1G", number&gt;;</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  tv: TVProduct[];</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  install: { solo: number; combo: number; };</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  gift: { solo: SpeedMap; combo: SpeedMap; };</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  bundle: BundleConfig;  // 통신사별 상이</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="49" t="inlineStr">
+        <is>
+          <t>}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="49" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="49" t="inlineStr">
+        <is>
+          <t>interface SetTop { id: string; name: string; fee: number; isDefault?: boolean; active: boolean; }</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="49" t="inlineStr">
+        <is>
+          <t>interface WiFi { id: string; name: string; fees: Record&lt;"100M"|"500M"|"1G", number&gt;; isDefault?: boolean; active: boolean; }</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="49" t="inlineStr">
+        <is>
+          <t>interface TVProduct { n: string; p: number; dc: number; }  // n=이름, p=단독가, dc=결합할인</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="49" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="49" t="inlineStr">
+        <is>
+          <t>type BundleConfig =</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  | { family: SktFamily }                              // SKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  | { ranges_total, total, ranges_fixed, fixed, premium }  // KT</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  | { chweyswun, together };                           // LGU+</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="49" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="49" t="inlineStr">
+        <is>
+          <t>interface SktFamily {</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  internet: SpeedMap;</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  iptv: number;  // 1100</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  mobilePerBySpeed: Record&lt;Speed, Record&lt;1|2|3|4|5, number&gt;&gt;;</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="49" t="inlineStr">
+        <is>
+          <t>}</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="49" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="49" t="inlineStr">
+        <is>
+          <t>interface KTTotal {</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  internet: Record&lt;Speed, number[]&gt;;  // 6구간</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  mobile: Record&lt;Speed, number[]&gt;;    // 6구간</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="49" t="inlineStr">
+        <is>
+          <t>}</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="49" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="49" t="inlineStr">
+        <is>
+          <t>interface KTPremium {</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  internet: 5500;</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  planCatalog: Array&lt;{ v: number; label: string; dc: number; prem: boolean }&gt;;</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="49" t="inlineStr">
+        <is>
+          <t>}</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="49" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="49" t="inlineStr">
+        <is>
+          <t>interface LguChweyswun {</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  internet: SpeedMap;</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  planLabels: string[];  // 3개</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  mobile: number[][];    // 3 (요금구간) × 3 (회선수)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="49" t="inlineStr">
+        <is>
+          <t>}</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="49" t="inlineStr">
+        <is>
+          <t>interface LguTogether {</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  internet: SpeedMap;  // 100M=0 (불가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  mobile: [number, number, number];  // 2/3/4+회선</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="49" t="inlineStr">
+        <is>
+          <t>}</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="49" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="49" t="inlineStr">
+        <is>
+          <t>type Speed = "100M" | "500M" | "1G";</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="49" t="inlineStr">
+        <is>
+          <t>type SpeedMap = Record&lt;Speed, number&gt;;</t>
         </is>
       </c>
     </row>

--- a/docs/bongi-calculator-data.xlsx
+++ b/docs/bongi-calculator-data.xlsx
@@ -26,7 +26,10 @@
     <sheet name="31_CALC_Example_SKT" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="31b_CALC_Example_KT_Total" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="32_CALC_Example_KT_Premium" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="20_Schema" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="40_CALC_Interactive_SKT" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="41_CALC_Interactive_KT" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="42_CALC_Interactive_LGU" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="20_Schema" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -35,8 +38,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="22">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0&quot;원&quot;"/>
+  </numFmts>
+  <fonts count="34">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -161,8 +166,77 @@
       <color rgb="001a2744"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Noto Sans KR"/>
+      <b val="1"/>
+      <color rgb="00ffffff"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Noto Sans KR"/>
+      <b val="1"/>
+      <color rgb="001a2744"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Noto Sans KR"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Noto Sans KR"/>
+      <i val="1"/>
+      <color rgb="00d97706"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Noto Sans KR"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Noto Sans KR"/>
+      <color rgb="00333333"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Noto Sans KR"/>
+      <b val="1"/>
+      <color rgb="00666666"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Noto Sans KR"/>
+      <b val="1"/>
+      <color rgb="00ef4444"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="SF Mono"/>
+      <b val="1"/>
+      <color rgb="00ef4444"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Noto Sans KR"/>
+      <b val="1"/>
+      <color rgb="00666666"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="SF Mono"/>
+      <b val="1"/>
+      <color rgb="002563eb"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="SF Mono"/>
+      <b val="1"/>
+      <color rgb="00e40981"/>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -199,6 +273,21 @@
         <fgColor rgb="00f0f0f0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ef4444"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002563eb"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00e40981"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -226,7 +315,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -288,6 +377,47 @@
     <xf numFmtId="0" fontId="21" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="30" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -4347,6 +4477,979 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="49" t="inlineStr">
+        <is>
+          <t>🧮 SKT 요즘가족결합 계산기</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="50" t="inlineStr">
+        <is>
+          <t>📝 입력 (노란 셀 수정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="51" t="inlineStr">
+        <is>
+          <t>속도</t>
+        </is>
+      </c>
+      <c r="B4" s="52" t="inlineStr">
+        <is>
+          <t>500M</t>
+        </is>
+      </c>
+      <c r="C4" s="53" t="inlineStr">
+        <is>
+          <t>← 여기 수정</t>
+        </is>
+      </c>
+      <c r="D4" s="54" t="inlineStr">
+        <is>
+          <t>D.skt.internet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="51" t="inlineStr">
+        <is>
+          <t>TV 상품 (1=없음, 2~10=선택)</t>
+        </is>
+      </c>
+      <c r="B5" s="52" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="53" t="inlineStr">
+        <is>
+          <t>← 여기 수정</t>
+        </is>
+      </c>
+      <c r="D5" s="54" t="inlineStr">
+        <is>
+          <t>1=TV없음, 2=이코노미, 3=스탠다드, 4=올, ..., 10=올넷프리미엄</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="51" t="inlineStr">
+        <is>
+          <t>WiFi 사용</t>
+        </is>
+      </c>
+      <c r="B6" s="52" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C6" s="53" t="inlineStr">
+        <is>
+          <t>← 여기 수정</t>
+        </is>
+      </c>
+      <c r="D6" s="54" t="inlineStr">
+        <is>
+          <t>Y/N</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="51" t="inlineStr">
+        <is>
+          <t>휴대폰 회선수</t>
+        </is>
+      </c>
+      <c r="B7" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="53" t="inlineStr">
+        <is>
+          <t>← 여기 수정</t>
+        </is>
+      </c>
+      <c r="D7" s="54" t="inlineStr">
+        <is>
+          <t>1~5 (0=결합 없음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="50" t="inlineStr">
+        <is>
+          <t>🧮 자동 계산</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="55" t="inlineStr">
+        <is>
+          <t>인터넷 단독가</t>
+        </is>
+      </c>
+      <c r="B10" s="56">
+        <f>IF(B4="100M",22000,IF(B4="500M",33000,38500))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="55" t="inlineStr">
+        <is>
+          <t>TV 상품 가격 (p)</t>
+        </is>
+      </c>
+      <c r="B11" s="56">
+        <f>IF(B5=1,0,CHOOSE(B5-1,12100,15400,18700,23100,24200,27700,30200,30700,33200))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="55" t="inlineStr">
+        <is>
+          <t>TV 결합 할인 (dc)</t>
+        </is>
+      </c>
+      <c r="B12" s="56">
+        <f>IF(B5=1,0,2200)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="55" t="inlineStr">
+        <is>
+          <t>WiFi 추가금</t>
+        </is>
+      </c>
+      <c r="B13" s="56">
+        <f>IF(B6="Y",1100,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="55" t="inlineStr">
+        <is>
+          <t>tvInternetNoWifi</t>
+        </is>
+      </c>
+      <c r="B14" s="56">
+        <f>IF(B4="100M",19800,IF(B4="500M",27500,33000))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="55" t="inlineStr">
+        <is>
+          <t>tvInternetWithWifi</t>
+        </is>
+      </c>
+      <c r="B15" s="56">
+        <f>IF(B4="100M",22000,IF(B4="500M",28600,34100))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="55" t="inlineStr">
+        <is>
+          <t>요즘가족결합 인터넷 할인</t>
+        </is>
+      </c>
+      <c r="B16" s="56">
+        <f>IF(B7=0,0,IF(B4="100M",4400,IF(B4="500M",11000,13200)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="55" t="inlineStr">
+        <is>
+          <t>IPTV 추가 할인 (TV 있고 결합 시)</t>
+        </is>
+      </c>
+      <c r="B17" s="56">
+        <f>IF(AND(B7&gt;0,B5&gt;1),1100,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="55" t="inlineStr">
+        <is>
+          <t>휴대폰 인당 할인</t>
+        </is>
+      </c>
+      <c r="B18" s="56">
+        <f>IF(B7=0,0,IF(B4="100M",CHOOSE(B7,3500,3500,6000,4500,3600),CHOOSE(B7,3500,3500,6000,6000,4800)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="55" t="inlineStr">
+        <is>
+          <t>휴대폰 총 할인 (인당 × 회선수)</t>
+        </is>
+      </c>
+      <c r="B19" s="56">
+        <f>B18*B7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="50" t="inlineStr">
+        <is>
+          <t>💰 결과</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="57" t="inlineStr">
+        <is>
+          <t>【경로 A】 휴대폰 결합 X</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  월 기본요금 (요즘우리집)</t>
+        </is>
+      </c>
+      <c r="B23" s="58">
+        <f>IF(B5=1,B10+B13,IF(B6="Y",B15,B14)+(B11-B12)+4400)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="59" t="inlineStr">
+        <is>
+          <t>【경로 B】 휴대폰 결합 O (요즘가족)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  인터넷 (단독가 - 요즘가족할인)</t>
+        </is>
+      </c>
+      <c r="B25" s="58">
+        <f>B10+B13-B16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TV (기본 - 결합할인 - IPTV 추가)</t>
+        </is>
+      </c>
+      <c r="B26" s="58">
+        <f>IF(B5=1,0,B11-B12-B17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  셋톱박스 (TV 있을 때만)</t>
+        </is>
+      </c>
+      <c r="B27" s="58">
+        <f>IF(B5=1,0,4400)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  = 인터넷+TV 월 실납부</t>
+        </is>
+      </c>
+      <c r="B28" s="58">
+        <f>B25+B26+B27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 휴대폰 고지서 별도 차감</t>
+        </is>
+      </c>
+      <c r="B29" s="58">
+        <f>-B19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="55" t="inlineStr">
+        <is>
+          <t>🎉 혜택가 (최종)</t>
+        </is>
+      </c>
+      <c r="B30" s="60">
+        <f>B28-B19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="61" t="inlineStr">
+        <is>
+          <t>🎁 부가 (참고)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  설치비 (1회성)</t>
+        </is>
+      </c>
+      <c r="B33" s="56">
+        <f>IF(B5=1,36300,56100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  사은품 (속도×TV결합)</t>
+        </is>
+      </c>
+      <c r="B34" s="56">
+        <f>IF(B5=1,IF(B4="100M",110000,170000),CHOOSE(MATCH(B4,{"100M","500M","1G"},0),400000,430000,490000))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>※ B4(속도)·B5(TV)·B6(WiFi)·B7(회선) 입력 셀만 수정하면 자동 재계산됩니다.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A37:E37"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"100M,500M,1G"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="62" t="inlineStr">
+        <is>
+          <t>🧮 KT 총액결합 계산기 (STACK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="50" t="inlineStr">
+        <is>
+          <t>📝 입력</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="51" t="inlineStr">
+        <is>
+          <t>속도</t>
+        </is>
+      </c>
+      <c r="B4" s="52" t="inlineStr">
+        <is>
+          <t>500M</t>
+        </is>
+      </c>
+      <c r="C4" s="53" t="inlineStr">
+        <is>
+          <t>← 여기 수정</t>
+        </is>
+      </c>
+      <c r="D4" s="54" t="inlineStr">
+        <is>
+          <t>100M/500M/1G</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="51" t="inlineStr">
+        <is>
+          <t>TV 상품 (1=없음, 2~6=선택)</t>
+        </is>
+      </c>
+      <c r="B5" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="53" t="inlineStr">
+        <is>
+          <t>← 여기 수정</t>
+        </is>
+      </c>
+      <c r="D5" s="54" t="inlineStr">
+        <is>
+          <t>1=없음, 2=베이직, 3=라이트, 4=에센스, 5=모든G, 6=디즈니+</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="51" t="inlineStr">
+        <is>
+          <t>WiFi 사용</t>
+        </is>
+      </c>
+      <c r="B6" s="52" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C6" s="53" t="inlineStr">
+        <is>
+          <t>← 여기 수정</t>
+        </is>
+      </c>
+      <c r="D6" s="54" t="inlineStr">
+        <is>
+          <t>Y/N</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="51" t="inlineStr">
+        <is>
+          <t>총액결합 구간 (1~6)</t>
+        </is>
+      </c>
+      <c r="B7" s="52" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="53" t="inlineStr">
+        <is>
+          <t>← 여기 수정</t>
+        </is>
+      </c>
+      <c r="D7" s="54" t="inlineStr">
+        <is>
+          <t>1=22K↓, 2=22K↑, 3=64.9K↑, 4=108.9K↑, 5=141.9K↑, 6=174.9K↑</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="50" t="inlineStr">
+        <is>
+          <t>🧮 자동 계산</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="55" t="inlineStr">
+        <is>
+          <t>인터넷 단독가</t>
+        </is>
+      </c>
+      <c r="B10" s="56">
+        <f>IF(B4="100M",22000,IF(B4="500M",33000,38500))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="55" t="inlineStr">
+        <is>
+          <t>TV 가격</t>
+        </is>
+      </c>
+      <c r="B11" s="56">
+        <f>IF(B5=1,0,CHOOSE(B5-1,14740,15840,20240,21340,28100))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="55" t="inlineStr">
+        <is>
+          <t>TV 결합할인</t>
+        </is>
+      </c>
+      <c r="B12" s="56">
+        <f>IF(B5=1,0,CHOOSE(B5-1,2640,2640,3740,4400,6600))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="55" t="inlineStr">
+        <is>
+          <t>WiFi 추가금 (속도별)</t>
+        </is>
+      </c>
+      <c r="B13" s="56">
+        <f>IF(B6="Y",IF(B4="1G",0,1100),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="55" t="inlineStr">
+        <is>
+          <t>tvInternetNoWifi</t>
+        </is>
+      </c>
+      <c r="B14" s="56">
+        <f>IF(B4="100M",22000,IF(B4="500M",27500,33000))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="55" t="inlineStr">
+        <is>
+          <t>tvInternetWithWifi</t>
+        </is>
+      </c>
+      <c r="B15" s="56">
+        <f>IF(B4="100M",23100,IF(B4="500M",28600,33000))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="55" t="inlineStr">
+        <is>
+          <t>총액결합 인터넷 할인</t>
+        </is>
+      </c>
+      <c r="B16" s="56">
+        <f>IF(B4="100M",CHOOSE(B7,1650,3300,5500,5500,5500,5500),IF(B4="500M",CHOOSE(B7,2200,5500,5500,5500,5500,5500),CHOOSE(B7,2200,5500,5500,5500,5500,5500)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="55" t="inlineStr">
+        <is>
+          <t>총액결합 휴대폰 할인</t>
+        </is>
+      </c>
+      <c r="B17" s="56">
+        <f>IF(B4="100M",CHOOSE(B7,0,0,3300,14300,18700,23100),CHOOSE(B7,0,0,5500,16610,22110,27610))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="50" t="inlineStr">
+        <is>
+          <t>💰 결과</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  인터넷 결합가 (기본 TV결합)</t>
+        </is>
+      </c>
+      <c r="B20" s="63">
+        <f>IF(B5=1,B10+B13,IF(B6="Y",B15,B14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 총액결합 추가 할인 (STACK)</t>
+        </is>
+      </c>
+      <c r="B21" s="63">
+        <f>-B16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TV 최종</t>
+        </is>
+      </c>
+      <c r="B22" s="63">
+        <f>IF(B5=1,0,B11-B12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  셋톱박스</t>
+        </is>
+      </c>
+      <c r="B23" s="63">
+        <f>IF(B5=1,0,4400)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  = 인터넷+TV 월 실납부</t>
+        </is>
+      </c>
+      <c r="B24" s="63">
+        <f>B20-B16+B22+B23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 휴대폰 고지서 별도 차감</t>
+        </is>
+      </c>
+      <c r="B25" s="63">
+        <f>-B17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="55" t="inlineStr">
+        <is>
+          <t>🎉 혜택가 (최종)</t>
+        </is>
+      </c>
+      <c r="B26" s="64">
+        <f>B24-B17</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"100M,500M,1G"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="65" t="inlineStr">
+        <is>
+          <t>🧮 LG U+ 참쉬운가족결합 계산기</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="50" t="inlineStr">
+        <is>
+          <t>📝 입력</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="51" t="inlineStr">
+        <is>
+          <t>속도</t>
+        </is>
+      </c>
+      <c r="B4" s="52" t="inlineStr">
+        <is>
+          <t>500M</t>
+        </is>
+      </c>
+      <c r="C4" s="53" t="inlineStr">
+        <is>
+          <t>← 여기 수정</t>
+        </is>
+      </c>
+      <c r="D4" s="54" t="inlineStr">
+        <is>
+          <t>100M/500M/1G</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="51" t="inlineStr">
+        <is>
+          <t>TV 상품 (1=없음, 2~5=선택)</t>
+        </is>
+      </c>
+      <c r="B5" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="53" t="inlineStr">
+        <is>
+          <t>← 여기 수정</t>
+        </is>
+      </c>
+      <c r="D5" s="54" t="inlineStr">
+        <is>
+          <t>1=없음, 2=실속형, 3=기본형, 4=프리미엄, 5=프리미엄 VOD</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="51" t="inlineStr">
+        <is>
+          <t>휴대폰 요금 구간 (1~3)</t>
+        </is>
+      </c>
+      <c r="B6" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="53" t="inlineStr">
+        <is>
+          <t>← 여기 수정</t>
+        </is>
+      </c>
+      <c r="D6" s="54" t="inlineStr">
+        <is>
+          <t>1=69K미만, 2=69K↑, 3=88K↑</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="51" t="inlineStr">
+        <is>
+          <t>결합 회선수 (2~4)</t>
+        </is>
+      </c>
+      <c r="B7" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="53" t="inlineStr">
+        <is>
+          <t>← 여기 수정</t>
+        </is>
+      </c>
+      <c r="D7" s="54" t="inlineStr">
+        <is>
+          <t>2/3/4+ (1회선은 결합 불가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="50" t="inlineStr">
+        <is>
+          <t>🧮 자동 계산</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="55" t="inlineStr">
+        <is>
+          <t>인터넷 단독가</t>
+        </is>
+      </c>
+      <c r="B10" s="56">
+        <f>IF(B4="100M",22000,IF(B4="500M",33000,38500))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="55" t="inlineStr">
+        <is>
+          <t>TV 가격</t>
+        </is>
+      </c>
+      <c r="B11" s="56">
+        <f>IF(B5=1,0,CHOOSE(B5-1,15400,16500,18700,24200))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="55" t="inlineStr">
+        <is>
+          <t>TV 결합할인</t>
+        </is>
+      </c>
+      <c r="B12" s="56">
+        <f>IF(B5=1,0,CHOOSE(B5-1,2200,2200,2200,5500))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="55" t="inlineStr">
+        <is>
+          <t>WiFi 추가금 (전속도 무료)</t>
+        </is>
+      </c>
+      <c r="B13" s="56">
+        <f>0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="55" t="inlineStr">
+        <is>
+          <t>참쉬운 인터넷 할인</t>
+        </is>
+      </c>
+      <c r="B14" s="56">
+        <f>IF(B4="100M",5500,IF(B4="500M",9900,13200))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="55" t="inlineStr">
+        <is>
+          <t>참쉬운 휴대폰 인당 할인</t>
+        </is>
+      </c>
+      <c r="B15" s="56">
+        <f>CHOOSE(B6,CHOOSE(MIN(B7,4)-1,2200,3300,4400),CHOOSE(MIN(B7,4)-1,3300,5500,6600),CHOOSE(MIN(B7,4)-1,4400,6600,8800))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="55" t="inlineStr">
+        <is>
+          <t>휴대폰 총 할인</t>
+        </is>
+      </c>
+      <c r="B16" s="56">
+        <f>B15*MIN(B7,4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="50" t="inlineStr">
+        <is>
+          <t>💰 결과</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  인터넷 (단독가 - 참쉬운할인)</t>
+        </is>
+      </c>
+      <c r="B19" s="66">
+        <f>B10+B13-B14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TV 최종</t>
+        </is>
+      </c>
+      <c r="B20" s="66">
+        <f>IF(B5=1,0,B11-B12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  셋톱박스</t>
+        </is>
+      </c>
+      <c r="B21" s="66">
+        <f>IF(B5=1,0,4400)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  = 인터넷+TV 월 실납부</t>
+        </is>
+      </c>
+      <c r="B22" s="66">
+        <f>B19+B20+B21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 휴대폰 고지서 별도 차감</t>
+        </is>
+      </c>
+      <c r="B23" s="66">
+        <f>-B16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="55" t="inlineStr">
+        <is>
+          <t>🎉 혜택가 (최종)</t>
+        </is>
+      </c>
+      <c r="B24" s="67">
+        <f>B22-B16</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"100M,500M,1G"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4361,346 +5464,346 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="49" t="inlineStr">
+      <c r="A3" s="68" t="inlineStr">
         <is>
           <t>interface CarrierData {</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="49" t="inlineStr">
+      <c r="A4" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">  name: string;          // "SKT (B tv)"</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="49" t="inlineStr">
+      <c r="A5" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">  prefix: string;        // "SK" | "KT" | "LG"</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="49" t="inlineStr">
+      <c r="A6" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">  internet: Record&lt;"100M"|"500M"|"1G", number&gt;;</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="49" t="inlineStr">
+      <c r="A7" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">  wifiCost?: number;     // SKT, LGU+ 사용 (단일값)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="49" t="inlineStr">
+      <c r="A8" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">  wifiPrice?: Record&lt;"100M"|"500M"|"1G", number&gt;;  // KT 사용 (속도별)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="49" t="inlineStr">
+      <c r="A9" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">  setTopOptions: SetTop[];</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="49" t="inlineStr">
+      <c r="A10" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">  wifiOptions: WiFi[];</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="49" t="inlineStr">
+      <c r="A11" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">  tvInternetNoWifi: Record&lt;"100M"|"500M"|"1G", number&gt;;</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="49" t="inlineStr">
+      <c r="A12" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">  tvInternetWithWifi: Record&lt;"100M"|"500M"|"1G", number&gt;;</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="49" t="inlineStr">
+      <c r="A13" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">  tv: TVProduct[];</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="49" t="inlineStr">
+      <c r="A14" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">  install: { solo: number; combo: number; };</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="49" t="inlineStr">
+      <c r="A15" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">  gift: { solo: SpeedMap; combo: SpeedMap; };</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="49" t="inlineStr">
+      <c r="A16" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">  bundle: BundleConfig;  // 통신사별 상이</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="49" t="inlineStr">
+      <c r="A17" s="68" t="inlineStr">
         <is>
           <t>}</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="49" t="inlineStr"/>
+      <c r="A18" s="68" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="49" t="inlineStr">
+      <c r="A19" s="68" t="inlineStr">
         <is>
           <t>interface SetTop { id: string; name: string; fee: number; isDefault?: boolean; active: boolean; }</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="49" t="inlineStr">
+      <c r="A20" s="68" t="inlineStr">
         <is>
           <t>interface WiFi { id: string; name: string; fees: Record&lt;"100M"|"500M"|"1G", number&gt;; isDefault?: boolean; active: boolean; }</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="49" t="inlineStr">
+      <c r="A21" s="68" t="inlineStr">
         <is>
           <t>interface TVProduct { n: string; p: number; dc: number; }  // n=이름, p=단독가, dc=결합할인</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="49" t="inlineStr"/>
+      <c r="A22" s="68" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="49" t="inlineStr">
+      <c r="A23" s="68" t="inlineStr">
         <is>
           <t>type BundleConfig =</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="49" t="inlineStr">
+      <c r="A24" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">  | { family: SktFamily }                              // SKT</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="49" t="inlineStr">
+      <c r="A25" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">  | { ranges_total, total, ranges_fixed, fixed, premium }  // KT</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="49" t="inlineStr">
+      <c r="A26" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">  | { chweyswun, together };                           // LGU+</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="49" t="inlineStr"/>
+      <c r="A27" s="68" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="49" t="inlineStr">
+      <c r="A28" s="68" t="inlineStr">
         <is>
           <t>interface SktFamily {</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="49" t="inlineStr">
+      <c r="A29" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">  internet: SpeedMap;</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="49" t="inlineStr">
+      <c r="A30" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">  iptv: number;  // 1100</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="49" t="inlineStr">
+      <c r="A31" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">  mobilePerBySpeed: Record&lt;Speed, Record&lt;1|2|3|4|5, number&gt;&gt;;</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="49" t="inlineStr">
+      <c r="A32" s="68" t="inlineStr">
         <is>
           <t>}</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="49" t="inlineStr"/>
+      <c r="A33" s="68" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="49" t="inlineStr">
+      <c r="A34" s="68" t="inlineStr">
         <is>
           <t>interface KTTotal {</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="49" t="inlineStr">
+      <c r="A35" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">  internet: Record&lt;Speed, number[]&gt;;  // 6구간</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="49" t="inlineStr">
+      <c r="A36" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">  mobile: Record&lt;Speed, number[]&gt;;    // 6구간</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="49" t="inlineStr">
+      <c r="A37" s="68" t="inlineStr">
         <is>
           <t>}</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="49" t="inlineStr"/>
+      <c r="A38" s="68" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="49" t="inlineStr">
+      <c r="A39" s="68" t="inlineStr">
         <is>
           <t>interface KTPremium {</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="49" t="inlineStr">
+      <c r="A40" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">  internet: 5500;</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="49" t="inlineStr">
+      <c r="A41" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">  planCatalog: Array&lt;{ v: number; label: string; dc: number; prem: boolean }&gt;;</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="49" t="inlineStr">
+      <c r="A42" s="68" t="inlineStr">
         <is>
           <t>}</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="49" t="inlineStr"/>
+      <c r="A43" s="68" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="49" t="inlineStr">
+      <c r="A44" s="68" t="inlineStr">
         <is>
           <t>interface LguChweyswun {</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="49" t="inlineStr">
+      <c r="A45" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">  internet: SpeedMap;</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="49" t="inlineStr">
+      <c r="A46" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">  planLabels: string[];  // 3개</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="49" t="inlineStr">
+      <c r="A47" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">  mobile: number[][];    // 3 (요금구간) × 3 (회선수)</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="49" t="inlineStr">
+      <c r="A48" s="68" t="inlineStr">
         <is>
           <t>}</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="49" t="inlineStr"/>
+      <c r="A49" s="68" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="49" t="inlineStr">
+      <c r="A50" s="68" t="inlineStr">
         <is>
           <t>interface LguTogether {</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="49" t="inlineStr">
+      <c r="A51" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">  internet: SpeedMap;  // 100M=0 (불가)</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="49" t="inlineStr">
+      <c r="A52" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">  mobile: [number, number, number];  // 2/3/4+회선</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="49" t="inlineStr">
+      <c r="A53" s="68" t="inlineStr">
         <is>
           <t>}</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="49" t="inlineStr"/>
+      <c r="A54" s="68" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="49" t="inlineStr">
+      <c r="A55" s="68" t="inlineStr">
         <is>
           <t>type Speed = "100M" | "500M" | "1G";</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="49" t="inlineStr">
+      <c r="A56" s="68" t="inlineStr">
         <is>
           <t>type SpeedMap = Record&lt;Speed, number&gt;;</t>
         </is>

--- a/docs/bongi-calculator-data.xlsx
+++ b/docs/bongi-calculator-data.xlsx
@@ -36,7 +36,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0&quot;원&quot;"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="31">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -125,6 +125,12 @@
     </font>
     <font>
       <name val="Noto Sans KR"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Noto Sans KR"/>
       <b val="1"/>
       <color rgb="00666666"/>
       <sz val="11"/>
@@ -160,6 +166,12 @@
     </font>
     <font>
       <name val="Noto Sans KR"/>
+      <i val="1"/>
+      <color rgb="0092400e"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Noto Sans KR"/>
       <b val="1"/>
       <color rgb="00ef4444"/>
       <sz val="14"/>
@@ -175,12 +187,6 @@
       <b val="1"/>
       <color rgb="00d97706"/>
       <sz val="14"/>
-    </font>
-    <font>
-      <name val="Noto Sans KR"/>
-      <i val="1"/>
-      <color rgb="0092400e"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Noto Sans KR"/>
@@ -269,7 +275,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -296,38 +302,41 @@
     <xf numFmtId="164" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="20" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="21" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1876,7 +1885,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>🏷️ SKT 요즘가족결합</t>
         </is>
@@ -1915,332 +1924,332 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B4" s="22" t="n">
+      <c r="B4" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="22" t="n">
+      <c r="C4" s="24" t="n">
         <v>3500</v>
       </c>
-      <c r="D4" s="22" t="n">
+      <c r="D4" s="24" t="n">
         <v>4400</v>
       </c>
-      <c r="E4" s="22" t="n">
+      <c r="E4" s="24" t="n">
         <v>1100</v>
       </c>
-      <c r="F4" s="22" t="n">
+      <c r="F4" s="24" t="n">
         <v>9000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B5" s="22" t="n">
+      <c r="B5" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="22" t="n">
+      <c r="C5" s="24" t="n">
         <v>7000</v>
       </c>
-      <c r="D5" s="22" t="n">
+      <c r="D5" s="24" t="n">
         <v>4400</v>
       </c>
-      <c r="E5" s="22" t="n">
+      <c r="E5" s="24" t="n">
         <v>1100</v>
       </c>
-      <c r="F5" s="22" t="n">
+      <c r="F5" s="24" t="n">
         <v>12500</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="22" t="inlineStr">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B6" s="22" t="n">
+      <c r="B6" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="22" t="n">
+      <c r="C6" s="24" t="n">
         <v>18000</v>
       </c>
-      <c r="D6" s="22" t="n">
+      <c r="D6" s="24" t="n">
         <v>4400</v>
       </c>
-      <c r="E6" s="22" t="n">
+      <c r="E6" s="24" t="n">
         <v>1100</v>
       </c>
-      <c r="F6" s="22" t="n">
+      <c r="F6" s="24" t="n">
         <v>23500</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="inlineStr">
+      <c r="A7" s="24" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B7" s="22" t="n">
+      <c r="B7" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="C7" s="22" t="n">
+      <c r="C7" s="24" t="n">
         <v>18000</v>
       </c>
-      <c r="D7" s="22" t="n">
+      <c r="D7" s="24" t="n">
         <v>4400</v>
       </c>
-      <c r="E7" s="22" t="n">
+      <c r="E7" s="24" t="n">
         <v>1100</v>
       </c>
-      <c r="F7" s="22" t="n">
+      <c r="F7" s="24" t="n">
         <v>23500</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B8" s="22" t="n">
+      <c r="B8" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="C8" s="22" t="n">
+      <c r="C8" s="24" t="n">
         <v>18000</v>
       </c>
-      <c r="D8" s="22" t="n">
+      <c r="D8" s="24" t="n">
         <v>4400</v>
       </c>
-      <c r="E8" s="22" t="n">
+      <c r="E8" s="24" t="n">
         <v>1100</v>
       </c>
-      <c r="F8" s="22" t="n">
+      <c r="F8" s="24" t="n">
         <v>23500</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="inlineStr">
+      <c r="A9" s="24" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B9" s="22" t="n">
+      <c r="B9" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="22" t="n">
+      <c r="C9" s="24" t="n">
         <v>3500</v>
       </c>
-      <c r="D9" s="22" t="n">
+      <c r="D9" s="24" t="n">
         <v>11000</v>
       </c>
-      <c r="E9" s="22" t="n">
+      <c r="E9" s="24" t="n">
         <v>1100</v>
       </c>
-      <c r="F9" s="22" t="n">
+      <c r="F9" s="24" t="n">
         <v>15600</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="inlineStr">
+      <c r="A10" s="24" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B10" s="22" t="n">
+      <c r="B10" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="22" t="n">
+      <c r="C10" s="24" t="n">
         <v>7000</v>
       </c>
-      <c r="D10" s="22" t="n">
+      <c r="D10" s="24" t="n">
         <v>11000</v>
       </c>
-      <c r="E10" s="22" t="n">
+      <c r="E10" s="24" t="n">
         <v>1100</v>
       </c>
-      <c r="F10" s="22" t="n">
+      <c r="F10" s="24" t="n">
         <v>19100</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="A11" s="24" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B11" s="22" t="n">
+      <c r="B11" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="C11" s="22" t="n">
+      <c r="C11" s="24" t="n">
         <v>18000</v>
       </c>
-      <c r="D11" s="22" t="n">
+      <c r="D11" s="24" t="n">
         <v>11000</v>
       </c>
-      <c r="E11" s="22" t="n">
+      <c r="E11" s="24" t="n">
         <v>1100</v>
       </c>
-      <c r="F11" s="22" t="n">
+      <c r="F11" s="24" t="n">
         <v>30100</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="inlineStr">
+      <c r="A12" s="24" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B12" s="22" t="n">
+      <c r="B12" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="C12" s="22" t="n">
+      <c r="C12" s="24" t="n">
         <v>24000</v>
       </c>
-      <c r="D12" s="22" t="n">
+      <c r="D12" s="24" t="n">
         <v>11000</v>
       </c>
-      <c r="E12" s="22" t="n">
+      <c r="E12" s="24" t="n">
         <v>1100</v>
       </c>
-      <c r="F12" s="22" t="n">
+      <c r="F12" s="24" t="n">
         <v>36100</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="24" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B13" s="22" t="n">
+      <c r="B13" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="C13" s="22" t="n">
+      <c r="C13" s="24" t="n">
         <v>24000</v>
       </c>
-      <c r="D13" s="22" t="n">
+      <c r="D13" s="24" t="n">
         <v>11000</v>
       </c>
-      <c r="E13" s="22" t="n">
+      <c r="E13" s="24" t="n">
         <v>1100</v>
       </c>
-      <c r="F13" s="22" t="n">
+      <c r="F13" s="24" t="n">
         <v>36100</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="inlineStr">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B14" s="22" t="n">
+      <c r="B14" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="22" t="n">
+      <c r="C14" s="24" t="n">
         <v>3500</v>
       </c>
-      <c r="D14" s="22" t="n">
+      <c r="D14" s="24" t="n">
         <v>13200</v>
       </c>
-      <c r="E14" s="22" t="n">
+      <c r="E14" s="24" t="n">
         <v>1100</v>
       </c>
-      <c r="F14" s="22" t="n">
+      <c r="F14" s="24" t="n">
         <v>17800</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="inlineStr">
+      <c r="A15" s="24" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B15" s="22" t="n">
+      <c r="B15" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="22" t="n">
+      <c r="C15" s="24" t="n">
         <v>7000</v>
       </c>
-      <c r="D15" s="22" t="n">
+      <c r="D15" s="24" t="n">
         <v>13200</v>
       </c>
-      <c r="E15" s="22" t="n">
+      <c r="E15" s="24" t="n">
         <v>1100</v>
       </c>
-      <c r="F15" s="22" t="n">
+      <c r="F15" s="24" t="n">
         <v>21300</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="22" t="inlineStr">
+      <c r="A16" s="24" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B16" s="22" t="n">
+      <c r="B16" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="C16" s="22" t="n">
+      <c r="C16" s="24" t="n">
         <v>18000</v>
       </c>
-      <c r="D16" s="22" t="n">
+      <c r="D16" s="24" t="n">
         <v>13200</v>
       </c>
-      <c r="E16" s="22" t="n">
+      <c r="E16" s="24" t="n">
         <v>1100</v>
       </c>
-      <c r="F16" s="22" t="n">
+      <c r="F16" s="24" t="n">
         <v>32300</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="inlineStr">
+      <c r="A17" s="24" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B17" s="22" t="n">
+      <c r="B17" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="C17" s="22" t="n">
+      <c r="C17" s="24" t="n">
         <v>24000</v>
       </c>
-      <c r="D17" s="22" t="n">
+      <c r="D17" s="24" t="n">
         <v>13200</v>
       </c>
-      <c r="E17" s="22" t="n">
+      <c r="E17" s="24" t="n">
         <v>1100</v>
       </c>
-      <c r="F17" s="22" t="n">
+      <c r="F17" s="24" t="n">
         <v>38300</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="22" t="inlineStr">
+      <c r="A18" s="24" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B18" s="22" t="n">
+      <c r="B18" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="C18" s="22" t="n">
+      <c r="C18" s="24" t="n">
         <v>24000</v>
       </c>
-      <c r="D18" s="22" t="n">
+      <c r="D18" s="24" t="n">
         <v>13200</v>
       </c>
-      <c r="E18" s="22" t="n">
+      <c r="E18" s="24" t="n">
         <v>1100</v>
       </c>
-      <c r="F18" s="22" t="n">
+      <c r="F18" s="24" t="n">
         <v>38300</v>
       </c>
     </row>
@@ -2266,7 +2275,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>🏷️ KT 총액결합할인</t>
         </is>
@@ -2300,380 +2309,380 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="26" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="26" t="inlineStr">
         <is>
           <t>22K 이하</t>
         </is>
       </c>
-      <c r="C4" s="24" t="n">
+      <c r="C4" s="26" t="n">
         <v>1650</v>
       </c>
-      <c r="D4" s="24" t="n">
+      <c r="D4" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="24" t="n">
+      <c r="E4" s="26" t="n">
         <v>1650</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>22K 이상</t>
         </is>
       </c>
-      <c r="C5" s="24" t="n">
+      <c r="C5" s="26" t="n">
         <v>3300</v>
       </c>
-      <c r="D5" s="24" t="n">
+      <c r="D5" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="24" t="n">
+      <c r="E5" s="26" t="n">
         <v>3300</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="26" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>64.9K 이상</t>
         </is>
       </c>
-      <c r="C6" s="24" t="n">
+      <c r="C6" s="26" t="n">
         <v>5500</v>
       </c>
-      <c r="D6" s="24" t="n">
+      <c r="D6" s="26" t="n">
         <v>3300</v>
       </c>
-      <c r="E6" s="24" t="n">
+      <c r="E6" s="26" t="n">
         <v>8800</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="26" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>108.9K 이상</t>
         </is>
       </c>
-      <c r="C7" s="24" t="n">
+      <c r="C7" s="26" t="n">
         <v>5500</v>
       </c>
-      <c r="D7" s="24" t="n">
+      <c r="D7" s="26" t="n">
         <v>14300</v>
       </c>
-      <c r="E7" s="24" t="n">
+      <c r="E7" s="26" t="n">
         <v>19800</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="26" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>141.9K 이상</t>
         </is>
       </c>
-      <c r="C8" s="24" t="n">
+      <c r="C8" s="26" t="n">
         <v>5500</v>
       </c>
-      <c r="D8" s="24" t="n">
+      <c r="D8" s="26" t="n">
         <v>18700</v>
       </c>
-      <c r="E8" s="24" t="n">
+      <c r="E8" s="26" t="n">
         <v>24200</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="26" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>174.9K 이상</t>
         </is>
       </c>
-      <c r="C9" s="24" t="n">
+      <c r="C9" s="26" t="n">
         <v>5500</v>
       </c>
-      <c r="D9" s="24" t="n">
+      <c r="D9" s="26" t="n">
         <v>23100</v>
       </c>
-      <c r="E9" s="24" t="n">
+      <c r="E9" s="26" t="n">
         <v>28600</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="26" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>22K 이하</t>
         </is>
       </c>
-      <c r="C10" s="24" t="n">
+      <c r="C10" s="26" t="n">
         <v>2200</v>
       </c>
-      <c r="D10" s="24" t="n">
+      <c r="D10" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="24" t="n">
+      <c r="E10" s="26" t="n">
         <v>2200</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="A11" s="26" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="26" t="inlineStr">
         <is>
           <t>22K 이상</t>
         </is>
       </c>
-      <c r="C11" s="24" t="n">
+      <c r="C11" s="26" t="n">
         <v>5500</v>
       </c>
-      <c r="D11" s="24" t="n">
+      <c r="D11" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="24" t="n">
+      <c r="E11" s="26" t="n">
         <v>5500</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="A12" s="26" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>64.9K 이상</t>
         </is>
       </c>
-      <c r="C12" s="24" t="n">
+      <c r="C12" s="26" t="n">
         <v>5500</v>
       </c>
-      <c r="D12" s="24" t="n">
+      <c r="D12" s="26" t="n">
         <v>5500</v>
       </c>
-      <c r="E12" s="24" t="n">
+      <c r="E12" s="26" t="n">
         <v>11000</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="26" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B13" s="24" t="inlineStr">
+      <c r="B13" s="26" t="inlineStr">
         <is>
           <t>108.9K 이상</t>
         </is>
       </c>
-      <c r="C13" s="24" t="n">
+      <c r="C13" s="26" t="n">
         <v>5500</v>
       </c>
-      <c r="D13" s="24" t="n">
+      <c r="D13" s="26" t="n">
         <v>16610</v>
       </c>
-      <c r="E13" s="24" t="n">
+      <c r="E13" s="26" t="n">
         <v>22110</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="A14" s="26" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B14" s="24" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>141.9K 이상</t>
         </is>
       </c>
-      <c r="C14" s="24" t="n">
+      <c r="C14" s="26" t="n">
         <v>5500</v>
       </c>
-      <c r="D14" s="24" t="n">
+      <c r="D14" s="26" t="n">
         <v>22110</v>
       </c>
-      <c r="E14" s="24" t="n">
+      <c r="E14" s="26" t="n">
         <v>27610</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="A15" s="26" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B15" s="24" t="inlineStr">
+      <c r="B15" s="26" t="inlineStr">
         <is>
           <t>174.9K 이상</t>
         </is>
       </c>
-      <c r="C15" s="24" t="n">
+      <c r="C15" s="26" t="n">
         <v>5500</v>
       </c>
-      <c r="D15" s="24" t="n">
+      <c r="D15" s="26" t="n">
         <v>27610</v>
       </c>
-      <c r="E15" s="24" t="n">
+      <c r="E15" s="26" t="n">
         <v>33110</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="24" t="inlineStr">
+      <c r="A16" s="26" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B16" s="24" t="inlineStr">
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>22K 이하</t>
         </is>
       </c>
-      <c r="C16" s="24" t="n">
+      <c r="C16" s="26" t="n">
         <v>2200</v>
       </c>
-      <c r="D16" s="24" t="n">
+      <c r="D16" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="24" t="n">
+      <c r="E16" s="26" t="n">
         <v>2200</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="inlineStr">
+      <c r="A17" s="26" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>22K 이상</t>
         </is>
       </c>
-      <c r="C17" s="24" t="n">
+      <c r="C17" s="26" t="n">
         <v>5500</v>
       </c>
-      <c r="D17" s="24" t="n">
+      <c r="D17" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="24" t="n">
+      <c r="E17" s="26" t="n">
         <v>5500</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="inlineStr">
+      <c r="A18" s="26" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B18" s="24" t="inlineStr">
+      <c r="B18" s="26" t="inlineStr">
         <is>
           <t>64.9K 이상</t>
         </is>
       </c>
-      <c r="C18" s="24" t="n">
+      <c r="C18" s="26" t="n">
         <v>5500</v>
       </c>
-      <c r="D18" s="24" t="n">
+      <c r="D18" s="26" t="n">
         <v>5500</v>
       </c>
-      <c r="E18" s="24" t="n">
+      <c r="E18" s="26" t="n">
         <v>11000</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="24" t="inlineStr">
+      <c r="A19" s="26" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B19" s="24" t="inlineStr">
+      <c r="B19" s="26" t="inlineStr">
         <is>
           <t>108.9K 이상</t>
         </is>
       </c>
-      <c r="C19" s="24" t="n">
+      <c r="C19" s="26" t="n">
         <v>5500</v>
       </c>
-      <c r="D19" s="24" t="n">
+      <c r="D19" s="26" t="n">
         <v>16610</v>
       </c>
-      <c r="E19" s="24" t="n">
+      <c r="E19" s="26" t="n">
         <v>22110</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="24" t="inlineStr">
+      <c r="A20" s="26" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B20" s="24" t="inlineStr">
+      <c r="B20" s="26" t="inlineStr">
         <is>
           <t>141.9K 이상</t>
         </is>
       </c>
-      <c r="C20" s="24" t="n">
+      <c r="C20" s="26" t="n">
         <v>5500</v>
       </c>
-      <c r="D20" s="24" t="n">
+      <c r="D20" s="26" t="n">
         <v>22110</v>
       </c>
-      <c r="E20" s="24" t="n">
+      <c r="E20" s="26" t="n">
         <v>27610</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="24" t="inlineStr">
+      <c r="A21" s="26" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B21" s="24" t="inlineStr">
+      <c r="B21" s="26" t="inlineStr">
         <is>
           <t>174.9K 이상</t>
         </is>
       </c>
-      <c r="C21" s="24" t="n">
+      <c r="C21" s="26" t="n">
         <v>5500</v>
       </c>
-      <c r="D21" s="24" t="n">
+      <c r="D21" s="26" t="n">
         <v>27610</v>
       </c>
-      <c r="E21" s="24" t="n">
+      <c r="E21" s="26" t="n">
         <v>33110</v>
       </c>
     </row>
@@ -2698,7 +2707,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>🏷️ KT 정액결합할인</t>
         </is>
@@ -2727,66 +2736,66 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="26" t="inlineStr">
         <is>
           <t>37K 이하</t>
         </is>
       </c>
-      <c r="B4" s="24" t="n">
+      <c r="B4" s="26" t="n">
         <v>5500</v>
       </c>
-      <c r="C4" s="24" t="n">
+      <c r="C4" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="24" t="n">
+      <c r="D4" s="26" t="n">
         <v>5500</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>37K 이상</t>
         </is>
       </c>
-      <c r="B5" s="24" t="n">
+      <c r="B5" s="26" t="n">
         <v>5500</v>
       </c>
-      <c r="C5" s="24" t="n">
+      <c r="C5" s="26" t="n">
         <v>3000</v>
       </c>
-      <c r="D5" s="24" t="n">
+      <c r="D5" s="26" t="n">
         <v>8500</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="26" t="inlineStr">
         <is>
           <t>61K 이상</t>
         </is>
       </c>
-      <c r="B6" s="24" t="n">
+      <c r="B6" s="26" t="n">
         <v>5500</v>
       </c>
-      <c r="C6" s="24" t="n">
+      <c r="C6" s="26" t="n">
         <v>5000</v>
       </c>
-      <c r="D6" s="24" t="n">
+      <c r="D6" s="26" t="n">
         <v>10500</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="26" t="inlineStr">
         <is>
           <t>77K 이상</t>
         </is>
       </c>
-      <c r="B7" s="24" t="n">
+      <c r="B7" s="26" t="n">
         <v>5500</v>
       </c>
-      <c r="C7" s="24" t="n">
+      <c r="C7" s="26" t="n">
         <v>7000</v>
       </c>
-      <c r="D7" s="24" t="n">
+      <c r="D7" s="26" t="n">
         <v>12500</v>
       </c>
     </row>
@@ -2811,14 +2820,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="25" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>💎 KT 프리미엄 가족결합</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="26" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>자격: 77K↑ 요금제 2회선 이상 | 대표자 총액결합만 | 인터넷 -5,500 고정</t>
         </is>
@@ -2847,162 +2856,162 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="n">
+      <c r="A6" s="28" t="n">
         <v>77000</v>
       </c>
-      <c r="B6" s="27" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>77,000원 (임계값)</t>
         </is>
       </c>
-      <c r="C6" s="27" t="n">
+      <c r="C6" s="28" t="n">
         <v>19250</v>
       </c>
-      <c r="D6" s="27" t="inlineStr">
+      <c r="D6" s="28" t="inlineStr">
         <is>
           <t>≈25%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="n">
+      <c r="A7" s="28" t="n">
         <v>80000</v>
       </c>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>80,000원 (5G 슈퍼플랜 베이직)</t>
         </is>
       </c>
-      <c r="C7" s="27" t="n">
+      <c r="C7" s="28" t="n">
         <v>20000</v>
       </c>
-      <c r="D7" s="27" t="inlineStr">
+      <c r="D7" s="28" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="n">
+      <c r="A8" s="28" t="n">
         <v>87890</v>
       </c>
-      <c r="B8" s="27" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>87,890원 (데이터선택 87.8)</t>
         </is>
       </c>
-      <c r="C8" s="27" t="n">
+      <c r="C8" s="28" t="n">
         <v>22000</v>
       </c>
-      <c r="D8" s="27" t="inlineStr">
+      <c r="D8" s="28" t="inlineStr">
         <is>
           <t>≈25%</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="n">
+      <c r="A9" s="28" t="n">
         <v>89000</v>
       </c>
-      <c r="B9" s="27" t="inlineStr">
+      <c r="B9" s="28" t="inlineStr">
         <is>
           <t>89,000원 (데이터ON 프리미엄)</t>
         </is>
       </c>
-      <c r="C9" s="27" t="n">
+      <c r="C9" s="28" t="n">
         <v>22250</v>
       </c>
-      <c r="D9" s="27" t="inlineStr">
+      <c r="D9" s="28" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="n">
+      <c r="A10" s="28" t="n">
         <v>90000</v>
       </c>
-      <c r="B10" s="27" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>90,000원 (슈퍼플랜 베이직 Plus/초이스)</t>
         </is>
       </c>
-      <c r="C10" s="27" t="n">
+      <c r="C10" s="28" t="n">
         <v>22500</v>
       </c>
-      <c r="D10" s="27" t="inlineStr">
+      <c r="D10" s="28" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="n">
+      <c r="A11" s="28" t="n">
         <v>100000</v>
       </c>
-      <c r="B11" s="27" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>100,000원 (슈퍼플랜 스페셜)</t>
         </is>
       </c>
-      <c r="C11" s="27" t="n">
+      <c r="C11" s="28" t="n">
         <v>25000</v>
       </c>
-      <c r="D11" s="27" t="inlineStr">
+      <c r="D11" s="28" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="27" t="n">
+      <c r="A12" s="28" t="n">
         <v>109000</v>
       </c>
-      <c r="B12" s="27" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>109,000원 (데이터선택 109)</t>
         </is>
       </c>
-      <c r="C12" s="27" t="n">
+      <c r="C12" s="28" t="n">
         <v>27500</v>
       </c>
-      <c r="D12" s="27" t="inlineStr">
+      <c r="D12" s="28" t="inlineStr">
         <is>
           <t>≈25%</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="n">
+      <c r="A13" s="28" t="n">
         <v>110000</v>
       </c>
-      <c r="B13" s="27" t="inlineStr">
+      <c r="B13" s="28" t="inlineStr">
         <is>
           <t>110,000원 (슈퍼플랜 스페셜 Plus/초이스)</t>
         </is>
       </c>
-      <c r="C13" s="27" t="n">
+      <c r="C13" s="28" t="n">
         <v>27500</v>
       </c>
-      <c r="D13" s="27" t="inlineStr">
+      <c r="D13" s="28" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="n">
+      <c r="A14" s="28" t="n">
         <v>130000</v>
       </c>
-      <c r="B14" s="27" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>130,000원 (슈퍼플랜 프리미엄/초이스)</t>
         </is>
       </c>
-      <c r="C14" s="27" t="n">
+      <c r="C14" s="28" t="n">
         <v>32500</v>
       </c>
-      <c r="D14" s="27" t="inlineStr">
+      <c r="D14" s="28" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -3034,7 +3043,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="28" t="inlineStr">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>🏷️ LG U+ 참쉬운가족결합</t>
         </is>
@@ -3063,23 +3072,23 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>인터넷 할인 (3년)</t>
         </is>
       </c>
-      <c r="B4" s="29" t="n">
+      <c r="B4" s="30" t="n">
         <v>5500</v>
       </c>
-      <c r="C4" s="29" t="n">
+      <c r="C4" s="30" t="n">
         <v>9900</v>
       </c>
-      <c r="D4" s="29" t="n">
+      <c r="D4" s="30" t="n">
         <v>13200</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="30" t="inlineStr">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>휴대폰 할인 매트릭스 (인당)</t>
         </is>
@@ -3108,50 +3117,50 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>69K 미만</t>
         </is>
       </c>
-      <c r="B8" s="29" t="n">
+      <c r="B8" s="30" t="n">
         <v>2200</v>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="30" t="n">
         <v>3300</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="30" t="n">
         <v>4400</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>69K 이상</t>
         </is>
       </c>
-      <c r="B9" s="29" t="n">
+      <c r="B9" s="30" t="n">
         <v>3300</v>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="30" t="n">
         <v>5500</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="30" t="n">
         <v>6600</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>88K 이상</t>
         </is>
       </c>
-      <c r="B10" s="29" t="n">
+      <c r="B10" s="30" t="n">
         <v>4400</v>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="30" t="n">
         <v>6600</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="30" t="n">
         <v>8800</v>
       </c>
     </row>
@@ -3176,14 +3185,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="28" t="inlineStr">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>🏷️ LG U+ 투게더 결합 (85K↑)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="26" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>자격: 5G 85K↑ + 500M+ 인터넷 (100M 결합 불가)</t>
         </is>
@@ -3212,20 +3221,20 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>인터넷 할인</t>
         </is>
       </c>
-      <c r="B6" s="29" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>불가</t>
         </is>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="30" t="n">
         <v>11000</v>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="30" t="n">
         <v>11000</v>
       </c>
     </row>
@@ -3242,32 +3251,32 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>2회선</t>
         </is>
       </c>
-      <c r="B9" s="29" t="n">
+      <c r="B9" s="30" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>3회선</t>
         </is>
       </c>
-      <c r="B10" s="29" t="n">
+      <c r="B10" s="30" t="n">
         <v>14000</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t>4~5회선</t>
         </is>
       </c>
-      <c r="B11" s="29" t="n">
+      <c r="B11" s="30" t="n">
         <v>20000</v>
       </c>
     </row>
@@ -3299,149 +3308,149 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="31" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>interface CarrierData {</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="31" t="inlineStr">
+      <c r="A4" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  name: string; prefix: string;</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="31" t="inlineStr">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  internet: Record&lt;"100M"|"500M"|"1G", number&gt;;</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="31" t="inlineStr">
+      <c r="A6" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  wifiCost?: number; wifiPrice?: Record&lt;Speed, number&gt;;</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="31" t="inlineStr">
+      <c r="A7" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  setTopOptions: SetTop[]; wifiOptions: WiFi[];</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="31" t="inlineStr">
+      <c r="A8" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  tvInternetNoWifi: Record&lt;Speed, number&gt;;</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  tvInternetWithWifi: Record&lt;Speed, number&gt;;</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  tv: TVProduct[];</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="A11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  install: { solo: number; combo: number };</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="A12" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  gift: { solo: SpeedMap; combo: SpeedMap };</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="31" t="inlineStr">
+      <c r="A13" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  bundle: BundleConfig;</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="32" t="inlineStr">
         <is>
           <t>}</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="31" t="inlineStr"/>
+      <c r="A15" s="32" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="31" t="inlineStr">
+      <c r="A16" s="32" t="inlineStr">
         <is>
           <t>interface TVProduct { n: string; p: number; dc: number; }</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="31" t="inlineStr">
+      <c r="A17" s="32" t="inlineStr">
         <is>
           <t>interface SetTop { id, name, fee, isDefault?, active }</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="31" t="inlineStr">
+      <c r="A18" s="32" t="inlineStr">
         <is>
           <t>interface WiFi { id, name, fees: SpeedMap, isDefault?, active }</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="31" t="inlineStr"/>
+      <c r="A19" s="32" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="31" t="inlineStr">
+      <c r="A20" s="32" t="inlineStr">
         <is>
           <t>// BundleConfig — 통신사별 상이:</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="31" t="inlineStr">
+      <c r="A21" s="32" t="inlineStr">
         <is>
           <t>// SKT: { family: { internet, iptv, mobilePerBySpeed } }</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="31" t="inlineStr">
+      <c r="A22" s="32" t="inlineStr">
         <is>
           <t>// KT: { ranges_total, total, ranges_fixed, fixed, premium }</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="31" t="inlineStr">
+      <c r="A23" s="32" t="inlineStr">
         <is>
           <t>// LGU: { chweyswun: { internet, planLabels, mobile[][]} , together: { internet, mobile[] } }</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="31" t="inlineStr"/>
+      <c r="A24" s="32" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="31" t="inlineStr">
+      <c r="A25" s="32" t="inlineStr">
         <is>
           <t>type Speed = "100M" | "500M" | "1G";</t>
         </is>
@@ -3473,42 +3482,42 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="32" t="inlineStr">
+      <c r="A3" s="33" t="inlineStr">
         <is>
           <t>⚠️ 3사 결합할인 적용 방식 핵심 차이</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="33" t="inlineStr">
+      <c r="A4" s="34" t="inlineStr">
         <is>
           <t>• SKT 요즘가족결합: 단독가 REPLACE (요즘우리집 대체) → tvInternet 값 사용 안함</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="33" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>• KT 총액/정액: 기본 TV결합할인 + 추가할인 STACK (중복 적용)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="33" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>• KT 프리미엄: 대표자+일반구성원은 총액결합, 77K↑ 구성원은 프리미엄 (독립)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="33" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>• LG U+ 참쉬운: 단독가 REPLACE</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="33" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>• LG U+ 투게더: 단독가 REPLACE + 100M 결합 불가</t>
         </is>
@@ -3522,60 +3531,60 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="A12" s="35" t="inlineStr">
         <is>
           <t>기본 월요금 (결합없음)</t>
         </is>
       </c>
-      <c r="B12" s="35" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>base = (TV있?(tvInetWithWifi[sp]+tvFinal+setTop):(internet[sp]+wifiFee))</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="34" t="inlineStr">
+      <c r="A13" s="35" t="inlineStr">
         <is>
           <t>SKT REPLACE</t>
         </is>
       </c>
-      <c r="B13" s="35" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>bundleFee = (internet[sp]+wifiFee - famInet) + (tvP - tvDc - iptv) + setTop</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="34" t="inlineStr">
+      <c r="A14" s="35" t="inlineStr">
         <is>
           <t>KT STACK</t>
         </is>
       </c>
-      <c r="B14" s="35" t="inlineStr">
+      <c r="B14" s="36" t="inlineStr">
         <is>
           <t>bundleFee = (tvInet(wifi) - totalInet) + (tvP - tvDc) + setTop</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="35" t="inlineStr">
         <is>
           <t>LGU REPLACE</t>
         </is>
       </c>
-      <c r="B15" s="35" t="inlineStr">
+      <c r="B15" s="36" t="inlineStr">
         <is>
           <t>bundleFee = (internet[sp] - chwInet) + (tvP - tvDc) + setTop</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="34" t="inlineStr">
+      <c r="A16" s="35" t="inlineStr">
         <is>
           <t>혜택가</t>
         </is>
       </c>
-      <c r="B16" s="35" t="inlineStr">
+      <c r="B16" s="36" t="inlineStr">
         <is>
           <t>finalFee = bundleFee - 휴대폰_고지서_별도_차감</t>
         </is>
@@ -4116,6 +4125,11 @@
         <f>IF(B5="100M",22000,IF(B5="500M",33000,38500))</f>
         <v/>
       </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>→ 01_Internet 시트 · 3사 동일 요금</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>LG U+</t>
@@ -4143,6 +4157,11 @@
         <f>IFERROR(SUMPRODUCT(($G$2:$G$22=B4)*($H$2:$H$22=B6)*($I$2:$I$22)),0)</f>
         <v/>
       </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>→ 02_TV 시트 · 통신사+상품명 조회 (숨김 G~J)</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>LG U+</t>
@@ -4170,6 +4189,11 @@
         <f>IFERROR(SUMPRODUCT(($G$2:$G$22=B4)*($H$2:$H$22=B6)*($J$2:$J$22)),0)</f>
         <v/>
       </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>→ 02_TV 시트 · 인터넷 결합 시 TV 할인</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>LG U+</t>
@@ -4197,6 +4221,11 @@
         <f>IF(B6="TV 없음",0,1)</f>
         <v/>
       </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>0 = 인터넷 단독 / 1 = TV 결합</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
@@ -4208,6 +4237,11 @@
         <f>IF(B7="N",0,IF(B4="SKT",1100,IF(B4="KT",IF(B5="1G",0,1100),0)))</f>
         <v/>
       </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>→ 05_WiFi 기본 모델 · SKT 1,100 / KT 100M·500M 1,100, 1G 무료 / LGU+ 전속도 무료</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -4219,6 +4253,11 @@
         <f>IF(B4="SKT",IF(B5="100M",19800,IF(B5="500M",27500,33000)),IF(B4="KT",IF(B5="100M",22000,IF(B5="500M",27500,33000)),IF(B5="100M",22000,IF(B5="500M",27500,33000))))</f>
         <v/>
       </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>→ 03_TV_Internet 시트 · TV 결합 시 인터넷가 (WiFi 미포함)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
@@ -4230,6 +4269,11 @@
         <f>IF(B4="SKT",IF(B5="100M",22000,IF(B5="500M",28600,34100)),IF(B4="KT",IF(B5="100M",23100,IF(B5="500M",28600,33000)),IF(B5="100M",22000,IF(B5="500M",27500,33000))))</f>
         <v/>
       </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>→ 03_TV_Internet 시트 · TV+WiFi 결합 시 인터넷가</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
@@ -4241,27 +4285,32 @@
         <f>4400</f>
         <v/>
       </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>→ 04_SetTop 기본 모델 · SKT 스마트3 / KT 기가지니3 / LGU+ U+tv UHD4 (모두 4,400원)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="inlineStr">
+      <c r="A29" s="17" t="inlineStr">
         <is>
           <t>【경로 A】 결합없음 / 기본 TV 결합만</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="17" t="inlineStr">
+      <c r="A30" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  기본 월요금</t>
         </is>
       </c>
-      <c r="B30" s="18">
+      <c r="B30" s="19">
         <f>IF(B23=0,B24+B24,IF(B7="Y",B26,B25)+(B21-B22)+B27)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="19" t="inlineStr">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>【경로 B】 휴대폰 결합 할인 적용</t>
         </is>
@@ -4277,6 +4326,11 @@
         <f>IF(AND(B4="SKT",B8="요즘가족결합",B9&gt;0),IF(B5="100M",4400,IF(B5="500M",11000,13200)),0)</f>
         <v/>
       </c>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>→ 10_SKT_Bundle · 단독가 REPLACE 방식</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
@@ -4288,6 +4342,11 @@
         <f>IF(AND(B4="SKT",B8="요즘가족결합",B9&gt;0,B23=1),1100,0)</f>
         <v/>
       </c>
+      <c r="C34" s="16" t="inlineStr">
+        <is>
+          <t>TV 결합 시에만 추가 -1,100원</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
@@ -4299,6 +4358,11 @@
         <f>IF(AND(B4="SKT",B8="요즘가족결합",B9&gt;0),IF(B5="100M",CHOOSE(B9,3500,3500,6000,4500,3600),CHOOSE(B9,3500,3500,6000,6000,4800)),0)</f>
         <v/>
       </c>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>→ 10_SKT_Bundle · 속도+회선수별 인당</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
@@ -4310,6 +4374,11 @@
         <f>B35*IF(AND(B4="SKT",B8="요즘가족결합"),B9,0)</f>
         <v/>
       </c>
+      <c r="C36" s="16" t="inlineStr">
+        <is>
+          <t>인당 × 회선수 (휴대폰 고지서 별도 차감)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
@@ -4321,6 +4390,11 @@
         <f>IF(AND(B4="KT",B8="총액결합"),IF(B5="100M",CHOOSE(B10,1650,3300,5500,5500,5500,5500),CHOOSE(B10,2200,5500,5500,5500,5500,5500)),0)</f>
         <v/>
       </c>
+      <c r="C37" s="16" t="inlineStr">
+        <is>
+          <t>→ 11_KT_Total · 구간 1~6 · 기본 TV결합과 STACK</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
@@ -4332,6 +4406,11 @@
         <f>IF(AND(B4="KT",B8="총액결합"),IF(B5="100M",CHOOSE(B10,0,0,3300,14300,18700,23100),CHOOSE(B10,0,0,5500,16610,22110,27610)),0)</f>
         <v/>
       </c>
+      <c r="C38" s="16" t="inlineStr">
+        <is>
+          <t>→ 11_KT_Total · 휴대폰 고지서 별도 차감</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
@@ -4343,6 +4422,11 @@
         <f>IF(AND(B4="LG U+",B8="참쉬운 가족결합",B9&gt;=2),IF(B5="100M",5500,IF(B5="500M",9900,13200)),0)</f>
         <v/>
       </c>
+      <c r="C39" s="16" t="inlineStr">
+        <is>
+          <t>→ 14_LGU_Chweyswun · 단독가 REPLACE · 2회선부터</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
@@ -4354,6 +4438,11 @@
         <f>IF(AND(B4="LG U+",B8="참쉬운 가족결합",B9&gt;=2),CHOOSE(B10,CHOOSE(MIN(B9,4)-1,2200,3300,4400),CHOOSE(MIN(B9,4)-1,3300,5500,6600),CHOOSE(MIN(B9,4)-1,4400,6600,8800)),0)</f>
         <v/>
       </c>
+      <c r="C40" s="16" t="inlineStr">
+        <is>
+          <t>→ 14_LGU_Chweyswun · 요금구간(1~3) × 회선(2~4+)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
@@ -4365,6 +4454,11 @@
         <f>B40*IF(AND(B4="LG U+",B8="참쉬운 가족결합"),MIN(B9,4),0)</f>
         <v/>
       </c>
+      <c r="C41" s="16" t="inlineStr">
+        <is>
+          <t>인당 × 회선수</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
@@ -4374,12 +4468,12 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="17" t="inlineStr">
+      <c r="A44" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  인터넷+TV 월 실납부 (결합 적용)</t>
         </is>
       </c>
-      <c r="B44" s="18">
+      <c r="B44" s="19">
         <f>IF(B8="결합없음",B30,IF(AND(B4="SKT",B8="요즘가족결합"),(B20+B24-B33)+IF(B23=1,B21-B22-B34+B27,0),IF(AND(B4="KT",B8="총액결합"),IF(B23=0,B20+B24-B37,(IF(B7="Y",B26,B25)-B37)+(B21-B22)+B27),IF(AND(B4="LG U+",B8="참쉬운 가족결합"),(B20+B24-B39)+IF(B23=1,B21-B22+B27,0),B30))))</f>
         <v/>
       </c>
@@ -4396,18 +4490,18 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="17" t="inlineStr">
+      <c r="A46" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  🎉 혜택가 (최종 월요금)</t>
         </is>
       </c>
-      <c r="B46" s="20">
+      <c r="B46" s="21">
         <f>B44-(B36+B38+B41)</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="16" t="inlineStr">
+      <c r="A48" s="17" t="inlineStr">
         <is>
           <t>🎁 부가 (참고)</t>
         </is>
@@ -4436,15 +4530,32 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="25">
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="C27:E27"/>
     <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C33:E33"/>
     <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="C26:E26"/>
     <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C25:E25"/>
   </mergeCells>
   <dataValidations count="7">
     <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -5251,7 +5362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5260,6 +5371,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -5270,94 +5382,46 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
+        <is>
+          <t>💬 기본값(isDefault) 선정 기준: 매장 판매량 1위 · 가격 대비 기능 균형 · 고객 선호 · 요금 계산 시 기본 적용</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>통신사</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>모델명</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>월 임대료</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>smart3</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>스마트3</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>4400</v>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>smart3-mini</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>스마트3 미니</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>4400</v>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>💬 설명</t>
         </is>
       </c>
     </row>
@@ -5369,25 +5433,30 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>ai-nugu</t>
+          <t>smart3</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>AI NUGU</t>
+          <t>스마트3</t>
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>6600</v>
+        <v>4400</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
           <t>O</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>✅ 기본값 · SKT 표준 셋톱 · OTT 대부분 지원 · 매장 판매 1위</t>
         </is>
       </c>
     </row>
@@ -5399,16 +5468,16 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>sound-max</t>
+          <t>smart3-mini</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>사운드 맥스</t>
+          <t>스마트3 미니</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>8800</v>
+        <v>4400</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
@@ -5418,6 +5487,11 @@
       <c r="F7" s="5" t="inlineStr">
         <is>
           <t>O</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>저가형 · 일부 OTT(넷플릭스 등) 미지원</t>
         </is>
       </c>
     </row>
@@ -5429,12 +5503,12 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>apple-tv</t>
+          <t>ai-nugu</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>애플TV</t>
+          <t>AI NUGU</t>
         </is>
       </c>
       <c r="D8" s="5" t="n">
@@ -5450,55 +5524,65 @@
           <t>O</t>
         </is>
       </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>AI 음성인식 특화 · 가격 인상형</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>SKT</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>genie-3</t>
+          <t>sound-max</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>기가지니3</t>
+          <t>사운드 맥스</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>4400</v>
+        <v>8800</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>사운드바 일체형 · OTT 거의 불가</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>SKT</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>genie-a</t>
+          <t>apple-tv</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>기가지니A</t>
+          <t>애플TV</t>
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>3300</v>
+        <v>6600</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
@@ -5508,6 +5592,11 @@
       <c r="F10" s="5" t="inlineStr">
         <is>
           <t>O</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>아이폰 연동형 · 쿠팡/애플TV 특화</t>
         </is>
       </c>
     </row>
@@ -5519,89 +5608,177 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>soundbar</t>
+          <t>genie-3</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>지니TV 올인원 사운드바</t>
+          <t>기가지니3</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>8800</v>
+        <v>4400</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
           <t>O</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>✅ 기본값 · KT 대표 모델 · AI 블루투스 스피커 일체 · 고객 선호 1위</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>LG U+</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>uhd4</t>
+          <t>genie-a</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>U+tv UHD4</t>
+          <t>기가지니A</t>
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>4400</v>
+        <v>3300</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>저가형 (3,300원) · 기본 기능만</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>soundbar</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>지니TV 올인원 사운드바</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>8800</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>사운드바+공유기 일체 · 고가형</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
           <t>LG U+</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>uhd4</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>U+tv UHD4</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>4400</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>✅ 기본값 · LG U+ 표준 · AI 음향기술 탑재</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>soundbar-black</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>U+tv 사운드바 블랙</t>
         </is>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="D15" s="5" t="n">
         <v>6600</v>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>돌비비전 지원 고급형</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:G3"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5612,17 +5789,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -5633,116 +5811,56 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
+        <is>
+          <t>💬 기본값 선정 기준: 속도별 단가가 낮은 표준 모델 · 가입 시 자동 지급 · 요금 계산 기본 대상</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>통신사</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>모델명</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>giga-wifi</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>GIGA WiFi</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>1100</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>1100</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>1100</v>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>giga-wifi-6</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>GIGA WiFi 6</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>1100</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>1100</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>1100</v>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>💬 설명</t>
         </is>
       </c>
     </row>
@@ -5754,31 +5872,36 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>giga-wifi-prem</t>
+          <t>giga-wifi</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>GIGA WiFi 프리미엄</t>
+          <t>GIGA WiFi</t>
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>5500</v>
+        <v>1100</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>5500</v>
+        <v>1100</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>5500</v>
+        <v>1100</v>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
           <t>O</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>✅ 기본값 · SKT 표준 WiFi · 속도 관계없이 1,100원 균일</t>
         </is>
       </c>
     </row>
@@ -5790,22 +5913,22 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>wings</t>
+          <t>giga-wifi-6</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>윙즈</t>
+          <t>GIGA WiFi 6</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1650</v>
+        <v>1100</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1650</v>
+        <v>1100</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1650</v>
+        <v>1100</v>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
@@ -5815,69 +5938,79 @@
       <c r="H7" s="5" t="inlineStr">
         <is>
           <t>O</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>WiFi-6 지원 · 같은 요금이나 수요 부족으로 비활성</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>SKT</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>wave2</t>
+          <t>giga-wifi-prem</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>KT GIGA WAVE2</t>
+          <t>GIGA WiFi 프리미엄</t>
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>1100</v>
+        <v>5500</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1100</v>
+        <v>5500</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0</v>
+        <v>5500</v>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>최대 1.7Gbps · 고급 사용자용 · 인터넷+TV 결합 시 3,300 할인</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>SKT</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>home-ax</t>
+          <t>wings</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>GIGA WIFI 홈AX</t>
+          <t>윙즈</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0</v>
+        <v>1650</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1100</v>
+        <v>1650</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0</v>
+        <v>1650</v>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
@@ -5887,6 +6020,11 @@
       <c r="H9" s="5" t="inlineStr">
         <is>
           <t>O</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>WiFi 증폭기 · 기존 WiFi에 추가</t>
         </is>
       </c>
     </row>
@@ -5898,31 +6036,36 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>buddy</t>
+          <t>wave2</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>GIGA WIFI BUDDY</t>
+          <t>KT GIGA WAVE2</t>
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>1650</v>
+        <v>1100</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>1650</v>
+        <v>1100</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>1650</v>
+        <v>0</v>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
           <t>O</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>✅ 기본값 · KT 표준 · 1G 속도 시 무료 제공 (요금 변동 없음)</t>
         </is>
       </c>
     </row>
@@ -5934,22 +6077,22 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>prem-24</t>
+          <t>home-ax</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>GIGA WIFI 프리미엄 2.4</t>
+          <t>GIGA WIFI 홈AX</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>4400</v>
+        <v>0</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>4400</v>
+        <v>1100</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>4400</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
@@ -5959,6 +6102,11 @@
       <c r="H11" s="5" t="inlineStr">
         <is>
           <t>O</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>WiFi-6 · 100M/1G 무료, 500M만 유료</t>
         </is>
       </c>
     </row>
@@ -5970,22 +6118,22 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>prem-24-6e</t>
+          <t>buddy</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>GIGA WIFI 프리미엄 2.4 (6E)</t>
+          <t>GIGA WIFI BUDDY</t>
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>4400</v>
+        <v>1650</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>4400</v>
+        <v>1650</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>4400</v>
+        <v>1650</v>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
@@ -5995,6 +6143,11 @@
       <c r="H12" s="5" t="inlineStr">
         <is>
           <t>O</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>WiFi 증폭기 · 홈AX와 호환</t>
         </is>
       </c>
     </row>
@@ -6006,12 +6159,12 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>prem-48</t>
+          <t>prem-24</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>GIGA WIFI 프리미엄 4.8</t>
+          <t>GIGA WIFI 프리미엄 2.4</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -6033,67 +6186,77 @@
           <t>O</t>
         </is>
       </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>최대 10Gbps 고급형 · 2.4GHz</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>LG U+</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>giga-wifi</t>
+          <t>prem-24-6e</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>기가와이파이</t>
+          <t>GIGA WIFI 프리미엄 2.4 (6E)</t>
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>0</v>
+        <v>4400</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0</v>
+        <v>4400</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0</v>
+        <v>4400</v>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>2.4GHz + 6E 지원</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>LG U+</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>giga-wifi-6</t>
+          <t>prem-48</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>기가와이파이6</t>
+          <t>GIGA WIFI 프리미엄 4.8</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>0</v>
+        <v>4400</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0</v>
+        <v>4400</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0</v>
+        <v>4400</v>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
@@ -6103,6 +6266,11 @@
       <c r="H15" s="5" t="inlineStr">
         <is>
           <t>O</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>4.8GHz 대역</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6282,12 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>giga-wifi-mesh</t>
+          <t>giga-wifi</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>기가와이파이 메쉬</t>
+          <t>기가와이파이</t>
         </is>
       </c>
       <c r="D16" s="5" t="n">
@@ -6133,16 +6301,106 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>✅ 기본값 · LG U+ 전 속도 무료 · 대표 WiFi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>giga-wifi-6</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>기가와이파이6</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
           <t>X</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>WiFi-6 · 500M+ 가입 시 기본 (동일 무료)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>giga-wifi-mesh</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>기가와이파이 메쉬</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>메쉬 지원 · 500M+ 선택 가능</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:I3"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/bongi-calculator-data.xlsx
+++ b/docs/bongi-calculator-data.xlsx
@@ -8,23 +8,25 @@
   </bookViews>
   <sheets>
     <sheet name="INDEX" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="🧮 CALC" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="01_Internet" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="02_TV" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="03_TV_Internet" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="04_SetTop" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="05_WiFi" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="06_Install" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="07_Gift" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="08_Cards" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="10_SKT_Bundle" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="11_KT_Total" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="12_KT_Fixed" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="13_KT_Premium" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="14_LGU_Chweyswun" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="15_LGU_Together" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="20_Schema" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="30_CALC_Formula" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="🧮 SKT 계산기" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="🧮 KT 계산기" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="🧮 LG U+ 계산기" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="01_Internet" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="02_TV" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="03_TV_Internet" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="04_SetTop" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="05_WiFi" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="06_Install" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="07_Gift" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="08_Cards" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="10_SKT_Bundle" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="11_KT_Total" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="12_KT_Fixed" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="13_KT_Premium" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="14_LGU_Chweyswun" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="15_LGU_Together" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="20_Schema" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="30_Formula" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -36,7 +38,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0&quot;원&quot;"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="32">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -104,17 +106,6 @@
     <font>
       <name val="Noto Sans KR"/>
       <i val="1"/>
-      <color rgb="00d97706"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Noto Sans KR"/>
-      <b val="1"/>
-      <color rgb="00666666"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Noto Sans KR"/>
       <color rgb="00666666"/>
       <sz val="9"/>
     </font>
@@ -122,12 +113,6 @@
       <name val="SF Mono"/>
       <color rgb="001a2744"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Noto Sans KR"/>
-      <i val="1"/>
-      <color rgb="00666666"/>
-      <sz val="9"/>
     </font>
     <font>
       <name val="Noto Sans KR"/>
@@ -166,6 +151,42 @@
     </font>
     <font>
       <name val="Noto Sans KR"/>
+      <b val="1"/>
+      <color rgb="002563eb"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="SF Mono"/>
+      <b val="1"/>
+      <color rgb="002563eb"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="SF Mono"/>
+      <b val="1"/>
+      <color rgb="002563eb"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Noto Sans KR"/>
+      <b val="1"/>
+      <color rgb="00e40981"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="SF Mono"/>
+      <b val="1"/>
+      <color rgb="00e40981"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="SF Mono"/>
+      <b val="1"/>
+      <color rgb="00e40981"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Noto Sans KR"/>
       <i val="1"/>
       <color rgb="0092400e"/>
       <sz val="10"/>
@@ -195,12 +216,6 @@
       <sz val="14"/>
     </font>
     <font>
-      <name val="Noto Sans KR"/>
-      <b val="1"/>
-      <color rgb="00e40981"/>
-      <sz val="11"/>
-    </font>
-    <font>
       <name val="SF Mono"/>
       <color rgb="001a2744"/>
       <sz val="10"/>
@@ -211,12 +226,8 @@
       <color rgb="00dc2626"/>
       <sz val="12"/>
     </font>
-    <font>
-      <name val="SF Mono"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -226,6 +237,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001a2744"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ef4444"/>
       </patternFill>
     </fill>
     <fill>
@@ -240,7 +256,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00fee2e2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002563eb"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00eff6ff"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00e40981"/>
       </patternFill>
     </fill>
     <fill>
@@ -275,7 +306,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -288,55 +319,79 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="21" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="21" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="12" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -702,18 +757,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🧮 봉이모바일 — 통신 3사 요금 계산기 Excel</t>
+          <t>🧮 봉이모바일 — 3사 통신 요금 계산기</t>
         </is>
       </c>
     </row>
@@ -751,63 +806,63 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>🧮 CALC</t>
+          <t>🧮 SKT 계산기</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>대화형 계산기 (3사 통합 · 드롭다운 선택)</t>
+          <t>SKT 전용 요즘가족결합 계산기 (드롭다운)</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>★ 메인</t>
+          <t>★ 계산</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>01_Internet</t>
+          <t>🧮 KT 계산기</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>인터넷 단독 요금 (속도별)</t>
+          <t>KT 전용 총액/정액/프리미엄 계산기</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>데이터</t>
+          <t>★ 계산</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>02_TV</t>
+          <t>🧮 LG U+ 계산기</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>TV 상품 (채널/가격/결합할인)</t>
+          <t>LG U+ 전용 참쉬운/투게더 계산기</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>데이터</t>
+          <t>★ 계산</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>03_TV_Internet</t>
+          <t>01_Internet</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>TV 결합 시 인터넷 요금 (WiFi 유/무)</t>
+          <t>인터넷 단독 요금</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -819,12 +874,12 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>04_SetTop</t>
+          <t>02_TV</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>셋톱박스 옵션</t>
+          <t>TV 상품 (3사 전체)</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -836,12 +891,12 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>05_WiFi</t>
+          <t>03_TV_Internet</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>WiFi 옵션</t>
+          <t>TV 결합 시 인터넷 (WiFi 유/무)</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -853,12 +908,12 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>06_Install</t>
+          <t>04_SetTop</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>설치비</t>
+          <t>셋톱박스 (기본값 설명 포함)</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -870,12 +925,12 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>07_Gift</t>
+          <t>05_WiFi</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>사은품 (속도 × TV결합)</t>
+          <t>WiFi (기본값 설명 포함)</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -887,12 +942,12 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>08_Cards</t>
+          <t>06_Install</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>제휴카드</t>
+          <t>설치비</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -904,46 +959,46 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>10_SKT_Bundle</t>
+          <t>07_Gift</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>SKT 요즘가족결합 (15조합)</t>
+          <t>사은품</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>결합</t>
+          <t>데이터</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>11_KT_Total</t>
+          <t>08_Cards</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>KT 총액결합 (6구간)</t>
+          <t>제휴카드 (26종)</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>결합</t>
+          <t>데이터</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>12_KT_Fixed</t>
+          <t>10_SKT_Bundle</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>KT 정액결합 (4구간)</t>
+          <t>SKT 요즘가족결합 (15조합)</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -955,12 +1010,12 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>13_KT_Premium</t>
+          <t>11_KT_Total</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>KT 💎 프리미엄 가족결합</t>
+          <t>KT 총액결합 (6구간)</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -972,12 +1027,12 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>14_LGU_Chweyswun</t>
+          <t>12_KT_Fixed</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>LG U+ 참쉬운 가족결합</t>
+          <t>KT 정액결합 (4구간)</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -989,12 +1044,12 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>15_LGU_Together</t>
+          <t>13_KT_Premium</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>LG U+ 투게더 결합</t>
+          <t>KT 💎 프리미엄 요금제 카탈로그</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -1006,104 +1061,114 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>20_Schema</t>
+          <t>14_LGU_Chweyswun</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>TypeScript 인터페이스</t>
+          <t>LG U+ 참쉬운가족결합</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>개발</t>
+          <t>결합</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>30_CALC_Formula</t>
+          <t>15_LGU_Together</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>계산 공식 + 결합할인 분기</t>
+          <t>LG U+ 투게더 결합</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
+          <t>결합</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>20_Schema</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>TypeScript 인터페이스</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
           <t>개발</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>⚡ 대화형 계산기 사용법</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>1. 🧮 CALC 시트로 이동</t>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>30_Formula</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>계산 공식 (REPLACE vs STACK)</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>개발</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>2. 노란 셀 클릭 → 드롭다운에서 선택 (통신사/속도/TV/WiFi/결합/회선)</t>
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>⚡ 사용법</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>3. 하단에 자동 계산 결과 (기본요금 · 결합할인 · 혜택가)</t>
+          <t>1. 🧮 SKT / KT / LG U+ 계산기 중 고객 통신사 시트 선택</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>4. 통신사별 결합할인 방식:</t>
+          <t>2. 노란 셀 클릭 → 드롭다운에서 속도/TV/WiFi/결합 선택</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   · SKT 요즘가족결합 → 단독가 REPLACE (요즘우리집 대체)</t>
+          <t>3. 하단에 단계별 계산 결과 + 🎉 혜택가 자동 표시</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   · KT 총액결합 → 기본 TV결합 + 총액 STACK (중복)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   · LG U+ 참쉬운 → 단독가 REPLACE</t>
+          <t>4. 각 행에 출처 데이터 시트 주석 (→ 01_Internet 등)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="7">
     <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A33:C33"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A32:C32"/>
     <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A27:C27"/>
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A26:C26"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1111,6 +1176,290 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>🔧 설치비</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>통신사</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>36300</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>56100</v>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>주말 +25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>36000</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>56200</v>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>주말 +25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>36300</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>56100</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>주말 +25%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>🎁 사은품</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>통신사</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>100M</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>500M</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>1G</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>solo</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>110000</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>170000</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>170000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>combo</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>400000</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>430000</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>solo</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>90000</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>140000</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>140000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>combo</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>370000</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>450000</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>solo</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>230000</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>230000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>combo</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>400000</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>470000</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>470000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1129,7 +1478,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>💳 제휴카드 (총 26종)</t>
+          <t>💳 제휴카드 (26종)</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1527,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>50만원</t>
+          <t>50만</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -1205,7 +1554,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>30만원</t>
+          <t>30만</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -1232,7 +1581,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>30만원</t>
+          <t>30만</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -1259,12 +1608,12 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>30만원</t>
+          <t>30만</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>-13,000원 (1~24M)</t>
+          <t>-13,000원</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1635,12 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>100만원</t>
+          <t>100만</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>-22,000원 (1~36M)</t>
+          <t>-22,000원</t>
         </is>
       </c>
     </row>
@@ -1313,7 +1662,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>30만원</t>
+          <t>30만</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1340,7 +1689,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>30만원</t>
+          <t>30만</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1367,7 +1716,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>50만원</t>
+          <t>50만</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1394,7 +1743,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>30만원</t>
+          <t>30만</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1448,7 +1797,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>30만원</t>
+          <t>30만</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -1475,7 +1824,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>40만원</t>
+          <t>40만</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -1502,7 +1851,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>40만원</t>
+          <t>40만</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -1529,7 +1878,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>30만원</t>
+          <t>30만</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -1556,7 +1905,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>40만원</t>
+          <t>40만</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -1583,7 +1932,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>40만원</t>
+          <t>40만</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -1610,7 +1959,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>40만원</t>
+          <t>40만</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -1637,7 +1986,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>30만원</t>
+          <t>30만</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -1659,17 +2008,17 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>KT멤버십x케이뱅크 더블혜택</t>
+          <t>KT멤버십x케이뱅크</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>20만원</t>
+          <t>20만</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>5% 캐시백 (최대5천)</t>
+          <t>5% 캐시백</t>
         </is>
       </c>
     </row>
@@ -1691,7 +2040,7 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>30만원</t>
+          <t>30만</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -1718,7 +2067,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>50만원</t>
+          <t>50만</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -1745,7 +2094,7 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>30만원</t>
+          <t>30만</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -1772,12 +2121,12 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>30만원</t>
+          <t>30만</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>통신료 25% 청구</t>
+          <t>통신료 25%</t>
         </is>
       </c>
     </row>
@@ -1799,7 +2148,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>70만원</t>
+          <t>70만</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -1826,7 +2175,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>30만원</t>
+          <t>30만</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -1853,7 +2202,7 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>30만원</t>
+          <t>30만</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -1867,7 +2216,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1885,7 +2234,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="32" t="inlineStr">
         <is>
           <t>🏷️ SKT 요즘가족결합</t>
         </is>
@@ -1924,332 +2273,332 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B4" s="24" t="n">
+      <c r="B4" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="24" t="n">
+      <c r="C4" s="33" t="n">
         <v>3500</v>
       </c>
-      <c r="D4" s="24" t="n">
+      <c r="D4" s="33" t="n">
         <v>4400</v>
       </c>
-      <c r="E4" s="24" t="n">
+      <c r="E4" s="33" t="n">
         <v>1100</v>
       </c>
-      <c r="F4" s="24" t="n">
+      <c r="F4" s="33" t="n">
         <v>9000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="33" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B5" s="24" t="n">
+      <c r="B5" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="24" t="n">
+      <c r="C5" s="33" t="n">
         <v>7000</v>
       </c>
-      <c r="D5" s="24" t="n">
+      <c r="D5" s="33" t="n">
         <v>4400</v>
       </c>
-      <c r="E5" s="24" t="n">
+      <c r="E5" s="33" t="n">
         <v>1100</v>
       </c>
-      <c r="F5" s="24" t="n">
+      <c r="F5" s="33" t="n">
         <v>12500</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="33" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B6" s="24" t="n">
+      <c r="B6" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="24" t="n">
+      <c r="C6" s="33" t="n">
         <v>18000</v>
       </c>
-      <c r="D6" s="24" t="n">
+      <c r="D6" s="33" t="n">
         <v>4400</v>
       </c>
-      <c r="E6" s="24" t="n">
+      <c r="E6" s="33" t="n">
         <v>1100</v>
       </c>
-      <c r="F6" s="24" t="n">
+      <c r="F6" s="33" t="n">
         <v>23500</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="33" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B7" s="24" t="n">
+      <c r="B7" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="C7" s="24" t="n">
+      <c r="C7" s="33" t="n">
         <v>18000</v>
       </c>
-      <c r="D7" s="24" t="n">
+      <c r="D7" s="33" t="n">
         <v>4400</v>
       </c>
-      <c r="E7" s="24" t="n">
+      <c r="E7" s="33" t="n">
         <v>1100</v>
       </c>
-      <c r="F7" s="24" t="n">
+      <c r="F7" s="33" t="n">
         <v>23500</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="33" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B8" s="24" t="n">
+      <c r="B8" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="C8" s="24" t="n">
+      <c r="C8" s="33" t="n">
         <v>18000</v>
       </c>
-      <c r="D8" s="24" t="n">
+      <c r="D8" s="33" t="n">
         <v>4400</v>
       </c>
-      <c r="E8" s="24" t="n">
+      <c r="E8" s="33" t="n">
         <v>1100</v>
       </c>
-      <c r="F8" s="24" t="n">
+      <c r="F8" s="33" t="n">
         <v>23500</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="33" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B9" s="24" t="n">
+      <c r="B9" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="24" t="n">
+      <c r="C9" s="33" t="n">
         <v>3500</v>
       </c>
-      <c r="D9" s="24" t="n">
+      <c r="D9" s="33" t="n">
         <v>11000</v>
       </c>
-      <c r="E9" s="24" t="n">
+      <c r="E9" s="33" t="n">
         <v>1100</v>
       </c>
-      <c r="F9" s="24" t="n">
+      <c r="F9" s="33" t="n">
         <v>15600</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="33" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B10" s="24" t="n">
+      <c r="B10" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="24" t="n">
+      <c r="C10" s="33" t="n">
         <v>7000</v>
       </c>
-      <c r="D10" s="24" t="n">
+      <c r="D10" s="33" t="n">
         <v>11000</v>
       </c>
-      <c r="E10" s="24" t="n">
+      <c r="E10" s="33" t="n">
         <v>1100</v>
       </c>
-      <c r="F10" s="24" t="n">
+      <c r="F10" s="33" t="n">
         <v>19100</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B11" s="24" t="n">
+      <c r="B11" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="C11" s="24" t="n">
+      <c r="C11" s="33" t="n">
         <v>18000</v>
       </c>
-      <c r="D11" s="24" t="n">
+      <c r="D11" s="33" t="n">
         <v>11000</v>
       </c>
-      <c r="E11" s="24" t="n">
+      <c r="E11" s="33" t="n">
         <v>1100</v>
       </c>
-      <c r="F11" s="24" t="n">
+      <c r="F11" s="33" t="n">
         <v>30100</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="A12" s="33" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B12" s="24" t="n">
+      <c r="B12" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="C12" s="24" t="n">
+      <c r="C12" s="33" t="n">
         <v>24000</v>
       </c>
-      <c r="D12" s="24" t="n">
+      <c r="D12" s="33" t="n">
         <v>11000</v>
       </c>
-      <c r="E12" s="24" t="n">
+      <c r="E12" s="33" t="n">
         <v>1100</v>
       </c>
-      <c r="F12" s="24" t="n">
+      <c r="F12" s="33" t="n">
         <v>36100</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="33" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B13" s="24" t="n">
+      <c r="B13" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="C13" s="24" t="n">
+      <c r="C13" s="33" t="n">
         <v>24000</v>
       </c>
-      <c r="D13" s="24" t="n">
+      <c r="D13" s="33" t="n">
         <v>11000</v>
       </c>
-      <c r="E13" s="24" t="n">
+      <c r="E13" s="33" t="n">
         <v>1100</v>
       </c>
-      <c r="F13" s="24" t="n">
+      <c r="F13" s="33" t="n">
         <v>36100</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="A14" s="33" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B14" s="24" t="n">
+      <c r="B14" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="24" t="n">
+      <c r="C14" s="33" t="n">
         <v>3500</v>
       </c>
-      <c r="D14" s="24" t="n">
+      <c r="D14" s="33" t="n">
         <v>13200</v>
       </c>
-      <c r="E14" s="24" t="n">
+      <c r="E14" s="33" t="n">
         <v>1100</v>
       </c>
-      <c r="F14" s="24" t="n">
+      <c r="F14" s="33" t="n">
         <v>17800</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="A15" s="33" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B15" s="24" t="n">
+      <c r="B15" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="24" t="n">
+      <c r="C15" s="33" t="n">
         <v>7000</v>
       </c>
-      <c r="D15" s="24" t="n">
+      <c r="D15" s="33" t="n">
         <v>13200</v>
       </c>
-      <c r="E15" s="24" t="n">
+      <c r="E15" s="33" t="n">
         <v>1100</v>
       </c>
-      <c r="F15" s="24" t="n">
+      <c r="F15" s="33" t="n">
         <v>21300</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="24" t="inlineStr">
+      <c r="A16" s="33" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B16" s="24" t="n">
+      <c r="B16" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="C16" s="24" t="n">
+      <c r="C16" s="33" t="n">
         <v>18000</v>
       </c>
-      <c r="D16" s="24" t="n">
+      <c r="D16" s="33" t="n">
         <v>13200</v>
       </c>
-      <c r="E16" s="24" t="n">
+      <c r="E16" s="33" t="n">
         <v>1100</v>
       </c>
-      <c r="F16" s="24" t="n">
+      <c r="F16" s="33" t="n">
         <v>32300</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="inlineStr">
+      <c r="A17" s="33" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B17" s="24" t="n">
+      <c r="B17" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="C17" s="24" t="n">
+      <c r="C17" s="33" t="n">
         <v>24000</v>
       </c>
-      <c r="D17" s="24" t="n">
+      <c r="D17" s="33" t="n">
         <v>13200</v>
       </c>
-      <c r="E17" s="24" t="n">
+      <c r="E17" s="33" t="n">
         <v>1100</v>
       </c>
-      <c r="F17" s="24" t="n">
+      <c r="F17" s="33" t="n">
         <v>38300</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="inlineStr">
+      <c r="A18" s="33" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B18" s="24" t="n">
+      <c r="B18" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="C18" s="24" t="n">
+      <c r="C18" s="33" t="n">
         <v>24000</v>
       </c>
-      <c r="D18" s="24" t="n">
+      <c r="D18" s="33" t="n">
         <v>13200</v>
       </c>
-      <c r="E18" s="24" t="n">
+      <c r="E18" s="33" t="n">
         <v>1100</v>
       </c>
-      <c r="F18" s="24" t="n">
+      <c r="F18" s="33" t="n">
         <v>38300</v>
       </c>
     </row>
@@ -2258,7 +2607,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2275,9 +2624,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="25" t="inlineStr">
-        <is>
-          <t>🏷️ KT 총액결합할인</t>
+      <c r="A1" s="34" t="inlineStr">
+        <is>
+          <t>🏷️ KT 총액결합 (STACK)</t>
         </is>
       </c>
     </row>
@@ -2309,380 +2658,380 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="35" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>22K 이하</t>
         </is>
       </c>
-      <c r="C4" s="26" t="n">
+      <c r="C4" s="35" t="n">
         <v>1650</v>
       </c>
-      <c r="D4" s="26" t="n">
+      <c r="D4" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="26" t="n">
+      <c r="E4" s="35" t="n">
         <v>1650</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr">
         <is>
           <t>22K 이상</t>
         </is>
       </c>
-      <c r="C5" s="26" t="n">
+      <c r="C5" s="35" t="n">
         <v>3300</v>
       </c>
-      <c r="D5" s="26" t="n">
+      <c r="D5" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="26" t="n">
+      <c r="E5" s="35" t="n">
         <v>3300</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>64.9K 이상</t>
         </is>
       </c>
-      <c r="C6" s="26" t="n">
+      <c r="C6" s="35" t="n">
         <v>5500</v>
       </c>
-      <c r="D6" s="26" t="n">
+      <c r="D6" s="35" t="n">
         <v>3300</v>
       </c>
-      <c r="E6" s="26" t="n">
+      <c r="E6" s="35" t="n">
         <v>8800</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>108.9K 이상</t>
         </is>
       </c>
-      <c r="C7" s="26" t="n">
+      <c r="C7" s="35" t="n">
         <v>5500</v>
       </c>
-      <c r="D7" s="26" t="n">
+      <c r="D7" s="35" t="n">
         <v>14300</v>
       </c>
-      <c r="E7" s="26" t="n">
+      <c r="E7" s="35" t="n">
         <v>19800</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>141.9K 이상</t>
         </is>
       </c>
-      <c r="C8" s="26" t="n">
+      <c r="C8" s="35" t="n">
         <v>5500</v>
       </c>
-      <c r="D8" s="26" t="n">
+      <c r="D8" s="35" t="n">
         <v>18700</v>
       </c>
-      <c r="E8" s="26" t="n">
+      <c r="E8" s="35" t="n">
         <v>24200</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="A9" s="35" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t>174.9K 이상</t>
         </is>
       </c>
-      <c r="C9" s="26" t="n">
+      <c r="C9" s="35" t="n">
         <v>5500</v>
       </c>
-      <c r="D9" s="26" t="n">
+      <c r="D9" s="35" t="n">
         <v>23100</v>
       </c>
-      <c r="E9" s="26" t="n">
+      <c r="E9" s="35" t="n">
         <v>28600</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>22K 이하</t>
         </is>
       </c>
-      <c r="C10" s="26" t="n">
+      <c r="C10" s="35" t="n">
         <v>2200</v>
       </c>
-      <c r="D10" s="26" t="n">
+      <c r="D10" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="26" t="n">
+      <c r="E10" s="35" t="n">
         <v>2200</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="26" t="inlineStr">
+      <c r="A11" s="35" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="35" t="inlineStr">
         <is>
           <t>22K 이상</t>
         </is>
       </c>
-      <c r="C11" s="26" t="n">
+      <c r="C11" s="35" t="n">
         <v>5500</v>
       </c>
-      <c r="D11" s="26" t="n">
+      <c r="D11" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="26" t="n">
+      <c r="E11" s="35" t="n">
         <v>5500</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="A12" s="35" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="35" t="inlineStr">
         <is>
           <t>64.9K 이상</t>
         </is>
       </c>
-      <c r="C12" s="26" t="n">
+      <c r="C12" s="35" t="n">
         <v>5500</v>
       </c>
-      <c r="D12" s="26" t="n">
+      <c r="D12" s="35" t="n">
         <v>5500</v>
       </c>
-      <c r="E12" s="26" t="n">
+      <c r="E12" s="35" t="n">
         <v>11000</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="35" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B13" s="26" t="inlineStr">
+      <c r="B13" s="35" t="inlineStr">
         <is>
           <t>108.9K 이상</t>
         </is>
       </c>
-      <c r="C13" s="26" t="n">
+      <c r="C13" s="35" t="n">
         <v>5500</v>
       </c>
-      <c r="D13" s="26" t="n">
+      <c r="D13" s="35" t="n">
         <v>16610</v>
       </c>
-      <c r="E13" s="26" t="n">
+      <c r="E13" s="35" t="n">
         <v>22110</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="inlineStr">
+      <c r="A14" s="35" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>141.9K 이상</t>
         </is>
       </c>
-      <c r="C14" s="26" t="n">
+      <c r="C14" s="35" t="n">
         <v>5500</v>
       </c>
-      <c r="D14" s="26" t="n">
+      <c r="D14" s="35" t="n">
         <v>22110</v>
       </c>
-      <c r="E14" s="26" t="n">
+      <c r="E14" s="35" t="n">
         <v>27610</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="26" t="inlineStr">
+      <c r="A15" s="35" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B15" s="26" t="inlineStr">
+      <c r="B15" s="35" t="inlineStr">
         <is>
           <t>174.9K 이상</t>
         </is>
       </c>
-      <c r="C15" s="26" t="n">
+      <c r="C15" s="35" t="n">
         <v>5500</v>
       </c>
-      <c r="D15" s="26" t="n">
+      <c r="D15" s="35" t="n">
         <v>27610</v>
       </c>
-      <c r="E15" s="26" t="n">
+      <c r="E15" s="35" t="n">
         <v>33110</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="26" t="inlineStr">
+      <c r="A16" s="35" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B16" s="35" t="inlineStr">
         <is>
           <t>22K 이하</t>
         </is>
       </c>
-      <c r="C16" s="26" t="n">
+      <c r="C16" s="35" t="n">
         <v>2200</v>
       </c>
-      <c r="D16" s="26" t="n">
+      <c r="D16" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="26" t="n">
+      <c r="E16" s="35" t="n">
         <v>2200</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="26" t="inlineStr">
+      <c r="A17" s="35" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B17" s="26" t="inlineStr">
+      <c r="B17" s="35" t="inlineStr">
         <is>
           <t>22K 이상</t>
         </is>
       </c>
-      <c r="C17" s="26" t="n">
+      <c r="C17" s="35" t="n">
         <v>5500</v>
       </c>
-      <c r="D17" s="26" t="n">
+      <c r="D17" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="26" t="n">
+      <c r="E17" s="35" t="n">
         <v>5500</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="26" t="inlineStr">
+      <c r="A18" s="35" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B18" s="26" t="inlineStr">
+      <c r="B18" s="35" t="inlineStr">
         <is>
           <t>64.9K 이상</t>
         </is>
       </c>
-      <c r="C18" s="26" t="n">
+      <c r="C18" s="35" t="n">
         <v>5500</v>
       </c>
-      <c r="D18" s="26" t="n">
+      <c r="D18" s="35" t="n">
         <v>5500</v>
       </c>
-      <c r="E18" s="26" t="n">
+      <c r="E18" s="35" t="n">
         <v>11000</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="26" t="inlineStr">
+      <c r="A19" s="35" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B19" s="26" t="inlineStr">
+      <c r="B19" s="35" t="inlineStr">
         <is>
           <t>108.9K 이상</t>
         </is>
       </c>
-      <c r="C19" s="26" t="n">
+      <c r="C19" s="35" t="n">
         <v>5500</v>
       </c>
-      <c r="D19" s="26" t="n">
+      <c r="D19" s="35" t="n">
         <v>16610</v>
       </c>
-      <c r="E19" s="26" t="n">
+      <c r="E19" s="35" t="n">
         <v>22110</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="26" t="inlineStr">
+      <c r="A20" s="35" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B20" s="26" t="inlineStr">
+      <c r="B20" s="35" t="inlineStr">
         <is>
           <t>141.9K 이상</t>
         </is>
       </c>
-      <c r="C20" s="26" t="n">
+      <c r="C20" s="35" t="n">
         <v>5500</v>
       </c>
-      <c r="D20" s="26" t="n">
+      <c r="D20" s="35" t="n">
         <v>22110</v>
       </c>
-      <c r="E20" s="26" t="n">
+      <c r="E20" s="35" t="n">
         <v>27610</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="26" t="inlineStr">
+      <c r="A21" s="35" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B21" s="26" t="inlineStr">
+      <c r="B21" s="35" t="inlineStr">
         <is>
           <t>174.9K 이상</t>
         </is>
       </c>
-      <c r="C21" s="26" t="n">
+      <c r="C21" s="35" t="n">
         <v>5500</v>
       </c>
-      <c r="D21" s="26" t="n">
+      <c r="D21" s="35" t="n">
         <v>27610</v>
       </c>
-      <c r="E21" s="26" t="n">
+      <c r="E21" s="35" t="n">
         <v>33110</v>
       </c>
     </row>
@@ -2691,7 +3040,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2707,9 +3056,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="25" t="inlineStr">
-        <is>
-          <t>🏷️ KT 정액결합할인</t>
+      <c r="A1" s="34" t="inlineStr">
+        <is>
+          <t>🏷️ KT 정액결합</t>
         </is>
       </c>
     </row>
@@ -2736,432 +3085,67 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="35" t="inlineStr">
         <is>
           <t>37K 이하</t>
         </is>
       </c>
-      <c r="B4" s="26" t="n">
+      <c r="B4" s="35" t="n">
         <v>5500</v>
       </c>
-      <c r="C4" s="26" t="n">
+      <c r="C4" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="26" t="n">
+      <c r="D4" s="35" t="n">
         <v>5500</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>37K 이상</t>
         </is>
       </c>
-      <c r="B5" s="26" t="n">
+      <c r="B5" s="35" t="n">
         <v>5500</v>
       </c>
-      <c r="C5" s="26" t="n">
+      <c r="C5" s="35" t="n">
         <v>3000</v>
       </c>
-      <c r="D5" s="26" t="n">
+      <c r="D5" s="35" t="n">
         <v>8500</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>61K 이상</t>
         </is>
       </c>
-      <c r="B6" s="26" t="n">
+      <c r="B6" s="35" t="n">
         <v>5500</v>
       </c>
-      <c r="C6" s="26" t="n">
+      <c r="C6" s="35" t="n">
         <v>5000</v>
       </c>
-      <c r="D6" s="26" t="n">
+      <c r="D6" s="35" t="n">
         <v>10500</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>77K 이상</t>
         </is>
       </c>
-      <c r="B7" s="26" t="n">
+      <c r="B7" s="35" t="n">
         <v>5500</v>
       </c>
-      <c r="C7" s="26" t="n">
+      <c r="C7" s="35" t="n">
         <v>7000</v>
       </c>
-      <c r="D7" s="26" t="n">
+      <c r="D7" s="35" t="n">
         <v>12500</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="27" t="inlineStr">
-        <is>
-          <t>💎 KT 프리미엄 가족결합</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="22" t="inlineStr">
-        <is>
-          <t>자격: 77K↑ 요금제 2회선 이상 | 대표자 총액결합만 | 인터넷 -5,500 고정</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>월정액</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>요금제명</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>할인액</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>비율</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="28" t="n">
-        <v>77000</v>
-      </c>
-      <c r="B6" s="28" t="inlineStr">
-        <is>
-          <t>77,000원 (임계값)</t>
-        </is>
-      </c>
-      <c r="C6" s="28" t="n">
-        <v>19250</v>
-      </c>
-      <c r="D6" s="28" t="inlineStr">
-        <is>
-          <t>≈25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="28" t="n">
-        <v>80000</v>
-      </c>
-      <c r="B7" s="28" t="inlineStr">
-        <is>
-          <t>80,000원 (5G 슈퍼플랜 베이직)</t>
-        </is>
-      </c>
-      <c r="C7" s="28" t="n">
-        <v>20000</v>
-      </c>
-      <c r="D7" s="28" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="28" t="n">
-        <v>87890</v>
-      </c>
-      <c r="B8" s="28" t="inlineStr">
-        <is>
-          <t>87,890원 (데이터선택 87.8)</t>
-        </is>
-      </c>
-      <c r="C8" s="28" t="n">
-        <v>22000</v>
-      </c>
-      <c r="D8" s="28" t="inlineStr">
-        <is>
-          <t>≈25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="28" t="n">
-        <v>89000</v>
-      </c>
-      <c r="B9" s="28" t="inlineStr">
-        <is>
-          <t>89,000원 (데이터ON 프리미엄)</t>
-        </is>
-      </c>
-      <c r="C9" s="28" t="n">
-        <v>22250</v>
-      </c>
-      <c r="D9" s="28" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="28" t="n">
-        <v>90000</v>
-      </c>
-      <c r="B10" s="28" t="inlineStr">
-        <is>
-          <t>90,000원 (슈퍼플랜 베이직 Plus/초이스)</t>
-        </is>
-      </c>
-      <c r="C10" s="28" t="n">
-        <v>22500</v>
-      </c>
-      <c r="D10" s="28" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="28" t="n">
-        <v>100000</v>
-      </c>
-      <c r="B11" s="28" t="inlineStr">
-        <is>
-          <t>100,000원 (슈퍼플랜 스페셜)</t>
-        </is>
-      </c>
-      <c r="C11" s="28" t="n">
-        <v>25000</v>
-      </c>
-      <c r="D11" s="28" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="28" t="n">
-        <v>109000</v>
-      </c>
-      <c r="B12" s="28" t="inlineStr">
-        <is>
-          <t>109,000원 (데이터선택 109)</t>
-        </is>
-      </c>
-      <c r="C12" s="28" t="n">
-        <v>27500</v>
-      </c>
-      <c r="D12" s="28" t="inlineStr">
-        <is>
-          <t>≈25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="28" t="n">
-        <v>110000</v>
-      </c>
-      <c r="B13" s="28" t="inlineStr">
-        <is>
-          <t>110,000원 (슈퍼플랜 스페셜 Plus/초이스)</t>
-        </is>
-      </c>
-      <c r="C13" s="28" t="n">
-        <v>27500</v>
-      </c>
-      <c r="D13" s="28" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="28" t="n">
-        <v>130000</v>
-      </c>
-      <c r="B14" s="28" t="inlineStr">
-        <is>
-          <t>130,000원 (슈퍼플랜 프리미엄/초이스)</t>
-        </is>
-      </c>
-      <c r="C14" s="28" t="n">
-        <v>32500</v>
-      </c>
-      <c r="D14" s="28" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A3:D3"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="29" t="inlineStr">
-        <is>
-          <t>🏷️ LG U+ 참쉬운가족결합</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>100M</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>500M</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>1G</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="30" t="inlineStr">
-        <is>
-          <t>인터넷 할인 (3년)</t>
-        </is>
-      </c>
-      <c r="B4" s="30" t="n">
-        <v>5500</v>
-      </c>
-      <c r="C4" s="30" t="n">
-        <v>9900</v>
-      </c>
-      <c r="D4" s="30" t="n">
-        <v>13200</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="31" t="inlineStr">
-        <is>
-          <t>휴대폰 할인 매트릭스 (인당)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>요금구간</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>2회선</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>3회선</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>4+회선</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="30" t="inlineStr">
-        <is>
-          <t>69K 미만</t>
-        </is>
-      </c>
-      <c r="B8" s="30" t="n">
-        <v>2200</v>
-      </c>
-      <c r="C8" s="30" t="n">
-        <v>3300</v>
-      </c>
-      <c r="D8" s="30" t="n">
-        <v>4400</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="30" t="inlineStr">
-        <is>
-          <t>69K 이상</t>
-        </is>
-      </c>
-      <c r="B9" s="30" t="n">
-        <v>3300</v>
-      </c>
-      <c r="C9" s="30" t="n">
-        <v>5500</v>
-      </c>
-      <c r="D9" s="30" t="n">
-        <v>6600</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="30" t="inlineStr">
-        <is>
-          <t>88K 이상</t>
-        </is>
-      </c>
-      <c r="B10" s="30" t="n">
-        <v>4400</v>
-      </c>
-      <c r="C10" s="30" t="n">
-        <v>6600</v>
-      </c>
-      <c r="D10" s="30" t="n">
-        <v>8800</v>
       </c>
     </row>
   </sheetData>
@@ -3175,114 +3159,382 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="29" t="inlineStr">
-        <is>
-          <t>🏷️ LG U+ 투게더 결합 (85K↑)</t>
+      <c r="A1" s="36" t="inlineStr">
+        <is>
+          <t>💎 KT 프리미엄 가족결합 (원본 planCatalog 14종)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="inlineStr">
-        <is>
-          <t>자격: 5G 85K↑ + 500M+ 인터넷 (100M 결합 불가)</t>
+      <c r="A3" s="31" t="inlineStr">
+        <is>
+          <t>자격: 77,000원↑ 요금제 2회선 이상 필수 · 대표자는 총액결합만 · 구성원 77K↑만 프리미엄 선택 가능 · 인터넷 -5,500원 기본</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>구분</t>
+          <t>월정액 (v)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>100M</t>
+          <t>요금제명 (label)</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>500M</t>
+          <t>prem 자격</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>1G</t>
+          <t>할인액 (dc)</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>비율</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="30" t="inlineStr">
-        <is>
-          <t>인터넷 할인</t>
-        </is>
-      </c>
-      <c r="B6" s="30" t="inlineStr">
-        <is>
-          <t>불가</t>
-        </is>
-      </c>
-      <c r="C6" s="30" t="n">
-        <v>11000</v>
-      </c>
-      <c r="D6" s="30" t="n">
-        <v>11000</v>
+      <c r="A6" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="B6" s="37" t="inlineStr">
+        <is>
+          <t>— 회선 없음 —</t>
+        </is>
+      </c>
+      <c r="C6" s="37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D6" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="37" t="n">
+        <v>32890</v>
+      </c>
+      <c r="B7" s="37" t="inlineStr">
+        <is>
+          <t>32,890원 (LTE 데이터선택)</t>
+        </is>
+      </c>
+      <c r="C7" s="37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D7" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>회선수</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>휴대폰 할인 (인당)</t>
+      <c r="A8" s="37" t="n">
+        <v>47000</v>
+      </c>
+      <c r="B8" s="37" t="inlineStr">
+        <is>
+          <t>47,000원</t>
+        </is>
+      </c>
+      <c r="C8" s="37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D8" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="30" t="inlineStr">
-        <is>
-          <t>2회선</t>
-        </is>
-      </c>
-      <c r="B9" s="30" t="n">
-        <v>10000</v>
+      <c r="A9" s="37" t="n">
+        <v>55000</v>
+      </c>
+      <c r="B9" s="37" t="inlineStr">
+        <is>
+          <t>55,000원</t>
+        </is>
+      </c>
+      <c r="C9" s="37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D9" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="30" t="inlineStr">
-        <is>
-          <t>3회선</t>
-        </is>
-      </c>
-      <c r="B10" s="30" t="n">
-        <v>14000</v>
+      <c r="A10" s="37" t="n">
+        <v>65000</v>
+      </c>
+      <c r="B10" s="37" t="inlineStr">
+        <is>
+          <t>65,000원</t>
+        </is>
+      </c>
+      <c r="C10" s="37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D10" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="30" t="inlineStr">
-        <is>
-          <t>4~5회선</t>
-        </is>
-      </c>
-      <c r="B11" s="30" t="n">
+      <c r="A11" s="37" t="n">
+        <v>77000</v>
+      </c>
+      <c r="B11" s="37" t="inlineStr">
+        <is>
+          <t>77,000원 (임계값)</t>
+        </is>
+      </c>
+      <c r="C11" s="37" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D11" s="37" t="n">
+        <v>19250</v>
+      </c>
+      <c r="E11" s="37" t="inlineStr">
+        <is>
+          <t>≈25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="37" t="n">
+        <v>80000</v>
+      </c>
+      <c r="B12" s="37" t="inlineStr">
+        <is>
+          <t>80,000원 (5G 슈퍼플랜 베이직)</t>
+        </is>
+      </c>
+      <c r="C12" s="37" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D12" s="37" t="n">
         <v>20000</v>
+      </c>
+      <c r="E12" s="37" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="37" t="n">
+        <v>87890</v>
+      </c>
+      <c r="B13" s="37" t="inlineStr">
+        <is>
+          <t>87,890원 (데이터선택 87.8)</t>
+        </is>
+      </c>
+      <c r="C13" s="37" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D13" s="37" t="n">
+        <v>22000</v>
+      </c>
+      <c r="E13" s="37" t="inlineStr">
+        <is>
+          <t>≈25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="37" t="n">
+        <v>89000</v>
+      </c>
+      <c r="B14" s="37" t="inlineStr">
+        <is>
+          <t>89,000원 (데이터ON 프리미엄)</t>
+        </is>
+      </c>
+      <c r="C14" s="37" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D14" s="37" t="n">
+        <v>22250</v>
+      </c>
+      <c r="E14" s="37" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="37" t="n">
+        <v>90000</v>
+      </c>
+      <c r="B15" s="37" t="inlineStr">
+        <is>
+          <t>90,000원 (슈퍼플랜 베이직 Plus/초이스)</t>
+        </is>
+      </c>
+      <c r="C15" s="37" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D15" s="37" t="n">
+        <v>22500</v>
+      </c>
+      <c r="E15" s="37" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="37" t="n">
+        <v>100000</v>
+      </c>
+      <c r="B16" s="37" t="inlineStr">
+        <is>
+          <t>100,000원 (슈퍼플랜 스페셜)</t>
+        </is>
+      </c>
+      <c r="C16" s="37" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D16" s="37" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E16" s="37" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="37" t="n">
+        <v>109000</v>
+      </c>
+      <c r="B17" s="37" t="inlineStr">
+        <is>
+          <t>109,000원 (데이터선택 109)</t>
+        </is>
+      </c>
+      <c r="C17" s="37" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D17" s="37" t="n">
+        <v>27500</v>
+      </c>
+      <c r="E17" s="37" t="inlineStr">
+        <is>
+          <t>≈25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="37" t="n">
+        <v>110000</v>
+      </c>
+      <c r="B18" s="37" t="inlineStr">
+        <is>
+          <t>110,000원 (슈퍼플랜 스페셜 Plus/초이스)</t>
+        </is>
+      </c>
+      <c r="C18" s="37" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D18" s="37" t="n">
+        <v>27500</v>
+      </c>
+      <c r="E18" s="37" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="37" t="n">
+        <v>130000</v>
+      </c>
+      <c r="B19" s="37" t="inlineStr">
+        <is>
+          <t>130,000원 (슈퍼플랜 프리미엄/초이스)</t>
+        </is>
+      </c>
+      <c r="C19" s="37" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D19" s="37" t="n">
+        <v>32500</v>
+      </c>
+      <c r="E19" s="37" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3294,166 +3546,129 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="90" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>📐 TypeScript 인터페이스 (D 객체)</t>
+      <c r="A1" s="38" t="inlineStr">
+        <is>
+          <t>🏷️ LG U+ 참쉬운가족결합</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="32" t="inlineStr">
-        <is>
-          <t>interface CarrierData {</t>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>100M</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>500M</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>1G</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  name: string; prefix: string;</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  internet: Record&lt;"100M"|"500M"|"1G", number&gt;;</t>
-        </is>
+      <c r="A4" s="39" t="inlineStr">
+        <is>
+          <t>인터넷 할인</t>
+        </is>
+      </c>
+      <c r="B4" s="39" t="n">
+        <v>5500</v>
+      </c>
+      <c r="C4" s="39" t="n">
+        <v>9900</v>
+      </c>
+      <c r="D4" s="39" t="n">
+        <v>13200</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  wifiCost?: number; wifiPrice?: Record&lt;Speed, number&gt;;</t>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>요금구간</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>2회선</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>3회선</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>4+회선</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  setTopOptions: SetTop[]; wifiOptions: WiFi[];</t>
-        </is>
+      <c r="A7" s="39" t="inlineStr">
+        <is>
+          <t>69K 미만</t>
+        </is>
+      </c>
+      <c r="B7" s="39" t="n">
+        <v>2200</v>
+      </c>
+      <c r="C7" s="39" t="n">
+        <v>3300</v>
+      </c>
+      <c r="D7" s="39" t="n">
+        <v>4400</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  tvInternetNoWifi: Record&lt;Speed, number&gt;;</t>
-        </is>
+      <c r="A8" s="39" t="inlineStr">
+        <is>
+          <t>69K 이상</t>
+        </is>
+      </c>
+      <c r="B8" s="39" t="n">
+        <v>3300</v>
+      </c>
+      <c r="C8" s="39" t="n">
+        <v>5500</v>
+      </c>
+      <c r="D8" s="39" t="n">
+        <v>6600</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  tvInternetWithWifi: Record&lt;Speed, number&gt;;</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  tv: TVProduct[];</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  install: { solo: number; combo: number };</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  gift: { solo: SpeedMap; combo: SpeedMap };</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  bundle: BundleConfig;</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="32" t="inlineStr">
-        <is>
-          <t>}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="32" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="32" t="inlineStr">
-        <is>
-          <t>interface TVProduct { n: string; p: number; dc: number; }</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="32" t="inlineStr">
-        <is>
-          <t>interface SetTop { id, name, fee, isDefault?, active }</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="32" t="inlineStr">
-        <is>
-          <t>interface WiFi { id, name, fees: SpeedMap, isDefault?, active }</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="32" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="32" t="inlineStr">
-        <is>
-          <t>// BundleConfig — 통신사별 상이:</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="32" t="inlineStr">
-        <is>
-          <t>// SKT: { family: { internet, iptv, mobilePerBySpeed } }</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="32" t="inlineStr">
-        <is>
-          <t>// KT: { ranges_total, total, ranges_fixed, fixed, premium }</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="32" t="inlineStr">
-        <is>
-          <t>// LGU: { chweyswun: { internet, planLabels, mobile[][]} , together: { internet, mobile[] } }</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="32" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="32" t="inlineStr">
-        <is>
-          <t>type Speed = "100M" | "500M" | "1G";</t>
-        </is>
+      <c r="A9" s="39" t="inlineStr">
+        <is>
+          <t>88K 이상</t>
+        </is>
+      </c>
+      <c r="B9" s="39" t="n">
+        <v>4400</v>
+      </c>
+      <c r="C9" s="39" t="n">
+        <v>6600</v>
+      </c>
+      <c r="D9" s="39" t="n">
+        <v>8800</v>
       </c>
     </row>
   </sheetData>
@@ -3467,7 +3682,740 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="38" t="inlineStr">
+        <is>
+          <t>🏷️ LG U+ 투게더 (85K↑)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>100M</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>500M</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>1G</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="39" t="inlineStr">
+        <is>
+          <t>인터넷</t>
+        </is>
+      </c>
+      <c r="B4" s="39" t="inlineStr">
+        <is>
+          <t>불가</t>
+        </is>
+      </c>
+      <c r="C4" s="39" t="n">
+        <v>11000</v>
+      </c>
+      <c r="D4" s="39" t="n">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>회선수</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>휴대폰 할인 (인당)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="39" t="inlineStr">
+        <is>
+          <t>2회선</t>
+        </is>
+      </c>
+      <c r="B7" s="39" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="39" t="inlineStr">
+        <is>
+          <t>3회선</t>
+        </is>
+      </c>
+      <c r="B8" s="39" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="39" t="inlineStr">
+        <is>
+          <t>4~5회선</t>
+        </is>
+      </c>
+      <c r="B9" s="39" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="90" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>📐 TypeScript 인터페이스</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="40" t="inlineStr">
+        <is>
+          <t>interface CarrierData {</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  name, prefix;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  internet: Record&lt;"100M"|"500M"|"1G", number&gt;;</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  wifiCost? | wifiPrice?: Record&lt;Speed, number&gt;;</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  setTopOptions: SetTop[]; wifiOptions: WiFi[];</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  tvInternetNoWifi, tvInternetWithWifi: Record&lt;Speed, number&gt;;</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  tv: TVProduct[];</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  install: { solo, combo };</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  gift: { solo: SpeedMap, combo: SpeedMap };</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  bundle: BundleConfig;  // 3사별 상이</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="40" t="inlineStr">
+        <is>
+          <t>}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="40" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="40" t="inlineStr">
+        <is>
+          <t>// SKT: bundle.family { internet, iptv, mobilePerBySpeed }</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="40" t="inlineStr">
+        <is>
+          <t>// KT:  bundle.{ranges_total, total, ranges_fixed, fixed, premium}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="40" t="inlineStr">
+        <is>
+          <t>// LGU: bundle.{chweyswun, together}</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>🧮 SKT 요즘가족결합 계산기</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>📝 입력 (노란 셀 클릭 → 드롭다운)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>속도</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>500M</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>100M / 500M / 1G</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>TV 상품</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>B tv 올</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>SKT B tv 9종</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>WiFi 사용</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Y=+1,100원 / N=미사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>휴대폰 회선수</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>0=결합없음 / 1~5</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>🧮 자동 계산</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>TV 인덱스</t>
+        </is>
+      </c>
+      <c r="B10" s="13">
+        <f>MATCH(B5,{"TV 없음","B tv 이코노미","B tv 스탠다드","B tv 올","B tv 스탠다드 플러스","B tv 올 플러스","B tv 스탠다드 넷플릭스","B tv 올 넷플릭스","B tv 스탠다드 넷플릭스 프리미엄","B tv 올 넷플릭스 프리미엄"},0)</f>
+        <v/>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>드롭다운 이름 → 숫자 인덱스</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>TV 선택 여부</t>
+        </is>
+      </c>
+      <c r="B11" s="13">
+        <f>IF(B5="TV 없음",0,1)</f>
+        <v/>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>1=TV 결합 / 0=인터넷 단독</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>📊 데이터 조회</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>인터넷 단독가</t>
+        </is>
+      </c>
+      <c r="B14" s="13">
+        <f>IF(B4="100M",22000,IF(B4="500M",33000,38500))</f>
+        <v/>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>→ 01_Internet · SKT 단독가</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>TV 상품 가격 (p)</t>
+        </is>
+      </c>
+      <c r="B15" s="13">
+        <f>IF(B11=0,0,CHOOSE(B10-1,12100,15400,18700,23100,24200,27700,30200,30700,33200))</f>
+        <v/>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>→ 02_TV · SKT TV 9종</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>TV 결합할인 (dc)</t>
+        </is>
+      </c>
+      <c r="B16" s="13">
+        <f>IF(B11=0,0,2200)</f>
+        <v/>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>→ 02_TV · SKT 전 상품 -2,200 균일</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>WiFi 추가금</t>
+        </is>
+      </c>
+      <c r="B17" s="13">
+        <f>IF(B6="Y",1100,0)</f>
+        <v/>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>→ 05_WiFi · SKT GIGA WiFi (기본) 속도 균일 1,100원</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>tvInternetNoWifi</t>
+        </is>
+      </c>
+      <c r="B18" s="13">
+        <f>IF(B4="100M",19800,IF(B4="500M",27500,33000))</f>
+        <v/>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>→ 03_TV_Internet · WiFi 미포함 결합가</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>tvInternetWithWifi</t>
+        </is>
+      </c>
+      <c r="B19" s="13">
+        <f>IF(B4="100M",22000,IF(B4="500M",28600,34100))</f>
+        <v/>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>→ 03_TV_Internet · WiFi 포함 결합가</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>셋톱박스 (스마트3)</t>
+        </is>
+      </c>
+      <c r="B20" s="13">
+        <f>4400</f>
+        <v/>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>→ 04_SetTop · 기본 모델 (매장 판매 1위)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>【경로 A】 결합없음 (휴대폰 결합 X)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  월 기본요금 (요즘우리집)</t>
+        </is>
+      </c>
+      <c r="B23" s="17">
+        <f>IF(B11=0,B14+B17,IF(B6="Y",B19,B18)+B15-B16+B20)</f>
+        <v/>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>TV 있으면: tvInternet + (p-dc) + 셋톱 / 없으면: 단독+WiFi</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>【경로 B】 요즘가족결합 (휴대폰 결합 · 단독가 REPLACE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  요즘가족 인터넷 할인</t>
+        </is>
+      </c>
+      <c r="B26" s="13">
+        <f>IF(B7=0,0,IF(B4="100M",4400,IF(B4="500M",11000,13200)))</f>
+        <v/>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>→ 10_SKT_Bundle · 단독가 기준 차감 (요즘우리집 REPLACE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  IPTV 추가 (TV+결합 시)</t>
+        </is>
+      </c>
+      <c r="B27" s="13">
+        <f>IF(AND(B7&gt;0,B11=1),1100,0)</f>
+        <v/>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>TV 결합 시에만 추가 -1,100원</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  휴대폰 인당 할인</t>
+        </is>
+      </c>
+      <c r="B28" s="13">
+        <f>IF(B7=0,0,IF(B4="100M",CHOOSE(B7,3500,3500,6000,4500,3600),CHOOSE(B7,3500,3500,6000,6000,4800)))</f>
+        <v/>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>→ 10_SKT_Bundle · 속도+회선수별 인당</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  휴대폰 총 할인</t>
+        </is>
+      </c>
+      <c r="B29" s="13">
+        <f>B28*B7</f>
+        <v/>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>인당 × 회선수 (휴대폰 고지서 별도 차감)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  → 인터넷 (단독 - 요즘가족할인)</t>
+        </is>
+      </c>
+      <c r="B31" s="19">
+        <f>B14+B17-B26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  → TV (p - dc - iptv)</t>
+        </is>
+      </c>
+      <c r="B32" s="19">
+        <f>IF(B11=0,0,B15-B16-B27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  → 셋톱 (TV 있을 때만)</t>
+        </is>
+      </c>
+      <c r="B33" s="19">
+        <f>IF(B11=0,0,B20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  = 인터넷+TV 월 실납부 (결합 적용)</t>
+        </is>
+      </c>
+      <c r="B34" s="17">
+        <f>(B14+B17-B26)+IF(B11=0,0,B15-B16-B27+B20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 휴대폰 고지서 별도 차감</t>
+        </is>
+      </c>
+      <c r="B35" s="19">
+        <f>-B29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>🎉 혜택가 (최종 월요금)</t>
+        </is>
+      </c>
+      <c r="B36" s="20">
+        <f>IF(B7=0,B23,B34-B29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>🎁 부가 혜택</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  설치비 (1회성)</t>
+        </is>
+      </c>
+      <c r="B39" s="13">
+        <f>IF(B11=0,36300,56100)</f>
+        <v/>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>→ 06_Install</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  사은품 (속도×TV결합)</t>
+        </is>
+      </c>
+      <c r="B40" s="13">
+        <f>IF(B11=0,IF(B4="100M",110000,170000),CHOOSE(MATCH(B4,{"100M","500M","1G"},0),400000,430000,490000))</f>
+        <v/>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
+        <is>
+          <t>→ 07_Gift</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="25">
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="C10:E10"/>
+  </mergeCells>
+  <dataValidations count="4">
+    <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"100M,500M,1G"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"TV 없음,B tv 이코노미,B tv 스탠다드,B tv 올,B tv 스탠다드 플러스,B tv 올 플러스,B tv 스탠다드 넷플릭스,B tv 올 넷플릭스,B tv 스탠다드 넷플릭스 프리미엄,B tv 올 넷플릭스 프리미엄"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"0,1,2,3,4,5"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3477,116 +4425,49 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>🧮 월 요금 계산 공식</t>
+          <t>🧮 계산 공식</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="33" t="inlineStr">
-        <is>
-          <t>⚠️ 3사 결합할인 적용 방식 핵심 차이</t>
+      <c r="A3" s="41" t="inlineStr">
+        <is>
+          <t>⚠️ 3사 결합할인 적용 방식 차이</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="34" t="inlineStr">
-        <is>
-          <t>• SKT 요즘가족결합: 단독가 REPLACE (요즘우리집 대체) → tvInternet 값 사용 안함</t>
+      <c r="A4" s="42" t="inlineStr">
+        <is>
+          <t>• SKT 요즘가족결합: 단독가 REPLACE (요즘우리집 대체) → tvInternet 사용 X</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="34" t="inlineStr">
-        <is>
-          <t>• KT 총액/정액: 기본 TV결합할인 + 추가할인 STACK (중복 적용)</t>
+      <c r="A5" s="42" t="inlineStr">
+        <is>
+          <t>• KT 총액/정액: 기본 TV결합 + 추가할인 STACK (중복)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="34" t="inlineStr">
-        <is>
-          <t>• KT 프리미엄: 대표자+일반구성원은 총액결합, 77K↑ 구성원은 프리미엄 (독립)</t>
+      <c r="A6" s="42" t="inlineStr">
+        <is>
+          <t>• KT 프리미엄: 대표자+77K미만은 총액결합 / 77K↑ 구성원은 프리미엄 (독립)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="A7" s="42" t="inlineStr">
         <is>
           <t>• LG U+ 참쉬운: 단독가 REPLACE</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="A8" s="42" t="inlineStr">
         <is>
           <t>• LG U+ 투게더: 단독가 REPLACE + 100M 결합 불가</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>계산 단계 (공식)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="35" t="inlineStr">
-        <is>
-          <t>기본 월요금 (결합없음)</t>
-        </is>
-      </c>
-      <c r="B12" s="36" t="inlineStr">
-        <is>
-          <t>base = (TV있?(tvInetWithWifi[sp]+tvFinal+setTop):(internet[sp]+wifiFee))</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="35" t="inlineStr">
-        <is>
-          <t>SKT REPLACE</t>
-        </is>
-      </c>
-      <c r="B13" s="36" t="inlineStr">
-        <is>
-          <t>bundleFee = (internet[sp]+wifiFee - famInet) + (tvP - tvDc - iptv) + setTop</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="35" t="inlineStr">
-        <is>
-          <t>KT STACK</t>
-        </is>
-      </c>
-      <c r="B14" s="36" t="inlineStr">
-        <is>
-          <t>bundleFee = (tvInet(wifi) - totalInet) + (tvP - tvDc) + setTop</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="35" t="inlineStr">
-        <is>
-          <t>LGU REPLACE</t>
-        </is>
-      </c>
-      <c r="B15" s="36" t="inlineStr">
-        <is>
-          <t>bundleFee = (internet[sp] - chwInet) + (tvP - tvDc) + setTop</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="35" t="inlineStr">
-        <is>
-          <t>혜택가</t>
-        </is>
-      </c>
-      <c r="B16" s="36" t="inlineStr">
-        <is>
-          <t>finalFee = bundleFee - 휴대폰_고지서_별도_차감</t>
         </is>
       </c>
     </row>
@@ -3603,988 +4484,968 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col hidden="1" width="13" customWidth="1" min="7" max="7"/>
-    <col hidden="1" width="13" customWidth="1" min="8" max="8"/>
-    <col hidden="1" width="13" customWidth="1" min="9" max="9"/>
-    <col hidden="1" width="13" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>🧮 통신 3사 요금 계산기</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>carrier</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>tv_name</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>dc</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>TV 없음</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>🧮 KT 총액/정액 결합 계산기</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>📝 입력 (노란 셀 클릭 → 드롭다운)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>B tv 이코노미</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>12100</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2200</v>
+          <t>📝 입력</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>통신사</t>
+          <t>속도</t>
         </is>
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>SKT</t>
+          <t>500M</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>← 클릭</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>B tv 스탠다드</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>15400</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2200</v>
+          <t>100M / 500M / 1G</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>속도</t>
+          <t>TV 상품</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>500M</t>
+          <t>지니TV 에센스</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>← 클릭</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>B tv 올</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>18700</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2200</v>
+          <t>KT 지니TV 5종</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>TV 상품</t>
+          <t>WiFi 사용</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>B tv 올</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>← 클릭</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>B tv 스탠다드 플러스</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>23100</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2200</v>
+          <t>Y=1,100원 (1G는 무료) / N</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>WiFi 사용</t>
+          <t>결합 종류</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>총액결합</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>← 클릭</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>B tv 올 플러스</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>24200</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2200</v>
+          <t>결합없음/총액/정액</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>결합 종류</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>요즘가족결합</t>
-        </is>
+          <t>총액결합 구간 (1~6)</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n">
+        <v>4</v>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>← 클릭</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>B tv 스탠다드 넷플릭스</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>27700</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2200</v>
+          <t>1=22K↓, 2=22K↑, 3=64.9K↑, 4=108.9K↑, 5=141.9K↑, 6=174.9K↑</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>휴대폰 회선수</t>
+          <t>정액결합 구간 (1~4)</t>
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>← 클릭</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>B tv 올 넷플릭스</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>30200</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>KT 합산구간 / LGU 요금구간 (해당 시)</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>← 클릭</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>B tv 스탠다드 넷플릭스 프리미엄</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>30700</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2200</v>
+          <t>1=37K↓, 2=37K↑, 3=61K↑, 4=77K↑</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>B tv 올 넷플릭스 프리미엄</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>33200</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2200</v>
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>🧮 자동 계산</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>ℹ️ 통신사별 결합 안내</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>KT</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>TV 없음</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>TV 인덱스</t>
+        </is>
+      </c>
+      <c r="B12" s="13">
+        <f>MATCH(B5,{"TV 없음","지니TV 베이직","지니TV 라이트","지니TV 에센스","지니TV 모든G","지니TV 디즈니+모든G"},0)</f>
+        <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>• SKT: 요즘가족결합 (1~5회선) — 단독가 REPLACE + 휴대폰 별도 차감</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>KT</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>지니TV 베이직</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>14740</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2640</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>• KT: 총액/정액결합 (구간 1~6, 1~4) — 기본 TV결합 + STACK 중복</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>KT</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>지니TV 라이트</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>15840</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2640</v>
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>TV 선택 여부</t>
+        </is>
+      </c>
+      <c r="B13" s="13">
+        <f>IF(B5="TV 없음",0,1)</f>
+        <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>• KT: 프리미엄 가족결합 — 77K+ 2회선 이상 (별도 계산)</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>KT</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>지니TV 에센스</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>20240</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3740</v>
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>📊 데이터 조회</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>• LG U+: 참쉬운(2~4회선) — 요금구간(1=69K-, 2=69K+, 3=88K+) + 단독가 REPLACE</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>KT</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>지니TV 모든G</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>21340</v>
-      </c>
-      <c r="J16" t="n">
-        <v>4400</v>
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>인터넷 단독가</t>
+        </is>
+      </c>
+      <c r="B16" s="13">
+        <f>IF(B4="100M",22000,IF(B4="500M",33000,38500))</f>
+        <v/>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>→ 01_Internet</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>• LG U+: 투게더 — 85K+ 고가요금제, 500M+ 전용 (100M 불가)</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KT</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>지니TV 디즈니+모든G</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>28100</v>
-      </c>
-      <c r="J17" t="n">
-        <v>6600</v>
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>TV 가격 (p)</t>
+        </is>
+      </c>
+      <c r="B17" s="13">
+        <f>IF(B13=0,0,CHOOSE(B12-1,14740,15840,20240,21340,28100))</f>
+        <v/>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>→ 02_TV · KT 지니TV</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>LG U+</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>TV 없음</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>TV 결합할인 (dc)</t>
+        </is>
+      </c>
+      <c r="B18" s="13">
+        <f>IF(B13=0,0,CHOOSE(B12-1,2640,2640,3740,4400,6600))</f>
+        <v/>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>→ 02_TV · KT 상품별 차등</t>
+        </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>🧮 자동 계산 (수식)</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>LG U+</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>U+tv 실속형</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>15400</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2200</v>
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>WiFi 추가금 (속도별)</t>
+        </is>
+      </c>
+      <c r="B19" s="13">
+        <f>IF(B6="Y",IF(B4="1G",0,1100),0)</f>
+        <v/>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>→ 05_WiFi · KT WAVE2 (기본) · 1G는 무료</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>인터넷 단독가</t>
-        </is>
-      </c>
-      <c r="B20" s="15">
-        <f>IF(B5="100M",22000,IF(B5="500M",33000,38500))</f>
+          <t>tvInternetNoWifi</t>
+        </is>
+      </c>
+      <c r="B20" s="13">
+        <f>IF(B4="100M",22000,IF(B4="500M",27500,33000))</f>
         <v/>
       </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>→ 01_Internet 시트 · 3사 동일 요금</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>LG U+</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>U+tv 기본형</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>16500</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2200</v>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>→ 03_TV_Internet</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>TV 가격 (p)</t>
-        </is>
-      </c>
-      <c r="B21" s="15">
-        <f>IFERROR(SUMPRODUCT(($G$2:$G$22=B4)*($H$2:$H$22=B6)*($I$2:$I$22)),0)</f>
+          <t>tvInternetWithWifi</t>
+        </is>
+      </c>
+      <c r="B21" s="13">
+        <f>IF(B4="100M",23100,IF(B4="500M",28600,33000))</f>
         <v/>
       </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>→ 02_TV 시트 · 통신사+상품명 조회 (숨김 G~J)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>LG U+</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>U+tv 프리미엄</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>18700</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2200</v>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>→ 03_TV_Internet · 1G는 동일</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>TV 결합할인 (dc)</t>
-        </is>
-      </c>
-      <c r="B22" s="15">
-        <f>IFERROR(SUMPRODUCT(($G$2:$G$22=B4)*($H$2:$H$22=B6)*($J$2:$J$22)),0)</f>
-        <v/>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>→ 02_TV 시트 · 인터넷 결합 시 TV 할인</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>LG U+</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>U+tv 프리미엄 VOD</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>24200</v>
-      </c>
-      <c r="J22" t="n">
-        <v>5500</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>TV 선택 여부</t>
-        </is>
-      </c>
-      <c r="B23" s="15">
-        <f>IF(B6="TV 없음",0,1)</f>
-        <v/>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>0 = 인터넷 단독 / 1 = TV 결합</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>WiFi 추가금 (속도별)</t>
-        </is>
-      </c>
-      <c r="B24" s="15">
-        <f>IF(B7="N",0,IF(B4="SKT",1100,IF(B4="KT",IF(B5="1G",0,1100),0)))</f>
-        <v/>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>→ 05_WiFi 기본 모델 · SKT 1,100 / KT 100M·500M 1,100, 1G 무료 / LGU+ 전속도 무료</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>tvInternetNoWifi</t>
-        </is>
-      </c>
-      <c r="B25" s="15">
-        <f>IF(B4="SKT",IF(B5="100M",19800,IF(B5="500M",27500,33000)),IF(B4="KT",IF(B5="100M",22000,IF(B5="500M",27500,33000)),IF(B5="100M",22000,IF(B5="500M",27500,33000))))</f>
-        <v/>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>→ 03_TV_Internet 시트 · TV 결합 시 인터넷가 (WiFi 미포함)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>tvInternetWithWifi</t>
-        </is>
-      </c>
-      <c r="B26" s="15">
-        <f>IF(B4="SKT",IF(B5="100M",22000,IF(B5="500M",28600,34100)),IF(B4="KT",IF(B5="100M",23100,IF(B5="500M",28600,33000)),IF(B5="100M",22000,IF(B5="500M",27500,33000))))</f>
-        <v/>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>→ 03_TV_Internet 시트 · TV+WiFi 결합 시 인터넷가</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>셋톱박스 (기본)</t>
-        </is>
-      </c>
-      <c r="B27" s="15">
+          <t>셋톱박스 (기가지니3)</t>
+        </is>
+      </c>
+      <c r="B22" s="13">
         <f>4400</f>
         <v/>
       </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>→ 04_SetTop 기본 모델 · SKT 스마트3 / KT 기가지니3 / LGU+ U+tv UHD4 (모두 4,400원)</t>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>→ 04_SetTop · 기본 모델 · 고객 선호 1위</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>【경로 A】 결합없음 (기본 TV 결합)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  월 기본요금</t>
+        </is>
+      </c>
+      <c r="B25" s="22">
+        <f>IF(B13=0,B16+B19,IF(B6="Y",B21,B20)+B17-B18+B22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="23" t="inlineStr">
+        <is>
+          <t>【경로 B】 결합 적용 (STACK — 기본 TV결합 + 추가할인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  [총액] 인터넷 추가 할인</t>
+        </is>
+      </c>
+      <c r="B28" s="13">
+        <f>IF(B7="총액결합",IF(B4="100M",CHOOSE(B8,1650,3300,5500,5500,5500,5500),CHOOSE(B8,2200,5500,5500,5500,5500,5500)),0)</f>
+        <v/>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>→ 11_KT_Total · STACK 중복 적용</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="17" t="inlineStr">
-        <is>
-          <t>【경로 A】 결합없음 / 기본 TV 결합만</t>
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  [총액] 휴대폰 할인</t>
+        </is>
+      </c>
+      <c r="B29" s="13">
+        <f>IF(B7="총액결합",IF(B4="100M",CHOOSE(B8,0,0,3300,14300,18700,23100),CHOOSE(B8,0,0,5500,16610,22110,27610)),0)</f>
+        <v/>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>→ 11_KT_Total · 휴대폰 고지서 별도</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  기본 월요금</t>
-        </is>
-      </c>
-      <c r="B30" s="19">
-        <f>IF(B23=0,B24+B24,IF(B7="Y",B26,B25)+(B21-B22)+B27)</f>
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  [정액] 인터넷 할인</t>
+        </is>
+      </c>
+      <c r="B30" s="13">
+        <f>IF(B7="정액결합",5500,0)</f>
         <v/>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="20" t="inlineStr">
-        <is>
-          <t>【경로 B】 휴대폰 결합 할인 적용</t>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>→ 12_KT_Fixed · 전구간 5,500 고정</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  [정액] 휴대폰 할인</t>
+        </is>
+      </c>
+      <c r="B31" s="13">
+        <f>IF(B7="정액결합",CHOOSE(B9,0,3000,5000,7000),0)</f>
+        <v/>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>→ 12_KT_Fixed · 4구간</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  [SKT] 요즘가족 인터넷 할인</t>
-        </is>
-      </c>
-      <c r="B33" s="15">
-        <f>IF(AND(B4="SKT",B8="요즘가족결합",B9&gt;0),IF(B5="100M",4400,IF(B5="500M",11000,13200)),0)</f>
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  = 인터넷+TV 월 실납부</t>
+        </is>
+      </c>
+      <c r="B33" s="22">
+        <f>B25-B28-B30</f>
         <v/>
-      </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>→ 10_SKT_Bundle · 단독가 REPLACE 방식</t>
-        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  [SKT] IPTV 추가 (TV결합 시)</t>
-        </is>
-      </c>
-      <c r="B34" s="15">
-        <f>IF(AND(B4="SKT",B8="요즘가족결합",B9&gt;0,B23=1),1100,0)</f>
+          <t xml:space="preserve">  - 휴대폰 고지서 별도 차감</t>
+        </is>
+      </c>
+      <c r="B34" s="24">
+        <f>-(B29+B31)</f>
         <v/>
       </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
-          <t>TV 결합 시에만 추가 -1,100원</t>
-        </is>
-      </c>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  [SKT] 휴대폰 인당 할인</t>
-        </is>
-      </c>
-      <c r="B35" s="15">
-        <f>IF(AND(B4="SKT",B8="요즘가족결합",B9&gt;0),IF(B5="100M",CHOOSE(B9,3500,3500,6000,4500,3600),CHOOSE(B9,3500,3500,6000,6000,4800)),0)</f>
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>🎉 혜택가 (최종 월요금)</t>
+        </is>
+      </c>
+      <c r="B35" s="25">
+        <f>IF(B7="결합없음",B25,B33-(B29+B31))</f>
         <v/>
       </c>
-      <c r="C35" s="16" t="inlineStr">
-        <is>
-          <t>→ 10_SKT_Bundle · 속도+회선수별 인당</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  [SKT] 휴대폰 총 할인</t>
-        </is>
-      </c>
-      <c r="B36" s="15">
-        <f>B35*IF(AND(B4="SKT",B8="요즘가족결합"),B9,0)</f>
-        <v/>
-      </c>
-      <c r="C36" s="16" t="inlineStr">
-        <is>
-          <t>인당 × 회선수 (휴대폰 고지서 별도 차감)</t>
-        </is>
-      </c>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  [KT] 총액결합 인터넷 할인</t>
-        </is>
-      </c>
-      <c r="B37" s="15">
-        <f>IF(AND(B4="KT",B8="총액결합"),IF(B5="100M",CHOOSE(B10,1650,3300,5500,5500,5500,5500),CHOOSE(B10,2200,5500,5500,5500,5500,5500)),0)</f>
-        <v/>
-      </c>
-      <c r="C37" s="16" t="inlineStr">
-        <is>
-          <t>→ 11_KT_Total · 구간 1~6 · 기본 TV결합과 STACK</t>
+      <c r="A37" s="15" t="inlineStr">
+        <is>
+          <t>🎁 부가</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  [KT] 총액결합 휴대폰 할인</t>
-        </is>
-      </c>
-      <c r="B38" s="15">
-        <f>IF(AND(B4="KT",B8="총액결합"),IF(B5="100M",CHOOSE(B10,0,0,3300,14300,18700,23100),CHOOSE(B10,0,0,5500,16610,22110,27610)),0)</f>
+          <t xml:space="preserve">  설치비</t>
+        </is>
+      </c>
+      <c r="B38" s="13">
+        <f>IF(B13=0,36000,56200)</f>
         <v/>
       </c>
-      <c r="C38" s="16" t="inlineStr">
-        <is>
-          <t>→ 11_KT_Total · 휴대폰 고지서 별도 차감</t>
+      <c r="C38" s="14" t="inlineStr">
+        <is>
+          <t>→ 06_Install</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  [LGU+] 참쉬운 인터넷 할인</t>
-        </is>
-      </c>
-      <c r="B39" s="15">
-        <f>IF(AND(B4="LG U+",B8="참쉬운 가족결합",B9&gt;=2),IF(B5="100M",5500,IF(B5="500M",9900,13200)),0)</f>
+          <t xml:space="preserve">  사은품</t>
+        </is>
+      </c>
+      <c r="B39" s="13">
+        <f>IF(B13=0,IF(B4="100M",90000,140000),CHOOSE(MATCH(B4,{"100M","500M","1G"},0),370000,450000,450000))</f>
         <v/>
       </c>
-      <c r="C39" s="16" t="inlineStr">
-        <is>
-          <t>→ 14_LGU_Chweyswun · 단독가 REPLACE · 2회선부터</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  [LGU+] 참쉬운 휴대폰 인당 할인</t>
-        </is>
-      </c>
-      <c r="B40" s="15">
-        <f>IF(AND(B4="LG U+",B8="참쉬운 가족결합",B9&gt;=2),CHOOSE(B10,CHOOSE(MIN(B9,4)-1,2200,3300,4400),CHOOSE(MIN(B9,4)-1,3300,5500,6600),CHOOSE(MIN(B9,4)-1,4400,6600,8800)),0)</f>
-        <v/>
-      </c>
-      <c r="C40" s="16" t="inlineStr">
-        <is>
-          <t>→ 14_LGU_Chweyswun · 요금구간(1~3) × 회선(2~4+)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  [LGU+] 참쉬운 휴대폰 총 할인</t>
-        </is>
-      </c>
-      <c r="B41" s="15">
-        <f>B40*IF(AND(B4="LG U+",B8="참쉬운 가족결합"),MIN(B9,4),0)</f>
-        <v/>
-      </c>
-      <c r="C41" s="16" t="inlineStr">
-        <is>
-          <t>인당 × 회선수</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="9" t="inlineStr">
-        <is>
-          <t>💰 결합 적용 월요금</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  인터넷+TV 월 실납부 (결합 적용)</t>
-        </is>
-      </c>
-      <c r="B44" s="19">
-        <f>IF(B8="결합없음",B30,IF(AND(B4="SKT",B8="요즘가족결합"),(B20+B24-B33)+IF(B23=1,B21-B22-B34+B27,0),IF(AND(B4="KT",B8="총액결합"),IF(B23=0,B20+B24-B37,(IF(B7="Y",B26,B25)-B37)+(B21-B22)+B27),IF(AND(B4="LG U+",B8="참쉬운 가족결합"),(B20+B24-B39)+IF(B23=1,B21-B22+B27,0),B30))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 휴대폰 고지서 별도 차감</t>
-        </is>
-      </c>
-      <c r="B45" s="15">
-        <f>-(B36+B38+B41)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  🎉 혜택가 (최종 월요금)</t>
-        </is>
-      </c>
-      <c r="B46" s="21">
-        <f>B44-(B36+B38+B41)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="17" t="inlineStr">
-        <is>
-          <t>🎁 부가 (참고)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  설치비 (1회성)</t>
-        </is>
-      </c>
-      <c r="B49" s="15">
-        <f>IF(B4="KT",IF(B23=0,36000,56200),IF(B23=0,36300,56100))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  사은품</t>
-        </is>
-      </c>
-      <c r="B50" s="15">
-        <f>IF(B4="SKT",IF(B23=0,IF(B5="100M",110000,170000),CHOOSE(MATCH(B5,{"100M","500M","1G"},0),400000,430000,490000)),IF(B4="KT",IF(B23=0,IF(B5="100M",90000,140000),CHOOSE(MATCH(B5,{"100M","500M","1G"},0),370000,450000,450000)),IF(B23=0,IF(B5="100M",200000,230000),CHOOSE(MATCH(B5,{"100M","500M","1G"},0),400000,470000,470000))))</f>
-        <v/>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>→ 07_Gift</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="25">
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="A15:E15"/>
+  <mergeCells count="24">
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="C31:E31"/>
     <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="A11:E11"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="C23:E23"/>
     <mergeCell ref="C39:E39"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="A27:E27"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="C38:E38"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C29:E29"/>
     <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C25:E25"/>
   </mergeCells>
-  <dataValidations count="7">
+  <dataValidations count="6">
     <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"SKT,KT,LG U+"</formula1>
+      <formula1>"100M,500M,1G"</formula1>
     </dataValidation>
     <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"100M,500M,1G"</formula1>
+      <formula1>"TV 없음,지니TV 베이직,지니TV 라이트,지니TV 에센스,지니TV 모든G,지니TV 디즈니+모든G"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Y,N"</formula1>
     </dataValidation>
     <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"Y,N"</formula1>
+      <formula1>"결합없음,총액결합,정액결합"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"1,2,3,4,5,6"</formula1>
     </dataValidation>
     <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"0,1,2,3,4,5"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"1,2,3,4,5,6"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"TV 없음,B tv 이코노미,B tv 스탠다드,B tv 올,B tv 스탠다드 플러스,B tv 올 플러스,B tv 스탠다드 넷플릭스,B tv 올 넷플릭스,B tv 스탠다드 넷플릭스 프리미엄,B tv 올 넷플릭스 프리미엄,지니TV 베이직,지니TV 라이트,지니TV 에센스,지니TV 모든G,지니TV 디즈니+모든G,U+tv 실속형,U+tv 기본형,U+tv 프리미엄,U+tv 프리미엄 VOD"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"요즘가족결합,총액결합,정액결합,프리미엄 가족결합,참쉬운 가족결합,투게더,결합없음"</formula1>
+      <formula1>"1,2,3,4"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>🧮 LG U+ 참쉬운/투게더 결합 계산기</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>📝 입력</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>속도</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>500M</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>100M / 500M / 1G</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>TV 상품</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>U+tv 기본형</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>LG U+tv 4종</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>결합 종류</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>참쉬운 가족결합</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>결합없음/참쉬운/투게더</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>요금구간 (참쉬운, 1~3)</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>1=69K미만, 2=69K+, 3=88K+</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>결합 회선수</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>참쉬운 2~4+ / 투게더 2~5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>🧮 자동 계산</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>TV 인덱스</t>
+        </is>
+      </c>
+      <c r="B11" s="13">
+        <f>MATCH(B5,{"TV 없음","U+tv 실속형","U+tv 기본형","U+tv 프리미엄","U+tv 프리미엄 VOD"},0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>TV 선택 여부</t>
+        </is>
+      </c>
+      <c r="B12" s="13">
+        <f>IF(B5="TV 없음",0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>📊 데이터 조회</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>인터넷 단독가</t>
+        </is>
+      </c>
+      <c r="B15" s="13">
+        <f>IF(B4="100M",22000,IF(B4="500M",33000,38500))</f>
+        <v/>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>→ 01_Internet</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>TV 가격 (p)</t>
+        </is>
+      </c>
+      <c r="B16" s="13">
+        <f>IF(B12=0,0,CHOOSE(B11-1,15400,16500,18700,24200))</f>
+        <v/>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>→ 02_TV · LG U+tv</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>TV 결합할인 (dc)</t>
+        </is>
+      </c>
+      <c r="B17" s="13">
+        <f>IF(B12=0,0,CHOOSE(B11-1,2200,2200,2200,5500))</f>
+        <v/>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>→ 02_TV · 전 상품 -2,200 (VOD만 -5,500)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>WiFi 추가금</t>
+        </is>
+      </c>
+      <c r="B18" s="13">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>→ 05_WiFi · LG U+ 전속도 무료 (기가와이파이 기본)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>셋톱박스 (U+tv UHD4)</t>
+        </is>
+      </c>
+      <c r="B19" s="13">
+        <f>4400</f>
+        <v/>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>→ 04_SetTop · 기본 모델 · AI음향 기술</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>【경로 A】 결합없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  월 기본요금</t>
+        </is>
+      </c>
+      <c r="B22" s="27">
+        <f>IF(B12=0,B15,IF(B4="100M",22000,IF(B4="500M",27500,33000))+B16-B17+B19)</f>
+        <v/>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>TV 없으면 단독가 / TV 있으면 tvInternet(LGU+ WiFi 유무 동일) + TV + 셋톱</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="28" t="inlineStr">
+        <is>
+          <t>【경로 B】 결합 적용 (REPLACE — 단독가 기준)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  [참쉬운] 인터넷 할인</t>
+        </is>
+      </c>
+      <c r="B25" s="13">
+        <f>IF(B6="참쉬운 가족결합",IF(B4="100M",5500,IF(B4="500M",9900,13200)),0)</f>
+        <v/>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>→ 14_LGU_Chweyswun · 단독가 REPLACE</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  [참쉬운] 휴대폰 인당 할인</t>
+        </is>
+      </c>
+      <c r="B26" s="13">
+        <f>IF(B6="참쉬운 가족결합",CHOOSE(B7,CHOOSE(MIN(B8,4)-1,2200,3300,4400),CHOOSE(MIN(B8,4)-1,3300,5500,6600),CHOOSE(MIN(B8,4)-1,4400,6600,8800)),0)</f>
+        <v/>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>→ 14_LGU_Chweyswun · 요금구간 × 회선수</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  [참쉬운] 휴대폰 총 할인</t>
+        </is>
+      </c>
+      <c r="B27" s="13">
+        <f>B26*IF(B6="참쉬운 가족결합",MIN(B8,4),0)</f>
+        <v/>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>인당 × min(회선수,4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  [투게더] 인터넷 할인</t>
+        </is>
+      </c>
+      <c r="B28" s="13">
+        <f>IF(B6="투게더 결합",IF(B4="100M",0,11000),0)</f>
+        <v/>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>→ 15_LGU_Together · 100M 결합불가 · 단독가 REPLACE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  [투게더] 휴대폰 인당 할인</t>
+        </is>
+      </c>
+      <c r="B29" s="13">
+        <f>IF(B6="투게더 결합",CHOOSE(MIN(B8,4)-1,10000,14000,20000),0)</f>
+        <v/>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>→ 15_LGU_Together · 2/3/4+ 회선</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  [투게더] 휴대폰 총 할인</t>
+        </is>
+      </c>
+      <c r="B30" s="13">
+        <f>B29*IF(B6="투게더 결합",MIN(B8,5),0)</f>
+        <v/>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>인당 × 회선수</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  = 인터넷+TV 월 실납부 (결합 적용)</t>
+        </is>
+      </c>
+      <c r="B32" s="27">
+        <f>(B15-B25-B28)+IF(B12=0,0,B16-B17+B19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 휴대폰 고지서 별도 차감</t>
+        </is>
+      </c>
+      <c r="B33" s="29">
+        <f>-(B27+B30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>🎉 혜택가 (최종 월요금)</t>
+        </is>
+      </c>
+      <c r="B34" s="30">
+        <f>IF(B6="결합없음",B22,B32-(B27+B30))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="15" t="inlineStr">
+        <is>
+          <t>🎁 부가</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  설치비</t>
+        </is>
+      </c>
+      <c r="B37" s="13">
+        <f>IF(B12=0,36300,56100)</f>
+        <v/>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>→ 06_Install</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  사은품</t>
+        </is>
+      </c>
+      <c r="B38" s="13">
+        <f>IF(B12=0,IF(B4="100M",200000,230000),CHOOSE(MATCH(B4,{"100M","500M","1G"},0),400000,470000,470000))</f>
+        <v/>
+      </c>
+      <c r="C38" s="14" t="inlineStr">
+        <is>
+          <t>→ 07_Gift</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C25:E25"/>
+  </mergeCells>
+  <dataValidations count="5">
+    <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"100M,500M,1G"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"TV 없음,U+tv 실속형,U+tv 기본형,U+tv 프리미엄,U+tv 프리미엄 VOD"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"결합없음,참쉬운 가족결합,투게더 결합"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"1,2,3"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"2,3,4,5"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4603,7 +5464,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>📡 인터넷 단독 요금 (3사 공통)</t>
+          <t>📡 인터넷 단독 요금</t>
         </is>
       </c>
     </row>
@@ -4702,7 +5563,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4723,7 +5584,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>📺 TV 상품 (3사 전체)</t>
+          <t>📺 TV 상품 (3사)</t>
         </is>
       </c>
     </row>
@@ -4745,7 +5606,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>TV 단독</t>
+          <t>단독가</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -4755,7 +5616,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>인터넷 결합 시</t>
+          <t>결합가</t>
         </is>
       </c>
     </row>
@@ -5196,7 +6057,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5215,7 +6076,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>🔗 TV 결합 시 인터넷 요금 (WiFi 유/무)</t>
+          <t>🔗 TV 결합 시 인터넷 요금</t>
         </is>
       </c>
     </row>
@@ -5227,7 +6088,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>WiFi 유무</t>
+          <t>WiFi</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -5254,7 +6115,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>WiFi 미포함</t>
+          <t>미포함</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
@@ -5275,7 +6136,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>WiFi 포함</t>
+          <t>포함</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
@@ -5296,7 +6157,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>WiFi 미포함</t>
+          <t>미포함</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
@@ -5317,7 +6178,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>WiFi 포함 (1G=동일)</t>
+          <t>포함 (1G=동일)</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
@@ -5338,7 +6199,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>모든 속도 동일</t>
+          <t>공통</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
@@ -5356,7 +6217,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5377,14 +6238,14 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>📦 셋톱박스 옵션</t>
+          <t>📦 셋톱박스</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="inlineStr">
-        <is>
-          <t>💬 기본값(isDefault) 선정 기준: 매장 판매량 1위 · 가격 대비 기능 균형 · 고객 선호 · 요금 계산 시 기본 적용</t>
+      <c r="A3" s="31" t="inlineStr">
+        <is>
+          <t>💬 기본값(isDefault): 매장 판매 1위 + 가격/기능 균형 · 가입 시 자동 설정 · 요금 계산 기본</t>
         </is>
       </c>
     </row>
@@ -5456,7 +6317,7 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>✅ 기본값 · SKT 표준 셋톱 · OTT 대부분 지원 · 매장 판매 1위</t>
+          <t>✅ 기본 · SKT 표준 · OTT 대부분 지원 · 매장 판매 1위</t>
         </is>
       </c>
     </row>
@@ -5491,7 +6352,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>저가형 · 일부 OTT(넷플릭스 등) 미지원</t>
+          <t>저가형 · 넷플릭스 미지원</t>
         </is>
       </c>
     </row>
@@ -5526,7 +6387,7 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>AI 음성인식 특화 · 가격 인상형</t>
+          <t>AI 음성인식 특화</t>
         </is>
       </c>
     </row>
@@ -5561,7 +6422,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>사운드바 일체형 · OTT 거의 불가</t>
+          <t>사운드바 일체 · OTT 거의 불가</t>
         </is>
       </c>
     </row>
@@ -5596,7 +6457,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>아이폰 연동형 · 쿠팡/애플TV 특화</t>
+          <t>아이폰 연동</t>
         </is>
       </c>
     </row>
@@ -5631,7 +6492,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>✅ 기본값 · KT 대표 모델 · AI 블루투스 스피커 일체 · 고객 선호 1위</t>
+          <t>✅ 기본 · KT 대표 · AI 블루투스 일체 · 선호 1위</t>
         </is>
       </c>
     </row>
@@ -5666,7 +6527,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>저가형 (3,300원) · 기본 기능만</t>
+          <t>저가형 (3,300원)</t>
         </is>
       </c>
     </row>
@@ -5701,7 +6562,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>사운드바+공유기 일체 · 고가형</t>
+          <t>사운드바+공유기 일체</t>
         </is>
       </c>
     </row>
@@ -5736,7 +6597,7 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>✅ 기본값 · LG U+ 표준 · AI 음향기술 탑재</t>
+          <t>✅ 기본 · AI 음향기술</t>
         </is>
       </c>
     </row>
@@ -5771,7 +6632,7 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>돌비비전 지원 고급형</t>
+          <t>돌비비전 지원</t>
         </is>
       </c>
     </row>
@@ -5783,7 +6644,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5806,14 +6667,14 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>📡 WiFi 옵션</t>
+          <t>📡 WiFi</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="inlineStr">
-        <is>
-          <t>💬 기본값 선정 기준: 속도별 단가가 낮은 표준 모델 · 가입 시 자동 지급 · 요금 계산 기본 대상</t>
+      <c r="A3" s="31" t="inlineStr">
+        <is>
+          <t>💬 기본값: 속도별 단가가 낮은 표준 모델 · 가입 시 자동 지급 · 요금 계산 대상</t>
         </is>
       </c>
     </row>
@@ -5901,7 +6762,7 @@
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>✅ 기본값 · SKT 표준 WiFi · 속도 관계없이 1,100원 균일</t>
+          <t>✅ 기본 · SKT 표준 · 속도 균일 1,100원</t>
         </is>
       </c>
     </row>
@@ -5942,7 +6803,7 @@
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>WiFi-6 지원 · 같은 요금이나 수요 부족으로 비활성</t>
+          <t>WiFi-6 · 같은 요금</t>
         </is>
       </c>
     </row>
@@ -5983,7 +6844,7 @@
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>최대 1.7Gbps · 고급 사용자용 · 인터넷+TV 결합 시 3,300 할인</t>
+          <t>최대 1.7Gbps · 고급형</t>
         </is>
       </c>
     </row>
@@ -6024,7 +6885,7 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>WiFi 증폭기 · 기존 WiFi에 추가</t>
+          <t>WiFi 증폭기</t>
         </is>
       </c>
     </row>
@@ -6065,7 +6926,7 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>✅ 기본값 · KT 표준 · 1G 속도 시 무료 제공 (요금 변동 없음)</t>
+          <t>✅ 기본 · KT 표준 · 1G 무료</t>
         </is>
       </c>
     </row>
@@ -6106,7 +6967,7 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>WiFi-6 · 100M/1G 무료, 500M만 유료</t>
+          <t>WiFi-6 · 100M/1G 무료</t>
         </is>
       </c>
     </row>
@@ -6147,7 +7008,7 @@
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>WiFi 증폭기 · 홈AX와 호환</t>
+          <t>증폭기 (홈AX 호환)</t>
         </is>
       </c>
     </row>
@@ -6188,7 +7049,7 @@
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>최대 10Gbps 고급형 · 2.4GHz</t>
+          <t>고급형 10Gbps</t>
         </is>
       </c>
     </row>
@@ -6205,7 +7066,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>GIGA WIFI 프리미엄 2.4 (6E)</t>
+          <t>프리미엄 2.4 (6E)</t>
         </is>
       </c>
       <c r="D14" s="5" t="n">
@@ -6229,7 +7090,7 @@
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>2.4GHz + 6E 지원</t>
+          <t>6E 지원</t>
         </is>
       </c>
     </row>
@@ -6246,7 +7107,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>GIGA WIFI 프리미엄 4.8</t>
+          <t>프리미엄 4.8</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -6311,7 +7172,7 @@
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>✅ 기본값 · LG U+ 전 속도 무료 · 대표 WiFi</t>
+          <t>✅ 기본 · 전속도 무료</t>
         </is>
       </c>
     </row>
@@ -6352,7 +7213,7 @@
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>WiFi-6 · 500M+ 가입 시 기본 (동일 무료)</t>
+          <t>WiFi-6 · 동일 무료</t>
         </is>
       </c>
     </row>
@@ -6393,7 +7254,7 @@
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>메쉬 지원 · 500M+ 선택 가능</t>
+          <t>메쉬 · 500M+ 선택</t>
         </is>
       </c>
     </row>
@@ -6403,288 +7264,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>🔧 설치비</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>통신사</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>단독 (solo)</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>결합 (combo)</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>36300</v>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>56100</v>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>주말 +25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>KT</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>36000</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>56200</v>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>주말 +25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>LG U+</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>36300</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>56100</v>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>주말 +25%</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>🎁 사은품 (원)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>통신사</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>100M</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>500M</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>1G</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>solo</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>110000</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>170000</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>170000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>combo</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>400000</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>430000</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>490000</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>KT</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>solo</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>90000</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>140000</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>140000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>KT</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>combo</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>370000</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>450000</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>450000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>LG U+</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>solo</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>200000</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>230000</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>230000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>LG U+</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>combo</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>400000</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>470000</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>470000</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/bongi-calculator-data.xlsx
+++ b/docs/bongi-calculator-data.xlsx
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="B31" s="19">
-        <f>B14+B17-B26</f>
+        <f>IF(B7=0,"-",B14+B17-B26)</f>
         <v/>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
         </is>
       </c>
       <c r="B32" s="19">
-        <f>IF(B11=0,0,B15-B16-B27)</f>
+        <f>IF(B7=0,"-",IF(B11=0,0,B15-B16-B27))</f>
         <v/>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
         </is>
       </c>
       <c r="B33" s="19">
-        <f>IF(B11=0,0,B20)</f>
+        <f>IF(B7=0,"-",IF(B11=0,0,B20))</f>
         <v/>
       </c>
     </row>
@@ -4298,7 +4298,7 @@
         </is>
       </c>
       <c r="B34" s="17">
-        <f>(B14+B17-B26)+IF(B11=0,0,B15-B16-B27+B20)</f>
+        <f>IF(B7=0,"-",(B14+B17-B26)+IF(B11=0,0,B15-B16-B27+B20))</f>
         <v/>
       </c>
     </row>
@@ -4309,7 +4309,7 @@
         </is>
       </c>
       <c r="B35" s="19">
-        <f>-B29</f>
+        <f>IF(B7=0,"-",-B29)</f>
         <v/>
       </c>
     </row>
@@ -4323,6 +4323,11 @@
         <f>IF(B7=0,B23,B34-B29)</f>
         <v/>
       </c>
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>결합없음이면 경로 A 값 / 결합 있으면 경로 B - 휴대폰할인</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="15" t="inlineStr">
@@ -4364,10 +4369,11 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="26">
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="C40:E40"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="C36:E36"/>
     <mergeCell ref="C11:E11"/>
     <mergeCell ref="C27:E27"/>
     <mergeCell ref="C23:E23"/>

--- a/docs/bongi-calculator-data.xlsx
+++ b/docs/bongi-calculator-data.xlsx
@@ -4496,7 +4496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>결합없음/총액/정액</t>
+          <t>결합없음/총액/정액/💎프리미엄</t>
         </is>
       </c>
     </row>
@@ -4618,343 +4618,457 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>💎 프리미엄 요금제</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>89,000원</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>77K+ 요금제 (드롭다운)</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>💎 프리미엄 회선수</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>대표자 제외 구성원 77K+ 회선수 (최소 1명)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>🧮 자동 계산</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>TV 인덱스</t>
         </is>
       </c>
-      <c r="B12" s="13">
+      <c r="B14" s="13">
         <f>MATCH(B5,{"TV 없음","지니TV 베이직","지니TV 라이트","지니TV 에센스","지니TV 모든G","지니TV 디즈니+모든G"},0)</f>
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>TV 선택 여부</t>
         </is>
       </c>
-      <c r="B13" s="13">
+      <c r="B15" s="13">
         <f>IF(B5="TV 없음",0,1)</f>
         <v/>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>📊 데이터 조회</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>인터넷 단독가</t>
         </is>
       </c>
-      <c r="B16" s="13">
+      <c r="B18" s="13">
         <f>IF(B4="100M",22000,IF(B4="500M",33000,38500))</f>
         <v/>
       </c>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="C18" s="14" t="inlineStr">
         <is>
           <t>→ 01_Internet</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>TV 가격 (p)</t>
-        </is>
-      </c>
-      <c r="B17" s="13">
-        <f>IF(B13=0,0,CHOOSE(B12-1,14740,15840,20240,21340,28100))</f>
-        <v/>
-      </c>
-      <c r="C17" s="14" t="inlineStr">
-        <is>
-          <t>→ 02_TV · KT 지니TV</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>TV 결합할인 (dc)</t>
-        </is>
-      </c>
-      <c r="B18" s="13">
-        <f>IF(B13=0,0,CHOOSE(B12-1,2640,2640,3740,4400,6600))</f>
-        <v/>
-      </c>
-      <c r="C18" s="14" t="inlineStr">
-        <is>
-          <t>→ 02_TV · KT 상품별 차등</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
+          <t>TV 가격 (p)</t>
+        </is>
+      </c>
+      <c r="B19" s="13">
+        <f>IF(B15=0,0,CHOOSE(B14-1,14740,15840,20240,21340,28100))</f>
+        <v/>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>→ 02_TV · KT 지니TV</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>TV 결합할인 (dc)</t>
+        </is>
+      </c>
+      <c r="B20" s="13">
+        <f>IF(B15=0,0,CHOOSE(B14-1,2640,2640,3740,4400,6600))</f>
+        <v/>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>→ 02_TV · KT 상품별 차등</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
           <t>WiFi 추가금 (속도별)</t>
         </is>
       </c>
-      <c r="B19" s="13">
+      <c r="B21" s="13">
         <f>IF(B6="Y",IF(B4="1G",0,1100),0)</f>
         <v/>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C21" s="14" t="inlineStr">
         <is>
           <t>→ 05_WiFi · KT WAVE2 (기본) · 1G는 무료</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>tvInternetNoWifi</t>
         </is>
       </c>
-      <c r="B20" s="13">
+      <c r="B22" s="13">
         <f>IF(B4="100M",22000,IF(B4="500M",27500,33000))</f>
         <v/>
       </c>
-      <c r="C20" s="14" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>→ 03_TV_Internet</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>tvInternetWithWifi</t>
         </is>
       </c>
-      <c r="B21" s="13">
+      <c r="B23" s="13">
         <f>IF(B4="100M",23100,IF(B4="500M",28600,33000))</f>
         <v/>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>→ 03_TV_Internet · 1G는 동일</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>셋톱박스 (기가지니3)</t>
         </is>
       </c>
-      <c r="B22" s="13">
+      <c r="B24" s="13">
         <f>4400</f>
         <v/>
       </c>
-      <c r="C22" s="14" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>→ 04_SetTop · 기본 모델 · 고객 선호 1위</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>【경로 A】 결합없음 (기본 TV 결합)</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="16" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  월 기본요금</t>
         </is>
       </c>
-      <c r="B25" s="22">
-        <f>IF(B13=0,B16+B19,IF(B6="Y",B21,B20)+B17-B18+B22)</f>
+      <c r="B27" s="22">
+        <f>IF(B15=0,B18+B21,IF(B6="Y",B23,B22)+B19-B20+B24)</f>
         <v/>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="23" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="23" t="inlineStr">
         <is>
           <t>【경로 B】 결합 적용 (STACK — 기본 TV결합 + 추가할인)</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  [총액] 인터넷 추가 할인</t>
         </is>
       </c>
-      <c r="B28" s="13">
+      <c r="B30" s="13">
         <f>IF(B7="총액결합",IF(B4="100M",CHOOSE(B8,1650,3300,5500,5500,5500,5500),CHOOSE(B8,2200,5500,5500,5500,5500,5500)),0)</f>
         <v/>
       </c>
-      <c r="C28" s="14" t="inlineStr">
+      <c r="C30" s="14" t="inlineStr">
         <is>
           <t>→ 11_KT_Total · STACK 중복 적용</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  [총액] 휴대폰 할인</t>
         </is>
       </c>
-      <c r="B29" s="13">
+      <c r="B31" s="13">
         <f>IF(B7="총액결합",IF(B4="100M",CHOOSE(B8,0,0,3300,14300,18700,23100),CHOOSE(B8,0,0,5500,16610,22110,27610)),0)</f>
         <v/>
       </c>
-      <c r="C29" s="14" t="inlineStr">
+      <c r="C31" s="14" t="inlineStr">
         <is>
           <t>→ 11_KT_Total · 휴대폰 고지서 별도</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  [정액] 인터넷 할인</t>
         </is>
       </c>
-      <c r="B30" s="13">
+      <c r="B32" s="13">
         <f>IF(B7="정액결합",5500,0)</f>
         <v/>
       </c>
-      <c r="C30" s="14" t="inlineStr">
+      <c r="C32" s="14" t="inlineStr">
         <is>
           <t>→ 12_KT_Fixed · 전구간 5,500 고정</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  [정액] 휴대폰 할인</t>
         </is>
       </c>
-      <c r="B31" s="13">
+      <c r="B33" s="13">
         <f>IF(B7="정액결합",CHOOSE(B9,0,3000,5000,7000),0)</f>
         <v/>
       </c>
-      <c r="C31" s="14" t="inlineStr">
+      <c r="C33" s="14" t="inlineStr">
         <is>
           <t>→ 12_KT_Fixed · 4구간</t>
         </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  = 인터넷+TV 월 실납부</t>
-        </is>
-      </c>
-      <c r="B33" s="22">
-        <f>B25-B28-B30</f>
-        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">  [💎프리미엄] 인터넷 할인 (고정)</t>
+        </is>
+      </c>
+      <c r="B34" s="13">
+        <f>IF(B7="💎 프리미엄 가족결합",5500,0)</f>
+        <v/>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>→ 13_KT_Premium · 인터넷 또는 대표자 휴대폰 고정 -5,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  [💎프리미엄] 대표자 총액결합 (합산=요금제1명)</t>
+        </is>
+      </c>
+      <c r="B35" s="13">
+        <f>IF(B7="💎 프리미엄 가족결합",IF(B4="100M",CHOOSE(B8,0,0,3300,14300,18700,23100),CHOOSE(B8,0,0,5500,16610,22110,27610)),0)</f>
+        <v/>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>총액결합 구간 활용 (대표자 1명 기준)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  [💎프리미엄] 요금제별 할인액</t>
+        </is>
+      </c>
+      <c r="B36" s="13">
+        <f>IF(B7="💎 프리미엄 가족결합",CHOOSE(MATCH(B10,{"77,000원","80,000원","87,890원","89,000원","90,000원","100,000원","109,000원","110,000원","130,000원"},0),19250,20000,22000,22250,22500,25000,27500,27500,32500),0)</f>
+        <v/>
+      </c>
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>→ 13_KT_Premium · planCatalog dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  [💎프리미엄] 구성원 총 할인 (dc × 회선수)</t>
+        </is>
+      </c>
+      <c r="B37" s="13">
+        <f>B36*IF(B7="💎 프리미엄 가족결합",B11,0)</f>
+        <v/>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>77K+ 구성원만 해당 (대표자 제외)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  = 인터넷+TV 월 실납부</t>
+        </is>
+      </c>
+      <c r="B39" s="22">
+        <f>IF(B7="💎 프리미엄 가족결합",B27-B34,B27-B30-B32)</f>
+        <v/>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>프리미엄: -5,500 고정 / 총액+정액: 해당 할인</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">  - 휴대폰 고지서 별도 차감</t>
         </is>
       </c>
-      <c r="B34" s="24">
-        <f>-(B29+B31)</f>
+      <c r="B40" s="24">
+        <f>-(B31+B33+B35+B37)</f>
         <v/>
       </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="16" t="inlineStr">
+      <c r="C40" s="14" t="inlineStr">
+        <is>
+          <t>총액/정액 + 프리미엄(대표자 총액 + 구성원 프리미엄)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>🎉 혜택가 (최종 월요금)</t>
         </is>
       </c>
-      <c r="B35" s="25">
-        <f>IF(B7="결합없음",B25,B33-(B29+B31))</f>
+      <c r="B41" s="25">
+        <f>IF(B7="결합없음",B27,B39-(B31+B33+B35+B37))</f>
         <v/>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="15" t="inlineStr">
         <is>
           <t>🎁 부가</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  설치비</t>
         </is>
       </c>
-      <c r="B38" s="13">
-        <f>IF(B13=0,36000,56200)</f>
+      <c r="B44" s="13">
+        <f>IF(B15=0,36000,56200)</f>
         <v/>
       </c>
-      <c r="C38" s="14" t="inlineStr">
+      <c r="C44" s="14" t="inlineStr">
         <is>
           <t>→ 06_Install</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  사은품</t>
         </is>
       </c>
-      <c r="B39" s="13">
-        <f>IF(B13=0,IF(B4="100M",90000,140000),CHOOSE(MATCH(B4,{"100M","500M","1G"},0),370000,450000,450000))</f>
+      <c r="B45" s="13">
+        <f>IF(B15=0,IF(B4="100M",90000,140000),CHOOSE(MATCH(B4,{"100M","500M","1G"},0),370000,450000,450000))</f>
         <v/>
       </c>
-      <c r="C39" s="14" t="inlineStr">
+      <c r="C45" s="14" t="inlineStr">
         <is>
           <t>→ 07_Gift</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="A24:E24"/>
+  <mergeCells count="32">
+    <mergeCell ref="C44:E44"/>
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C40:E40"/>
     <mergeCell ref="C9:E9"/>
-    <mergeCell ref="A11:E11"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C23:E23"/>
     <mergeCell ref="C39:E39"/>
     <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C17:E17"/>
     <mergeCell ref="C7:E7"/>
-    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="C32:E32"/>
     <mergeCell ref="A3:E3"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="A26:E26"/>
     <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C37:E37"/>
     <mergeCell ref="C18:E18"/>
     <mergeCell ref="C30:E30"/>
+    <mergeCell ref="C34:E34"/>
     <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="C33:E33"/>
     <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C45:E45"/>
     <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="C35:E35"/>
     <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C10:E10"/>
   </mergeCells>
-  <dataValidations count="6">
+  <dataValidations count="8">
     <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"100M,500M,1G"</formula1>
     </dataValidation>
@@ -4965,12 +5079,18 @@
       <formula1>"Y,N"</formula1>
     </dataValidation>
     <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"결합없음,총액결합,정액결합"</formula1>
+      <formula1>"결합없음,총액결합,정액결합,💎 프리미엄 가족결합"</formula1>
     </dataValidation>
     <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"1,2,3,4,5,6"</formula1>
     </dataValidation>
     <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"1,2,3,4"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"77,000원,80,000원,87,890원,89,000원,90,000원,100,000원,109,000원,110,000원,130,000원"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"1,2,3,4"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/bongi-calculator-data.xlsx
+++ b/docs/bongi-calculator-data.xlsx
@@ -306,7 +306,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -328,13 +328,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -2234,7 +2237,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="32" t="inlineStr">
+      <c r="A1" s="33" t="inlineStr">
         <is>
           <t>🏷️ SKT 요즘가족결합</t>
         </is>
@@ -2273,332 +2276,332 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="33" t="inlineStr">
+      <c r="A4" s="34" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B4" s="33" t="n">
+      <c r="B4" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="33" t="n">
+      <c r="C4" s="34" t="n">
         <v>3500</v>
       </c>
-      <c r="D4" s="33" t="n">
+      <c r="D4" s="34" t="n">
         <v>4400</v>
       </c>
-      <c r="E4" s="33" t="n">
+      <c r="E4" s="34" t="n">
         <v>1100</v>
       </c>
-      <c r="F4" s="33" t="n">
+      <c r="F4" s="34" t="n">
         <v>9000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="33" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B5" s="33" t="n">
+      <c r="B5" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="33" t="n">
+      <c r="C5" s="34" t="n">
         <v>7000</v>
       </c>
-      <c r="D5" s="33" t="n">
+      <c r="D5" s="34" t="n">
         <v>4400</v>
       </c>
-      <c r="E5" s="33" t="n">
+      <c r="E5" s="34" t="n">
         <v>1100</v>
       </c>
-      <c r="F5" s="33" t="n">
+      <c r="F5" s="34" t="n">
         <v>12500</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="33" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B6" s="33" t="n">
+      <c r="B6" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="33" t="n">
+      <c r="C6" s="34" t="n">
         <v>18000</v>
       </c>
-      <c r="D6" s="33" t="n">
+      <c r="D6" s="34" t="n">
         <v>4400</v>
       </c>
-      <c r="E6" s="33" t="n">
+      <c r="E6" s="34" t="n">
         <v>1100</v>
       </c>
-      <c r="F6" s="33" t="n">
+      <c r="F6" s="34" t="n">
         <v>23500</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="33" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B7" s="33" t="n">
+      <c r="B7" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="C7" s="33" t="n">
+      <c r="C7" s="34" t="n">
         <v>18000</v>
       </c>
-      <c r="D7" s="33" t="n">
+      <c r="D7" s="34" t="n">
         <v>4400</v>
       </c>
-      <c r="E7" s="33" t="n">
+      <c r="E7" s="34" t="n">
         <v>1100</v>
       </c>
-      <c r="F7" s="33" t="n">
+      <c r="F7" s="34" t="n">
         <v>23500</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="33" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B8" s="33" t="n">
+      <c r="B8" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="C8" s="33" t="n">
+      <c r="C8" s="34" t="n">
         <v>18000</v>
       </c>
-      <c r="D8" s="33" t="n">
+      <c r="D8" s="34" t="n">
         <v>4400</v>
       </c>
-      <c r="E8" s="33" t="n">
+      <c r="E8" s="34" t="n">
         <v>1100</v>
       </c>
-      <c r="F8" s="33" t="n">
+      <c r="F8" s="34" t="n">
         <v>23500</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="33" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B9" s="33" t="n">
+      <c r="B9" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="33" t="n">
+      <c r="C9" s="34" t="n">
         <v>3500</v>
       </c>
-      <c r="D9" s="33" t="n">
+      <c r="D9" s="34" t="n">
         <v>11000</v>
       </c>
-      <c r="E9" s="33" t="n">
+      <c r="E9" s="34" t="n">
         <v>1100</v>
       </c>
-      <c r="F9" s="33" t="n">
+      <c r="F9" s="34" t="n">
         <v>15600</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="33" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B10" s="33" t="n">
+      <c r="B10" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="33" t="n">
+      <c r="C10" s="34" t="n">
         <v>7000</v>
       </c>
-      <c r="D10" s="33" t="n">
+      <c r="D10" s="34" t="n">
         <v>11000</v>
       </c>
-      <c r="E10" s="33" t="n">
+      <c r="E10" s="34" t="n">
         <v>1100</v>
       </c>
-      <c r="F10" s="33" t="n">
+      <c r="F10" s="34" t="n">
         <v>19100</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B11" s="33" t="n">
+      <c r="B11" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="C11" s="33" t="n">
+      <c r="C11" s="34" t="n">
         <v>18000</v>
       </c>
-      <c r="D11" s="33" t="n">
+      <c r="D11" s="34" t="n">
         <v>11000</v>
       </c>
-      <c r="E11" s="33" t="n">
+      <c r="E11" s="34" t="n">
         <v>1100</v>
       </c>
-      <c r="F11" s="33" t="n">
+      <c r="F11" s="34" t="n">
         <v>30100</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="33" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B12" s="33" t="n">
+      <c r="B12" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="C12" s="33" t="n">
+      <c r="C12" s="34" t="n">
         <v>24000</v>
       </c>
-      <c r="D12" s="33" t="n">
+      <c r="D12" s="34" t="n">
         <v>11000</v>
       </c>
-      <c r="E12" s="33" t="n">
+      <c r="E12" s="34" t="n">
         <v>1100</v>
       </c>
-      <c r="F12" s="33" t="n">
+      <c r="F12" s="34" t="n">
         <v>36100</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="33" t="inlineStr">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B13" s="33" t="n">
+      <c r="B13" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="C13" s="33" t="n">
+      <c r="C13" s="34" t="n">
         <v>24000</v>
       </c>
-      <c r="D13" s="33" t="n">
+      <c r="D13" s="34" t="n">
         <v>11000</v>
       </c>
-      <c r="E13" s="33" t="n">
+      <c r="E13" s="34" t="n">
         <v>1100</v>
       </c>
-      <c r="F13" s="33" t="n">
+      <c r="F13" s="34" t="n">
         <v>36100</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="33" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B14" s="33" t="n">
+      <c r="B14" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="33" t="n">
+      <c r="C14" s="34" t="n">
         <v>3500</v>
       </c>
-      <c r="D14" s="33" t="n">
+      <c r="D14" s="34" t="n">
         <v>13200</v>
       </c>
-      <c r="E14" s="33" t="n">
+      <c r="E14" s="34" t="n">
         <v>1100</v>
       </c>
-      <c r="F14" s="33" t="n">
+      <c r="F14" s="34" t="n">
         <v>17800</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="33" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B15" s="33" t="n">
+      <c r="B15" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="33" t="n">
+      <c r="C15" s="34" t="n">
         <v>7000</v>
       </c>
-      <c r="D15" s="33" t="n">
+      <c r="D15" s="34" t="n">
         <v>13200</v>
       </c>
-      <c r="E15" s="33" t="n">
+      <c r="E15" s="34" t="n">
         <v>1100</v>
       </c>
-      <c r="F15" s="33" t="n">
+      <c r="F15" s="34" t="n">
         <v>21300</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="33" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B16" s="33" t="n">
+      <c r="B16" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="C16" s="33" t="n">
+      <c r="C16" s="34" t="n">
         <v>18000</v>
       </c>
-      <c r="D16" s="33" t="n">
+      <c r="D16" s="34" t="n">
         <v>13200</v>
       </c>
-      <c r="E16" s="33" t="n">
+      <c r="E16" s="34" t="n">
         <v>1100</v>
       </c>
-      <c r="F16" s="33" t="n">
+      <c r="F16" s="34" t="n">
         <v>32300</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="33" t="inlineStr">
+      <c r="A17" s="34" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B17" s="33" t="n">
+      <c r="B17" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="C17" s="33" t="n">
+      <c r="C17" s="34" t="n">
         <v>24000</v>
       </c>
-      <c r="D17" s="33" t="n">
+      <c r="D17" s="34" t="n">
         <v>13200</v>
       </c>
-      <c r="E17" s="33" t="n">
+      <c r="E17" s="34" t="n">
         <v>1100</v>
       </c>
-      <c r="F17" s="33" t="n">
+      <c r="F17" s="34" t="n">
         <v>38300</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="33" t="inlineStr">
+      <c r="A18" s="34" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B18" s="33" t="n">
+      <c r="B18" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="C18" s="33" t="n">
+      <c r="C18" s="34" t="n">
         <v>24000</v>
       </c>
-      <c r="D18" s="33" t="n">
+      <c r="D18" s="34" t="n">
         <v>13200</v>
       </c>
-      <c r="E18" s="33" t="n">
+      <c r="E18" s="34" t="n">
         <v>1100</v>
       </c>
-      <c r="F18" s="33" t="n">
+      <c r="F18" s="34" t="n">
         <v>38300</v>
       </c>
     </row>
@@ -2624,7 +2627,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="34" t="inlineStr">
+      <c r="A1" s="35" t="inlineStr">
         <is>
           <t>🏷️ KT 총액결합 (STACK)</t>
         </is>
@@ -2658,380 +2661,380 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="35" t="inlineStr">
+      <c r="A4" s="36" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B4" s="35" t="inlineStr">
+      <c r="B4" s="36" t="inlineStr">
         <is>
           <t>22K 이하</t>
         </is>
       </c>
-      <c r="C4" s="35" t="n">
+      <c r="C4" s="36" t="n">
         <v>1650</v>
       </c>
-      <c r="D4" s="35" t="n">
+      <c r="D4" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="35" t="n">
+      <c r="E4" s="36" t="n">
         <v>1650</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="35" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B5" s="35" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>22K 이상</t>
         </is>
       </c>
-      <c r="C5" s="35" t="n">
+      <c r="C5" s="36" t="n">
         <v>3300</v>
       </c>
-      <c r="D5" s="35" t="n">
+      <c r="D5" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="35" t="n">
+      <c r="E5" s="36" t="n">
         <v>3300</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="35" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B6" s="35" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>64.9K 이상</t>
         </is>
       </c>
-      <c r="C6" s="35" t="n">
+      <c r="C6" s="36" t="n">
         <v>5500</v>
       </c>
-      <c r="D6" s="35" t="n">
+      <c r="D6" s="36" t="n">
         <v>3300</v>
       </c>
-      <c r="E6" s="35" t="n">
+      <c r="E6" s="36" t="n">
         <v>8800</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="35" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B7" s="35" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>108.9K 이상</t>
         </is>
       </c>
-      <c r="C7" s="35" t="n">
+      <c r="C7" s="36" t="n">
         <v>5500</v>
       </c>
-      <c r="D7" s="35" t="n">
+      <c r="D7" s="36" t="n">
         <v>14300</v>
       </c>
-      <c r="E7" s="35" t="n">
+      <c r="E7" s="36" t="n">
         <v>19800</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="35" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B8" s="35" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr">
         <is>
           <t>141.9K 이상</t>
         </is>
       </c>
-      <c r="C8" s="35" t="n">
+      <c r="C8" s="36" t="n">
         <v>5500</v>
       </c>
-      <c r="D8" s="35" t="n">
+      <c r="D8" s="36" t="n">
         <v>18700</v>
       </c>
-      <c r="E8" s="35" t="n">
+      <c r="E8" s="36" t="n">
         <v>24200</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="35" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B9" s="35" t="inlineStr">
+      <c r="B9" s="36" t="inlineStr">
         <is>
           <t>174.9K 이상</t>
         </is>
       </c>
-      <c r="C9" s="35" t="n">
+      <c r="C9" s="36" t="n">
         <v>5500</v>
       </c>
-      <c r="D9" s="35" t="n">
+      <c r="D9" s="36" t="n">
         <v>23100</v>
       </c>
-      <c r="E9" s="35" t="n">
+      <c r="E9" s="36" t="n">
         <v>28600</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="35" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B10" s="35" t="inlineStr">
+      <c r="B10" s="36" t="inlineStr">
         <is>
           <t>22K 이하</t>
         </is>
       </c>
-      <c r="C10" s="35" t="n">
+      <c r="C10" s="36" t="n">
         <v>2200</v>
       </c>
-      <c r="D10" s="35" t="n">
+      <c r="D10" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="35" t="n">
+      <c r="E10" s="36" t="n">
         <v>2200</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="35" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B11" s="35" t="inlineStr">
+      <c r="B11" s="36" t="inlineStr">
         <is>
           <t>22K 이상</t>
         </is>
       </c>
-      <c r="C11" s="35" t="n">
+      <c r="C11" s="36" t="n">
         <v>5500</v>
       </c>
-      <c r="D11" s="35" t="n">
+      <c r="D11" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="35" t="n">
+      <c r="E11" s="36" t="n">
         <v>5500</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="35" t="inlineStr">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B12" s="35" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>64.9K 이상</t>
         </is>
       </c>
-      <c r="C12" s="35" t="n">
+      <c r="C12" s="36" t="n">
         <v>5500</v>
       </c>
-      <c r="D12" s="35" t="n">
+      <c r="D12" s="36" t="n">
         <v>5500</v>
       </c>
-      <c r="E12" s="35" t="n">
+      <c r="E12" s="36" t="n">
         <v>11000</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="35" t="inlineStr">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B13" s="35" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>108.9K 이상</t>
         </is>
       </c>
-      <c r="C13" s="35" t="n">
+      <c r="C13" s="36" t="n">
         <v>5500</v>
       </c>
-      <c r="D13" s="35" t="n">
+      <c r="D13" s="36" t="n">
         <v>16610</v>
       </c>
-      <c r="E13" s="35" t="n">
+      <c r="E13" s="36" t="n">
         <v>22110</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="35" t="inlineStr">
+      <c r="A14" s="36" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B14" s="35" t="inlineStr">
+      <c r="B14" s="36" t="inlineStr">
         <is>
           <t>141.9K 이상</t>
         </is>
       </c>
-      <c r="C14" s="35" t="n">
+      <c r="C14" s="36" t="n">
         <v>5500</v>
       </c>
-      <c r="D14" s="35" t="n">
+      <c r="D14" s="36" t="n">
         <v>22110</v>
       </c>
-      <c r="E14" s="35" t="n">
+      <c r="E14" s="36" t="n">
         <v>27610</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="35" t="inlineStr">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B15" s="35" t="inlineStr">
+      <c r="B15" s="36" t="inlineStr">
         <is>
           <t>174.9K 이상</t>
         </is>
       </c>
-      <c r="C15" s="35" t="n">
+      <c r="C15" s="36" t="n">
         <v>5500</v>
       </c>
-      <c r="D15" s="35" t="n">
+      <c r="D15" s="36" t="n">
         <v>27610</v>
       </c>
-      <c r="E15" s="35" t="n">
+      <c r="E15" s="36" t="n">
         <v>33110</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="35" t="inlineStr">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B16" s="35" t="inlineStr">
+      <c r="B16" s="36" t="inlineStr">
         <is>
           <t>22K 이하</t>
         </is>
       </c>
-      <c r="C16" s="35" t="n">
+      <c r="C16" s="36" t="n">
         <v>2200</v>
       </c>
-      <c r="D16" s="35" t="n">
+      <c r="D16" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="35" t="n">
+      <c r="E16" s="36" t="n">
         <v>2200</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="35" t="inlineStr">
+      <c r="A17" s="36" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B17" s="35" t="inlineStr">
+      <c r="B17" s="36" t="inlineStr">
         <is>
           <t>22K 이상</t>
         </is>
       </c>
-      <c r="C17" s="35" t="n">
+      <c r="C17" s="36" t="n">
         <v>5500</v>
       </c>
-      <c r="D17" s="35" t="n">
+      <c r="D17" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="35" t="n">
+      <c r="E17" s="36" t="n">
         <v>5500</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="35" t="inlineStr">
+      <c r="A18" s="36" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B18" s="35" t="inlineStr">
+      <c r="B18" s="36" t="inlineStr">
         <is>
           <t>64.9K 이상</t>
         </is>
       </c>
-      <c r="C18" s="35" t="n">
+      <c r="C18" s="36" t="n">
         <v>5500</v>
       </c>
-      <c r="D18" s="35" t="n">
+      <c r="D18" s="36" t="n">
         <v>5500</v>
       </c>
-      <c r="E18" s="35" t="n">
+      <c r="E18" s="36" t="n">
         <v>11000</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="35" t="inlineStr">
+      <c r="A19" s="36" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B19" s="35" t="inlineStr">
+      <c r="B19" s="36" t="inlineStr">
         <is>
           <t>108.9K 이상</t>
         </is>
       </c>
-      <c r="C19" s="35" t="n">
+      <c r="C19" s="36" t="n">
         <v>5500</v>
       </c>
-      <c r="D19" s="35" t="n">
+      <c r="D19" s="36" t="n">
         <v>16610</v>
       </c>
-      <c r="E19" s="35" t="n">
+      <c r="E19" s="36" t="n">
         <v>22110</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="35" t="inlineStr">
+      <c r="A20" s="36" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B20" s="35" t="inlineStr">
+      <c r="B20" s="36" t="inlineStr">
         <is>
           <t>141.9K 이상</t>
         </is>
       </c>
-      <c r="C20" s="35" t="n">
+      <c r="C20" s="36" t="n">
         <v>5500</v>
       </c>
-      <c r="D20" s="35" t="n">
+      <c r="D20" s="36" t="n">
         <v>22110</v>
       </c>
-      <c r="E20" s="35" t="n">
+      <c r="E20" s="36" t="n">
         <v>27610</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="35" t="inlineStr">
+      <c r="A21" s="36" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B21" s="35" t="inlineStr">
+      <c r="B21" s="36" t="inlineStr">
         <is>
           <t>174.9K 이상</t>
         </is>
       </c>
-      <c r="C21" s="35" t="n">
+      <c r="C21" s="36" t="n">
         <v>5500</v>
       </c>
-      <c r="D21" s="35" t="n">
+      <c r="D21" s="36" t="n">
         <v>27610</v>
       </c>
-      <c r="E21" s="35" t="n">
+      <c r="E21" s="36" t="n">
         <v>33110</v>
       </c>
     </row>
@@ -3056,7 +3059,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="34" t="inlineStr">
+      <c r="A1" s="35" t="inlineStr">
         <is>
           <t>🏷️ KT 정액결합</t>
         </is>
@@ -3085,66 +3088,66 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="35" t="inlineStr">
+      <c r="A4" s="36" t="inlineStr">
         <is>
           <t>37K 이하</t>
         </is>
       </c>
-      <c r="B4" s="35" t="n">
+      <c r="B4" s="36" t="n">
         <v>5500</v>
       </c>
-      <c r="C4" s="35" t="n">
+      <c r="C4" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="35" t="n">
+      <c r="D4" s="36" t="n">
         <v>5500</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="35" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>37K 이상</t>
         </is>
       </c>
-      <c r="B5" s="35" t="n">
+      <c r="B5" s="36" t="n">
         <v>5500</v>
       </c>
-      <c r="C5" s="35" t="n">
+      <c r="C5" s="36" t="n">
         <v>3000</v>
       </c>
-      <c r="D5" s="35" t="n">
+      <c r="D5" s="36" t="n">
         <v>8500</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="35" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>61K 이상</t>
         </is>
       </c>
-      <c r="B6" s="35" t="n">
+      <c r="B6" s="36" t="n">
         <v>5500</v>
       </c>
-      <c r="C6" s="35" t="n">
+      <c r="C6" s="36" t="n">
         <v>5000</v>
       </c>
-      <c r="D6" s="35" t="n">
+      <c r="D6" s="36" t="n">
         <v>10500</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="35" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>77K 이상</t>
         </is>
       </c>
-      <c r="B7" s="35" t="n">
+      <c r="B7" s="36" t="n">
         <v>5500</v>
       </c>
-      <c r="C7" s="35" t="n">
+      <c r="C7" s="36" t="n">
         <v>7000</v>
       </c>
-      <c r="D7" s="35" t="n">
+      <c r="D7" s="36" t="n">
         <v>12500</v>
       </c>
     </row>
@@ -3170,14 +3173,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="36" t="inlineStr">
+      <c r="A1" s="37" t="inlineStr">
         <is>
           <t>💎 KT 프리미엄 가족결합 (원본 planCatalog 14종)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="31" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>자격: 77,000원↑ 요금제 2회선 이상 필수 · 대표자는 총액결합만 · 구성원 77K↑만 프리미엄 선택 가능 · 인터넷 -5,500원 기본</t>
         </is>
@@ -3211,322 +3214,322 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="37" t="n">
+      <c r="A6" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="B6" s="37" t="inlineStr">
+      <c r="B6" s="38" t="inlineStr">
         <is>
           <t>— 회선 없음 —</t>
         </is>
       </c>
-      <c r="C6" s="37" t="inlineStr">
+      <c r="C6" s="38" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D6" s="37" t="n">
+      <c r="D6" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="37" t="inlineStr">
+      <c r="E6" s="38" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="37" t="n">
+      <c r="A7" s="38" t="n">
         <v>32890</v>
       </c>
-      <c r="B7" s="37" t="inlineStr">
+      <c r="B7" s="38" t="inlineStr">
         <is>
           <t>32,890원 (LTE 데이터선택)</t>
         </is>
       </c>
-      <c r="C7" s="37" t="inlineStr">
+      <c r="C7" s="38" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D7" s="37" t="n">
+      <c r="D7" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="37" t="inlineStr">
+      <c r="E7" s="38" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="37" t="n">
+      <c r="A8" s="38" t="n">
         <v>47000</v>
       </c>
-      <c r="B8" s="37" t="inlineStr">
+      <c r="B8" s="38" t="inlineStr">
         <is>
           <t>47,000원</t>
         </is>
       </c>
-      <c r="C8" s="37" t="inlineStr">
+      <c r="C8" s="38" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D8" s="37" t="n">
+      <c r="D8" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="37" t="inlineStr">
+      <c r="E8" s="38" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="37" t="n">
+      <c r="A9" s="38" t="n">
         <v>55000</v>
       </c>
-      <c r="B9" s="37" t="inlineStr">
+      <c r="B9" s="38" t="inlineStr">
         <is>
           <t>55,000원</t>
         </is>
       </c>
-      <c r="C9" s="37" t="inlineStr">
+      <c r="C9" s="38" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D9" s="37" t="n">
+      <c r="D9" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="37" t="inlineStr">
+      <c r="E9" s="38" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="37" t="n">
+      <c r="A10" s="38" t="n">
         <v>65000</v>
       </c>
-      <c r="B10" s="37" t="inlineStr">
+      <c r="B10" s="38" t="inlineStr">
         <is>
           <t>65,000원</t>
         </is>
       </c>
-      <c r="C10" s="37" t="inlineStr">
+      <c r="C10" s="38" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D10" s="37" t="n">
+      <c r="D10" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="37" t="inlineStr">
+      <c r="E10" s="38" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="37" t="n">
+      <c r="A11" s="38" t="n">
         <v>77000</v>
       </c>
-      <c r="B11" s="37" t="inlineStr">
+      <c r="B11" s="38" t="inlineStr">
         <is>
           <t>77,000원 (임계값)</t>
         </is>
       </c>
-      <c r="C11" s="37" t="inlineStr">
+      <c r="C11" s="38" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D11" s="37" t="n">
+      <c r="D11" s="38" t="n">
         <v>19250</v>
       </c>
-      <c r="E11" s="37" t="inlineStr">
+      <c r="E11" s="38" t="inlineStr">
         <is>
           <t>≈25%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="37" t="n">
+      <c r="A12" s="38" t="n">
         <v>80000</v>
       </c>
-      <c r="B12" s="37" t="inlineStr">
+      <c r="B12" s="38" t="inlineStr">
         <is>
           <t>80,000원 (5G 슈퍼플랜 베이직)</t>
         </is>
       </c>
-      <c r="C12" s="37" t="inlineStr">
+      <c r="C12" s="38" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D12" s="37" t="n">
+      <c r="D12" s="38" t="n">
         <v>20000</v>
       </c>
-      <c r="E12" s="37" t="inlineStr">
+      <c r="E12" s="38" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="37" t="n">
+      <c r="A13" s="38" t="n">
         <v>87890</v>
       </c>
-      <c r="B13" s="37" t="inlineStr">
+      <c r="B13" s="38" t="inlineStr">
         <is>
           <t>87,890원 (데이터선택 87.8)</t>
         </is>
       </c>
-      <c r="C13" s="37" t="inlineStr">
+      <c r="C13" s="38" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D13" s="37" t="n">
+      <c r="D13" s="38" t="n">
         <v>22000</v>
       </c>
-      <c r="E13" s="37" t="inlineStr">
+      <c r="E13" s="38" t="inlineStr">
         <is>
           <t>≈25%</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="37" t="n">
+      <c r="A14" s="38" t="n">
         <v>89000</v>
       </c>
-      <c r="B14" s="37" t="inlineStr">
+      <c r="B14" s="38" t="inlineStr">
         <is>
           <t>89,000원 (데이터ON 프리미엄)</t>
         </is>
       </c>
-      <c r="C14" s="37" t="inlineStr">
+      <c r="C14" s="38" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D14" s="37" t="n">
+      <c r="D14" s="38" t="n">
         <v>22250</v>
       </c>
-      <c r="E14" s="37" t="inlineStr">
+      <c r="E14" s="38" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="37" t="n">
+      <c r="A15" s="38" t="n">
         <v>90000</v>
       </c>
-      <c r="B15" s="37" t="inlineStr">
+      <c r="B15" s="38" t="inlineStr">
         <is>
           <t>90,000원 (슈퍼플랜 베이직 Plus/초이스)</t>
         </is>
       </c>
-      <c r="C15" s="37" t="inlineStr">
+      <c r="C15" s="38" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D15" s="37" t="n">
+      <c r="D15" s="38" t="n">
         <v>22500</v>
       </c>
-      <c r="E15" s="37" t="inlineStr">
+      <c r="E15" s="38" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="37" t="n">
+      <c r="A16" s="38" t="n">
         <v>100000</v>
       </c>
-      <c r="B16" s="37" t="inlineStr">
+      <c r="B16" s="38" t="inlineStr">
         <is>
           <t>100,000원 (슈퍼플랜 스페셜)</t>
         </is>
       </c>
-      <c r="C16" s="37" t="inlineStr">
+      <c r="C16" s="38" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D16" s="37" t="n">
+      <c r="D16" s="38" t="n">
         <v>25000</v>
       </c>
-      <c r="E16" s="37" t="inlineStr">
+      <c r="E16" s="38" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="37" t="n">
+      <c r="A17" s="38" t="n">
         <v>109000</v>
       </c>
-      <c r="B17" s="37" t="inlineStr">
+      <c r="B17" s="38" t="inlineStr">
         <is>
           <t>109,000원 (데이터선택 109)</t>
         </is>
       </c>
-      <c r="C17" s="37" t="inlineStr">
+      <c r="C17" s="38" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D17" s="37" t="n">
+      <c r="D17" s="38" t="n">
         <v>27500</v>
       </c>
-      <c r="E17" s="37" t="inlineStr">
+      <c r="E17" s="38" t="inlineStr">
         <is>
           <t>≈25%</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="37" t="n">
+      <c r="A18" s="38" t="n">
         <v>110000</v>
       </c>
-      <c r="B18" s="37" t="inlineStr">
+      <c r="B18" s="38" t="inlineStr">
         <is>
           <t>110,000원 (슈퍼플랜 스페셜 Plus/초이스)</t>
         </is>
       </c>
-      <c r="C18" s="37" t="inlineStr">
+      <c r="C18" s="38" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D18" s="37" t="n">
+      <c r="D18" s="38" t="n">
         <v>27500</v>
       </c>
-      <c r="E18" s="37" t="inlineStr">
+      <c r="E18" s="38" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="37" t="n">
+      <c r="A19" s="38" t="n">
         <v>130000</v>
       </c>
-      <c r="B19" s="37" t="inlineStr">
+      <c r="B19" s="38" t="inlineStr">
         <is>
           <t>130,000원 (슈퍼플랜 프리미엄/초이스)</t>
         </is>
       </c>
-      <c r="C19" s="37" t="inlineStr">
+      <c r="C19" s="38" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D19" s="37" t="n">
+      <c r="D19" s="38" t="n">
         <v>32500</v>
       </c>
-      <c r="E19" s="37" t="inlineStr">
+      <c r="E19" s="38" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -3557,7 +3560,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="38" t="inlineStr">
+      <c r="A1" s="39" t="inlineStr">
         <is>
           <t>🏷️ LG U+ 참쉬운가족결합</t>
         </is>
@@ -3586,18 +3589,18 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="39" t="inlineStr">
+      <c r="A4" s="40" t="inlineStr">
         <is>
           <t>인터넷 할인</t>
         </is>
       </c>
-      <c r="B4" s="39" t="n">
+      <c r="B4" s="40" t="n">
         <v>5500</v>
       </c>
-      <c r="C4" s="39" t="n">
+      <c r="C4" s="40" t="n">
         <v>9900</v>
       </c>
-      <c r="D4" s="39" t="n">
+      <c r="D4" s="40" t="n">
         <v>13200</v>
       </c>
     </row>
@@ -3624,50 +3627,50 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="39" t="inlineStr">
+      <c r="A7" s="40" t="inlineStr">
         <is>
           <t>69K 미만</t>
         </is>
       </c>
-      <c r="B7" s="39" t="n">
+      <c r="B7" s="40" t="n">
         <v>2200</v>
       </c>
-      <c r="C7" s="39" t="n">
+      <c r="C7" s="40" t="n">
         <v>3300</v>
       </c>
-      <c r="D7" s="39" t="n">
+      <c r="D7" s="40" t="n">
         <v>4400</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="39" t="inlineStr">
+      <c r="A8" s="40" t="inlineStr">
         <is>
           <t>69K 이상</t>
         </is>
       </c>
-      <c r="B8" s="39" t="n">
+      <c r="B8" s="40" t="n">
         <v>3300</v>
       </c>
-      <c r="C8" s="39" t="n">
+      <c r="C8" s="40" t="n">
         <v>5500</v>
       </c>
-      <c r="D8" s="39" t="n">
+      <c r="D8" s="40" t="n">
         <v>6600</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="39" t="inlineStr">
+      <c r="A9" s="40" t="inlineStr">
         <is>
           <t>88K 이상</t>
         </is>
       </c>
-      <c r="B9" s="39" t="n">
+      <c r="B9" s="40" t="n">
         <v>4400</v>
       </c>
-      <c r="C9" s="39" t="n">
+      <c r="C9" s="40" t="n">
         <v>6600</v>
       </c>
-      <c r="D9" s="39" t="n">
+      <c r="D9" s="40" t="n">
         <v>8800</v>
       </c>
     </row>
@@ -3692,7 +3695,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="38" t="inlineStr">
+      <c r="A1" s="39" t="inlineStr">
         <is>
           <t>🏷️ LG U+ 투게더 (85K↑)</t>
         </is>
@@ -3721,20 +3724,20 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="39" t="inlineStr">
+      <c r="A4" s="40" t="inlineStr">
         <is>
           <t>인터넷</t>
         </is>
       </c>
-      <c r="B4" s="39" t="inlineStr">
+      <c r="B4" s="40" t="inlineStr">
         <is>
           <t>불가</t>
         </is>
       </c>
-      <c r="C4" s="39" t="n">
+      <c r="C4" s="40" t="n">
         <v>11000</v>
       </c>
-      <c r="D4" s="39" t="n">
+      <c r="D4" s="40" t="n">
         <v>11000</v>
       </c>
     </row>
@@ -3751,32 +3754,32 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="39" t="inlineStr">
+      <c r="A7" s="40" t="inlineStr">
         <is>
           <t>2회선</t>
         </is>
       </c>
-      <c r="B7" s="39" t="n">
+      <c r="B7" s="40" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="39" t="inlineStr">
+      <c r="A8" s="40" t="inlineStr">
         <is>
           <t>3회선</t>
         </is>
       </c>
-      <c r="B8" s="39" t="n">
+      <c r="B8" s="40" t="n">
         <v>14000</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="39" t="inlineStr">
+      <c r="A9" s="40" t="inlineStr">
         <is>
           <t>4~5회선</t>
         </is>
       </c>
-      <c r="B9" s="39" t="n">
+      <c r="B9" s="40" t="n">
         <v>20000</v>
       </c>
     </row>
@@ -3805,101 +3808,101 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="40" t="inlineStr">
+      <c r="A3" s="41" t="inlineStr">
         <is>
           <t>interface CarrierData {</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="40" t="inlineStr">
+      <c r="A4" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">  name, prefix;</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="40" t="inlineStr">
+      <c r="A5" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">  internet: Record&lt;"100M"|"500M"|"1G", number&gt;;</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="40" t="inlineStr">
+      <c r="A6" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">  wifiCost? | wifiPrice?: Record&lt;Speed, number&gt;;</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="40" t="inlineStr">
+      <c r="A7" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">  setTopOptions: SetTop[]; wifiOptions: WiFi[];</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="40" t="inlineStr">
+      <c r="A8" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">  tvInternetNoWifi, tvInternetWithWifi: Record&lt;Speed, number&gt;;</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="40" t="inlineStr">
+      <c r="A9" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">  tv: TVProduct[];</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="40" t="inlineStr">
+      <c r="A10" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">  install: { solo, combo };</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="40" t="inlineStr">
+      <c r="A11" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">  gift: { solo: SpeedMap, combo: SpeedMap };</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="40" t="inlineStr">
+      <c r="A12" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">  bundle: BundleConfig;  // 3사별 상이</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="40" t="inlineStr">
+      <c r="A13" s="41" t="inlineStr">
         <is>
           <t>}</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="40" t="inlineStr"/>
+      <c r="A14" s="41" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="40" t="inlineStr">
+      <c r="A15" s="41" t="inlineStr">
         <is>
           <t>// SKT: bundle.family { internet, iptv, mobilePerBySpeed }</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="40" t="inlineStr">
+      <c r="A16" s="41" t="inlineStr">
         <is>
           <t>// KT:  bundle.{ranges_total, total, ranges_fixed, fixed, premium}</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="40" t="inlineStr">
+      <c r="A17" s="41" t="inlineStr">
         <is>
           <t>// LGU: bundle.{chweyswun, together}</t>
         </is>
@@ -4016,7 +4019,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>TV 인덱스</t>
+          <t>TV 인덱스 (내부 변환)</t>
         </is>
       </c>
       <c r="B10" s="13">
@@ -4025,14 +4028,14 @@
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>드롭다운 이름 → 숫자 인덱스</t>
+          <t>드롭다운 이름 → 배열 번호 (1=TV 없음, 2~10=상품) · 수식 조회용</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>TV 선택 여부</t>
+          <t>TV 선택 여부 (내부 변환)</t>
         </is>
       </c>
       <c r="B11" s="13">
@@ -4041,7 +4044,7 @@
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>1=TV 결합 / 0=인터넷 단독</t>
+          <t>0=TV 없음 (인터넷 단독) / 1=TV 결합 · 수식 분기용</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4061,7 @@
           <t>인터넷 단독가</t>
         </is>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="16">
         <f>IF(B4="100M",22000,IF(B4="500M",33000,38500))</f>
         <v/>
       </c>
@@ -4074,7 +4077,7 @@
           <t>TV 상품 가격 (p)</t>
         </is>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="16">
         <f>IF(B11=0,0,CHOOSE(B10-1,12100,15400,18700,23100,24200,27700,30200,30700,33200))</f>
         <v/>
       </c>
@@ -4090,7 +4093,7 @@
           <t>TV 결합할인 (dc)</t>
         </is>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="16">
         <f>IF(B11=0,0,2200)</f>
         <v/>
       </c>
@@ -4106,7 +4109,7 @@
           <t>WiFi 추가금</t>
         </is>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="16">
         <f>IF(B6="Y",1100,0)</f>
         <v/>
       </c>
@@ -4122,7 +4125,7 @@
           <t>tvInternetNoWifi</t>
         </is>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="16">
         <f>IF(B4="100M",19800,IF(B4="500M",27500,33000))</f>
         <v/>
       </c>
@@ -4138,7 +4141,7 @@
           <t>tvInternetWithWifi</t>
         </is>
       </c>
-      <c r="B19" s="13">
+      <c r="B19" s="16">
         <f>IF(B4="100M",22000,IF(B4="500M",28600,34100))</f>
         <v/>
       </c>
@@ -4154,7 +4157,7 @@
           <t>셋톱박스 (스마트3)</t>
         </is>
       </c>
-      <c r="B20" s="13">
+      <c r="B20" s="16">
         <f>4400</f>
         <v/>
       </c>
@@ -4172,23 +4175,23 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  월 기본요금 (요즘우리집)</t>
-        </is>
-      </c>
-      <c r="B23" s="17">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  월 기본요금 (요즘우리집 · 휴대폰결합 없을 때)</t>
+        </is>
+      </c>
+      <c r="B23" s="18">
         <f>IF(B11=0,B14+B17,IF(B6="Y",B19,B18)+B15-B16+B20)</f>
         <v/>
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>TV 있으면: tvInternet + (p-dc) + 셋톱 / 없으면: 단독+WiFi</t>
+          <t>TV 결합: tvInternet(WiFi반영) + (p-dc) + 셋톱 / TV 없음: 단독+WiFi</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>【경로 B】 요즘가족결합 (휴대폰 결합 · 단독가 REPLACE)</t>
         </is>
@@ -4200,7 +4203,7 @@
           <t xml:space="preserve">  요즘가족 인터넷 할인</t>
         </is>
       </c>
-      <c r="B26" s="13">
+      <c r="B26" s="16">
         <f>IF(B7=0,0,IF(B4="100M",4400,IF(B4="500M",11000,13200)))</f>
         <v/>
       </c>
@@ -4216,7 +4219,7 @@
           <t xml:space="preserve">  IPTV 추가 (TV+결합 시)</t>
         </is>
       </c>
-      <c r="B27" s="13">
+      <c r="B27" s="16">
         <f>IF(AND(B7&gt;0,B11=1),1100,0)</f>
         <v/>
       </c>
@@ -4232,7 +4235,7 @@
           <t xml:space="preserve">  휴대폰 인당 할인</t>
         </is>
       </c>
-      <c r="B28" s="13">
+      <c r="B28" s="16">
         <f>IF(B7=0,0,IF(B4="100M",CHOOSE(B7,3500,3500,6000,4500,3600),CHOOSE(B7,3500,3500,6000,6000,4800)))</f>
         <v/>
       </c>
@@ -4248,7 +4251,7 @@
           <t xml:space="preserve">  휴대폰 총 할인</t>
         </is>
       </c>
-      <c r="B29" s="13">
+      <c r="B29" s="16">
         <f>B28*B7</f>
         <v/>
       </c>
@@ -4264,7 +4267,7 @@
           <t xml:space="preserve">  → 인터넷 (단독 - 요즘가족할인)</t>
         </is>
       </c>
-      <c r="B31" s="19">
+      <c r="B31" s="20">
         <f>IF(B7=0,"-",B14+B17-B26)</f>
         <v/>
       </c>
@@ -4275,7 +4278,7 @@
           <t xml:space="preserve">  → TV (p - dc - iptv)</t>
         </is>
       </c>
-      <c r="B32" s="19">
+      <c r="B32" s="20">
         <f>IF(B7=0,"-",IF(B11=0,0,B15-B16-B27))</f>
         <v/>
       </c>
@@ -4286,18 +4289,18 @@
           <t xml:space="preserve">  → 셋톱 (TV 있을 때만)</t>
         </is>
       </c>
-      <c r="B33" s="19">
+      <c r="B33" s="20">
         <f>IF(B7=0,"-",IF(B11=0,0,B20))</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="inlineStr">
+      <c r="A34" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">  = 인터넷+TV 월 실납부 (결합 적용)</t>
         </is>
       </c>
-      <c r="B34" s="17">
+      <c r="B34" s="18">
         <f>IF(B7=0,"-",(B14+B17-B26)+IF(B11=0,0,B15-B16-B27+B20))</f>
         <v/>
       </c>
@@ -4308,18 +4311,18 @@
           <t xml:space="preserve">  - 휴대폰 고지서 별도 차감</t>
         </is>
       </c>
-      <c r="B35" s="19">
+      <c r="B35" s="20">
         <f>IF(B7=0,"-",-B29)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="16" t="inlineStr">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>🎉 혜택가 (최종 월요금)</t>
         </is>
       </c>
-      <c r="B36" s="20">
+      <c r="B36" s="21">
         <f>IF(B7=0,B23,B34-B29)</f>
         <v/>
       </c>
@@ -4342,7 +4345,7 @@
           <t xml:space="preserve">  설치비 (1회성)</t>
         </is>
       </c>
-      <c r="B39" s="13">
+      <c r="B39" s="16">
         <f>IF(B11=0,36300,56100)</f>
         <v/>
       </c>
@@ -4358,7 +4361,7 @@
           <t xml:space="preserve">  사은품 (속도×TV결합)</t>
         </is>
       </c>
-      <c r="B40" s="13">
+      <c r="B40" s="16">
         <f>IF(B11=0,IF(B4="100M",110000,170000),CHOOSE(MATCH(B4,{"100M","500M","1G"},0),400000,430000,490000))</f>
         <v/>
       </c>
@@ -4436,42 +4439,42 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="41" t="inlineStr">
+      <c r="A3" s="42" t="inlineStr">
         <is>
           <t>⚠️ 3사 결합할인 적용 방식 차이</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="42" t="inlineStr">
+      <c r="A4" s="43" t="inlineStr">
         <is>
           <t>• SKT 요즘가족결합: 단독가 REPLACE (요즘우리집 대체) → tvInternet 사용 X</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="42" t="inlineStr">
+      <c r="A5" s="43" t="inlineStr">
         <is>
           <t>• KT 총액/정액: 기본 TV결합 + 추가할인 STACK (중복)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="42" t="inlineStr">
+      <c r="A6" s="43" t="inlineStr">
         <is>
           <t>• KT 프리미엄: 대표자+77K미만은 총액결합 / 77K↑ 구성원은 프리미엄 (독립)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="42" t="inlineStr">
+      <c r="A7" s="43" t="inlineStr">
         <is>
           <t>• LG U+ 참쉬운: 단독가 REPLACE</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="42" t="inlineStr">
+      <c r="A8" s="43" t="inlineStr">
         <is>
           <t>• LG U+ 투게더: 단독가 REPLACE + 100M 결합 불가</t>
         </is>
@@ -4507,7 +4510,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>🧮 KT 총액/정액 결합 계산기</t>
         </is>
@@ -4660,24 +4663,34 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>TV 인덱스</t>
+          <t>TV 인덱스 (내부 변환)</t>
         </is>
       </c>
       <c r="B14" s="13">
         <f>MATCH(B5,{"TV 없음","지니TV 베이직","지니TV 라이트","지니TV 에센스","지니TV 모든G","지니TV 디즈니+모든G"},0)</f>
         <v/>
       </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>드롭다운 이름 → 배열 번호 (1=없음, 2~6=상품) · 수식 조회용</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>TV 선택 여부</t>
+          <t>TV 선택 여부 (내부 변환)</t>
         </is>
       </c>
       <c r="B15" s="13">
         <f>IF(B5="TV 없음",0,1)</f>
         <v/>
       </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>0=TV 없음 / 1=TV 결합 · 수식 분기용</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
@@ -4692,7 +4705,7 @@
           <t>인터넷 단독가</t>
         </is>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="16">
         <f>IF(B4="100M",22000,IF(B4="500M",33000,38500))</f>
         <v/>
       </c>
@@ -4708,7 +4721,7 @@
           <t>TV 가격 (p)</t>
         </is>
       </c>
-      <c r="B19" s="13">
+      <c r="B19" s="16">
         <f>IF(B15=0,0,CHOOSE(B14-1,14740,15840,20240,21340,28100))</f>
         <v/>
       </c>
@@ -4724,7 +4737,7 @@
           <t>TV 결합할인 (dc)</t>
         </is>
       </c>
-      <c r="B20" s="13">
+      <c r="B20" s="16">
         <f>IF(B15=0,0,CHOOSE(B14-1,2640,2640,3740,4400,6600))</f>
         <v/>
       </c>
@@ -4740,7 +4753,7 @@
           <t>WiFi 추가금 (속도별)</t>
         </is>
       </c>
-      <c r="B21" s="13">
+      <c r="B21" s="16">
         <f>IF(B6="Y",IF(B4="1G",0,1100),0)</f>
         <v/>
       </c>
@@ -4756,7 +4769,7 @@
           <t>tvInternetNoWifi</t>
         </is>
       </c>
-      <c r="B22" s="13">
+      <c r="B22" s="16">
         <f>IF(B4="100M",22000,IF(B4="500M",27500,33000))</f>
         <v/>
       </c>
@@ -4772,7 +4785,7 @@
           <t>tvInternetWithWifi</t>
         </is>
       </c>
-      <c r="B23" s="13">
+      <c r="B23" s="16">
         <f>IF(B4="100M",23100,IF(B4="500M",28600,33000))</f>
         <v/>
       </c>
@@ -4788,7 +4801,7 @@
           <t>셋톱박스 (기가지니3)</t>
         </is>
       </c>
-      <c r="B24" s="13">
+      <c r="B24" s="16">
         <f>4400</f>
         <v/>
       </c>
@@ -4806,18 +4819,23 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  월 기본요금</t>
-        </is>
-      </c>
-      <c r="B27" s="22">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  월 기본요금 (기본 TV결합 · 휴대폰결합 없을 때)</t>
+        </is>
+      </c>
+      <c r="B27" s="23">
         <f>IF(B15=0,B18+B21,IF(B6="Y",B23,B22)+B19-B20+B24)</f>
         <v/>
       </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>KT 기본 TV결합 할인 자동 적용 (tvInternetNoWifi/WithWifi)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="23" t="inlineStr">
+      <c r="A29" s="24" t="inlineStr">
         <is>
           <t>【경로 B】 결합 적용 (STACK — 기본 TV결합 + 추가할인)</t>
         </is>
@@ -4829,7 +4847,7 @@
           <t xml:space="preserve">  [총액] 인터넷 추가 할인</t>
         </is>
       </c>
-      <c r="B30" s="13">
+      <c r="B30" s="16">
         <f>IF(B7="총액결합",IF(B4="100M",CHOOSE(B8,1650,3300,5500,5500,5500,5500),CHOOSE(B8,2200,5500,5500,5500,5500,5500)),0)</f>
         <v/>
       </c>
@@ -4845,7 +4863,7 @@
           <t xml:space="preserve">  [총액] 휴대폰 할인</t>
         </is>
       </c>
-      <c r="B31" s="13">
+      <c r="B31" s="16">
         <f>IF(B7="총액결합",IF(B4="100M",CHOOSE(B8,0,0,3300,14300,18700,23100),CHOOSE(B8,0,0,5500,16610,22110,27610)),0)</f>
         <v/>
       </c>
@@ -4861,7 +4879,7 @@
           <t xml:space="preserve">  [정액] 인터넷 할인</t>
         </is>
       </c>
-      <c r="B32" s="13">
+      <c r="B32" s="16">
         <f>IF(B7="정액결합",5500,0)</f>
         <v/>
       </c>
@@ -4877,7 +4895,7 @@
           <t xml:space="preserve">  [정액] 휴대폰 할인</t>
         </is>
       </c>
-      <c r="B33" s="13">
+      <c r="B33" s="16">
         <f>IF(B7="정액결합",CHOOSE(B9,0,3000,5000,7000),0)</f>
         <v/>
       </c>
@@ -4893,7 +4911,7 @@
           <t xml:space="preserve">  [💎프리미엄] 인터넷 할인 (고정)</t>
         </is>
       </c>
-      <c r="B34" s="13">
+      <c r="B34" s="16">
         <f>IF(B7="💎 프리미엄 가족결합",5500,0)</f>
         <v/>
       </c>
@@ -4909,7 +4927,7 @@
           <t xml:space="preserve">  [💎프리미엄] 대표자 총액결합 (합산=요금제1명)</t>
         </is>
       </c>
-      <c r="B35" s="13">
+      <c r="B35" s="16">
         <f>IF(B7="💎 프리미엄 가족결합",IF(B4="100M",CHOOSE(B8,0,0,3300,14300,18700,23100),CHOOSE(B8,0,0,5500,16610,22110,27610)),0)</f>
         <v/>
       </c>
@@ -4925,7 +4943,7 @@
           <t xml:space="preserve">  [💎프리미엄] 요금제별 할인액</t>
         </is>
       </c>
-      <c r="B36" s="13">
+      <c r="B36" s="16">
         <f>IF(B7="💎 프리미엄 가족결합",CHOOSE(MATCH(B10,{"77,000원","80,000원","87,890원","89,000원","90,000원","100,000원","109,000원","110,000원","130,000원"},0),19250,20000,22000,22250,22500,25000,27500,27500,32500),0)</f>
         <v/>
       </c>
@@ -4941,7 +4959,7 @@
           <t xml:space="preserve">  [💎프리미엄] 구성원 총 할인 (dc × 회선수)</t>
         </is>
       </c>
-      <c r="B37" s="13">
+      <c r="B37" s="16">
         <f>B36*IF(B7="💎 프리미엄 가족결합",B11,0)</f>
         <v/>
       </c>
@@ -4952,12 +4970,12 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="16" t="inlineStr">
+      <c r="A39" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">  = 인터넷+TV 월 실납부</t>
         </is>
       </c>
-      <c r="B39" s="22">
+      <c r="B39" s="23">
         <f>IF(B7="💎 프리미엄 가족결합",B27-B34,B27-B30-B32)</f>
         <v/>
       </c>
@@ -4973,7 +4991,7 @@
           <t xml:space="preserve">  - 휴대폰 고지서 별도 차감</t>
         </is>
       </c>
-      <c r="B40" s="24">
+      <c r="B40" s="25">
         <f>-(B31+B33+B35+B37)</f>
         <v/>
       </c>
@@ -4984,12 +5002,12 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="16" t="inlineStr">
+      <c r="A41" s="17" t="inlineStr">
         <is>
           <t>🎉 혜택가 (최종 월요금)</t>
         </is>
       </c>
-      <c r="B41" s="25">
+      <c r="B41" s="26">
         <f>IF(B7="결합없음",B27,B39-(B31+B33+B35+B37))</f>
         <v/>
       </c>
@@ -5007,7 +5025,7 @@
           <t xml:space="preserve">  설치비</t>
         </is>
       </c>
-      <c r="B44" s="13">
+      <c r="B44" s="16">
         <f>IF(B15=0,36000,56200)</f>
         <v/>
       </c>
@@ -5023,7 +5041,7 @@
           <t xml:space="preserve">  사은품</t>
         </is>
       </c>
-      <c r="B45" s="13">
+      <c r="B45" s="16">
         <f>IF(B15=0,IF(B4="100M",90000,140000),CHOOSE(MATCH(B4,{"100M","500M","1G"},0),370000,450000,450000))</f>
         <v/>
       </c>
@@ -5034,7 +5052,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="32">
+  <mergeCells count="35">
     <mergeCell ref="C44:E44"/>
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="C22:E22"/>
@@ -5044,6 +5062,7 @@
     <mergeCell ref="C21:E21"/>
     <mergeCell ref="C36:E36"/>
     <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C27:E27"/>
     <mergeCell ref="C23:E23"/>
     <mergeCell ref="C39:E39"/>
     <mergeCell ref="C8:E8"/>
@@ -5056,9 +5075,11 @@
     <mergeCell ref="C18:E18"/>
     <mergeCell ref="C30:E30"/>
     <mergeCell ref="C34:E34"/>
+    <mergeCell ref="C15:E15"/>
     <mergeCell ref="C6:E6"/>
     <mergeCell ref="C24:E24"/>
     <mergeCell ref="A29:E29"/>
+    <mergeCell ref="C14:E14"/>
     <mergeCell ref="C33:E33"/>
     <mergeCell ref="C5:E5"/>
     <mergeCell ref="C45:E45"/>
@@ -5115,7 +5136,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="26" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>🧮 LG U+ 참쉬운/투게더 결합 계산기</t>
         </is>
@@ -5219,24 +5240,34 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>TV 인덱스</t>
+          <t>TV 인덱스 (내부 변환)</t>
         </is>
       </c>
       <c r="B11" s="13">
         <f>MATCH(B5,{"TV 없음","U+tv 실속형","U+tv 기본형","U+tv 프리미엄","U+tv 프리미엄 VOD"},0)</f>
         <v/>
       </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>드롭다운 이름 → 배열 번호 (1=없음, 2~5=상품) · 수식 조회용</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>TV 선택 여부</t>
+          <t>TV 선택 여부 (내부 변환)</t>
         </is>
       </c>
       <c r="B12" s="13">
         <f>IF(B5="TV 없음",0,1)</f>
         <v/>
       </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>0=TV 없음 / 1=TV 결합 · 수식 분기용</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
@@ -5251,7 +5282,7 @@
           <t>인터넷 단독가</t>
         </is>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="16">
         <f>IF(B4="100M",22000,IF(B4="500M",33000,38500))</f>
         <v/>
       </c>
@@ -5267,7 +5298,7 @@
           <t>TV 가격 (p)</t>
         </is>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="16">
         <f>IF(B12=0,0,CHOOSE(B11-1,15400,16500,18700,24200))</f>
         <v/>
       </c>
@@ -5283,7 +5314,7 @@
           <t>TV 결합할인 (dc)</t>
         </is>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="16">
         <f>IF(B12=0,0,CHOOSE(B11-1,2200,2200,2200,5500))</f>
         <v/>
       </c>
@@ -5299,7 +5330,7 @@
           <t>WiFi 추가금</t>
         </is>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="16">
         <f>0</f>
         <v/>
       </c>
@@ -5315,7 +5346,7 @@
           <t>셋톱박스 (U+tv UHD4)</t>
         </is>
       </c>
-      <c r="B19" s="13">
+      <c r="B19" s="16">
         <f>4400</f>
         <v/>
       </c>
@@ -5333,23 +5364,23 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">  월 기본요금</t>
         </is>
       </c>
-      <c r="B22" s="27">
+      <c r="B22" s="28">
         <f>IF(B12=0,B15,IF(B4="100M",22000,IF(B4="500M",27500,33000))+B16-B17+B19)</f>
         <v/>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>TV 없으면 단독가 / TV 있으면 tvInternet(LGU+ WiFi 유무 동일) + TV + 셋톱</t>
+          <t>TV 없으면 단독가 (WiFi 무료) / TV 있으면 tvInternet + (p-dc) + 셋톱</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="28" t="inlineStr">
+      <c r="A24" s="29" t="inlineStr">
         <is>
           <t>【경로 B】 결합 적용 (REPLACE — 단독가 기준)</t>
         </is>
@@ -5361,7 +5392,7 @@
           <t xml:space="preserve">  [참쉬운] 인터넷 할인</t>
         </is>
       </c>
-      <c r="B25" s="13">
+      <c r="B25" s="16">
         <f>IF(B6="참쉬운 가족결합",IF(B4="100M",5500,IF(B4="500M",9900,13200)),0)</f>
         <v/>
       </c>
@@ -5377,7 +5408,7 @@
           <t xml:space="preserve">  [참쉬운] 휴대폰 인당 할인</t>
         </is>
       </c>
-      <c r="B26" s="13">
+      <c r="B26" s="16">
         <f>IF(B6="참쉬운 가족결합",CHOOSE(B7,CHOOSE(MIN(B8,4)-1,2200,3300,4400),CHOOSE(MIN(B8,4)-1,3300,5500,6600),CHOOSE(MIN(B8,4)-1,4400,6600,8800)),0)</f>
         <v/>
       </c>
@@ -5393,7 +5424,7 @@
           <t xml:space="preserve">  [참쉬운] 휴대폰 총 할인</t>
         </is>
       </c>
-      <c r="B27" s="13">
+      <c r="B27" s="16">
         <f>B26*IF(B6="참쉬운 가족결합",MIN(B8,4),0)</f>
         <v/>
       </c>
@@ -5409,7 +5440,7 @@
           <t xml:space="preserve">  [투게더] 인터넷 할인</t>
         </is>
       </c>
-      <c r="B28" s="13">
+      <c r="B28" s="16">
         <f>IF(B6="투게더 결합",IF(B4="100M",0,11000),0)</f>
         <v/>
       </c>
@@ -5425,7 +5456,7 @@
           <t xml:space="preserve">  [투게더] 휴대폰 인당 할인</t>
         </is>
       </c>
-      <c r="B29" s="13">
+      <c r="B29" s="16">
         <f>IF(B6="투게더 결합",CHOOSE(MIN(B8,4)-1,10000,14000,20000),0)</f>
         <v/>
       </c>
@@ -5441,7 +5472,7 @@
           <t xml:space="preserve">  [투게더] 휴대폰 총 할인</t>
         </is>
       </c>
-      <c r="B30" s="13">
+      <c r="B30" s="16">
         <f>B29*IF(B6="투게더 결합",MIN(B8,5),0)</f>
         <v/>
       </c>
@@ -5452,12 +5483,12 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="inlineStr">
+      <c r="A32" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">  = 인터넷+TV 월 실납부 (결합 적용)</t>
         </is>
       </c>
-      <c r="B32" s="27">
+      <c r="B32" s="28">
         <f>(B15-B25-B28)+IF(B12=0,0,B16-B17+B19)</f>
         <v/>
       </c>
@@ -5468,18 +5499,18 @@
           <t xml:space="preserve">  - 휴대폰 고지서 별도 차감</t>
         </is>
       </c>
-      <c r="B33" s="29">
+      <c r="B33" s="30">
         <f>-(B27+B30)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="inlineStr">
+      <c r="A34" s="17" t="inlineStr">
         <is>
           <t>🎉 혜택가 (최종 월요금)</t>
         </is>
       </c>
-      <c r="B34" s="30">
+      <c r="B34" s="31">
         <f>IF(B6="결합없음",B22,B32-(B27+B30))</f>
         <v/>
       </c>
@@ -5497,7 +5528,7 @@
           <t xml:space="preserve">  설치비</t>
         </is>
       </c>
-      <c r="B37" s="13">
+      <c r="B37" s="16">
         <f>IF(B12=0,36300,56100)</f>
         <v/>
       </c>
@@ -5513,7 +5544,7 @@
           <t xml:space="preserve">  사은품</t>
         </is>
       </c>
-      <c r="B38" s="13">
+      <c r="B38" s="16">
         <f>IF(B12=0,IF(B4="100M",200000,230000),CHOOSE(MATCH(B4,{"100M","500M","1G"},0),400000,470000,470000))</f>
         <v/>
       </c>
@@ -5524,11 +5555,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="26">
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="C22:E22"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C11:E11"/>
     <mergeCell ref="C27:E27"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="C17:E17"/>
@@ -6369,7 +6402,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="31" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>💬 기본값(isDefault): 매장 판매 1위 + 가격/기능 균형 · 가입 시 자동 설정 · 요금 계산 기본</t>
         </is>
@@ -6798,7 +6831,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="31" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>💬 기본값: 속도별 단가가 낮은 표준 모델 · 가입 시 자동 지급 · 요금 계산 대상</t>
         </is>

--- a/docs/bongi-calculator-data.xlsx
+++ b/docs/bongi-calculator-data.xlsx
@@ -38,7 +38,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0&quot;원&quot;"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="39">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -79,6 +79,23 @@
       <b val="1"/>
       <color rgb="00ef4444"/>
       <sz val="13"/>
+    </font>
+    <font>
+      <name val="Noto Sans KR"/>
+      <b val="1"/>
+      <color rgb="002563eb"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Noto Sans KR"/>
+      <color rgb="002563eb"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="SF Mono"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Noto Sans KR"/>
@@ -198,6 +215,18 @@
       <sz val="14"/>
     </font>
     <font>
+      <name val="SF Mono"/>
+      <color rgb="001a2744"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Noto Sans KR"/>
+      <b val="1"/>
+      <color rgb="002563eb"/>
+      <sz val="11"/>
+      <u val="single"/>
+    </font>
+    <font>
       <name val="Noto Sans KR"/>
       <b val="1"/>
       <color rgb="002563eb"/>
@@ -212,13 +241,26 @@
     <font>
       <name val="Noto Sans KR"/>
       <b val="1"/>
+      <color rgb="00d97706"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Noto Sans KR"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Noto Sans KR"/>
+      <b val="1"/>
       <color rgb="00e40981"/>
       <sz val="14"/>
     </font>
     <font>
-      <name val="SF Mono"/>
-      <color rgb="001a2744"/>
-      <sz val="10"/>
+      <name val="Noto Sans KR"/>
+      <b val="1"/>
+      <color rgb="00e40981"/>
+      <sz val="13"/>
     </font>
     <font>
       <name val="Noto Sans KR"/>
@@ -227,7 +269,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -279,6 +321,11 @@
         <fgColor rgb="00fdf2f8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00f5f5f7"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -306,7 +353,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -319,82 +366,90 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="21" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="18" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="12" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="24" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -760,7 +815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1164,16 +1219,96 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>🔗 참고자료 (원본 출처)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>🔗 SK 상품 전체 안내 (요즘가족결합)</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>https://www.100mb.kr/01_product/sk.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>🔗 KT 프리미엄 가족결합 상세 해설</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>https://www.100mb.kr/bbs/board.php?bo_table=information&amp;wr_id=11986</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>🔗 LG U+ 상품 전체 안내 (참쉬운/투게더)</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>https://www.100mb.kr/01_product/lg.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>🔗 봉이모바일 통합 계산기 (원본 데이터 소스)</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>https://bongi-mobile-production.up.railway.app/docs/calculator.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>🔗 GitHub 리포지토리</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>https://github.com/vinsenzo83/bongi-mobile</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="13">
+    <mergeCell ref="B39:C39"/>
     <mergeCell ref="A28:C28"/>
+    <mergeCell ref="B38:C38"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A32:C32"/>
     <mergeCell ref="A31:C31"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="B40:C40"/>
     <mergeCell ref="A29:C29"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2225,387 +2360,880 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="33" t="inlineStr">
-        <is>
-          <t>🏷️ SKT 요즘가족결합</t>
+      <c r="A1" s="36" t="inlineStr">
+        <is>
+          <t>🏷️ SKT 요즘가족결합 (완전 명세)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>① 자격 조건</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="37" t="inlineStr">
+        <is>
+          <t>▶ 같은 명의자의 인터넷+휴대폰 1대 이상 필수</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="37" t="inlineStr">
+        <is>
+          <t>▶ 가족/동거인/친구 등 지인 결합 허용 (최대 5회선)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="37" t="inlineStr">
+        <is>
+          <t>▶ 적용 방식: 단독가 REPLACE (기존 요즘우리집 인터넷 할인 대체)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="37" t="inlineStr">
+        <is>
+          <t>▶ TV 결합 시: IPTV 추가 -1,100원 중복</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="37" t="inlineStr">
+        <is>
+          <t>▶ 인터넷 최대 2회선 + 휴대폰 최대 5회선</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>② 할인 테이블 (속도 × 회선수)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>속도</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>회선수</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>휴대폰</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>휴대폰 (총합)</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>인터넷</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>IPTV 추가</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>총할인</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="34" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="38" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B4" s="34" t="n">
+      <c r="B12" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="34" t="n">
+      <c r="C12" s="38" t="n">
         <v>3500</v>
       </c>
-      <c r="D4" s="34" t="n">
+      <c r="D12" s="38" t="n">
         <v>4400</v>
       </c>
-      <c r="E4" s="34" t="n">
+      <c r="E12" s="38" t="n">
         <v>1100</v>
       </c>
-      <c r="F4" s="34" t="n">
+      <c r="F12" s="38" t="n">
         <v>9000</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="34" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="38" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B5" s="34" t="n">
+      <c r="B13" s="38" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="34" t="n">
+      <c r="C13" s="38" t="n">
         <v>7000</v>
       </c>
-      <c r="D5" s="34" t="n">
+      <c r="D13" s="38" t="n">
         <v>4400</v>
       </c>
-      <c r="E5" s="34" t="n">
+      <c r="E13" s="38" t="n">
         <v>1100</v>
       </c>
-      <c r="F5" s="34" t="n">
+      <c r="F13" s="38" t="n">
         <v>12500</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="34" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="38" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B6" s="34" t="n">
+      <c r="B14" s="38" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="34" t="n">
+      <c r="C14" s="38" t="n">
         <v>18000</v>
       </c>
-      <c r="D6" s="34" t="n">
+      <c r="D14" s="38" t="n">
         <v>4400</v>
       </c>
-      <c r="E6" s="34" t="n">
+      <c r="E14" s="38" t="n">
         <v>1100</v>
       </c>
-      <c r="F6" s="34" t="n">
+      <c r="F14" s="38" t="n">
         <v>23500</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="34" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="38" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B7" s="34" t="n">
+      <c r="B15" s="38" t="n">
         <v>4</v>
       </c>
-      <c r="C7" s="34" t="n">
+      <c r="C15" s="38" t="n">
         <v>18000</v>
       </c>
-      <c r="D7" s="34" t="n">
+      <c r="D15" s="38" t="n">
         <v>4400</v>
       </c>
-      <c r="E7" s="34" t="n">
+      <c r="E15" s="38" t="n">
         <v>1100</v>
       </c>
-      <c r="F7" s="34" t="n">
+      <c r="F15" s="38" t="n">
         <v>23500</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="34" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="38" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B8" s="34" t="n">
+      <c r="B16" s="38" t="n">
         <v>5</v>
       </c>
-      <c r="C8" s="34" t="n">
+      <c r="C16" s="38" t="n">
         <v>18000</v>
       </c>
-      <c r="D8" s="34" t="n">
+      <c r="D16" s="38" t="n">
         <v>4400</v>
       </c>
-      <c r="E8" s="34" t="n">
+      <c r="E16" s="38" t="n">
         <v>1100</v>
       </c>
-      <c r="F8" s="34" t="n">
+      <c r="F16" s="38" t="n">
         <v>23500</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="38" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B9" s="34" t="n">
+      <c r="B17" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="34" t="n">
+      <c r="C17" s="38" t="n">
         <v>3500</v>
       </c>
-      <c r="D9" s="34" t="n">
+      <c r="D17" s="38" t="n">
         <v>11000</v>
       </c>
-      <c r="E9" s="34" t="n">
+      <c r="E17" s="38" t="n">
         <v>1100</v>
       </c>
-      <c r="F9" s="34" t="n">
+      <c r="F17" s="38" t="n">
         <v>15600</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="34" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="38" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B10" s="34" t="n">
+      <c r="B18" s="38" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="34" t="n">
+      <c r="C18" s="38" t="n">
         <v>7000</v>
       </c>
-      <c r="D10" s="34" t="n">
+      <c r="D18" s="38" t="n">
         <v>11000</v>
       </c>
-      <c r="E10" s="34" t="n">
+      <c r="E18" s="38" t="n">
         <v>1100</v>
       </c>
-      <c r="F10" s="34" t="n">
+      <c r="F18" s="38" t="n">
         <v>19100</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="34" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="38" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B11" s="34" t="n">
+      <c r="B19" s="38" t="n">
         <v>3</v>
       </c>
-      <c r="C11" s="34" t="n">
+      <c r="C19" s="38" t="n">
         <v>18000</v>
       </c>
-      <c r="D11" s="34" t="n">
+      <c r="D19" s="38" t="n">
         <v>11000</v>
       </c>
-      <c r="E11" s="34" t="n">
+      <c r="E19" s="38" t="n">
         <v>1100</v>
       </c>
-      <c r="F11" s="34" t="n">
+      <c r="F19" s="38" t="n">
         <v>30100</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="34" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="38" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B12" s="34" t="n">
+      <c r="B20" s="38" t="n">
         <v>4</v>
       </c>
-      <c r="C12" s="34" t="n">
+      <c r="C20" s="38" t="n">
         <v>24000</v>
       </c>
-      <c r="D12" s="34" t="n">
+      <c r="D20" s="38" t="n">
         <v>11000</v>
       </c>
-      <c r="E12" s="34" t="n">
+      <c r="E20" s="38" t="n">
         <v>1100</v>
       </c>
-      <c r="F12" s="34" t="n">
+      <c r="F20" s="38" t="n">
         <v>36100</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="34" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="38" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B13" s="34" t="n">
+      <c r="B21" s="38" t="n">
         <v>5</v>
       </c>
-      <c r="C13" s="34" t="n">
+      <c r="C21" s="38" t="n">
         <v>24000</v>
       </c>
-      <c r="D13" s="34" t="n">
+      <c r="D21" s="38" t="n">
         <v>11000</v>
       </c>
-      <c r="E13" s="34" t="n">
+      <c r="E21" s="38" t="n">
         <v>1100</v>
       </c>
-      <c r="F13" s="34" t="n">
+      <c r="F21" s="38" t="n">
         <v>36100</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="34" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="38" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B14" s="34" t="n">
+      <c r="B22" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="34" t="n">
+      <c r="C22" s="38" t="n">
         <v>3500</v>
       </c>
-      <c r="D14" s="34" t="n">
+      <c r="D22" s="38" t="n">
         <v>13200</v>
       </c>
-      <c r="E14" s="34" t="n">
+      <c r="E22" s="38" t="n">
         <v>1100</v>
       </c>
-      <c r="F14" s="34" t="n">
+      <c r="F22" s="38" t="n">
         <v>17800</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="34" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="38" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B15" s="34" t="n">
+      <c r="B23" s="38" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="34" t="n">
+      <c r="C23" s="38" t="n">
         <v>7000</v>
       </c>
-      <c r="D15" s="34" t="n">
+      <c r="D23" s="38" t="n">
         <v>13200</v>
       </c>
-      <c r="E15" s="34" t="n">
+      <c r="E23" s="38" t="n">
         <v>1100</v>
       </c>
-      <c r="F15" s="34" t="n">
+      <c r="F23" s="38" t="n">
         <v>21300</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="34" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="38" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B16" s="34" t="n">
+      <c r="B24" s="38" t="n">
         <v>3</v>
       </c>
-      <c r="C16" s="34" t="n">
+      <c r="C24" s="38" t="n">
         <v>18000</v>
       </c>
-      <c r="D16" s="34" t="n">
+      <c r="D24" s="38" t="n">
         <v>13200</v>
       </c>
-      <c r="E16" s="34" t="n">
+      <c r="E24" s="38" t="n">
         <v>1100</v>
       </c>
-      <c r="F16" s="34" t="n">
+      <c r="F24" s="38" t="n">
         <v>32300</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="34" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="38" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B17" s="34" t="n">
+      <c r="B25" s="38" t="n">
         <v>4</v>
       </c>
-      <c r="C17" s="34" t="n">
+      <c r="C25" s="38" t="n">
         <v>24000</v>
       </c>
-      <c r="D17" s="34" t="n">
+      <c r="D25" s="38" t="n">
         <v>13200</v>
       </c>
-      <c r="E17" s="34" t="n">
+      <c r="E25" s="38" t="n">
         <v>1100</v>
       </c>
-      <c r="F17" s="34" t="n">
+      <c r="F25" s="38" t="n">
         <v>38300</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="34" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="38" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B18" s="34" t="n">
+      <c r="B26" s="38" t="n">
         <v>5</v>
       </c>
-      <c r="C18" s="34" t="n">
+      <c r="C26" s="38" t="n">
         <v>24000</v>
       </c>
-      <c r="D18" s="34" t="n">
+      <c r="D26" s="38" t="n">
         <v>13200</v>
       </c>
-      <c r="E18" s="34" t="n">
+      <c r="E26" s="38" t="n">
         <v>1100</v>
       </c>
-      <c r="F18" s="34" t="n">
+      <c r="F26" s="38" t="n">
         <v>38300</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t>📌 휴대폰 인당 할인 (개발 참조)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>속도</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>1회선</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>2회선</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>3회선</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>4회선</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>5회선</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>100M (인당)</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>4500</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>500M·1G (인당)</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>③ 계산 알고리즘 (의사코드)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="39" t="inlineStr">
+        <is>
+          <t>// 입력: speed, tvIdx, wifi(bool), lines(1~5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="39" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="39" t="inlineStr">
+        <is>
+          <t>1. 단독가 기준으로 재계산 (요즘우리집 REPLACE):</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   netSingle = internet[speed] + (wifi ? wifiCost : 0)  // SKT wifiCost=1100</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   famInet = bundle.family.internet[speed]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   inetAfter = netSingle - famInet</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="39" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="39" t="inlineStr">
+        <is>
+          <t>2. TV 결합 시:</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   famIptv = hasTv ? bundle.family.iptv : 0  // iptv=1100</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   tvAfter = tv[tvIdx].p - tv[tvIdx].dc - famIptv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   monthlyFee = inetAfter + tvAfter + setTop</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="39" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="39" t="inlineStr">
+        <is>
+          <t>3. 휴대폰 별도 차감 (월):</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   perPerson = bundle.family.mobilePerBySpeed[speed][lines]</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   mobileDiscount = perPerson × lines  // 고지서에서 차감</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="39" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="39" t="inlineStr">
+        <is>
+          <t>4. 혜택가:</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   finalFee = monthlyFee - mobileDiscount</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>④ 검증 예시 — 500M + B tv 올 + WiFi X + 3회선</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>계산</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="38" t="inlineStr">
+        <is>
+          <t>단독가</t>
+        </is>
+      </c>
+      <c r="B55" s="38" t="inlineStr">
+        <is>
+          <t>33,000 + 0</t>
+        </is>
+      </c>
+      <c r="C55" s="38" t="inlineStr">
+        <is>
+          <t>33,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="38" t="inlineStr">
+        <is>
+          <t>요즘가족 인터넷 할인</t>
+        </is>
+      </c>
+      <c r="B56" s="38" t="inlineStr">
+        <is>
+          <t>-11,000</t>
+        </is>
+      </c>
+      <c r="C56" s="38" t="inlineStr">
+        <is>
+          <t>-11,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="38" t="inlineStr">
+        <is>
+          <t>인터넷 실질</t>
+        </is>
+      </c>
+      <c r="B57" s="38" t="inlineStr">
+        <is>
+          <t>33,000 - 11,000</t>
+        </is>
+      </c>
+      <c r="C57" s="38" t="inlineStr">
+        <is>
+          <t>22,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="38" t="inlineStr">
+        <is>
+          <t>TV 기본 (B tv 올)</t>
+        </is>
+      </c>
+      <c r="B58" s="38" t="inlineStr">
+        <is>
+          <t>18,700</t>
+        </is>
+      </c>
+      <c r="C58" s="38" t="inlineStr">
+        <is>
+          <t>18,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="38" t="inlineStr">
+        <is>
+          <t>TV 결합할인 + IPTV</t>
+        </is>
+      </c>
+      <c r="B59" s="38" t="inlineStr">
+        <is>
+          <t>-2,200 + -1,100</t>
+        </is>
+      </c>
+      <c r="C59" s="38" t="inlineStr">
+        <is>
+          <t>-3,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="38" t="inlineStr">
+        <is>
+          <t>TV 실질</t>
+        </is>
+      </c>
+      <c r="B60" s="38" t="inlineStr">
+        <is>
+          <t>18,700 - 3,300</t>
+        </is>
+      </c>
+      <c r="C60" s="38" t="inlineStr">
+        <is>
+          <t>15,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="38" t="inlineStr">
+        <is>
+          <t>셋톱 (스마트3)</t>
+        </is>
+      </c>
+      <c r="B61" s="38" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="C61" s="38" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="38">
+        <f> 월 실납부</f>
+        <v/>
+      </c>
+      <c r="B62" s="38" t="inlineStr">
+        <is>
+          <t>22,000 + 15,400 + 4,400</t>
+        </is>
+      </c>
+      <c r="C62" s="38" t="inlineStr">
+        <is>
+          <t>41,800</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="38" t="inlineStr">
+        <is>
+          <t>휴대폰 3회선 × 6,000</t>
+        </is>
+      </c>
+      <c r="B63" s="38" t="inlineStr">
+        <is>
+          <t>-18,000</t>
+        </is>
+      </c>
+      <c r="C63" s="38" t="inlineStr">
+        <is>
+          <t>-18,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="38" t="inlineStr">
+        <is>
+          <t>🎉 혜택가</t>
+        </is>
+      </c>
+      <c r="B64" s="38" t="inlineStr">
+        <is>
+          <t>41,800 - 18,000</t>
+        </is>
+      </c>
+      <c r="C64" s="38" t="inlineStr">
+        <is>
+          <t>23,800</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>⑤ 참고자료</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="40" t="inlineStr">
+        <is>
+          <t>🔗 백메가 SK 상품 전체 안내 (결합할인 원본)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    URL: https://www.100mb.kr/01_product/sk.php</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="25">
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A67:F67"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A49:F49"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2627,7 +3255,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="35" t="inlineStr">
+      <c r="A1" s="41" t="inlineStr">
         <is>
           <t>🏷️ KT 총액결합 (STACK)</t>
         </is>
@@ -2661,380 +3289,380 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="36" t="inlineStr">
+      <c r="A4" s="42" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B4" s="36" t="inlineStr">
+      <c r="B4" s="42" t="inlineStr">
         <is>
           <t>22K 이하</t>
         </is>
       </c>
-      <c r="C4" s="36" t="n">
+      <c r="C4" s="42" t="n">
         <v>1650</v>
       </c>
-      <c r="D4" s="36" t="n">
+      <c r="D4" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="36" t="n">
+      <c r="E4" s="42" t="n">
         <v>1650</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="36" t="inlineStr">
+      <c r="A5" s="42" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B5" s="36" t="inlineStr">
+      <c r="B5" s="42" t="inlineStr">
         <is>
           <t>22K 이상</t>
         </is>
       </c>
-      <c r="C5" s="36" t="n">
+      <c r="C5" s="42" t="n">
         <v>3300</v>
       </c>
-      <c r="D5" s="36" t="n">
+      <c r="D5" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="36" t="n">
+      <c r="E5" s="42" t="n">
         <v>3300</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="36" t="inlineStr">
+      <c r="A6" s="42" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B6" s="36" t="inlineStr">
+      <c r="B6" s="42" t="inlineStr">
         <is>
           <t>64.9K 이상</t>
         </is>
       </c>
-      <c r="C6" s="36" t="n">
+      <c r="C6" s="42" t="n">
         <v>5500</v>
       </c>
-      <c r="D6" s="36" t="n">
+      <c r="D6" s="42" t="n">
         <v>3300</v>
       </c>
-      <c r="E6" s="36" t="n">
+      <c r="E6" s="42" t="n">
         <v>8800</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="36" t="inlineStr">
+      <c r="A7" s="42" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B7" s="36" t="inlineStr">
+      <c r="B7" s="42" t="inlineStr">
         <is>
           <t>108.9K 이상</t>
         </is>
       </c>
-      <c r="C7" s="36" t="n">
+      <c r="C7" s="42" t="n">
         <v>5500</v>
       </c>
-      <c r="D7" s="36" t="n">
+      <c r="D7" s="42" t="n">
         <v>14300</v>
       </c>
-      <c r="E7" s="36" t="n">
+      <c r="E7" s="42" t="n">
         <v>19800</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="36" t="inlineStr">
+      <c r="A8" s="42" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B8" s="36" t="inlineStr">
+      <c r="B8" s="42" t="inlineStr">
         <is>
           <t>141.9K 이상</t>
         </is>
       </c>
-      <c r="C8" s="36" t="n">
+      <c r="C8" s="42" t="n">
         <v>5500</v>
       </c>
-      <c r="D8" s="36" t="n">
+      <c r="D8" s="42" t="n">
         <v>18700</v>
       </c>
-      <c r="E8" s="36" t="n">
+      <c r="E8" s="42" t="n">
         <v>24200</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="36" t="inlineStr">
+      <c r="A9" s="42" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B9" s="36" t="inlineStr">
+      <c r="B9" s="42" t="inlineStr">
         <is>
           <t>174.9K 이상</t>
         </is>
       </c>
-      <c r="C9" s="36" t="n">
+      <c r="C9" s="42" t="n">
         <v>5500</v>
       </c>
-      <c r="D9" s="36" t="n">
+      <c r="D9" s="42" t="n">
         <v>23100</v>
       </c>
-      <c r="E9" s="36" t="n">
+      <c r="E9" s="42" t="n">
         <v>28600</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="36" t="inlineStr">
+      <c r="A10" s="42" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B10" s="36" t="inlineStr">
+      <c r="B10" s="42" t="inlineStr">
         <is>
           <t>22K 이하</t>
         </is>
       </c>
-      <c r="C10" s="36" t="n">
+      <c r="C10" s="42" t="n">
         <v>2200</v>
       </c>
-      <c r="D10" s="36" t="n">
+      <c r="D10" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="36" t="n">
+      <c r="E10" s="42" t="n">
         <v>2200</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="42" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B11" s="36" t="inlineStr">
+      <c r="B11" s="42" t="inlineStr">
         <is>
           <t>22K 이상</t>
         </is>
       </c>
-      <c r="C11" s="36" t="n">
+      <c r="C11" s="42" t="n">
         <v>5500</v>
       </c>
-      <c r="D11" s="36" t="n">
+      <c r="D11" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="36" t="n">
+      <c r="E11" s="42" t="n">
         <v>5500</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="36" t="inlineStr">
+      <c r="A12" s="42" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B12" s="36" t="inlineStr">
+      <c r="B12" s="42" t="inlineStr">
         <is>
           <t>64.9K 이상</t>
         </is>
       </c>
-      <c r="C12" s="36" t="n">
+      <c r="C12" s="42" t="n">
         <v>5500</v>
       </c>
-      <c r="D12" s="36" t="n">
+      <c r="D12" s="42" t="n">
         <v>5500</v>
       </c>
-      <c r="E12" s="36" t="n">
+      <c r="E12" s="42" t="n">
         <v>11000</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="36" t="inlineStr">
+      <c r="A13" s="42" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B13" s="36" t="inlineStr">
+      <c r="B13" s="42" t="inlineStr">
         <is>
           <t>108.9K 이상</t>
         </is>
       </c>
-      <c r="C13" s="36" t="n">
+      <c r="C13" s="42" t="n">
         <v>5500</v>
       </c>
-      <c r="D13" s="36" t="n">
+      <c r="D13" s="42" t="n">
         <v>16610</v>
       </c>
-      <c r="E13" s="36" t="n">
+      <c r="E13" s="42" t="n">
         <v>22110</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="36" t="inlineStr">
+      <c r="A14" s="42" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B14" s="36" t="inlineStr">
+      <c r="B14" s="42" t="inlineStr">
         <is>
           <t>141.9K 이상</t>
         </is>
       </c>
-      <c r="C14" s="36" t="n">
+      <c r="C14" s="42" t="n">
         <v>5500</v>
       </c>
-      <c r="D14" s="36" t="n">
+      <c r="D14" s="42" t="n">
         <v>22110</v>
       </c>
-      <c r="E14" s="36" t="n">
+      <c r="E14" s="42" t="n">
         <v>27610</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="36" t="inlineStr">
+      <c r="A15" s="42" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B15" s="36" t="inlineStr">
+      <c r="B15" s="42" t="inlineStr">
         <is>
           <t>174.9K 이상</t>
         </is>
       </c>
-      <c r="C15" s="36" t="n">
+      <c r="C15" s="42" t="n">
         <v>5500</v>
       </c>
-      <c r="D15" s="36" t="n">
+      <c r="D15" s="42" t="n">
         <v>27610</v>
       </c>
-      <c r="E15" s="36" t="n">
+      <c r="E15" s="42" t="n">
         <v>33110</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="36" t="inlineStr">
+      <c r="A16" s="42" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B16" s="36" t="inlineStr">
+      <c r="B16" s="42" t="inlineStr">
         <is>
           <t>22K 이하</t>
         </is>
       </c>
-      <c r="C16" s="36" t="n">
+      <c r="C16" s="42" t="n">
         <v>2200</v>
       </c>
-      <c r="D16" s="36" t="n">
+      <c r="D16" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="36" t="n">
+      <c r="E16" s="42" t="n">
         <v>2200</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="36" t="inlineStr">
+      <c r="A17" s="42" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B17" s="36" t="inlineStr">
+      <c r="B17" s="42" t="inlineStr">
         <is>
           <t>22K 이상</t>
         </is>
       </c>
-      <c r="C17" s="36" t="n">
+      <c r="C17" s="42" t="n">
         <v>5500</v>
       </c>
-      <c r="D17" s="36" t="n">
+      <c r="D17" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="36" t="n">
+      <c r="E17" s="42" t="n">
         <v>5500</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="36" t="inlineStr">
+      <c r="A18" s="42" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B18" s="36" t="inlineStr">
+      <c r="B18" s="42" t="inlineStr">
         <is>
           <t>64.9K 이상</t>
         </is>
       </c>
-      <c r="C18" s="36" t="n">
+      <c r="C18" s="42" t="n">
         <v>5500</v>
       </c>
-      <c r="D18" s="36" t="n">
+      <c r="D18" s="42" t="n">
         <v>5500</v>
       </c>
-      <c r="E18" s="36" t="n">
+      <c r="E18" s="42" t="n">
         <v>11000</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="36" t="inlineStr">
+      <c r="A19" s="42" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B19" s="36" t="inlineStr">
+      <c r="B19" s="42" t="inlineStr">
         <is>
           <t>108.9K 이상</t>
         </is>
       </c>
-      <c r="C19" s="36" t="n">
+      <c r="C19" s="42" t="n">
         <v>5500</v>
       </c>
-      <c r="D19" s="36" t="n">
+      <c r="D19" s="42" t="n">
         <v>16610</v>
       </c>
-      <c r="E19" s="36" t="n">
+      <c r="E19" s="42" t="n">
         <v>22110</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="36" t="inlineStr">
+      <c r="A20" s="42" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B20" s="36" t="inlineStr">
+      <c r="B20" s="42" t="inlineStr">
         <is>
           <t>141.9K 이상</t>
         </is>
       </c>
-      <c r="C20" s="36" t="n">
+      <c r="C20" s="42" t="n">
         <v>5500</v>
       </c>
-      <c r="D20" s="36" t="n">
+      <c r="D20" s="42" t="n">
         <v>22110</v>
       </c>
-      <c r="E20" s="36" t="n">
+      <c r="E20" s="42" t="n">
         <v>27610</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="36" t="inlineStr">
+      <c r="A21" s="42" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B21" s="36" t="inlineStr">
+      <c r="B21" s="42" t="inlineStr">
         <is>
           <t>174.9K 이상</t>
         </is>
       </c>
-      <c r="C21" s="36" t="n">
+      <c r="C21" s="42" t="n">
         <v>5500</v>
       </c>
-      <c r="D21" s="36" t="n">
+      <c r="D21" s="42" t="n">
         <v>27610</v>
       </c>
-      <c r="E21" s="36" t="n">
+      <c r="E21" s="42" t="n">
         <v>33110</v>
       </c>
     </row>
@@ -3059,7 +3687,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="35" t="inlineStr">
+      <c r="A1" s="41" t="inlineStr">
         <is>
           <t>🏷️ KT 정액결합</t>
         </is>
@@ -3088,66 +3716,66 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="36" t="inlineStr">
+      <c r="A4" s="42" t="inlineStr">
         <is>
           <t>37K 이하</t>
         </is>
       </c>
-      <c r="B4" s="36" t="n">
+      <c r="B4" s="42" t="n">
         <v>5500</v>
       </c>
-      <c r="C4" s="36" t="n">
+      <c r="C4" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="36" t="n">
+      <c r="D4" s="42" t="n">
         <v>5500</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="36" t="inlineStr">
+      <c r="A5" s="42" t="inlineStr">
         <is>
           <t>37K 이상</t>
         </is>
       </c>
-      <c r="B5" s="36" t="n">
+      <c r="B5" s="42" t="n">
         <v>5500</v>
       </c>
-      <c r="C5" s="36" t="n">
+      <c r="C5" s="42" t="n">
         <v>3000</v>
       </c>
-      <c r="D5" s="36" t="n">
+      <c r="D5" s="42" t="n">
         <v>8500</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="36" t="inlineStr">
+      <c r="A6" s="42" t="inlineStr">
         <is>
           <t>61K 이상</t>
         </is>
       </c>
-      <c r="B6" s="36" t="n">
+      <c r="B6" s="42" t="n">
         <v>5500</v>
       </c>
-      <c r="C6" s="36" t="n">
+      <c r="C6" s="42" t="n">
         <v>5000</v>
       </c>
-      <c r="D6" s="36" t="n">
+      <c r="D6" s="42" t="n">
         <v>10500</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="36" t="inlineStr">
+      <c r="A7" s="42" t="inlineStr">
         <is>
           <t>77K 이상</t>
         </is>
       </c>
-      <c r="B7" s="36" t="n">
+      <c r="B7" s="42" t="n">
         <v>5500</v>
       </c>
-      <c r="C7" s="36" t="n">
+      <c r="C7" s="42" t="n">
         <v>7000</v>
       </c>
-      <c r="D7" s="36" t="n">
+      <c r="D7" s="42" t="n">
         <v>12500</v>
       </c>
     </row>
@@ -3162,7 +3790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:F103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3170,375 +3798,1347 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="37" t="inlineStr">
-        <is>
-          <t>💎 KT 프리미엄 가족결합 (원본 planCatalog 14종)</t>
+      <c r="A1" s="43" t="inlineStr">
+        <is>
+          <t>💎 KT 프리미엄 가족결합 (완전 명세서)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="32" t="inlineStr">
-        <is>
-          <t>자격: 77,000원↑ 요금제 2회선 이상 필수 · 대표자는 총액결합만 · 구성원 77K↑만 프리미엄 선택 가능 · 인터넷 -5,500원 기본</t>
+      <c r="A3" s="44" t="inlineStr">
+        <is>
+          <t>① 자격 조건</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="37" t="inlineStr">
+        <is>
+          <t>▶ 필수: 77,000원↑ 요금제 휴대폰 2회선 이상 결합</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
+        <is>
+          <t>▶ 대표명의자 1명 + 구성원 최대 N명 (총 5회선까지)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="37" t="inlineStr">
+        <is>
+          <t>▶ 자격 미충족 시: 총액결합만 가능 (프리미엄 선택 불가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="37" t="inlineStr">
+        <is>
+          <t>▶ 77,000원↑ 요금제가 1회선뿐 (대표자 본인) → 프리미엄 불가</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="44" t="inlineStr">
+        <is>
+          <t>② 회선별 분배 규칙 (누가 어디 속하는가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>회선 종류</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>조건</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>귀속 할인</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>대표명의자</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>무조건 (총대)</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>총액결합할인</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>프리미엄 불가 · 인터넷 -5,500 대체 가능</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>구성원 (77K↑)</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>선택 가능</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>프리미엄 가족결합</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>요금제별 고정 dc × 회선수</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>구성원 (77K↑)</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>선택 안 함</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>총액결합할인</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>합산에 포함 (구간 상승 효과)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>구성원 (77K미만)</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>무조건</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>총액결합할인</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>합산에 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="44" t="inlineStr">
+        <is>
+          <t>③ 요금제 카탈로그 (원본 planCatalog 14종)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>월정액 (v)</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>요금제명 (label)</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>prem 자격</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>할인액 (dc)</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>비율</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="38" t="n">
+    <row r="18">
+      <c r="A18" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="B6" s="38" t="inlineStr">
+      <c r="B18" s="45" t="inlineStr">
         <is>
           <t>— 회선 없음 —</t>
         </is>
       </c>
-      <c r="C6" s="38" t="inlineStr">
+      <c r="C18" s="45" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D6" s="38" t="n">
+      <c r="D18" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="38" t="inlineStr">
+      <c r="E18" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="38" t="n">
+    <row r="19">
+      <c r="A19" s="45" t="n">
         <v>32890</v>
       </c>
-      <c r="B7" s="38" t="inlineStr">
+      <c r="B19" s="45" t="inlineStr">
         <is>
           <t>32,890원 (LTE 데이터선택)</t>
         </is>
       </c>
-      <c r="C7" s="38" t="inlineStr">
+      <c r="C19" s="45" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D7" s="38" t="n">
+      <c r="D19" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="38" t="inlineStr">
+      <c r="E19" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="38" t="n">
+    <row r="20">
+      <c r="A20" s="45" t="n">
         <v>47000</v>
       </c>
-      <c r="B8" s="38" t="inlineStr">
+      <c r="B20" s="45" t="inlineStr">
         <is>
           <t>47,000원</t>
         </is>
       </c>
-      <c r="C8" s="38" t="inlineStr">
+      <c r="C20" s="45" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D8" s="38" t="n">
+      <c r="D20" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="38" t="inlineStr">
+      <c r="E20" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="38" t="n">
+    <row r="21">
+      <c r="A21" s="45" t="n">
         <v>55000</v>
       </c>
-      <c r="B9" s="38" t="inlineStr">
+      <c r="B21" s="45" t="inlineStr">
         <is>
           <t>55,000원</t>
         </is>
       </c>
-      <c r="C9" s="38" t="inlineStr">
+      <c r="C21" s="45" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D9" s="38" t="n">
+      <c r="D21" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="38" t="inlineStr">
+      <c r="E21" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="38" t="n">
+    <row r="22">
+      <c r="A22" s="45" t="n">
         <v>65000</v>
       </c>
-      <c r="B10" s="38" t="inlineStr">
+      <c r="B22" s="45" t="inlineStr">
         <is>
           <t>65,000원</t>
         </is>
       </c>
-      <c r="C10" s="38" t="inlineStr">
+      <c r="C22" s="45" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D10" s="38" t="n">
+      <c r="D22" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="38" t="inlineStr">
+      <c r="E22" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="38" t="n">
+    <row r="23">
+      <c r="A23" s="45" t="n">
         <v>77000</v>
       </c>
-      <c r="B11" s="38" t="inlineStr">
+      <c r="B23" s="45" t="inlineStr">
         <is>
           <t>77,000원 (임계값)</t>
         </is>
       </c>
-      <c r="C11" s="38" t="inlineStr">
+      <c r="C23" s="45" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D11" s="38" t="n">
+      <c r="D23" s="45" t="n">
         <v>19250</v>
       </c>
-      <c r="E11" s="38" t="inlineStr">
+      <c r="E23" s="45" t="inlineStr">
         <is>
           <t>≈25%</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="38" t="n">
+    <row r="24">
+      <c r="A24" s="45" t="n">
         <v>80000</v>
       </c>
-      <c r="B12" s="38" t="inlineStr">
+      <c r="B24" s="45" t="inlineStr">
         <is>
           <t>80,000원 (5G 슈퍼플랜 베이직)</t>
         </is>
       </c>
-      <c r="C12" s="38" t="inlineStr">
+      <c r="C24" s="45" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D12" s="38" t="n">
+      <c r="D24" s="45" t="n">
         <v>20000</v>
       </c>
-      <c r="E12" s="38" t="inlineStr">
+      <c r="E24" s="45" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="38" t="n">
+    <row r="25">
+      <c r="A25" s="45" t="n">
         <v>87890</v>
       </c>
-      <c r="B13" s="38" t="inlineStr">
+      <c r="B25" s="45" t="inlineStr">
         <is>
           <t>87,890원 (데이터선택 87.8)</t>
         </is>
       </c>
-      <c r="C13" s="38" t="inlineStr">
+      <c r="C25" s="45" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D13" s="38" t="n">
+      <c r="D25" s="45" t="n">
         <v>22000</v>
       </c>
-      <c r="E13" s="38" t="inlineStr">
+      <c r="E25" s="45" t="inlineStr">
         <is>
           <t>≈25%</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="38" t="n">
+    <row r="26">
+      <c r="A26" s="45" t="n">
         <v>89000</v>
       </c>
-      <c r="B14" s="38" t="inlineStr">
+      <c r="B26" s="45" t="inlineStr">
         <is>
           <t>89,000원 (데이터ON 프리미엄)</t>
         </is>
       </c>
-      <c r="C14" s="38" t="inlineStr">
+      <c r="C26" s="45" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D14" s="38" t="n">
+      <c r="D26" s="45" t="n">
         <v>22250</v>
       </c>
-      <c r="E14" s="38" t="inlineStr">
+      <c r="E26" s="45" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="38" t="n">
+    <row r="27">
+      <c r="A27" s="45" t="n">
         <v>90000</v>
       </c>
-      <c r="B15" s="38" t="inlineStr">
+      <c r="B27" s="45" t="inlineStr">
         <is>
           <t>90,000원 (슈퍼플랜 베이직 Plus/초이스)</t>
         </is>
       </c>
-      <c r="C15" s="38" t="inlineStr">
+      <c r="C27" s="45" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D15" s="38" t="n">
+      <c r="D27" s="45" t="n">
         <v>22500</v>
       </c>
-      <c r="E15" s="38" t="inlineStr">
+      <c r="E27" s="45" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="38" t="n">
+    <row r="28">
+      <c r="A28" s="45" t="n">
         <v>100000</v>
       </c>
-      <c r="B16" s="38" t="inlineStr">
+      <c r="B28" s="45" t="inlineStr">
         <is>
           <t>100,000원 (슈퍼플랜 스페셜)</t>
         </is>
       </c>
-      <c r="C16" s="38" t="inlineStr">
+      <c r="C28" s="45" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D16" s="38" t="n">
+      <c r="D28" s="45" t="n">
         <v>25000</v>
       </c>
-      <c r="E16" s="38" t="inlineStr">
+      <c r="E28" s="45" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="38" t="n">
+    <row r="29">
+      <c r="A29" s="45" t="n">
         <v>109000</v>
       </c>
-      <c r="B17" s="38" t="inlineStr">
+      <c r="B29" s="45" t="inlineStr">
         <is>
           <t>109,000원 (데이터선택 109)</t>
         </is>
       </c>
-      <c r="C17" s="38" t="inlineStr">
+      <c r="C29" s="45" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D17" s="38" t="n">
+      <c r="D29" s="45" t="n">
         <v>27500</v>
       </c>
-      <c r="E17" s="38" t="inlineStr">
+      <c r="E29" s="45" t="inlineStr">
         <is>
           <t>≈25%</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="38" t="n">
+    <row r="30">
+      <c r="A30" s="45" t="n">
         <v>110000</v>
       </c>
-      <c r="B18" s="38" t="inlineStr">
+      <c r="B30" s="45" t="inlineStr">
         <is>
           <t>110,000원 (슈퍼플랜 스페셜 Plus/초이스)</t>
         </is>
       </c>
-      <c r="C18" s="38" t="inlineStr">
+      <c r="C30" s="45" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D18" s="38" t="n">
+      <c r="D30" s="45" t="n">
         <v>27500</v>
       </c>
-      <c r="E18" s="38" t="inlineStr">
+      <c r="E30" s="45" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="38" t="n">
+    <row r="31">
+      <c r="A31" s="45" t="n">
         <v>130000</v>
       </c>
-      <c r="B19" s="38" t="inlineStr">
+      <c r="B31" s="45" t="inlineStr">
         <is>
           <t>130,000원 (슈퍼플랜 프리미엄/초이스)</t>
         </is>
       </c>
-      <c r="C19" s="38" t="inlineStr">
+      <c r="C31" s="45" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D19" s="38" t="n">
+      <c r="D31" s="45" t="n">
         <v>32500</v>
       </c>
-      <c r="E19" s="38" t="inlineStr">
+      <c r="E31" s="45" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="44" t="inlineStr">
+        <is>
+          <t>④ 계산 알고리즘 (의사코드)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="39" t="inlineStr">
+        <is>
+          <t>// 입력: members: Array&lt;{ isRep: boolean, planV: number, usePrem?: boolean }&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="39" t="inlineStr">
+        <is>
+          <t>//      speed: "100M" | "500M" | "1G"</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="39" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="39" t="inlineStr">
+        <is>
+          <t>1. 자격 체크:</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   highPlanCount = members.filter(m =&gt; m.planV &gt;= 77000).length</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   IF highPlanCount &lt; 2 THEN 프리미엄 불가 (총액결합만 사용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="39" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="39" t="inlineStr">
+        <is>
+          <t>2. 회선 분배:</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   premMembers = members.filter(m =&gt; !m.isRep &amp;&amp; m.usePrem &amp;&amp; m.planV &gt;= 77000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   totalMembers = members.filter(m =&gt; m.isRep || !m.usePrem || m.planV &lt; 77000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   IF premMembers.length == 0 THEN 프리미엄 불가 (총액결합만 사용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="39" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="39" t="inlineStr">
+        <is>
+          <t>3. 총액결합 합산액:</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   totalSum = sum(totalMembers.map(m =&gt; m.planV))</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="39" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="39" t="inlineStr">
+        <is>
+          <t>4. 총액결합 구간 판정:</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   rngIdx = 0 ~ 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   if totalSum &gt;= 174900: rngIdx = 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   else if totalSum &gt;= 141900: rngIdx = 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   else if totalSum &gt;= 108900: rngIdx = 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   else if totalSum &gt;= 64900:  rngIdx = 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   else if totalSum &gt;= 22000:  rngIdx = 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   else: rngIdx = 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="39" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="39" t="inlineStr">
+        <is>
+          <t>5. 할인 계산:</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   inetFixedDc = 5500  // 인터넷 또는 대표자 휴대폰 (기본: 대표자 휴대폰)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   totalMobDc = kt.total.mobile[speed][rngIdx]</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   premTotalDc = sum(premMembers.map(m =&gt; planCatalog[m.planV].dc))</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="39" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="39" t="inlineStr">
+        <is>
+          <t>6. 최종:</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   totalDiscount = inetFixedDc + totalMobDc + premTotalDc</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="44" t="inlineStr">
+        <is>
+          <t>⑤ 검증 예시 1 — 100M + 3회선 (모두 89,000원)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>구성</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>계산</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>할인액</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="45" t="inlineStr">
+        <is>
+          <t>회선 1</t>
+        </is>
+      </c>
+      <c r="B68" s="45" t="inlineStr">
+        <is>
+          <t>대표자 89K (총액)</t>
+        </is>
+      </c>
+      <c r="C68" s="45" t="inlineStr">
+        <is>
+          <t>자동</t>
+        </is>
+      </c>
+      <c r="D68" s="45" t="inlineStr">
+        <is>
+          <t>대표자는 총액결합 대상</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="45" t="inlineStr">
+        <is>
+          <t>회선 2</t>
+        </is>
+      </c>
+      <c r="B69" s="45" t="inlineStr">
+        <is>
+          <t>구성원 89K (프리미엄)</t>
+        </is>
+      </c>
+      <c r="C69" s="45" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="D69" s="45" t="inlineStr">
+        <is>
+          <t>프리미엄 대상</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="45" t="inlineStr">
+        <is>
+          <t>회선 3</t>
+        </is>
+      </c>
+      <c r="B70" s="45" t="inlineStr">
+        <is>
+          <t>구성원 89K (프리미엄)</t>
+        </is>
+      </c>
+      <c r="C70" s="45" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="D70" s="45" t="inlineStr">
+        <is>
+          <t>프리미엄 대상</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="45" t="inlineStr">
+        <is>
+          <t>총액 합산</t>
+        </is>
+      </c>
+      <c r="B71" s="45" t="inlineStr">
+        <is>
+          <t>대표자 1명 89,000원</t>
+        </is>
+      </c>
+      <c r="C71" s="45" t="inlineStr">
+        <is>
+          <t>rngIdx=2 (64.9K↑)</t>
+        </is>
+      </c>
+      <c r="D71" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="45" t="inlineStr">
+        <is>
+          <t>인터넷</t>
+        </is>
+      </c>
+      <c r="B72" s="45" t="inlineStr">
+        <is>
+          <t>대표자 휴대폰에 -5,500</t>
+        </is>
+      </c>
+      <c r="C72" s="45" t="inlineStr">
+        <is>
+          <t>고정</t>
+        </is>
+      </c>
+      <c r="D72" s="45" t="inlineStr">
+        <is>
+          <t>-5,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="45" t="inlineStr">
+        <is>
+          <t>대표자 총액결합</t>
+        </is>
+      </c>
+      <c r="B73" s="45" t="inlineStr">
+        <is>
+          <t>100M mobile[2]</t>
+        </is>
+      </c>
+      <c r="C73" s="45" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="D73" s="45" t="inlineStr">
+        <is>
+          <t>-3,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="45" t="inlineStr">
+        <is>
+          <t>구성원 프리미엄</t>
+        </is>
+      </c>
+      <c r="B74" s="45" t="inlineStr">
+        <is>
+          <t>89K × 2명</t>
+        </is>
+      </c>
+      <c r="C74" s="45" t="inlineStr">
+        <is>
+          <t>22,250 × 2</t>
+        </is>
+      </c>
+      <c r="D74" s="45" t="inlineStr">
+        <is>
+          <t>-44,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="45" t="inlineStr">
+        <is>
+          <t>🎉 총 할인</t>
+        </is>
+      </c>
+      <c r="B75" s="45" t="inlineStr">
+        <is>
+          <t>5,500 + 3,300 + 44,500</t>
+        </is>
+      </c>
+      <c r="C75" s="45" t="inlineStr"/>
+      <c r="D75" s="45" t="inlineStr">
+        <is>
+          <t>-53,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="45" t="inlineStr">
+        <is>
+          <t>비교 (총액결합만)</t>
+        </is>
+      </c>
+      <c r="B76" s="45" t="inlineStr">
+        <is>
+          <t>3×89K=267K → idx 5</t>
+        </is>
+      </c>
+      <c r="C76" s="45" t="inlineStr">
+        <is>
+          <t>mobile[5]=23,100 + 인터넷 5,500</t>
+        </is>
+      </c>
+      <c r="D76" s="45" t="inlineStr">
+        <is>
+          <t>-28,600</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="45" t="inlineStr">
+        <is>
+          <t>차액</t>
+        </is>
+      </c>
+      <c r="B77" s="45" t="inlineStr">
+        <is>
+          <t>프리미엄 선택 시 추가 혜택</t>
+        </is>
+      </c>
+      <c r="C77" s="45" t="inlineStr"/>
+      <c r="D77" s="45" t="inlineStr">
+        <is>
+          <t>+24,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="44" t="inlineStr">
+        <is>
+          <t>⑥ 검증 예시 2 — 100M + 4회선 (2×89K + 2×32.89K)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>구성</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>계산</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>할인액</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="45" t="inlineStr">
+        <is>
+          <t>회선 1</t>
+        </is>
+      </c>
+      <c r="B81" s="45" t="inlineStr">
+        <is>
+          <t>대표자 89K</t>
+        </is>
+      </c>
+      <c r="C81" s="45" t="inlineStr">
+        <is>
+          <t>총액</t>
+        </is>
+      </c>
+      <c r="D81" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="45" t="inlineStr">
+        <is>
+          <t>회선 2</t>
+        </is>
+      </c>
+      <c r="B82" s="45" t="inlineStr">
+        <is>
+          <t>구성원 89K (프리미엄)</t>
+        </is>
+      </c>
+      <c r="C82" s="45" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="D82" s="45" t="inlineStr">
+        <is>
+          <t>프리미엄 대상</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="45" t="inlineStr">
+        <is>
+          <t>회선 3</t>
+        </is>
+      </c>
+      <c r="B83" s="45" t="inlineStr">
+        <is>
+          <t>구성원 32.89K</t>
+        </is>
+      </c>
+      <c r="C83" s="45" t="inlineStr">
+        <is>
+          <t>77K미만 → 자동 총액</t>
+        </is>
+      </c>
+      <c r="D83" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="45" t="inlineStr">
+        <is>
+          <t>회선 4</t>
+        </is>
+      </c>
+      <c r="B84" s="45" t="inlineStr">
+        <is>
+          <t>구성원 32.89K</t>
+        </is>
+      </c>
+      <c r="C84" s="45" t="inlineStr">
+        <is>
+          <t>77K미만 → 자동 총액</t>
+        </is>
+      </c>
+      <c r="D84" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="45" t="inlineStr">
+        <is>
+          <t>총액 합산</t>
+        </is>
+      </c>
+      <c r="B85" s="45" t="inlineStr">
+        <is>
+          <t>89 + 32.89×2 = 154,780</t>
+        </is>
+      </c>
+      <c r="C85" s="45" t="inlineStr">
+        <is>
+          <t>rngIdx=4 (141.9K↑)</t>
+        </is>
+      </c>
+      <c r="D85" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="45" t="inlineStr">
+        <is>
+          <t>인터넷</t>
+        </is>
+      </c>
+      <c r="B86" s="45" t="inlineStr">
+        <is>
+          <t>고정</t>
+        </is>
+      </c>
+      <c r="C86" s="45" t="inlineStr"/>
+      <c r="D86" s="45" t="inlineStr">
+        <is>
+          <t>-5,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="45" t="inlineStr">
+        <is>
+          <t>대표자+일반 총액결합</t>
+        </is>
+      </c>
+      <c r="B87" s="45" t="inlineStr">
+        <is>
+          <t>100M mobile[4]</t>
+        </is>
+      </c>
+      <c r="C87" s="45" t="inlineStr">
+        <is>
+          <t>18,700</t>
+        </is>
+      </c>
+      <c r="D87" s="45" t="inlineStr">
+        <is>
+          <t>-18,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="45" t="inlineStr">
+        <is>
+          <t>프리미엄 89K</t>
+        </is>
+      </c>
+      <c r="B88" s="45" t="inlineStr">
+        <is>
+          <t>1명</t>
+        </is>
+      </c>
+      <c r="C88" s="45" t="inlineStr">
+        <is>
+          <t>22,250</t>
+        </is>
+      </c>
+      <c r="D88" s="45" t="inlineStr">
+        <is>
+          <t>-22,250</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="45" t="inlineStr">
+        <is>
+          <t>🎉 총 할인</t>
+        </is>
+      </c>
+      <c r="B89" s="45" t="inlineStr">
+        <is>
+          <t>5,500 + 18,700 + 22,250</t>
+        </is>
+      </c>
+      <c r="C89" s="45" t="inlineStr"/>
+      <c r="D89" s="45" t="inlineStr">
+        <is>
+          <t>-46,450</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="44" t="inlineStr">
+        <is>
+          <t>⑦ 엣지 케이스 처리</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>처리</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>77K+ 요금제가 1명만 (대표자만)</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>프리미엄 선택 불가 → 총액결합으로만 계산</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>77K+ 구성원 중 프리미엄 체크 0명</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>프리미엄 미적용 (전원 총액)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>대표자 요금제가 77K 미만</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>가능 · 대표자는 항상 총액결합</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>모든 구성원이 77K 미만</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>프리미엄 불가 (자격 미달)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>1회선만 결합</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>프리미엄 불가 (2회선 이상 필수)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>프리미엄 구성원 5명+</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>현실적으로 5회선까지 결합 가능 (KT 규정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="44" t="inlineStr">
+        <is>
+          <t>⑧ 참고자료 (원본 출처)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="40" t="inlineStr">
+        <is>
+          <t>🔗 백메가 블로그 — KT 프리미엄 가족결합 상세 해설 (원본 소스)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    URL: https://www.100mb.kr/bbs/board.php?bo_table=information&amp;wr_id=11986</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    · 자격 조건, 대표자/구성원 분배 규칙, 실제 계산 예시 2건 원본</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A3:E3"/>
+  <mergeCells count="38">
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="A54:F54"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="A101:F101"/>
+    <mergeCell ref="A55:F55"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A62:F62"/>
+    <mergeCell ref="A53:F53"/>
+    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A102:F102"/>
+    <mergeCell ref="A58:F58"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A64:F64"/>
+    <mergeCell ref="A59:F59"/>
+    <mergeCell ref="A49:F49"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A60:F60"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A103:F103"/>
+    <mergeCell ref="A61:F61"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3549,132 +5149,300 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="39" t="inlineStr">
-        <is>
-          <t>🏷️ LG U+ 참쉬운가족결합</t>
+      <c r="A1" s="47" t="inlineStr">
+        <is>
+          <t>🏷️ LG U+ 참쉬운가족결합 (완전 명세)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="48" t="inlineStr">
+        <is>
+          <t>① 자격 조건</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="37" t="inlineStr">
+        <is>
+          <t>▶ 휴대폰 2회선부터 결합 (1회선 불가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="37" t="inlineStr">
+        <is>
+          <t>▶ 알뜰폰 결합 가능 (추가 할인 대당 -440원)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="37" t="inlineStr">
+        <is>
+          <t>▶ 휴대폰 최대 10대 + 인터넷 최대 3대</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="37" t="inlineStr">
+        <is>
+          <t>▶ 적용 방식: 단독가 REPLACE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="48" t="inlineStr">
+        <is>
+          <t>② 인터넷 할인 (3년 약정 기준)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="40" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="49" t="inlineStr">
         <is>
           <t>인터넷 할인</t>
         </is>
       </c>
-      <c r="B4" s="40" t="n">
+      <c r="B11" s="49" t="n">
         <v>5500</v>
       </c>
-      <c r="C4" s="40" t="n">
+      <c r="C11" s="49" t="n">
         <v>9900</v>
       </c>
-      <c r="D4" s="40" t="n">
+      <c r="D11" s="49" t="n">
         <v>13200</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="48" t="inlineStr">
+        <is>
+          <t>③ 휴대폰 인당 할인 매트릭스 (요금구간 × 회선수)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>요금구간</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>2회선</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>3회선</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>4+회선</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="40" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="49" t="inlineStr">
         <is>
           <t>69K 미만</t>
         </is>
       </c>
-      <c r="B7" s="40" t="n">
+      <c r="B15" s="49" t="n">
         <v>2200</v>
       </c>
-      <c r="C7" s="40" t="n">
+      <c r="C15" s="49" t="n">
         <v>3300</v>
       </c>
-      <c r="D7" s="40" t="n">
+      <c r="D15" s="49" t="n">
         <v>4400</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="40" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="49" t="inlineStr">
         <is>
           <t>69K 이상</t>
         </is>
       </c>
-      <c r="B8" s="40" t="n">
+      <c r="B16" s="49" t="n">
         <v>3300</v>
       </c>
-      <c r="C8" s="40" t="n">
+      <c r="C16" s="49" t="n">
         <v>5500</v>
       </c>
-      <c r="D8" s="40" t="n">
+      <c r="D16" s="49" t="n">
         <v>6600</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="40" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="49" t="inlineStr">
         <is>
           <t>88K 이상</t>
         </is>
       </c>
-      <c r="B9" s="40" t="n">
+      <c r="B17" s="49" t="n">
         <v>4400</v>
       </c>
-      <c r="C9" s="40" t="n">
+      <c r="C17" s="49" t="n">
         <v>6600</v>
       </c>
-      <c r="D9" s="40" t="n">
+      <c r="D17" s="49" t="n">
         <v>8800</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="48" t="inlineStr">
+        <is>
+          <t>④ 계산 알고리즘</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="39" t="inlineStr">
+        <is>
+          <t>// 입력: speed, tvIdx, planRange(1~3), lines(2~4+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="39" t="inlineStr">
+        <is>
+          <t>1. lguInet = bundle.chweyswun.internet[speed]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="39" t="inlineStr">
+        <is>
+          <t>2. netSingle = internet[speed]  // LGU+ WiFi 전속도 무료</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="39" t="inlineStr">
+        <is>
+          <t>3. inetAfter = netSingle - lguInet  // REPLACE 방식</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="39" t="inlineStr">
+        <is>
+          <t>4. 휴대폰: idx = min(lines, 4) - 2  // 2회선=0 / 3회선=1 / 4+=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   perPerson = bundle.chweyswun.mobile[planRange-1][idx]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   mobileDc = perPerson × min(lines, 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="39" t="inlineStr">
+        <is>
+          <t>5. TV: tvAfter = tv[tvIdx].p - tv[tvIdx].dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="39" t="inlineStr">
+        <is>
+          <t>6. monthlyFee = inetAfter + tvAfter + setTop(4,400)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="39" t="inlineStr">
+        <is>
+          <t>7. finalFee = monthlyFee - mobileDc</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="48" t="inlineStr">
+        <is>
+          <t>⑤ 참고자료</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="40" t="inlineStr">
+        <is>
+          <t>🔗 백메가 LG U+ 상품 전체 안내 (결합할인 원본 소스)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    URL: https://www.100mb.kr/01_product/lg.php</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A27:E27"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3685,105 +5453,194 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="39" t="inlineStr">
-        <is>
-          <t>🏷️ LG U+ 투게더 (85K↑)</t>
+      <c r="A1" s="47" t="inlineStr">
+        <is>
+          <t>🏷️ LG U+ 투게더 결합 (85,000원↑ 고가요금제)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="48" t="inlineStr">
+        <is>
+          <t>① 자격 조건</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="37" t="inlineStr">
+        <is>
+          <t>▶ 5G 85,000원 이상 요금제 필수</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="37" t="inlineStr">
+        <is>
+          <t>▶ 500M 이상 인터넷 (100M 결합 불가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="37" t="inlineStr">
+        <is>
+          <t>▶ 휴대폰 최대 5회선 + 인터넷 최대 5회선</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="37" t="inlineStr">
+        <is>
+          <t>▶ 선택약정 25% 중복 가능</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="37" t="inlineStr">
+        <is>
+          <t>▶ 적용 방식: 단독가 REPLACE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="48" t="inlineStr">
+        <is>
+          <t>② 인터넷 할인</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="40" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="49" t="inlineStr">
         <is>
           <t>인터넷</t>
         </is>
       </c>
-      <c r="B4" s="40" t="inlineStr">
-        <is>
-          <t>불가</t>
-        </is>
-      </c>
-      <c r="C4" s="40" t="n">
+      <c r="B12" s="49" t="inlineStr">
+        <is>
+          <t>❌ 불가</t>
+        </is>
+      </c>
+      <c r="C12" s="49" t="n">
         <v>11000</v>
       </c>
-      <c r="D4" s="40" t="n">
+      <c r="D12" s="49" t="n">
         <v>11000</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="48" t="inlineStr">
+        <is>
+          <t>③ 휴대폰 인당 할인</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>회선수</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>휴대폰 할인 (인당)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="40" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>인당 할인</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="49" t="inlineStr">
         <is>
           <t>2회선</t>
         </is>
       </c>
-      <c r="B7" s="40" t="n">
+      <c r="B16" s="49" t="n">
         <v>10000</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="40" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="49" t="inlineStr">
         <is>
           <t>3회선</t>
         </is>
       </c>
-      <c r="B8" s="40" t="n">
+      <c r="B17" s="49" t="n">
         <v>14000</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="40" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="49" t="inlineStr">
         <is>
           <t>4~5회선</t>
         </is>
       </c>
-      <c r="B9" s="40" t="n">
+      <c r="B18" s="49" t="n">
         <v>20000</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>※ 추가 혜택: 청소년 가족할인 -10,000 / 시그니처 가족할인 자녀 1대 최대 -33,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="48" t="inlineStr">
+        <is>
+          <t>④ 참고자료</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="40" t="inlineStr">
+        <is>
+          <t>🔗 백메가 LG U+ 상품 안내</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A7:D7"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3808,101 +5665,101 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="41" t="inlineStr">
+      <c r="A3" s="50" t="inlineStr">
         <is>
           <t>interface CarrierData {</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="41" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">  name, prefix;</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="41" t="inlineStr">
+      <c r="A5" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">  internet: Record&lt;"100M"|"500M"|"1G", number&gt;;</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="41" t="inlineStr">
+      <c r="A6" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">  wifiCost? | wifiPrice?: Record&lt;Speed, number&gt;;</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="41" t="inlineStr">
+      <c r="A7" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">  setTopOptions: SetTop[]; wifiOptions: WiFi[];</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="41" t="inlineStr">
+      <c r="A8" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">  tvInternetNoWifi, tvInternetWithWifi: Record&lt;Speed, number&gt;;</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="41" t="inlineStr">
+      <c r="A9" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">  tv: TVProduct[];</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="41" t="inlineStr">
+      <c r="A10" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">  install: { solo, combo };</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="41" t="inlineStr">
+      <c r="A11" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">  gift: { solo: SpeedMap, combo: SpeedMap };</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="41" t="inlineStr">
+      <c r="A12" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">  bundle: BundleConfig;  // 3사별 상이</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="41" t="inlineStr">
+      <c r="A13" s="50" t="inlineStr">
         <is>
           <t>}</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="41" t="inlineStr"/>
+      <c r="A14" s="50" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="41" t="inlineStr">
+      <c r="A15" s="50" t="inlineStr">
         <is>
           <t>// SKT: bundle.family { internet, iptv, mobilePerBySpeed }</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="41" t="inlineStr">
+      <c r="A16" s="50" t="inlineStr">
         <is>
           <t>// KT:  bundle.{ranges_total, total, ranges_fixed, fixed, premium}</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="41" t="inlineStr">
+      <c r="A17" s="50" t="inlineStr">
         <is>
           <t>// LGU: bundle.{chweyswun, together}</t>
         </is>
@@ -3930,87 +5787,87 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>🧮 SKT 요즘가족결합 계산기</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>📝 입력 (노란 셀 클릭 → 드롭다운)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>속도</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>100M / 500M / 1G</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>TV 상품</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>B tv 올</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>SKT B tv 9종</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>WiFi 사용</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>Y=+1,100원 / N=미사용</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>휴대폰 회선수</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n">
+      <c r="B7" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>0=결합없음 / 1~5</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>🧮 자동 계산</t>
         </is>
@@ -4022,11 +5879,11 @@
           <t>TV 인덱스 (내부 변환)</t>
         </is>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="16">
         <f>MATCH(B5,{"TV 없음","B tv 이코노미","B tv 스탠다드","B tv 올","B tv 스탠다드 플러스","B tv 올 플러스","B tv 스탠다드 넷플릭스","B tv 올 넷플릭스","B tv 스탠다드 넷플릭스 프리미엄","B tv 올 넷플릭스 프리미엄"},0)</f>
         <v/>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>드롭다운 이름 → 배열 번호 (1=TV 없음, 2~10=상품) · 수식 조회용</t>
         </is>
@@ -4038,18 +5895,18 @@
           <t>TV 선택 여부 (내부 변환)</t>
         </is>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="16">
         <f>IF(B5="TV 없음",0,1)</f>
         <v/>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>0=TV 없음 (인터넷 단독) / 1=TV 결합 · 수식 분기용</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>📊 데이터 조회</t>
         </is>
@@ -4061,11 +5918,11 @@
           <t>인터넷 단독가</t>
         </is>
       </c>
-      <c r="B14" s="16">
+      <c r="B14" s="19">
         <f>IF(B4="100M",22000,IF(B4="500M",33000,38500))</f>
         <v/>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>→ 01_Internet · SKT 단독가</t>
         </is>
@@ -4077,11 +5934,11 @@
           <t>TV 상품 가격 (p)</t>
         </is>
       </c>
-      <c r="B15" s="16">
+      <c r="B15" s="19">
         <f>IF(B11=0,0,CHOOSE(B10-1,12100,15400,18700,23100,24200,27700,30200,30700,33200))</f>
         <v/>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>→ 02_TV · SKT TV 9종</t>
         </is>
@@ -4093,11 +5950,11 @@
           <t>TV 결합할인 (dc)</t>
         </is>
       </c>
-      <c r="B16" s="16">
+      <c r="B16" s="19">
         <f>IF(B11=0,0,2200)</f>
         <v/>
       </c>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>→ 02_TV · SKT 전 상품 -2,200 균일</t>
         </is>
@@ -4109,11 +5966,11 @@
           <t>WiFi 추가금</t>
         </is>
       </c>
-      <c r="B17" s="16">
+      <c r="B17" s="19">
         <f>IF(B6="Y",1100,0)</f>
         <v/>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>→ 05_WiFi · SKT GIGA WiFi (기본) 속도 균일 1,100원</t>
         </is>
@@ -4125,11 +5982,11 @@
           <t>tvInternetNoWifi</t>
         </is>
       </c>
-      <c r="B18" s="16">
+      <c r="B18" s="19">
         <f>IF(B4="100M",19800,IF(B4="500M",27500,33000))</f>
         <v/>
       </c>
-      <c r="C18" s="14" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>→ 03_TV_Internet · WiFi 미포함 결합가</t>
         </is>
@@ -4141,11 +5998,11 @@
           <t>tvInternetWithWifi</t>
         </is>
       </c>
-      <c r="B19" s="16">
+      <c r="B19" s="19">
         <f>IF(B4="100M",22000,IF(B4="500M",28600,34100))</f>
         <v/>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>→ 03_TV_Internet · WiFi 포함 결합가</t>
         </is>
@@ -4157,41 +6014,41 @@
           <t>셋톱박스 (스마트3)</t>
         </is>
       </c>
-      <c r="B20" s="16">
+      <c r="B20" s="19">
         <f>4400</f>
         <v/>
       </c>
-      <c r="C20" s="14" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>→ 04_SetTop · 기본 모델 (매장 판매 1위)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>【경로 A】 결합없음 (휴대폰 결합 X)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">  월 기본요금 (요즘우리집 · 휴대폰결합 없을 때)</t>
         </is>
       </c>
-      <c r="B23" s="18">
+      <c r="B23" s="21">
         <f>IF(B11=0,B14+B17,IF(B6="Y",B19,B18)+B15-B16+B20)</f>
         <v/>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C23" s="17" t="inlineStr">
         <is>
           <t>TV 결합: tvInternet(WiFi반영) + (p-dc) + 셋톱 / TV 없음: 단독+WiFi</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="19" t="inlineStr">
+      <c r="A25" s="22" t="inlineStr">
         <is>
           <t>【경로 B】 요즘가족결합 (휴대폰 결합 · 단독가 REPLACE)</t>
         </is>
@@ -4203,11 +6060,11 @@
           <t xml:space="preserve">  요즘가족 인터넷 할인</t>
         </is>
       </c>
-      <c r="B26" s="16">
+      <c r="B26" s="19">
         <f>IF(B7=0,0,IF(B4="100M",4400,IF(B4="500M",11000,13200)))</f>
         <v/>
       </c>
-      <c r="C26" s="14" t="inlineStr">
+      <c r="C26" s="17" t="inlineStr">
         <is>
           <t>→ 10_SKT_Bundle · 단독가 기준 차감 (요즘우리집 REPLACE)</t>
         </is>
@@ -4219,11 +6076,11 @@
           <t xml:space="preserve">  IPTV 추가 (TV+결합 시)</t>
         </is>
       </c>
-      <c r="B27" s="16">
+      <c r="B27" s="19">
         <f>IF(AND(B7&gt;0,B11=1),1100,0)</f>
         <v/>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C27" s="17" t="inlineStr">
         <is>
           <t>TV 결합 시에만 추가 -1,100원</t>
         </is>
@@ -4235,11 +6092,11 @@
           <t xml:space="preserve">  휴대폰 인당 할인</t>
         </is>
       </c>
-      <c r="B28" s="16">
+      <c r="B28" s="19">
         <f>IF(B7=0,0,IF(B4="100M",CHOOSE(B7,3500,3500,6000,4500,3600),CHOOSE(B7,3500,3500,6000,6000,4800)))</f>
         <v/>
       </c>
-      <c r="C28" s="14" t="inlineStr">
+      <c r="C28" s="17" t="inlineStr">
         <is>
           <t>→ 10_SKT_Bundle · 속도+회선수별 인당</t>
         </is>
@@ -4251,11 +6108,11 @@
           <t xml:space="preserve">  휴대폰 총 할인</t>
         </is>
       </c>
-      <c r="B29" s="16">
+      <c r="B29" s="19">
         <f>B28*B7</f>
         <v/>
       </c>
-      <c r="C29" s="14" t="inlineStr">
+      <c r="C29" s="17" t="inlineStr">
         <is>
           <t>인당 × 회선수 (휴대폰 고지서 별도 차감)</t>
         </is>
@@ -4267,7 +6124,7 @@
           <t xml:space="preserve">  → 인터넷 (단독 - 요즘가족할인)</t>
         </is>
       </c>
-      <c r="B31" s="20">
+      <c r="B31" s="23">
         <f>IF(B7=0,"-",B14+B17-B26)</f>
         <v/>
       </c>
@@ -4278,7 +6135,7 @@
           <t xml:space="preserve">  → TV (p - dc - iptv)</t>
         </is>
       </c>
-      <c r="B32" s="20">
+      <c r="B32" s="23">
         <f>IF(B7=0,"-",IF(B11=0,0,B15-B16-B27))</f>
         <v/>
       </c>
@@ -4289,18 +6146,18 @@
           <t xml:space="preserve">  → 셋톱 (TV 있을 때만)</t>
         </is>
       </c>
-      <c r="B33" s="20">
+      <c r="B33" s="23">
         <f>IF(B7=0,"-",IF(B11=0,0,B20))</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="17" t="inlineStr">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">  = 인터넷+TV 월 실납부 (결합 적용)</t>
         </is>
       </c>
-      <c r="B34" s="18">
+      <c r="B34" s="21">
         <f>IF(B7=0,"-",(B14+B17-B26)+IF(B11=0,0,B15-B16-B27+B20))</f>
         <v/>
       </c>
@@ -4311,29 +6168,29 @@
           <t xml:space="preserve">  - 휴대폰 고지서 별도 차감</t>
         </is>
       </c>
-      <c r="B35" s="20">
+      <c r="B35" s="23">
         <f>IF(B7=0,"-",-B29)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="17" t="inlineStr">
+      <c r="A36" s="20" t="inlineStr">
         <is>
           <t>🎉 혜택가 (최종 월요금)</t>
         </is>
       </c>
-      <c r="B36" s="21">
+      <c r="B36" s="24">
         <f>IF(B7=0,B23,B34-B29)</f>
         <v/>
       </c>
-      <c r="C36" s="14" t="inlineStr">
+      <c r="C36" s="17" t="inlineStr">
         <is>
           <t>결합없음이면 경로 A 값 / 결합 있으면 경로 B - 휴대폰할인</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="18" t="inlineStr">
         <is>
           <t>🎁 부가 혜택</t>
         </is>
@@ -4345,11 +6202,11 @@
           <t xml:space="preserve">  설치비 (1회성)</t>
         </is>
       </c>
-      <c r="B39" s="16">
+      <c r="B39" s="19">
         <f>IF(B11=0,36300,56100)</f>
         <v/>
       </c>
-      <c r="C39" s="14" t="inlineStr">
+      <c r="C39" s="17" t="inlineStr">
         <is>
           <t>→ 06_Install</t>
         </is>
@@ -4361,11 +6218,11 @@
           <t xml:space="preserve">  사은품 (속도×TV결합)</t>
         </is>
       </c>
-      <c r="B40" s="16">
+      <c r="B40" s="19">
         <f>IF(B11=0,IF(B4="100M",110000,170000),CHOOSE(MATCH(B4,{"100M","500M","1G"},0),400000,430000,490000))</f>
         <v/>
       </c>
-      <c r="C40" s="14" t="inlineStr">
+      <c r="C40" s="17" t="inlineStr">
         <is>
           <t>→ 07_Gift</t>
         </is>
@@ -4439,42 +6296,42 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="42" t="inlineStr">
+      <c r="A3" s="51" t="inlineStr">
         <is>
           <t>⚠️ 3사 결합할인 적용 방식 차이</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="43" t="inlineStr">
+      <c r="A4" s="37" t="inlineStr">
         <is>
           <t>• SKT 요즘가족결합: 단독가 REPLACE (요즘우리집 대체) → tvInternet 사용 X</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="43" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>• KT 총액/정액: 기본 TV결합 + 추가할인 STACK (중복)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="43" t="inlineStr">
+      <c r="A6" s="37" t="inlineStr">
         <is>
           <t>• KT 프리미엄: 대표자+77K미만은 총액결합 / 77K↑ 구성원은 프리미엄 (독립)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="43" t="inlineStr">
+      <c r="A7" s="37" t="inlineStr">
         <is>
           <t>• LG U+ 참쉬운: 단독가 REPLACE</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="43" t="inlineStr">
+      <c r="A8" s="37" t="inlineStr">
         <is>
           <t>• LG U+ 투게더: 단독가 REPLACE + 100M 결합 불가</t>
         </is>
@@ -4510,151 +6367,151 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>🧮 KT 총액/정액 결합 계산기</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>📝 입력</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>속도</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>100M / 500M / 1G</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>TV 상품</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>지니TV 에센스</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>KT 지니TV 5종</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>WiFi 사용</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>Y=1,100원 (1G는 무료) / N</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>결합 종류</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>총액결합</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>결합없음/총액/정액/💎프리미엄</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>총액결합 구간 (1~6)</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>1=22K↓, 2=22K↑, 3=64.9K↑, 4=108.9K↑, 5=141.9K↑, 6=174.9K↑</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>정액결합 구간 (1~4)</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>1=37K↓, 2=37K↑, 3=61K↑, 4=77K↑</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>💎 프리미엄 요금제</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>89,000원</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>77K+ 요금제 (드롭다운)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>💎 프리미엄 회선수</t>
         </is>
       </c>
-      <c r="B11" s="11" t="n">
+      <c r="B11" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>대표자 제외 구성원 77K+ 회선수 (최소 1명)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>🧮 자동 계산</t>
         </is>
@@ -4666,11 +6523,11 @@
           <t>TV 인덱스 (내부 변환)</t>
         </is>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="16">
         <f>MATCH(B5,{"TV 없음","지니TV 베이직","지니TV 라이트","지니TV 에센스","지니TV 모든G","지니TV 디즈니+모든G"},0)</f>
         <v/>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>드롭다운 이름 → 배열 번호 (1=없음, 2~6=상품) · 수식 조회용</t>
         </is>
@@ -4682,18 +6539,18 @@
           <t>TV 선택 여부 (내부 변환)</t>
         </is>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="16">
         <f>IF(B5="TV 없음",0,1)</f>
         <v/>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>0=TV 없음 / 1=TV 결합 · 수식 분기용</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>📊 데이터 조회</t>
         </is>
@@ -4705,11 +6562,11 @@
           <t>인터넷 단독가</t>
         </is>
       </c>
-      <c r="B18" s="16">
+      <c r="B18" s="19">
         <f>IF(B4="100M",22000,IF(B4="500M",33000,38500))</f>
         <v/>
       </c>
-      <c r="C18" s="14" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>→ 01_Internet</t>
         </is>
@@ -4721,11 +6578,11 @@
           <t>TV 가격 (p)</t>
         </is>
       </c>
-      <c r="B19" s="16">
+      <c r="B19" s="19">
         <f>IF(B15=0,0,CHOOSE(B14-1,14740,15840,20240,21340,28100))</f>
         <v/>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>→ 02_TV · KT 지니TV</t>
         </is>
@@ -4737,11 +6594,11 @@
           <t>TV 결합할인 (dc)</t>
         </is>
       </c>
-      <c r="B20" s="16">
+      <c r="B20" s="19">
         <f>IF(B15=0,0,CHOOSE(B14-1,2640,2640,3740,4400,6600))</f>
         <v/>
       </c>
-      <c r="C20" s="14" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>→ 02_TV · KT 상품별 차등</t>
         </is>
@@ -4753,11 +6610,11 @@
           <t>WiFi 추가금 (속도별)</t>
         </is>
       </c>
-      <c r="B21" s="16">
+      <c r="B21" s="19">
         <f>IF(B6="Y",IF(B4="1G",0,1100),0)</f>
         <v/>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C21" s="17" t="inlineStr">
         <is>
           <t>→ 05_WiFi · KT WAVE2 (기본) · 1G는 무료</t>
         </is>
@@ -4769,11 +6626,11 @@
           <t>tvInternetNoWifi</t>
         </is>
       </c>
-      <c r="B22" s="16">
+      <c r="B22" s="19">
         <f>IF(B4="100M",22000,IF(B4="500M",27500,33000))</f>
         <v/>
       </c>
-      <c r="C22" s="14" t="inlineStr">
+      <c r="C22" s="17" t="inlineStr">
         <is>
           <t>→ 03_TV_Internet</t>
         </is>
@@ -4785,11 +6642,11 @@
           <t>tvInternetWithWifi</t>
         </is>
       </c>
-      <c r="B23" s="16">
+      <c r="B23" s="19">
         <f>IF(B4="100M",23100,IF(B4="500M",28600,33000))</f>
         <v/>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C23" s="17" t="inlineStr">
         <is>
           <t>→ 03_TV_Internet · 1G는 동일</t>
         </is>
@@ -4801,41 +6658,41 @@
           <t>셋톱박스 (기가지니3)</t>
         </is>
       </c>
-      <c r="B24" s="16">
+      <c r="B24" s="19">
         <f>4400</f>
         <v/>
       </c>
-      <c r="C24" s="14" t="inlineStr">
+      <c r="C24" s="17" t="inlineStr">
         <is>
           <t>→ 04_SetTop · 기본 모델 · 고객 선호 1위</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="18" t="inlineStr">
         <is>
           <t>【경로 A】 결합없음 (기본 TV 결합)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">  월 기본요금 (기본 TV결합 · 휴대폰결합 없을 때)</t>
         </is>
       </c>
-      <c r="B27" s="23">
+      <c r="B27" s="26">
         <f>IF(B15=0,B18+B21,IF(B6="Y",B23,B22)+B19-B20+B24)</f>
         <v/>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C27" s="17" t="inlineStr">
         <is>
           <t>KT 기본 TV결합 할인 자동 적용 (tvInternetNoWifi/WithWifi)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="24" t="inlineStr">
+      <c r="A29" s="27" t="inlineStr">
         <is>
           <t>【경로 B】 결합 적용 (STACK — 기본 TV결합 + 추가할인)</t>
         </is>
@@ -4847,11 +6704,11 @@
           <t xml:space="preserve">  [총액] 인터넷 추가 할인</t>
         </is>
       </c>
-      <c r="B30" s="16">
+      <c r="B30" s="19">
         <f>IF(B7="총액결합",IF(B4="100M",CHOOSE(B8,1650,3300,5500,5500,5500,5500),CHOOSE(B8,2200,5500,5500,5500,5500,5500)),0)</f>
         <v/>
       </c>
-      <c r="C30" s="14" t="inlineStr">
+      <c r="C30" s="17" t="inlineStr">
         <is>
           <t>→ 11_KT_Total · STACK 중복 적용</t>
         </is>
@@ -4863,11 +6720,11 @@
           <t xml:space="preserve">  [총액] 휴대폰 할인</t>
         </is>
       </c>
-      <c r="B31" s="16">
+      <c r="B31" s="19">
         <f>IF(B7="총액결합",IF(B4="100M",CHOOSE(B8,0,0,3300,14300,18700,23100),CHOOSE(B8,0,0,5500,16610,22110,27610)),0)</f>
         <v/>
       </c>
-      <c r="C31" s="14" t="inlineStr">
+      <c r="C31" s="17" t="inlineStr">
         <is>
           <t>→ 11_KT_Total · 휴대폰 고지서 별도</t>
         </is>
@@ -4879,11 +6736,11 @@
           <t xml:space="preserve">  [정액] 인터넷 할인</t>
         </is>
       </c>
-      <c r="B32" s="16">
+      <c r="B32" s="19">
         <f>IF(B7="정액결합",5500,0)</f>
         <v/>
       </c>
-      <c r="C32" s="14" t="inlineStr">
+      <c r="C32" s="17" t="inlineStr">
         <is>
           <t>→ 12_KT_Fixed · 전구간 5,500 고정</t>
         </is>
@@ -4895,11 +6752,11 @@
           <t xml:space="preserve">  [정액] 휴대폰 할인</t>
         </is>
       </c>
-      <c r="B33" s="16">
+      <c r="B33" s="19">
         <f>IF(B7="정액결합",CHOOSE(B9,0,3000,5000,7000),0)</f>
         <v/>
       </c>
-      <c r="C33" s="14" t="inlineStr">
+      <c r="C33" s="17" t="inlineStr">
         <is>
           <t>→ 12_KT_Fixed · 4구간</t>
         </is>
@@ -4911,11 +6768,11 @@
           <t xml:space="preserve">  [💎프리미엄] 인터넷 할인 (고정)</t>
         </is>
       </c>
-      <c r="B34" s="16">
+      <c r="B34" s="19">
         <f>IF(B7="💎 프리미엄 가족결합",5500,0)</f>
         <v/>
       </c>
-      <c r="C34" s="14" t="inlineStr">
+      <c r="C34" s="17" t="inlineStr">
         <is>
           <t>→ 13_KT_Premium · 인터넷 또는 대표자 휴대폰 고정 -5,500</t>
         </is>
@@ -4927,11 +6784,11 @@
           <t xml:space="preserve">  [💎프리미엄] 대표자 총액결합 (합산=요금제1명)</t>
         </is>
       </c>
-      <c r="B35" s="16">
+      <c r="B35" s="19">
         <f>IF(B7="💎 프리미엄 가족결합",IF(B4="100M",CHOOSE(B8,0,0,3300,14300,18700,23100),CHOOSE(B8,0,0,5500,16610,22110,27610)),0)</f>
         <v/>
       </c>
-      <c r="C35" s="14" t="inlineStr">
+      <c r="C35" s="17" t="inlineStr">
         <is>
           <t>총액결합 구간 활용 (대표자 1명 기준)</t>
         </is>
@@ -4943,11 +6800,11 @@
           <t xml:space="preserve">  [💎프리미엄] 요금제별 할인액</t>
         </is>
       </c>
-      <c r="B36" s="16">
+      <c r="B36" s="19">
         <f>IF(B7="💎 프리미엄 가족결합",CHOOSE(MATCH(B10,{"77,000원","80,000원","87,890원","89,000원","90,000원","100,000원","109,000원","110,000원","130,000원"},0),19250,20000,22000,22250,22500,25000,27500,27500,32500),0)</f>
         <v/>
       </c>
-      <c r="C36" s="14" t="inlineStr">
+      <c r="C36" s="17" t="inlineStr">
         <is>
           <t>→ 13_KT_Premium · planCatalog dc</t>
         </is>
@@ -4959,27 +6816,27 @@
           <t xml:space="preserve">  [💎프리미엄] 구성원 총 할인 (dc × 회선수)</t>
         </is>
       </c>
-      <c r="B37" s="16">
+      <c r="B37" s="19">
         <f>B36*IF(B7="💎 프리미엄 가족결합",B11,0)</f>
         <v/>
       </c>
-      <c r="C37" s="14" t="inlineStr">
+      <c r="C37" s="17" t="inlineStr">
         <is>
           <t>77K+ 구성원만 해당 (대표자 제외)</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="17" t="inlineStr">
+      <c r="A39" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">  = 인터넷+TV 월 실납부</t>
         </is>
       </c>
-      <c r="B39" s="23">
+      <c r="B39" s="26">
         <f>IF(B7="💎 프리미엄 가족결합",B27-B34,B27-B30-B32)</f>
         <v/>
       </c>
-      <c r="C39" s="14" t="inlineStr">
+      <c r="C39" s="17" t="inlineStr">
         <is>
           <t>프리미엄: -5,500 고정 / 총액+정액: 해당 할인</t>
         </is>
@@ -4991,29 +6848,29 @@
           <t xml:space="preserve">  - 휴대폰 고지서 별도 차감</t>
         </is>
       </c>
-      <c r="B40" s="25">
+      <c r="B40" s="28">
         <f>-(B31+B33+B35+B37)</f>
         <v/>
       </c>
-      <c r="C40" s="14" t="inlineStr">
+      <c r="C40" s="17" t="inlineStr">
         <is>
           <t>총액/정액 + 프리미엄(대표자 총액 + 구성원 프리미엄)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="17" t="inlineStr">
+      <c r="A41" s="20" t="inlineStr">
         <is>
           <t>🎉 혜택가 (최종 월요금)</t>
         </is>
       </c>
-      <c r="B41" s="26">
+      <c r="B41" s="29">
         <f>IF(B7="결합없음",B27,B39-(B31+B33+B35+B37))</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="15" t="inlineStr">
+      <c r="A43" s="18" t="inlineStr">
         <is>
           <t>🎁 부가</t>
         </is>
@@ -5025,11 +6882,11 @@
           <t xml:space="preserve">  설치비</t>
         </is>
       </c>
-      <c r="B44" s="16">
+      <c r="B44" s="19">
         <f>IF(B15=0,36000,56200)</f>
         <v/>
       </c>
-      <c r="C44" s="14" t="inlineStr">
+      <c r="C44" s="17" t="inlineStr">
         <is>
           <t>→ 06_Install</t>
         </is>
@@ -5041,11 +6898,11 @@
           <t xml:space="preserve">  사은품</t>
         </is>
       </c>
-      <c r="B45" s="16">
+      <c r="B45" s="19">
         <f>IF(B15=0,IF(B4="100M",90000,140000),CHOOSE(MATCH(B4,{"100M","500M","1G"},0),370000,450000,450000))</f>
         <v/>
       </c>
-      <c r="C45" s="14" t="inlineStr">
+      <c r="C45" s="17" t="inlineStr">
         <is>
           <t>→ 07_Gift</t>
         </is>
@@ -5136,102 +6993,102 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="27" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>🧮 LG U+ 참쉬운/투게더 결합 계산기</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>📝 입력</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>속도</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>100M / 500M / 1G</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>TV 상품</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>U+tv 기본형</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>LG U+tv 4종</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>결합 종류</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>참쉬운 가족결합</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>결합없음/참쉬운/투게더</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>요금구간 (참쉬운, 1~3)</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n">
+      <c r="B7" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>1=69K미만, 2=69K+, 3=88K+</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>결합 회선수</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>참쉬운 2~4+ / 투게더 2~5</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>🧮 자동 계산</t>
         </is>
@@ -5243,11 +7100,11 @@
           <t>TV 인덱스 (내부 변환)</t>
         </is>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="16">
         <f>MATCH(B5,{"TV 없음","U+tv 실속형","U+tv 기본형","U+tv 프리미엄","U+tv 프리미엄 VOD"},0)</f>
         <v/>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>드롭다운 이름 → 배열 번호 (1=없음, 2~5=상품) · 수식 조회용</t>
         </is>
@@ -5259,18 +7116,18 @@
           <t>TV 선택 여부 (내부 변환)</t>
         </is>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="16">
         <f>IF(B5="TV 없음",0,1)</f>
         <v/>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>0=TV 없음 / 1=TV 결합 · 수식 분기용</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>📊 데이터 조회</t>
         </is>
@@ -5282,11 +7139,11 @@
           <t>인터넷 단독가</t>
         </is>
       </c>
-      <c r="B15" s="16">
+      <c r="B15" s="19">
         <f>IF(B4="100M",22000,IF(B4="500M",33000,38500))</f>
         <v/>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>→ 01_Internet</t>
         </is>
@@ -5298,11 +7155,11 @@
           <t>TV 가격 (p)</t>
         </is>
       </c>
-      <c r="B16" s="16">
+      <c r="B16" s="19">
         <f>IF(B12=0,0,CHOOSE(B11-1,15400,16500,18700,24200))</f>
         <v/>
       </c>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>→ 02_TV · LG U+tv</t>
         </is>
@@ -5314,11 +7171,11 @@
           <t>TV 결합할인 (dc)</t>
         </is>
       </c>
-      <c r="B17" s="16">
+      <c r="B17" s="19">
         <f>IF(B12=0,0,CHOOSE(B11-1,2200,2200,2200,5500))</f>
         <v/>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>→ 02_TV · 전 상품 -2,200 (VOD만 -5,500)</t>
         </is>
@@ -5330,11 +7187,11 @@
           <t>WiFi 추가금</t>
         </is>
       </c>
-      <c r="B18" s="16">
+      <c r="B18" s="19">
         <f>0</f>
         <v/>
       </c>
-      <c r="C18" s="14" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>→ 05_WiFi · LG U+ 전속도 무료 (기가와이파이 기본)</t>
         </is>
@@ -5346,41 +7203,41 @@
           <t>셋톱박스 (U+tv UHD4)</t>
         </is>
       </c>
-      <c r="B19" s="16">
+      <c r="B19" s="19">
         <f>4400</f>
         <v/>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>→ 04_SetTop · 기본 모델 · AI음향 기술</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="18" t="inlineStr">
         <is>
           <t>【경로 A】 결합없음</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">  월 기본요금</t>
         </is>
       </c>
-      <c r="B22" s="28">
+      <c r="B22" s="31">
         <f>IF(B12=0,B15,IF(B4="100M",22000,IF(B4="500M",27500,33000))+B16-B17+B19)</f>
         <v/>
       </c>
-      <c r="C22" s="14" t="inlineStr">
+      <c r="C22" s="17" t="inlineStr">
         <is>
           <t>TV 없으면 단독가 (WiFi 무료) / TV 있으면 tvInternet + (p-dc) + 셋톱</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="29" t="inlineStr">
+      <c r="A24" s="32" t="inlineStr">
         <is>
           <t>【경로 B】 결합 적용 (REPLACE — 단독가 기준)</t>
         </is>
@@ -5392,11 +7249,11 @@
           <t xml:space="preserve">  [참쉬운] 인터넷 할인</t>
         </is>
       </c>
-      <c r="B25" s="16">
+      <c r="B25" s="19">
         <f>IF(B6="참쉬운 가족결합",IF(B4="100M",5500,IF(B4="500M",9900,13200)),0)</f>
         <v/>
       </c>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="C25" s="17" t="inlineStr">
         <is>
           <t>→ 14_LGU_Chweyswun · 단독가 REPLACE</t>
         </is>
@@ -5408,11 +7265,11 @@
           <t xml:space="preserve">  [참쉬운] 휴대폰 인당 할인</t>
         </is>
       </c>
-      <c r="B26" s="16">
+      <c r="B26" s="19">
         <f>IF(B6="참쉬운 가족결합",CHOOSE(B7,CHOOSE(MIN(B8,4)-1,2200,3300,4400),CHOOSE(MIN(B8,4)-1,3300,5500,6600),CHOOSE(MIN(B8,4)-1,4400,6600,8800)),0)</f>
         <v/>
       </c>
-      <c r="C26" s="14" t="inlineStr">
+      <c r="C26" s="17" t="inlineStr">
         <is>
           <t>→ 14_LGU_Chweyswun · 요금구간 × 회선수</t>
         </is>
@@ -5424,11 +7281,11 @@
           <t xml:space="preserve">  [참쉬운] 휴대폰 총 할인</t>
         </is>
       </c>
-      <c r="B27" s="16">
+      <c r="B27" s="19">
         <f>B26*IF(B6="참쉬운 가족결합",MIN(B8,4),0)</f>
         <v/>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C27" s="17" t="inlineStr">
         <is>
           <t>인당 × min(회선수,4)</t>
         </is>
@@ -5440,11 +7297,11 @@
           <t xml:space="preserve">  [투게더] 인터넷 할인</t>
         </is>
       </c>
-      <c r="B28" s="16">
+      <c r="B28" s="19">
         <f>IF(B6="투게더 결합",IF(B4="100M",0,11000),0)</f>
         <v/>
       </c>
-      <c r="C28" s="14" t="inlineStr">
+      <c r="C28" s="17" t="inlineStr">
         <is>
           <t>→ 15_LGU_Together · 100M 결합불가 · 단독가 REPLACE</t>
         </is>
@@ -5456,11 +7313,11 @@
           <t xml:space="preserve">  [투게더] 휴대폰 인당 할인</t>
         </is>
       </c>
-      <c r="B29" s="16">
+      <c r="B29" s="19">
         <f>IF(B6="투게더 결합",CHOOSE(MIN(B8,4)-1,10000,14000,20000),0)</f>
         <v/>
       </c>
-      <c r="C29" s="14" t="inlineStr">
+      <c r="C29" s="17" t="inlineStr">
         <is>
           <t>→ 15_LGU_Together · 2/3/4+ 회선</t>
         </is>
@@ -5472,23 +7329,23 @@
           <t xml:space="preserve">  [투게더] 휴대폰 총 할인</t>
         </is>
       </c>
-      <c r="B30" s="16">
+      <c r="B30" s="19">
         <f>B29*IF(B6="투게더 결합",MIN(B8,5),0)</f>
         <v/>
       </c>
-      <c r="C30" s="14" t="inlineStr">
+      <c r="C30" s="17" t="inlineStr">
         <is>
           <t>인당 × 회선수</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="17" t="inlineStr">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">  = 인터넷+TV 월 실납부 (결합 적용)</t>
         </is>
       </c>
-      <c r="B32" s="28">
+      <c r="B32" s="31">
         <f>(B15-B25-B28)+IF(B12=0,0,B16-B17+B19)</f>
         <v/>
       </c>
@@ -5499,24 +7356,24 @@
           <t xml:space="preserve">  - 휴대폰 고지서 별도 차감</t>
         </is>
       </c>
-      <c r="B33" s="30">
+      <c r="B33" s="33">
         <f>-(B27+B30)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="17" t="inlineStr">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>🎉 혜택가 (최종 월요금)</t>
         </is>
       </c>
-      <c r="B34" s="31">
+      <c r="B34" s="34">
         <f>IF(B6="결합없음",B22,B32-(B27+B30))</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="18" t="inlineStr">
         <is>
           <t>🎁 부가</t>
         </is>
@@ -5528,11 +7385,11 @@
           <t xml:space="preserve">  설치비</t>
         </is>
       </c>
-      <c r="B37" s="16">
+      <c r="B37" s="19">
         <f>IF(B12=0,36300,56100)</f>
         <v/>
       </c>
-      <c r="C37" s="14" t="inlineStr">
+      <c r="C37" s="17" t="inlineStr">
         <is>
           <t>→ 06_Install</t>
         </is>
@@ -5544,11 +7401,11 @@
           <t xml:space="preserve">  사은품</t>
         </is>
       </c>
-      <c r="B38" s="16">
+      <c r="B38" s="19">
         <f>IF(B12=0,IF(B4="100M",200000,230000),CHOOSE(MATCH(B4,{"100M","500M","1G"},0),400000,470000,470000))</f>
         <v/>
       </c>
-      <c r="C38" s="14" t="inlineStr">
+      <c r="C38" s="17" t="inlineStr">
         <is>
           <t>→ 07_Gift</t>
         </is>
@@ -6402,7 +8259,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="32" t="inlineStr">
+      <c r="A3" s="35" t="inlineStr">
         <is>
           <t>💬 기본값(isDefault): 매장 판매 1위 + 가격/기능 균형 · 가입 시 자동 설정 · 요금 계산 기본</t>
         </is>
@@ -6831,7 +8688,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="32" t="inlineStr">
+      <c r="A3" s="35" t="inlineStr">
         <is>
           <t>💬 기본값: 속도별 단가가 낮은 표준 모델 · 가입 시 자동 지급 · 요금 계산 대상</t>
         </is>

--- a/docs/bongi-calculator-data.xlsx
+++ b/docs/bongi-calculator-data.xlsx
@@ -215,6 +215,12 @@
       <sz val="14"/>
     </font>
     <font>
+      <name val="Noto Sans KR"/>
+      <b val="1"/>
+      <color rgb="00dc2626"/>
+      <sz val="12"/>
+    </font>
+    <font>
       <name val="SF Mono"/>
       <color rgb="001a2744"/>
       <sz val="10"/>
@@ -261,12 +267,6 @@
       <b val="1"/>
       <color rgb="00e40981"/>
       <sz val="13"/>
-    </font>
-    <font>
-      <name val="Noto Sans KR"/>
-      <b val="1"/>
-      <color rgb="00dc2626"/>
-      <sz val="12"/>
     </font>
   </fonts>
   <fills count="12">
@@ -353,7 +353,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -431,25 +431,27 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2360,7 +2362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2790,9 +2792,9 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="inlineStr">
-        <is>
-          <t>📌 휴대폰 인당 할인 (개발 참조)</t>
+      <c r="A28" s="22" t="inlineStr">
+        <is>
+          <t>📌 휴대폰 인당 할인 (개발 참조 · ⚠️ 비선형 변화 주의)</t>
         </is>
       </c>
     </row>
@@ -2873,366 +2875,538 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="A33" s="39" t="inlineStr">
+        <is>
+          <t>⚠️ 매우 중요 — 인당 할인은 회선수에 따라 비선형적으로 변함</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="40" t="inlineStr">
+        <is>
+          <t>📍 근본 원리: "총 할인액 고정 후 회선수로 분배" 방식</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="40" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="40" t="inlineStr">
+        <is>
+          <t>💡 100M (메가급):</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 1회선 → 3,500원 (총 3,500)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 2회선 → 인당 3,500원 (총 7,000) ← 개별 계산</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 3회선부터 총 18,000원 고정 분배:</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       - 3회선: 18,000 ÷ 3 = 인당 6,000원 ★ 점프 구간 ★</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       - 4회선: 18,000 ÷ 4 = 인당 4,500원</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       - 5회선: 18,000 ÷ 5 = 인당 3,600원</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="40" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="40" t="inlineStr">
+        <is>
+          <t>💡 500M·1G (기가급):</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 1~2회선 → 인당 3,500원 (100M과 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 3회선 → 총 18,000 ÷ 3 = 인당 6,000원</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 4~5회선부터 총 24,000원 고정 분배:</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       - 4회선: 24,000 ÷ 4 = 인당 6,000원</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       - 5회선: 24,000 ÷ 5 = 인당 4,800원</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="40" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="40" t="inlineStr">
+        <is>
+          <t>🔑 개발 시 주의사항:</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - 인당 × 회선수 ≠ 단순 선형 계산</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - 단순히 "회선수 증가 시 인당 증가" 로직 작성 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - 반드시 상수 테이블로 접근 (mobilePerBySpeed[speed][lines])</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - 또는 총합 테이블(mobileTotalBySpeed[speed][lines])로 처리 가능</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>③ 계산 알고리즘 (의사코드)</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="39" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="41" t="inlineStr">
         <is>
           <t>// 입력: speed, tvIdx, wifi(bool), lines(1~5)</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="39" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="39" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="41" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="41" t="inlineStr">
         <is>
           <t>1. 단독가 기준으로 재계산 (요즘우리집 REPLACE):</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="39" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">   netSingle = internet[speed] + (wifi ? wifiCost : 0)  // SKT wifiCost=1100</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="39" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">   famInet = bundle.family.internet[speed]</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="39" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">   inetAfter = netSingle - famInet</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="39" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="39" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="41" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="41" t="inlineStr">
         <is>
           <t>2. TV 결합 시:</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="39" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">   famIptv = hasTv ? bundle.family.iptv : 0  // iptv=1100</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="39" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">   tvAfter = tv[tvIdx].p - tv[tvIdx].dc - famIptv</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="39" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">   monthlyFee = inetAfter + tvAfter + setTop</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="39" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="39" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="41" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="41" t="inlineStr">
         <is>
           <t>3. 휴대폰 별도 차감 (월):</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="39" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">   perPerson = bundle.family.mobilePerBySpeed[speed][lines]</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="39" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">   mobileDiscount = perPerson × lines  // 고지서에서 차감</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="39" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="39" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="41" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="41" t="inlineStr">
         <is>
           <t>4. 혜택가:</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="39" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">   finalFee = monthlyFee - mobileDiscount</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
         <is>
           <t>④ 검증 예시 — 500M + B tv 올 + WiFi X + 3회선</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B54" s="4" t="inlineStr">
+      <c r="B78" s="4" t="inlineStr">
         <is>
           <t>계산</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
+      <c r="C78" s="4" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="38" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="38" t="inlineStr">
         <is>
           <t>단독가</t>
         </is>
       </c>
-      <c r="B55" s="38" t="inlineStr">
+      <c r="B79" s="38" t="inlineStr">
         <is>
           <t>33,000 + 0</t>
         </is>
       </c>
-      <c r="C55" s="38" t="inlineStr">
+      <c r="C79" s="38" t="inlineStr">
         <is>
           <t>33,000</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="38" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="38" t="inlineStr">
         <is>
           <t>요즘가족 인터넷 할인</t>
         </is>
       </c>
-      <c r="B56" s="38" t="inlineStr">
+      <c r="B80" s="38" t="inlineStr">
         <is>
           <t>-11,000</t>
         </is>
       </c>
-      <c r="C56" s="38" t="inlineStr">
+      <c r="C80" s="38" t="inlineStr">
         <is>
           <t>-11,000</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="38" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="38" t="inlineStr">
         <is>
           <t>인터넷 실질</t>
         </is>
       </c>
-      <c r="B57" s="38" t="inlineStr">
+      <c r="B81" s="38" t="inlineStr">
         <is>
           <t>33,000 - 11,000</t>
         </is>
       </c>
-      <c r="C57" s="38" t="inlineStr">
+      <c r="C81" s="38" t="inlineStr">
         <is>
           <t>22,000</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="38" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="38" t="inlineStr">
         <is>
           <t>TV 기본 (B tv 올)</t>
         </is>
       </c>
-      <c r="B58" s="38" t="inlineStr">
+      <c r="B82" s="38" t="inlineStr">
         <is>
           <t>18,700</t>
         </is>
       </c>
-      <c r="C58" s="38" t="inlineStr">
+      <c r="C82" s="38" t="inlineStr">
         <is>
           <t>18,700</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="38" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="38" t="inlineStr">
         <is>
           <t>TV 결합할인 + IPTV</t>
         </is>
       </c>
-      <c r="B59" s="38" t="inlineStr">
+      <c r="B83" s="38" t="inlineStr">
         <is>
           <t>-2,200 + -1,100</t>
         </is>
       </c>
-      <c r="C59" s="38" t="inlineStr">
+      <c r="C83" s="38" t="inlineStr">
         <is>
           <t>-3,300</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="38" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="38" t="inlineStr">
         <is>
           <t>TV 실질</t>
         </is>
       </c>
-      <c r="B60" s="38" t="inlineStr">
+      <c r="B84" s="38" t="inlineStr">
         <is>
           <t>18,700 - 3,300</t>
         </is>
       </c>
-      <c r="C60" s="38" t="inlineStr">
+      <c r="C84" s="38" t="inlineStr">
         <is>
           <t>15,400</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="38" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="38" t="inlineStr">
         <is>
           <t>셋톱 (스마트3)</t>
         </is>
       </c>
-      <c r="B61" s="38" t="inlineStr">
+      <c r="B85" s="38" t="inlineStr">
         <is>
           <t>4,400</t>
         </is>
       </c>
-      <c r="C61" s="38" t="inlineStr">
+      <c r="C85" s="38" t="inlineStr">
         <is>
           <t>4,400</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="38">
+    <row r="86">
+      <c r="A86" s="38">
         <f> 월 실납부</f>
         <v/>
       </c>
-      <c r="B62" s="38" t="inlineStr">
+      <c r="B86" s="38" t="inlineStr">
         <is>
           <t>22,000 + 15,400 + 4,400</t>
         </is>
       </c>
-      <c r="C62" s="38" t="inlineStr">
+      <c r="C86" s="38" t="inlineStr">
         <is>
           <t>41,800</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="38" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="38" t="inlineStr">
         <is>
           <t>휴대폰 3회선 × 6,000</t>
         </is>
       </c>
-      <c r="B63" s="38" t="inlineStr">
+      <c r="B87" s="38" t="inlineStr">
         <is>
           <t>-18,000</t>
         </is>
       </c>
-      <c r="C63" s="38" t="inlineStr">
+      <c r="C87" s="38" t="inlineStr">
         <is>
           <t>-18,000</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="38" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="38" t="inlineStr">
         <is>
           <t>🎉 혜택가</t>
         </is>
       </c>
-      <c r="B64" s="38" t="inlineStr">
+      <c r="B88" s="38" t="inlineStr">
         <is>
           <t>41,800 - 18,000</t>
         </is>
       </c>
-      <c r="C64" s="38" t="inlineStr">
+      <c r="C88" s="38" t="inlineStr">
         <is>
           <t>23,800</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="6" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
         <is>
           <t>⑤ 참고자료</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="40" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="42" t="inlineStr">
         <is>
           <t>🔗 백메가 SK 상품 전체 안내 (결합할인 원본)</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="10" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">    URL: https://www.100mb.kr/01_product/sk.php</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="48">
     <mergeCell ref="A41:F41"/>
+    <mergeCell ref="A54:F54"/>
     <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A66:F66"/>
     <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A75:F75"/>
+    <mergeCell ref="A74:F74"/>
     <mergeCell ref="A50:F50"/>
+    <mergeCell ref="A55:F55"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A71:F71"/>
     <mergeCell ref="A47:F47"/>
     <mergeCell ref="A42:F42"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A35:F35"/>
     <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A62:F62"/>
+    <mergeCell ref="A53:F53"/>
+    <mergeCell ref="A72:F72"/>
+    <mergeCell ref="A91:F91"/>
     <mergeCell ref="A43:F43"/>
     <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="A52:F52"/>
     <mergeCell ref="A68:F68"/>
     <mergeCell ref="A44:F44"/>
     <mergeCell ref="A67:F67"/>
+    <mergeCell ref="A58:F58"/>
     <mergeCell ref="A34:F34"/>
     <mergeCell ref="A40:F40"/>
     <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A92:F92"/>
     <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A64:F64"/>
+    <mergeCell ref="A59:F59"/>
+    <mergeCell ref="A73:F73"/>
     <mergeCell ref="A49:F49"/>
     <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A60:F60"/>
     <mergeCell ref="A36:F36"/>
     <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A70:F70"/>
+    <mergeCell ref="A61:F61"/>
     <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A69:F69"/>
     <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A65:F65"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3244,429 +3418,616 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="41" t="inlineStr">
-        <is>
-          <t>🏷️ KT 총액결합 (STACK)</t>
+      <c r="A1" s="43" t="inlineStr">
+        <is>
+          <t>🏷️ KT 총액결합 (STACK 방식)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>① 특성 및 주의사항</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="37" t="inlineStr">
+        <is>
+          <t>▶ 적용 방식: STACK (중복 적용) — 기본 TV결합 할인 + 총액할인 같이 적용</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="37" t="inlineStr">
+        <is>
+          <t>▶ SKT/LGU+ REPLACE와 반대 — 기존 tvInternetNoWifi/WithWifi 값 그대로 유지</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="37" t="inlineStr">
+        <is>
+          <t>▶ ⚠️ 22,000원 이하 / 이상 2구간은 휴대폰 할인 0원 (인터넷만 할인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="37" t="inlineStr">
+        <is>
+          <t>▶ ⚠️ 100M (메가급) vs 500M·1G (기가급) 인터넷 할인 금액 다름</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="37" t="inlineStr">
+        <is>
+          <t>▶ 휴대폰 할인은 100M vs 500M·1G로 테이블 구분</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="37" t="inlineStr">
+        <is>
+          <t>▶ 1G 이상이면 WiFi 무료 → tvInternetWithWifi = tvInternetNoWifi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>② 할인 테이블 (18 조합)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>속도</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>구간</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>인터넷</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>휴대폰</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="42" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="44" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B4" s="42" t="inlineStr">
+      <c r="B13" s="44" t="inlineStr">
         <is>
           <t>22K 이하</t>
         </is>
       </c>
-      <c r="C4" s="42" t="n">
+      <c r="C13" s="44" t="n">
         <v>1650</v>
       </c>
-      <c r="D4" s="42" t="n">
+      <c r="D13" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="42" t="n">
+      <c r="E13" s="44" t="n">
         <v>1650</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="42" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="44" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B5" s="42" t="inlineStr">
+      <c r="B14" s="44" t="inlineStr">
         <is>
           <t>22K 이상</t>
         </is>
       </c>
-      <c r="C5" s="42" t="n">
+      <c r="C14" s="44" t="n">
         <v>3300</v>
       </c>
-      <c r="D5" s="42" t="n">
+      <c r="D14" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="42" t="n">
+      <c r="E14" s="44" t="n">
         <v>3300</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="42" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="44" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B6" s="42" t="inlineStr">
+      <c r="B15" s="44" t="inlineStr">
         <is>
           <t>64.9K 이상</t>
         </is>
       </c>
-      <c r="C6" s="42" t="n">
+      <c r="C15" s="44" t="n">
         <v>5500</v>
       </c>
-      <c r="D6" s="42" t="n">
+      <c r="D15" s="44" t="n">
         <v>3300</v>
       </c>
-      <c r="E6" s="42" t="n">
+      <c r="E15" s="44" t="n">
         <v>8800</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="42" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="44" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B7" s="42" t="inlineStr">
+      <c r="B16" s="44" t="inlineStr">
         <is>
           <t>108.9K 이상</t>
         </is>
       </c>
-      <c r="C7" s="42" t="n">
+      <c r="C16" s="44" t="n">
         <v>5500</v>
       </c>
-      <c r="D7" s="42" t="n">
+      <c r="D16" s="44" t="n">
         <v>14300</v>
       </c>
-      <c r="E7" s="42" t="n">
+      <c r="E16" s="44" t="n">
         <v>19800</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="42" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="44" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B8" s="42" t="inlineStr">
+      <c r="B17" s="44" t="inlineStr">
         <is>
           <t>141.9K 이상</t>
         </is>
       </c>
-      <c r="C8" s="42" t="n">
+      <c r="C17" s="44" t="n">
         <v>5500</v>
       </c>
-      <c r="D8" s="42" t="n">
+      <c r="D17" s="44" t="n">
         <v>18700</v>
       </c>
-      <c r="E8" s="42" t="n">
+      <c r="E17" s="44" t="n">
         <v>24200</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="42" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="44" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="B9" s="42" t="inlineStr">
+      <c r="B18" s="44" t="inlineStr">
         <is>
           <t>174.9K 이상</t>
         </is>
       </c>
-      <c r="C9" s="42" t="n">
+      <c r="C18" s="44" t="n">
         <v>5500</v>
       </c>
-      <c r="D9" s="42" t="n">
+      <c r="D18" s="44" t="n">
         <v>23100</v>
       </c>
-      <c r="E9" s="42" t="n">
+      <c r="E18" s="44" t="n">
         <v>28600</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="42" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="44" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B10" s="42" t="inlineStr">
+      <c r="B19" s="44" t="inlineStr">
         <is>
           <t>22K 이하</t>
         </is>
       </c>
-      <c r="C10" s="42" t="n">
+      <c r="C19" s="44" t="n">
         <v>2200</v>
       </c>
-      <c r="D10" s="42" t="n">
+      <c r="D19" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="42" t="n">
+      <c r="E19" s="44" t="n">
         <v>2200</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="42" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="44" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B11" s="42" t="inlineStr">
+      <c r="B20" s="44" t="inlineStr">
         <is>
           <t>22K 이상</t>
         </is>
       </c>
-      <c r="C11" s="42" t="n">
+      <c r="C20" s="44" t="n">
         <v>5500</v>
       </c>
-      <c r="D11" s="42" t="n">
+      <c r="D20" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="42" t="n">
+      <c r="E20" s="44" t="n">
         <v>5500</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="42" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="44" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B12" s="42" t="inlineStr">
+      <c r="B21" s="44" t="inlineStr">
         <is>
           <t>64.9K 이상</t>
         </is>
       </c>
-      <c r="C12" s="42" t="n">
+      <c r="C21" s="44" t="n">
         <v>5500</v>
       </c>
-      <c r="D12" s="42" t="n">
+      <c r="D21" s="44" t="n">
         <v>5500</v>
       </c>
-      <c r="E12" s="42" t="n">
+      <c r="E21" s="44" t="n">
         <v>11000</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="42" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="44" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B13" s="42" t="inlineStr">
+      <c r="B22" s="44" t="inlineStr">
         <is>
           <t>108.9K 이상</t>
         </is>
       </c>
-      <c r="C13" s="42" t="n">
+      <c r="C22" s="44" t="n">
         <v>5500</v>
       </c>
-      <c r="D13" s="42" t="n">
+      <c r="D22" s="44" t="n">
         <v>16610</v>
       </c>
-      <c r="E13" s="42" t="n">
+      <c r="E22" s="44" t="n">
         <v>22110</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="42" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="44" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B14" s="42" t="inlineStr">
+      <c r="B23" s="44" t="inlineStr">
         <is>
           <t>141.9K 이상</t>
         </is>
       </c>
-      <c r="C14" s="42" t="n">
+      <c r="C23" s="44" t="n">
         <v>5500</v>
       </c>
-      <c r="D14" s="42" t="n">
+      <c r="D23" s="44" t="n">
         <v>22110</v>
       </c>
-      <c r="E14" s="42" t="n">
+      <c r="E23" s="44" t="n">
         <v>27610</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="42" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="44" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="B15" s="42" t="inlineStr">
+      <c r="B24" s="44" t="inlineStr">
         <is>
           <t>174.9K 이상</t>
         </is>
       </c>
-      <c r="C15" s="42" t="n">
+      <c r="C24" s="44" t="n">
         <v>5500</v>
       </c>
-      <c r="D15" s="42" t="n">
+      <c r="D24" s="44" t="n">
         <v>27610</v>
       </c>
-      <c r="E15" s="42" t="n">
+      <c r="E24" s="44" t="n">
         <v>33110</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="42" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="44" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B16" s="42" t="inlineStr">
+      <c r="B25" s="44" t="inlineStr">
         <is>
           <t>22K 이하</t>
         </is>
       </c>
-      <c r="C16" s="42" t="n">
+      <c r="C25" s="44" t="n">
         <v>2200</v>
       </c>
-      <c r="D16" s="42" t="n">
+      <c r="D25" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="42" t="n">
+      <c r="E25" s="44" t="n">
         <v>2200</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="42" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="44" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B17" s="42" t="inlineStr">
+      <c r="B26" s="44" t="inlineStr">
         <is>
           <t>22K 이상</t>
         </is>
       </c>
-      <c r="C17" s="42" t="n">
+      <c r="C26" s="44" t="n">
         <v>5500</v>
       </c>
-      <c r="D17" s="42" t="n">
+      <c r="D26" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="42" t="n">
+      <c r="E26" s="44" t="n">
         <v>5500</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="42" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="44" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B18" s="42" t="inlineStr">
+      <c r="B27" s="44" t="inlineStr">
         <is>
           <t>64.9K 이상</t>
         </is>
       </c>
-      <c r="C18" s="42" t="n">
+      <c r="C27" s="44" t="n">
         <v>5500</v>
       </c>
-      <c r="D18" s="42" t="n">
+      <c r="D27" s="44" t="n">
         <v>5500</v>
       </c>
-      <c r="E18" s="42" t="n">
+      <c r="E27" s="44" t="n">
         <v>11000</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="42" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="44" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B19" s="42" t="inlineStr">
+      <c r="B28" s="44" t="inlineStr">
         <is>
           <t>108.9K 이상</t>
         </is>
       </c>
-      <c r="C19" s="42" t="n">
+      <c r="C28" s="44" t="n">
         <v>5500</v>
       </c>
-      <c r="D19" s="42" t="n">
+      <c r="D28" s="44" t="n">
         <v>16610</v>
       </c>
-      <c r="E19" s="42" t="n">
+      <c r="E28" s="44" t="n">
         <v>22110</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="42" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="44" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B20" s="42" t="inlineStr">
+      <c r="B29" s="44" t="inlineStr">
         <is>
           <t>141.9K 이상</t>
         </is>
       </c>
-      <c r="C20" s="42" t="n">
+      <c r="C29" s="44" t="n">
         <v>5500</v>
       </c>
-      <c r="D20" s="42" t="n">
+      <c r="D29" s="44" t="n">
         <v>22110</v>
       </c>
-      <c r="E20" s="42" t="n">
+      <c r="E29" s="44" t="n">
         <v>27610</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="42" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="44" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
-      <c r="B21" s="42" t="inlineStr">
+      <c r="B30" s="44" t="inlineStr">
         <is>
           <t>174.9K 이상</t>
         </is>
       </c>
-      <c r="C21" s="42" t="n">
+      <c r="C30" s="44" t="n">
         <v>5500</v>
       </c>
-      <c r="D21" s="42" t="n">
+      <c r="D30" s="44" t="n">
         <v>27610</v>
       </c>
-      <c r="E21" s="42" t="n">
+      <c r="E30" s="44" t="n">
         <v>33110</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>③ 계산 알고리즘</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="41" t="inlineStr">
+        <is>
+          <t>// KT STACK: 기본 TV결합 할인 + 총액할인 추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="41" t="inlineStr">
+        <is>
+          <t>1. 기본 월요금 (PATH_A 유지)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   monthlyBase = (hasTv ? tvInternet[wifi][speed] : internet[speed] + wifiFee)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                + (hasTv ? tv.p - tv.dc + setTop : 0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="41" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="41" t="inlineStr">
+        <is>
+          <t>2. 총액결합 구간 선택 (rangeIdx: 1~6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ※ 사용자가 직접 선택 (휴대폰 합산 요금 기반)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="41" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="41" t="inlineStr">
+        <is>
+          <t>3. 추가 할인:</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   inetDc = bundle.total.internet[speed][rangeIdx]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   mobDc  = bundle.total.mobile[speed][rangeIdx]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="41" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="41" t="inlineStr">
+        <is>
+          <t>4. 최종:</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   monthlyFee = monthlyBase - inetDc   // 인터넷+TV 청구</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   mobileDc   = mobDc                  // 휴대폰 고지서 별도</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   finalFee   = monthlyFee - mobileDc</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="22">
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A9:E9"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3677,7 +4038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3687,99 +4048,155 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="41" t="inlineStr">
-        <is>
-          <t>🏷️ KT 정액결합</t>
+      <c r="A1" s="43" t="inlineStr">
+        <is>
+          <t>🏷️ KT 정액결합 (간단형)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>① 특성 및 주의사항</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="37" t="inlineStr">
+        <is>
+          <t>▶ 적용 방식: STACK (총액결합과 동일, 기본 TV결합에 추가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="37" t="inlineStr">
+        <is>
+          <t>▶ 인터넷 할인: 전 구간 -5,500원 고정 (변동 없음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="37" t="inlineStr">
+        <is>
+          <t>▶ ⚠️ 37,000원 이하 구간은 휴대폰 할인 0원 (인터넷만)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="37" t="inlineStr">
+        <is>
+          <t>▶ 총액결합과의 차이: 4구간만 존재 / 속도 무관 / 인터넷 단일값</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="37" t="inlineStr">
+        <is>
+          <t>▶ 총액결합보다 할인액 작음 → 통상 총액결합이 유리</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>② 할인 테이블 (4구간)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>구간</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>인터넷</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>휴대폰</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="42" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="44" t="inlineStr">
         <is>
           <t>37K 이하</t>
         </is>
       </c>
-      <c r="B4" s="42" t="n">
+      <c r="B12" s="44" t="n">
         <v>5500</v>
       </c>
-      <c r="C4" s="42" t="n">
+      <c r="C12" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="42" t="n">
+      <c r="D12" s="44" t="n">
         <v>5500</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="42" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="44" t="inlineStr">
         <is>
           <t>37K 이상</t>
         </is>
       </c>
-      <c r="B5" s="42" t="n">
+      <c r="B13" s="44" t="n">
         <v>5500</v>
       </c>
-      <c r="C5" s="42" t="n">
+      <c r="C13" s="44" t="n">
         <v>3000</v>
       </c>
-      <c r="D5" s="42" t="n">
+      <c r="D13" s="44" t="n">
         <v>8500</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="42" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="44" t="inlineStr">
         <is>
           <t>61K 이상</t>
         </is>
       </c>
-      <c r="B6" s="42" t="n">
+      <c r="B14" s="44" t="n">
         <v>5500</v>
       </c>
-      <c r="C6" s="42" t="n">
+      <c r="C14" s="44" t="n">
         <v>5000</v>
       </c>
-      <c r="D6" s="42" t="n">
+      <c r="D14" s="44" t="n">
         <v>10500</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="42" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="44" t="inlineStr">
         <is>
           <t>77K 이상</t>
         </is>
       </c>
-      <c r="B7" s="42" t="n">
+      <c r="B15" s="44" t="n">
         <v>5500</v>
       </c>
-      <c r="C7" s="42" t="n">
+      <c r="C15" s="44" t="n">
         <v>7000</v>
       </c>
-      <c r="D7" s="42" t="n">
+      <c r="D15" s="44" t="n">
         <v>12500</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A7:D7"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3802,14 +4219,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="43" t="inlineStr">
+      <c r="A1" s="45" t="inlineStr">
         <is>
           <t>💎 KT 프리미엄 가족결합 (완전 명세서)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="44" t="inlineStr">
+      <c r="A3" s="46" t="inlineStr">
         <is>
           <t>① 자격 조건</t>
         </is>
@@ -3844,7 +4261,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="44" t="inlineStr">
+      <c r="A9" s="46" t="inlineStr">
         <is>
           <t>② 회선별 분배 규칙 (누가 어디 속하는가)</t>
         </is>
@@ -3961,7 +4378,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="44" t="inlineStr">
+      <c r="A16" s="46" t="inlineStr">
         <is>
           <t>③ 요금제 카탈로그 (원본 planCatalog 14종)</t>
         </is>
@@ -3995,529 +4412,529 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="45" t="n">
+      <c r="A18" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="B18" s="45" t="inlineStr">
+      <c r="B18" s="47" t="inlineStr">
         <is>
           <t>— 회선 없음 —</t>
         </is>
       </c>
-      <c r="C18" s="45" t="inlineStr">
+      <c r="C18" s="47" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D18" s="45" t="n">
+      <c r="D18" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="45" t="inlineStr">
+      <c r="E18" s="47" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="45" t="n">
+      <c r="A19" s="47" t="n">
         <v>32890</v>
       </c>
-      <c r="B19" s="45" t="inlineStr">
+      <c r="B19" s="47" t="inlineStr">
         <is>
           <t>32,890원 (LTE 데이터선택)</t>
         </is>
       </c>
-      <c r="C19" s="45" t="inlineStr">
+      <c r="C19" s="47" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D19" s="45" t="n">
+      <c r="D19" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="E19" s="45" t="inlineStr">
+      <c r="E19" s="47" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="45" t="n">
+      <c r="A20" s="47" t="n">
         <v>47000</v>
       </c>
-      <c r="B20" s="45" t="inlineStr">
+      <c r="B20" s="47" t="inlineStr">
         <is>
           <t>47,000원</t>
         </is>
       </c>
-      <c r="C20" s="45" t="inlineStr">
+      <c r="C20" s="47" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D20" s="45" t="n">
+      <c r="D20" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="45" t="inlineStr">
+      <c r="E20" s="47" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="45" t="n">
+      <c r="A21" s="47" t="n">
         <v>55000</v>
       </c>
-      <c r="B21" s="45" t="inlineStr">
+      <c r="B21" s="47" t="inlineStr">
         <is>
           <t>55,000원</t>
         </is>
       </c>
-      <c r="C21" s="45" t="inlineStr">
+      <c r="C21" s="47" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D21" s="45" t="n">
+      <c r="D21" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="45" t="inlineStr">
+      <c r="E21" s="47" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="45" t="n">
+      <c r="A22" s="47" t="n">
         <v>65000</v>
       </c>
-      <c r="B22" s="45" t="inlineStr">
+      <c r="B22" s="47" t="inlineStr">
         <is>
           <t>65,000원</t>
         </is>
       </c>
-      <c r="C22" s="45" t="inlineStr">
+      <c r="C22" s="47" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D22" s="45" t="n">
+      <c r="D22" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="E22" s="45" t="inlineStr">
+      <c r="E22" s="47" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="45" t="n">
+      <c r="A23" s="47" t="n">
         <v>77000</v>
       </c>
-      <c r="B23" s="45" t="inlineStr">
+      <c r="B23" s="47" t="inlineStr">
         <is>
           <t>77,000원 (임계값)</t>
         </is>
       </c>
-      <c r="C23" s="45" t="inlineStr">
+      <c r="C23" s="47" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D23" s="45" t="n">
+      <c r="D23" s="47" t="n">
         <v>19250</v>
       </c>
-      <c r="E23" s="45" t="inlineStr">
+      <c r="E23" s="47" t="inlineStr">
         <is>
           <t>≈25%</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="45" t="n">
+      <c r="A24" s="47" t="n">
         <v>80000</v>
       </c>
-      <c r="B24" s="45" t="inlineStr">
+      <c r="B24" s="47" t="inlineStr">
         <is>
           <t>80,000원 (5G 슈퍼플랜 베이직)</t>
         </is>
       </c>
-      <c r="C24" s="45" t="inlineStr">
+      <c r="C24" s="47" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D24" s="45" t="n">
+      <c r="D24" s="47" t="n">
         <v>20000</v>
       </c>
-      <c r="E24" s="45" t="inlineStr">
+      <c r="E24" s="47" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="45" t="n">
+      <c r="A25" s="47" t="n">
         <v>87890</v>
       </c>
-      <c r="B25" s="45" t="inlineStr">
+      <c r="B25" s="47" t="inlineStr">
         <is>
           <t>87,890원 (데이터선택 87.8)</t>
         </is>
       </c>
-      <c r="C25" s="45" t="inlineStr">
+      <c r="C25" s="47" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D25" s="45" t="n">
+      <c r="D25" s="47" t="n">
         <v>22000</v>
       </c>
-      <c r="E25" s="45" t="inlineStr">
+      <c r="E25" s="47" t="inlineStr">
         <is>
           <t>≈25%</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="45" t="n">
+      <c r="A26" s="47" t="n">
         <v>89000</v>
       </c>
-      <c r="B26" s="45" t="inlineStr">
+      <c r="B26" s="47" t="inlineStr">
         <is>
           <t>89,000원 (데이터ON 프리미엄)</t>
         </is>
       </c>
-      <c r="C26" s="45" t="inlineStr">
+      <c r="C26" s="47" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D26" s="45" t="n">
+      <c r="D26" s="47" t="n">
         <v>22250</v>
       </c>
-      <c r="E26" s="45" t="inlineStr">
+      <c r="E26" s="47" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="45" t="n">
+      <c r="A27" s="47" t="n">
         <v>90000</v>
       </c>
-      <c r="B27" s="45" t="inlineStr">
+      <c r="B27" s="47" t="inlineStr">
         <is>
           <t>90,000원 (슈퍼플랜 베이직 Plus/초이스)</t>
         </is>
       </c>
-      <c r="C27" s="45" t="inlineStr">
+      <c r="C27" s="47" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D27" s="45" t="n">
+      <c r="D27" s="47" t="n">
         <v>22500</v>
       </c>
-      <c r="E27" s="45" t="inlineStr">
+      <c r="E27" s="47" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="45" t="n">
+      <c r="A28" s="47" t="n">
         <v>100000</v>
       </c>
-      <c r="B28" s="45" t="inlineStr">
+      <c r="B28" s="47" t="inlineStr">
         <is>
           <t>100,000원 (슈퍼플랜 스페셜)</t>
         </is>
       </c>
-      <c r="C28" s="45" t="inlineStr">
+      <c r="C28" s="47" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D28" s="45" t="n">
+      <c r="D28" s="47" t="n">
         <v>25000</v>
       </c>
-      <c r="E28" s="45" t="inlineStr">
+      <c r="E28" s="47" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="45" t="n">
+      <c r="A29" s="47" t="n">
         <v>109000</v>
       </c>
-      <c r="B29" s="45" t="inlineStr">
+      <c r="B29" s="47" t="inlineStr">
         <is>
           <t>109,000원 (데이터선택 109)</t>
         </is>
       </c>
-      <c r="C29" s="45" t="inlineStr">
+      <c r="C29" s="47" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D29" s="45" t="n">
+      <c r="D29" s="47" t="n">
         <v>27500</v>
       </c>
-      <c r="E29" s="45" t="inlineStr">
+      <c r="E29" s="47" t="inlineStr">
         <is>
           <t>≈25%</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="45" t="n">
+      <c r="A30" s="47" t="n">
         <v>110000</v>
       </c>
-      <c r="B30" s="45" t="inlineStr">
+      <c r="B30" s="47" t="inlineStr">
         <is>
           <t>110,000원 (슈퍼플랜 스페셜 Plus/초이스)</t>
         </is>
       </c>
-      <c r="C30" s="45" t="inlineStr">
+      <c r="C30" s="47" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D30" s="45" t="n">
+      <c r="D30" s="47" t="n">
         <v>27500</v>
       </c>
-      <c r="E30" s="45" t="inlineStr">
+      <c r="E30" s="47" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="45" t="n">
+      <c r="A31" s="47" t="n">
         <v>130000</v>
       </c>
-      <c r="B31" s="45" t="inlineStr">
+      <c r="B31" s="47" t="inlineStr">
         <is>
           <t>130,000원 (슈퍼플랜 프리미엄/초이스)</t>
         </is>
       </c>
-      <c r="C31" s="45" t="inlineStr">
+      <c r="C31" s="47" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D31" s="45" t="n">
+      <c r="D31" s="47" t="n">
         <v>32500</v>
       </c>
-      <c r="E31" s="45" t="inlineStr">
+      <c r="E31" s="47" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="44" t="inlineStr">
+      <c r="A33" s="46" t="inlineStr">
         <is>
           <t>④ 계산 알고리즘 (의사코드)</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="39" t="inlineStr">
+      <c r="A34" s="41" t="inlineStr">
         <is>
           <t>// 입력: members: Array&lt;{ isRep: boolean, planV: number, usePrem?: boolean }&gt;</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="39" t="inlineStr">
+      <c r="A35" s="41" t="inlineStr">
         <is>
           <t>//      speed: "100M" | "500M" | "1G"</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="39" t="inlineStr"/>
+      <c r="A36" s="41" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="39" t="inlineStr">
+      <c r="A37" s="41" t="inlineStr">
         <is>
           <t>1. 자격 체크:</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="39" t="inlineStr">
+      <c r="A38" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">   highPlanCount = members.filter(m =&gt; m.planV &gt;= 77000).length</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="39" t="inlineStr">
+      <c r="A39" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">   IF highPlanCount &lt; 2 THEN 프리미엄 불가 (총액결합만 사용)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="39" t="inlineStr"/>
+      <c r="A40" s="41" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="39" t="inlineStr">
+      <c r="A41" s="41" t="inlineStr">
         <is>
           <t>2. 회선 분배:</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="39" t="inlineStr">
+      <c r="A42" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">   premMembers = members.filter(m =&gt; !m.isRep &amp;&amp; m.usePrem &amp;&amp; m.planV &gt;= 77000)</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="39" t="inlineStr">
+      <c r="A43" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">   totalMembers = members.filter(m =&gt; m.isRep || !m.usePrem || m.planV &lt; 77000)</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="39" t="inlineStr">
+      <c r="A44" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">   IF premMembers.length == 0 THEN 프리미엄 불가 (총액결합만 사용)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="39" t="inlineStr"/>
+      <c r="A45" s="41" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="39" t="inlineStr">
+      <c r="A46" s="41" t="inlineStr">
         <is>
           <t>3. 총액결합 합산액:</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="39" t="inlineStr">
+      <c r="A47" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">   totalSum = sum(totalMembers.map(m =&gt; m.planV))</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="39" t="inlineStr"/>
+      <c r="A48" s="41" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="39" t="inlineStr">
+      <c r="A49" s="41" t="inlineStr">
         <is>
           <t>4. 총액결합 구간 판정:</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="39" t="inlineStr">
+      <c r="A50" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">   rngIdx = 0 ~ 5</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="39" t="inlineStr">
+      <c r="A51" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">   if totalSum &gt;= 174900: rngIdx = 5</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="39" t="inlineStr">
+      <c r="A52" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">   else if totalSum &gt;= 141900: rngIdx = 4</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="39" t="inlineStr">
+      <c r="A53" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">   else if totalSum &gt;= 108900: rngIdx = 3</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="39" t="inlineStr">
+      <c r="A54" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">   else if totalSum &gt;= 64900:  rngIdx = 2</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="39" t="inlineStr">
+      <c r="A55" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">   else if totalSum &gt;= 22000:  rngIdx = 1</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="39" t="inlineStr">
+      <c r="A56" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">   else: rngIdx = 0</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="39" t="inlineStr"/>
+      <c r="A57" s="41" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="39" t="inlineStr">
+      <c r="A58" s="41" t="inlineStr">
         <is>
           <t>5. 할인 계산:</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="39" t="inlineStr">
+      <c r="A59" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">   inetFixedDc = 5500  // 인터넷 또는 대표자 휴대폰 (기본: 대표자 휴대폰)</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="39" t="inlineStr">
+      <c r="A60" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">   totalMobDc = kt.total.mobile[speed][rngIdx]</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="39" t="inlineStr">
+      <c r="A61" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">   premTotalDc = sum(premMembers.map(m =&gt; planCatalog[m.planV].dc))</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="39" t="inlineStr"/>
+      <c r="A62" s="41" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="39" t="inlineStr">
+      <c r="A63" s="41" t="inlineStr">
         <is>
           <t>6. 최종:</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="39" t="inlineStr">
+      <c r="A64" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">   totalDiscount = inetFixedDc + totalMobDc + premTotalDc</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="44" t="inlineStr">
+      <c r="A66" s="46" t="inlineStr">
         <is>
           <t>⑤ 검증 예시 1 — 100M + 3회선 (모두 89,000원)</t>
         </is>
@@ -4546,219 +4963,219 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="45" t="inlineStr">
+      <c r="A68" s="47" t="inlineStr">
         <is>
           <t>회선 1</t>
         </is>
       </c>
-      <c r="B68" s="45" t="inlineStr">
+      <c r="B68" s="47" t="inlineStr">
         <is>
           <t>대표자 89K (총액)</t>
         </is>
       </c>
-      <c r="C68" s="45" t="inlineStr">
+      <c r="C68" s="47" t="inlineStr">
         <is>
           <t>자동</t>
         </is>
       </c>
-      <c r="D68" s="45" t="inlineStr">
+      <c r="D68" s="47" t="inlineStr">
         <is>
           <t>대표자는 총액결합 대상</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="45" t="inlineStr">
+      <c r="A69" s="47" t="inlineStr">
         <is>
           <t>회선 2</t>
         </is>
       </c>
-      <c r="B69" s="45" t="inlineStr">
+      <c r="B69" s="47" t="inlineStr">
         <is>
           <t>구성원 89K (프리미엄)</t>
         </is>
       </c>
-      <c r="C69" s="45" t="inlineStr">
+      <c r="C69" s="47" t="inlineStr">
         <is>
           <t>체크</t>
         </is>
       </c>
-      <c r="D69" s="45" t="inlineStr">
+      <c r="D69" s="47" t="inlineStr">
         <is>
           <t>프리미엄 대상</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="45" t="inlineStr">
+      <c r="A70" s="47" t="inlineStr">
         <is>
           <t>회선 3</t>
         </is>
       </c>
-      <c r="B70" s="45" t="inlineStr">
+      <c r="B70" s="47" t="inlineStr">
         <is>
           <t>구성원 89K (프리미엄)</t>
         </is>
       </c>
-      <c r="C70" s="45" t="inlineStr">
+      <c r="C70" s="47" t="inlineStr">
         <is>
           <t>체크</t>
         </is>
       </c>
-      <c r="D70" s="45" t="inlineStr">
+      <c r="D70" s="47" t="inlineStr">
         <is>
           <t>프리미엄 대상</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="45" t="inlineStr">
+      <c r="A71" s="47" t="inlineStr">
         <is>
           <t>총액 합산</t>
         </is>
       </c>
-      <c r="B71" s="45" t="inlineStr">
+      <c r="B71" s="47" t="inlineStr">
         <is>
           <t>대표자 1명 89,000원</t>
         </is>
       </c>
-      <c r="C71" s="45" t="inlineStr">
+      <c r="C71" s="47" t="inlineStr">
         <is>
           <t>rngIdx=2 (64.9K↑)</t>
         </is>
       </c>
-      <c r="D71" s="45" t="inlineStr">
+      <c r="D71" s="47" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="45" t="inlineStr">
+      <c r="A72" s="47" t="inlineStr">
         <is>
           <t>인터넷</t>
         </is>
       </c>
-      <c r="B72" s="45" t="inlineStr">
+      <c r="B72" s="47" t="inlineStr">
         <is>
           <t>대표자 휴대폰에 -5,500</t>
         </is>
       </c>
-      <c r="C72" s="45" t="inlineStr">
+      <c r="C72" s="47" t="inlineStr">
         <is>
           <t>고정</t>
         </is>
       </c>
-      <c r="D72" s="45" t="inlineStr">
+      <c r="D72" s="47" t="inlineStr">
         <is>
           <t>-5,500</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="45" t="inlineStr">
+      <c r="A73" s="47" t="inlineStr">
         <is>
           <t>대표자 총액결합</t>
         </is>
       </c>
-      <c r="B73" s="45" t="inlineStr">
+      <c r="B73" s="47" t="inlineStr">
         <is>
           <t>100M mobile[2]</t>
         </is>
       </c>
-      <c r="C73" s="45" t="inlineStr">
+      <c r="C73" s="47" t="inlineStr">
         <is>
           <t>3,300</t>
         </is>
       </c>
-      <c r="D73" s="45" t="inlineStr">
+      <c r="D73" s="47" t="inlineStr">
         <is>
           <t>-3,300</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="45" t="inlineStr">
+      <c r="A74" s="47" t="inlineStr">
         <is>
           <t>구성원 프리미엄</t>
         </is>
       </c>
-      <c r="B74" s="45" t="inlineStr">
+      <c r="B74" s="47" t="inlineStr">
         <is>
           <t>89K × 2명</t>
         </is>
       </c>
-      <c r="C74" s="45" t="inlineStr">
+      <c r="C74" s="47" t="inlineStr">
         <is>
           <t>22,250 × 2</t>
         </is>
       </c>
-      <c r="D74" s="45" t="inlineStr">
+      <c r="D74" s="47" t="inlineStr">
         <is>
           <t>-44,500</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="45" t="inlineStr">
+      <c r="A75" s="47" t="inlineStr">
         <is>
           <t>🎉 총 할인</t>
         </is>
       </c>
-      <c r="B75" s="45" t="inlineStr">
+      <c r="B75" s="47" t="inlineStr">
         <is>
           <t>5,500 + 3,300 + 44,500</t>
         </is>
       </c>
-      <c r="C75" s="45" t="inlineStr"/>
-      <c r="D75" s="45" t="inlineStr">
+      <c r="C75" s="47" t="inlineStr"/>
+      <c r="D75" s="47" t="inlineStr">
         <is>
           <t>-53,300</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="45" t="inlineStr">
+      <c r="A76" s="47" t="inlineStr">
         <is>
           <t>비교 (총액결합만)</t>
         </is>
       </c>
-      <c r="B76" s="45" t="inlineStr">
+      <c r="B76" s="47" t="inlineStr">
         <is>
           <t>3×89K=267K → idx 5</t>
         </is>
       </c>
-      <c r="C76" s="45" t="inlineStr">
+      <c r="C76" s="47" t="inlineStr">
         <is>
           <t>mobile[5]=23,100 + 인터넷 5,500</t>
         </is>
       </c>
-      <c r="D76" s="45" t="inlineStr">
+      <c r="D76" s="47" t="inlineStr">
         <is>
           <t>-28,600</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="45" t="inlineStr">
+      <c r="A77" s="47" t="inlineStr">
         <is>
           <t>차액</t>
         </is>
       </c>
-      <c r="B77" s="45" t="inlineStr">
+      <c r="B77" s="47" t="inlineStr">
         <is>
           <t>프리미엄 선택 시 추가 혜택</t>
         </is>
       </c>
-      <c r="C77" s="45" t="inlineStr"/>
-      <c r="D77" s="45" t="inlineStr">
+      <c r="C77" s="47" t="inlineStr"/>
+      <c r="D77" s="47" t="inlineStr">
         <is>
           <t>+24,700</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="44" t="inlineStr">
+      <c r="A79" s="46" t="inlineStr">
         <is>
           <t>⑥ 검증 예시 2 — 100M + 4회선 (2×89K + 2×32.89K)</t>
         </is>
@@ -4787,197 +5204,197 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="45" t="inlineStr">
+      <c r="A81" s="47" t="inlineStr">
         <is>
           <t>회선 1</t>
         </is>
       </c>
-      <c r="B81" s="45" t="inlineStr">
+      <c r="B81" s="47" t="inlineStr">
         <is>
           <t>대표자 89K</t>
         </is>
       </c>
-      <c r="C81" s="45" t="inlineStr">
+      <c r="C81" s="47" t="inlineStr">
         <is>
           <t>총액</t>
         </is>
       </c>
-      <c r="D81" s="45" t="inlineStr">
+      <c r="D81" s="47" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="45" t="inlineStr">
+      <c r="A82" s="47" t="inlineStr">
         <is>
           <t>회선 2</t>
         </is>
       </c>
-      <c r="B82" s="45" t="inlineStr">
+      <c r="B82" s="47" t="inlineStr">
         <is>
           <t>구성원 89K (프리미엄)</t>
         </is>
       </c>
-      <c r="C82" s="45" t="inlineStr">
+      <c r="C82" s="47" t="inlineStr">
         <is>
           <t>체크</t>
         </is>
       </c>
-      <c r="D82" s="45" t="inlineStr">
+      <c r="D82" s="47" t="inlineStr">
         <is>
           <t>프리미엄 대상</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="45" t="inlineStr">
+      <c r="A83" s="47" t="inlineStr">
         <is>
           <t>회선 3</t>
         </is>
       </c>
-      <c r="B83" s="45" t="inlineStr">
+      <c r="B83" s="47" t="inlineStr">
         <is>
           <t>구성원 32.89K</t>
         </is>
       </c>
-      <c r="C83" s="45" t="inlineStr">
+      <c r="C83" s="47" t="inlineStr">
         <is>
           <t>77K미만 → 자동 총액</t>
         </is>
       </c>
-      <c r="D83" s="45" t="inlineStr">
+      <c r="D83" s="47" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="45" t="inlineStr">
+      <c r="A84" s="47" t="inlineStr">
         <is>
           <t>회선 4</t>
         </is>
       </c>
-      <c r="B84" s="45" t="inlineStr">
+      <c r="B84" s="47" t="inlineStr">
         <is>
           <t>구성원 32.89K</t>
         </is>
       </c>
-      <c r="C84" s="45" t="inlineStr">
+      <c r="C84" s="47" t="inlineStr">
         <is>
           <t>77K미만 → 자동 총액</t>
         </is>
       </c>
-      <c r="D84" s="45" t="inlineStr">
+      <c r="D84" s="47" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="45" t="inlineStr">
+      <c r="A85" s="47" t="inlineStr">
         <is>
           <t>총액 합산</t>
         </is>
       </c>
-      <c r="B85" s="45" t="inlineStr">
+      <c r="B85" s="47" t="inlineStr">
         <is>
           <t>89 + 32.89×2 = 154,780</t>
         </is>
       </c>
-      <c r="C85" s="45" t="inlineStr">
+      <c r="C85" s="47" t="inlineStr">
         <is>
           <t>rngIdx=4 (141.9K↑)</t>
         </is>
       </c>
-      <c r="D85" s="45" t="inlineStr">
+      <c r="D85" s="47" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="45" t="inlineStr">
+      <c r="A86" s="47" t="inlineStr">
         <is>
           <t>인터넷</t>
         </is>
       </c>
-      <c r="B86" s="45" t="inlineStr">
+      <c r="B86" s="47" t="inlineStr">
         <is>
           <t>고정</t>
         </is>
       </c>
-      <c r="C86" s="45" t="inlineStr"/>
-      <c r="D86" s="45" t="inlineStr">
+      <c r="C86" s="47" t="inlineStr"/>
+      <c r="D86" s="47" t="inlineStr">
         <is>
           <t>-5,500</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="45" t="inlineStr">
+      <c r="A87" s="47" t="inlineStr">
         <is>
           <t>대표자+일반 총액결합</t>
         </is>
       </c>
-      <c r="B87" s="45" t="inlineStr">
+      <c r="B87" s="47" t="inlineStr">
         <is>
           <t>100M mobile[4]</t>
         </is>
       </c>
-      <c r="C87" s="45" t="inlineStr">
+      <c r="C87" s="47" t="inlineStr">
         <is>
           <t>18,700</t>
         </is>
       </c>
-      <c r="D87" s="45" t="inlineStr">
+      <c r="D87" s="47" t="inlineStr">
         <is>
           <t>-18,700</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="45" t="inlineStr">
+      <c r="A88" s="47" t="inlineStr">
         <is>
           <t>프리미엄 89K</t>
         </is>
       </c>
-      <c r="B88" s="45" t="inlineStr">
+      <c r="B88" s="47" t="inlineStr">
         <is>
           <t>1명</t>
         </is>
       </c>
-      <c r="C88" s="45" t="inlineStr">
+      <c r="C88" s="47" t="inlineStr">
         <is>
           <t>22,250</t>
         </is>
       </c>
-      <c r="D88" s="45" t="inlineStr">
+      <c r="D88" s="47" t="inlineStr">
         <is>
           <t>-22,250</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="45" t="inlineStr">
+      <c r="A89" s="47" t="inlineStr">
         <is>
           <t>🎉 총 할인</t>
         </is>
       </c>
-      <c r="B89" s="45" t="inlineStr">
+      <c r="B89" s="47" t="inlineStr">
         <is>
           <t>5,500 + 18,700 + 22,250</t>
         </is>
       </c>
-      <c r="C89" s="45" t="inlineStr"/>
-      <c r="D89" s="45" t="inlineStr">
+      <c r="C89" s="47" t="inlineStr"/>
+      <c r="D89" s="47" t="inlineStr">
         <is>
           <t>-46,450</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="44" t="inlineStr">
+      <c r="A91" s="46" t="inlineStr">
         <is>
           <t>⑦ 엣지 케이스 처리</t>
         </is>
@@ -5068,14 +5485,14 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="44" t="inlineStr">
+      <c r="A100" s="46" t="inlineStr">
         <is>
           <t>⑧ 참고자료 (원본 출처)</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="40" t="inlineStr">
+      <c r="A101" s="42" t="inlineStr">
         <is>
           <t>🔗 백메가 블로그 — KT 프리미엄 가족결합 상세 해설 (원본 소스)</t>
         </is>
@@ -5089,7 +5506,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="46" t="inlineStr">
+      <c r="A103" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">    · 자격 조건, 대표자/구성원 분배 규칙, 실제 계산 예시 2건 원본</t>
         </is>
@@ -5149,7 +5566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5160,23 +5577,23 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="47" t="inlineStr">
+      <c r="A1" s="49" t="inlineStr">
         <is>
           <t>🏷️ LG U+ 참쉬운가족결합 (완전 명세)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="48" t="inlineStr">
-        <is>
-          <t>① 자격 조건</t>
+      <c r="A3" s="50" t="inlineStr">
+        <is>
+          <t>① 자격 조건 및 주의사항</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="37" t="inlineStr">
         <is>
-          <t>▶ 휴대폰 2회선부터 결합 (1회선 불가)</t>
+          <t>▶ 휴대폰 2회선부터 결합 (⚠️ 1회선 불가)</t>
         </is>
       </c>
     </row>
@@ -5197,251 +5614,275 @@
     <row r="7">
       <c r="A7" s="37" t="inlineStr">
         <is>
-          <t>▶ 적용 방식: 단독가 REPLACE</t>
+          <t>▶ 적용 방식: 단독가 REPLACE (SKT와 유사)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="37" t="inlineStr">
+        <is>
+          <t>▶ ⚠️ 할인 매트릭스 인덱싱: 요금구간 1~3 × 회선수 2/3/4+</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="48" t="inlineStr">
+      <c r="A9" s="37" t="inlineStr">
+        <is>
+          <t>▶ ⚠️ 4회선 이상 (5,6,7...회선) → 모두 "4+" 컬럼 사용 (캡 적용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="37" t="inlineStr">
+        <is>
+          <t>▶ 인당 × 실제 회선수 (최대 10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="50" t="inlineStr">
         <is>
           <t>② 인터넷 할인 (3년 약정 기준)</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="49" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="51" t="inlineStr">
         <is>
           <t>인터넷 할인</t>
         </is>
       </c>
-      <c r="B11" s="49" t="n">
+      <c r="B14" s="51" t="n">
         <v>5500</v>
       </c>
-      <c r="C11" s="49" t="n">
+      <c r="C14" s="51" t="n">
         <v>9900</v>
       </c>
-      <c r="D11" s="49" t="n">
+      <c r="D14" s="51" t="n">
         <v>13200</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="48" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="50" t="inlineStr">
         <is>
           <t>③ 휴대폰 인당 할인 매트릭스 (요금구간 × 회선수)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>요금구간</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>2회선</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>3회선</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>4+회선</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="49" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="51" t="inlineStr">
         <is>
           <t>69K 미만</t>
         </is>
       </c>
-      <c r="B15" s="49" t="n">
+      <c r="B18" s="51" t="n">
         <v>2200</v>
       </c>
-      <c r="C15" s="49" t="n">
+      <c r="C18" s="51" t="n">
         <v>3300</v>
       </c>
-      <c r="D15" s="49" t="n">
+      <c r="D18" s="51" t="n">
         <v>4400</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="49" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="51" t="inlineStr">
         <is>
           <t>69K 이상</t>
         </is>
       </c>
-      <c r="B16" s="49" t="n">
+      <c r="B19" s="51" t="n">
         <v>3300</v>
       </c>
-      <c r="C16" s="49" t="n">
+      <c r="C19" s="51" t="n">
         <v>5500</v>
       </c>
-      <c r="D16" s="49" t="n">
+      <c r="D19" s="51" t="n">
         <v>6600</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="49" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="51" t="inlineStr">
         <is>
           <t>88K 이상</t>
         </is>
       </c>
-      <c r="B17" s="49" t="n">
+      <c r="B20" s="51" t="n">
         <v>4400</v>
       </c>
-      <c r="C17" s="49" t="n">
+      <c r="C20" s="51" t="n">
         <v>6600</v>
       </c>
-      <c r="D17" s="49" t="n">
+      <c r="D20" s="51" t="n">
         <v>8800</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="48" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="50" t="inlineStr">
         <is>
           <t>④ 계산 알고리즘</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="39" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="41" t="inlineStr">
         <is>
           <t>// 입력: speed, tvIdx, planRange(1~3), lines(2~4+)</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="39" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="41" t="inlineStr">
         <is>
           <t>1. lguInet = bundle.chweyswun.internet[speed]</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="39" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="41" t="inlineStr">
         <is>
           <t>2. netSingle = internet[speed]  // LGU+ WiFi 전속도 무료</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="39" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="41" t="inlineStr">
         <is>
           <t>3. inetAfter = netSingle - lguInet  // REPLACE 방식</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="39" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="41" t="inlineStr">
         <is>
           <t>4. 휴대폰: idx = min(lines, 4) - 2  // 2회선=0 / 3회선=1 / 4+=2</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="39" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">   perPerson = bundle.chweyswun.mobile[planRange-1][idx]</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="39" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">   mobileDc = perPerson × min(lines, 4)</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="39" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="41" t="inlineStr">
         <is>
           <t>5. TV: tvAfter = tv[tvIdx].p - tv[tvIdx].dc</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="39" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="41" t="inlineStr">
         <is>
           <t>6. monthlyFee = inetAfter + tvAfter + setTop(4,400)</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="39" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="41" t="inlineStr">
         <is>
           <t>7. finalFee = monthlyFee - mobileDc</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="48" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="50" t="inlineStr">
         <is>
           <t>⑤ 참고자료</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="40" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="42" t="inlineStr">
         <is>
           <t>🔗 백메가 LG U+ 상품 전체 안내 (결합할인 원본 소스)</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="10" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">    URL: https://www.100mb.kr/01_product/lg.php</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A20:E20"/>
+  <mergeCells count="19">
+    <mergeCell ref="A30:E30"/>
     <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A6:E6"/>
     <mergeCell ref="A7:E7"/>
     <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A26:E26"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A32:E32"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5453,7 +5894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -5463,30 +5904,30 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="47" t="inlineStr">
+      <c r="A1" s="49" t="inlineStr">
         <is>
           <t>🏷️ LG U+ 투게더 결합 (85,000원↑ 고가요금제)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="48" t="inlineStr">
-        <is>
-          <t>① 자격 조건</t>
+      <c r="A3" s="50" t="inlineStr">
+        <is>
+          <t>① 자격 조건 및 주의사항</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="37" t="inlineStr">
         <is>
-          <t>▶ 5G 85,000원 이상 요금제 필수</t>
+          <t>▶ 5G 85,000원 이상 고가요금제 필수</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="37" t="inlineStr">
         <is>
-          <t>▶ 500M 이상 인터넷 (100M 결합 불가)</t>
+          <t>▶ ⚠️ 500M 이상 인터넷 (100M 결합 불가 · 금액 0원)</t>
         </is>
       </c>
     </row>
@@ -5511,135 +5952,151 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="37" t="inlineStr">
+        <is>
+          <t>▶ ⚠️ 4회선 이상 (5회선 포함) → "4~5회선" 구간 사용 (캡)</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
-      <c r="A10" s="48" t="inlineStr">
+      <c r="A10" s="37" t="inlineStr">
+        <is>
+          <t>▶ 참쉬운과 비교 후 유리한 결합 선택 (고가요금제는 투게더 유리)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="50" t="inlineStr">
         <is>
           <t>② 인터넷 할인</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>100M</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>500M</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="49" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="51" t="inlineStr">
         <is>
           <t>인터넷</t>
         </is>
       </c>
-      <c r="B12" s="49" t="inlineStr">
+      <c r="B14" s="51" t="inlineStr">
         <is>
           <t>❌ 불가</t>
         </is>
       </c>
-      <c r="C12" s="49" t="n">
+      <c r="C14" s="51" t="n">
         <v>11000</v>
       </c>
-      <c r="D12" s="49" t="n">
+      <c r="D14" s="51" t="n">
         <v>11000</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="48" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="50" t="inlineStr">
         <is>
           <t>③ 휴대폰 인당 할인</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>회선수</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>인당 할인</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="49" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="51" t="inlineStr">
         <is>
           <t>2회선</t>
         </is>
       </c>
-      <c r="B16" s="49" t="n">
+      <c r="B18" s="51" t="n">
         <v>10000</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="49" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="51" t="inlineStr">
         <is>
           <t>3회선</t>
         </is>
       </c>
-      <c r="B17" s="49" t="n">
+      <c r="B19" s="51" t="n">
         <v>14000</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="49" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="51" t="inlineStr">
         <is>
           <t>4~5회선</t>
         </is>
       </c>
-      <c r="B18" s="49" t="n">
+      <c r="B20" s="51" t="n">
         <v>20000</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>※ 추가 혜택: 청소년 가족할인 -10,000 / 시그니처 가족할인 자녀 1대 최대 -33,000</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="48" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="50" t="inlineStr">
         <is>
           <t>④ 참고자료</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="40" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="42" t="inlineStr">
         <is>
           <t>🔗 백메가 LG U+ 상품 안내</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="9">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A22:D22"/>
     <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A20:D20"/>
     <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5665,101 +6122,101 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="50" t="inlineStr">
+      <c r="A3" s="52" t="inlineStr">
         <is>
           <t>interface CarrierData {</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="50" t="inlineStr">
+      <c r="A4" s="52" t="inlineStr">
         <is>
           <t xml:space="preserve">  name, prefix;</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="50" t="inlineStr">
+      <c r="A5" s="52" t="inlineStr">
         <is>
           <t xml:space="preserve">  internet: Record&lt;"100M"|"500M"|"1G", number&gt;;</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="50" t="inlineStr">
+      <c r="A6" s="52" t="inlineStr">
         <is>
           <t xml:space="preserve">  wifiCost? | wifiPrice?: Record&lt;Speed, number&gt;;</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="50" t="inlineStr">
+      <c r="A7" s="52" t="inlineStr">
         <is>
           <t xml:space="preserve">  setTopOptions: SetTop[]; wifiOptions: WiFi[];</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="50" t="inlineStr">
+      <c r="A8" s="52" t="inlineStr">
         <is>
           <t xml:space="preserve">  tvInternetNoWifi, tvInternetWithWifi: Record&lt;Speed, number&gt;;</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="50" t="inlineStr">
+      <c r="A9" s="52" t="inlineStr">
         <is>
           <t xml:space="preserve">  tv: TVProduct[];</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="50" t="inlineStr">
+      <c r="A10" s="52" t="inlineStr">
         <is>
           <t xml:space="preserve">  install: { solo, combo };</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="50" t="inlineStr">
+      <c r="A11" s="52" t="inlineStr">
         <is>
           <t xml:space="preserve">  gift: { solo: SpeedMap, combo: SpeedMap };</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="50" t="inlineStr">
+      <c r="A12" s="52" t="inlineStr">
         <is>
           <t xml:space="preserve">  bundle: BundleConfig;  // 3사별 상이</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="50" t="inlineStr">
+      <c r="A13" s="52" t="inlineStr">
         <is>
           <t>}</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="50" t="inlineStr"/>
+      <c r="A14" s="52" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="50" t="inlineStr">
+      <c r="A15" s="52" t="inlineStr">
         <is>
           <t>// SKT: bundle.family { internet, iptv, mobilePerBySpeed }</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="50" t="inlineStr">
+      <c r="A16" s="52" t="inlineStr">
         <is>
           <t>// KT:  bundle.{ranges_total, total, ranges_fixed, fixed, premium}</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="50" t="inlineStr">
+      <c r="A17" s="52" t="inlineStr">
         <is>
           <t>// LGU: bundle.{chweyswun, together}</t>
         </is>
@@ -6296,7 +6753,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="51" t="inlineStr">
+      <c r="A3" s="53" t="inlineStr">
         <is>
           <t>⚠️ 3사 결합할인 적용 방식 차이</t>
         </is>

--- a/docs/bongi-calculator-data.xlsx
+++ b/docs/bongi-calculator-data.xlsx
@@ -817,7 +817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1267,7 +1267,7 @@
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>🔗 봉이모바일 통합 계산기 (원본 데이터 소스)</t>
+          <t>🔗 봉이모바일 통합 계산기 v1 (원본 · 상담원용 상세)</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
@@ -1279,17 +1279,29 @@
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
+          <t>🔗 봉이모바일 계산기 v2 (고객용 · 심플 카드형 UI)</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>https://bongi-mobile-production.up.railway.app/docs/calculator-v2.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
           <t>🔗 GitHub 리포지토리</t>
         </is>
       </c>
-      <c r="B40" s="10" t="inlineStr">
+      <c r="B41" s="10" t="inlineStr">
         <is>
           <t>https://github.com/vinsenzo83/bongi-mobile</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="B38:C38"/>
@@ -1297,6 +1309,7 @@
     <mergeCell ref="A32:C32"/>
     <mergeCell ref="A31:C31"/>
     <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B41:C41"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="A35:C35"/>
@@ -1310,6 +1323,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/bongi-calculator-data.xlsx
+++ b/docs/bongi-calculator-data.xlsx
@@ -1279,7 +1279,7 @@
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>🔗 봉이모바일 계산기 v2 (고객용 · 심플 카드형 UI)</t>
+          <t>🔗 봉이모바일 계산기 v2 (데이터 검증용)</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">

--- a/docs/bongi-calculator-data.xlsx
+++ b/docs/bongi-calculator-data.xlsx
@@ -27,6 +27,7 @@
     <sheet name="15_LGU_Together" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="20_Schema" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="30_Formula" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="07_Gift_Catalog" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -38,7 +39,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0&quot;원&quot;"/>
   </numFmts>
-  <fonts count="39">
+  <fonts count="41">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -268,8 +269,17 @@
       <color rgb="00e40981"/>
       <sz val="13"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001A2744"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -326,6 +336,26 @@
         <fgColor rgb="00f5f5f7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A2744"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF1E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F4FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE7F3"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -353,7 +383,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -452,6 +482,31 @@
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1312,10 +1367,10 @@
     <mergeCell ref="B41:C41"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="A30:C30"/>
+    <mergeCell ref="B40:C40"/>
     <mergeCell ref="A35:C35"/>
-    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="A2:C2"/>
     <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A2:C2"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId1"/>
@@ -6816,6 +6871,1513 @@
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A6:B6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E66"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="54" t="inlineStr">
+        <is>
+          <t>🎁 봉이 사은품 정책 카탈로그 (총 63개 상품)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="55" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="55" t="inlineStr">
+        <is>
+          <t>통신사</t>
+        </is>
+      </c>
+      <c r="C3" s="55" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="D3" s="55" t="inlineStr">
+        <is>
+          <t>상품 구성</t>
+        </is>
+      </c>
+      <c r="E3" s="55" t="inlineStr">
+        <is>
+          <t>사은품(원)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C4" s="56" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="D4" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 100M</t>
+        </is>
+      </c>
+      <c r="E4" s="58" t="n">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C5" s="56" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="D5" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 500M</t>
+        </is>
+      </c>
+      <c r="E5" s="58" t="n">
+        <v>170000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C6" s="56" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="D6" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 1G</t>
+        </is>
+      </c>
+      <c r="E6" s="58" t="n">
+        <v>170000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C7" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D7" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 100M + B tv 이코노미</t>
+        </is>
+      </c>
+      <c r="E7" s="58" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C8" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D8" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 100M + B tv 스탠다드</t>
+        </is>
+      </c>
+      <c r="E8" s="58" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="56" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C9" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D9" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 100M + B tv 올</t>
+        </is>
+      </c>
+      <c r="E9" s="58" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="56" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C10" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D10" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 100M + B tv 스탠다드 플러스</t>
+        </is>
+      </c>
+      <c r="E10" s="58" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="56" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C11" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D11" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 100M + B tv 올 플러스</t>
+        </is>
+      </c>
+      <c r="E11" s="58" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="56" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C12" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D12" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 100M + B tv 스탠다드 넷플릭스</t>
+        </is>
+      </c>
+      <c r="E12" s="58" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="56" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C13" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D13" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 100M + B tv 올 넷플릭스</t>
+        </is>
+      </c>
+      <c r="E13" s="58" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="56" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C14" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D14" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 100M + B tv 스탠다드 넷플릭스 프리미엄</t>
+        </is>
+      </c>
+      <c r="E14" s="58" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="56" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C15" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D15" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 100M + B tv 올 넷플릭스 프리미엄</t>
+        </is>
+      </c>
+      <c r="E15" s="58" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="56" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C16" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D16" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 500M + B tv 이코노미</t>
+        </is>
+      </c>
+      <c r="E16" s="58" t="n">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="56" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C17" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D17" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 500M + B tv 스탠다드</t>
+        </is>
+      </c>
+      <c r="E17" s="58" t="n">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="56" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C18" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D18" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 500M + B tv 올</t>
+        </is>
+      </c>
+      <c r="E18" s="58" t="n">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="56" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C19" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D19" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 500M + B tv 스탠다드 플러스</t>
+        </is>
+      </c>
+      <c r="E19" s="58" t="n">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="56" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C20" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D20" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 500M + B tv 올 플러스</t>
+        </is>
+      </c>
+      <c r="E20" s="58" t="n">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="56" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C21" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D21" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 500M + B tv 스탠다드 넷플릭스</t>
+        </is>
+      </c>
+      <c r="E21" s="58" t="n">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="56" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C22" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D22" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 500M + B tv 올 넷플릭스</t>
+        </is>
+      </c>
+      <c r="E22" s="58" t="n">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="56" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C23" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D23" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 500M + B tv 스탠다드 넷플릭스 프리미엄</t>
+        </is>
+      </c>
+      <c r="E23" s="58" t="n">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="56" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C24" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D24" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 500M + B tv 올 넷플릭스 프리미엄</t>
+        </is>
+      </c>
+      <c r="E24" s="58" t="n">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="56" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C25" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D25" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 1G + B tv 이코노미</t>
+        </is>
+      </c>
+      <c r="E25" s="58" t="n">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="56" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C26" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D26" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 1G + B tv 스탠다드</t>
+        </is>
+      </c>
+      <c r="E26" s="58" t="n">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="56" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C27" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D27" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 1G + B tv 올</t>
+        </is>
+      </c>
+      <c r="E27" s="58" t="n">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="56" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C28" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D28" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 1G + B tv 스탠다드 플러스</t>
+        </is>
+      </c>
+      <c r="E28" s="58" t="n">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="56" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C29" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D29" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 1G + B tv 올 플러스</t>
+        </is>
+      </c>
+      <c r="E29" s="58" t="n">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="56" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C30" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D30" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 1G + B tv 스탠다드 넷플릭스</t>
+        </is>
+      </c>
+      <c r="E30" s="58" t="n">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="56" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C31" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D31" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 1G + B tv 올 넷플릭스</t>
+        </is>
+      </c>
+      <c r="E31" s="58" t="n">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="56" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C32" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D32" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 1G + B tv 스탠다드 넷플릭스 프리미엄</t>
+        </is>
+      </c>
+      <c r="E32" s="58" t="n">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="56" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C33" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D33" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 1G + B tv 올 넷플릭스 프리미엄</t>
+        </is>
+      </c>
+      <c r="E33" s="58" t="n">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="59" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" s="59" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C34" s="59" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="D34" s="60" t="inlineStr">
+        <is>
+          <t>인터넷 100M</t>
+        </is>
+      </c>
+      <c r="E34" s="61" t="n">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="59" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" s="59" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C35" s="59" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="D35" s="60" t="inlineStr">
+        <is>
+          <t>인터넷 500M</t>
+        </is>
+      </c>
+      <c r="E35" s="61" t="n">
+        <v>140000</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="59" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" s="59" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C36" s="59" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="D36" s="60" t="inlineStr">
+        <is>
+          <t>인터넷 1G</t>
+        </is>
+      </c>
+      <c r="E36" s="61" t="n">
+        <v>140000</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="59" t="n">
+        <v>34</v>
+      </c>
+      <c r="B37" s="59" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C37" s="59" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D37" s="60" t="inlineStr">
+        <is>
+          <t>인터넷 100M + 지니TV 베이직</t>
+        </is>
+      </c>
+      <c r="E37" s="61" t="n">
+        <v>370000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="59" t="n">
+        <v>35</v>
+      </c>
+      <c r="B38" s="59" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C38" s="59" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D38" s="60" t="inlineStr">
+        <is>
+          <t>인터넷 100M + 지니TV 라이트</t>
+        </is>
+      </c>
+      <c r="E38" s="61" t="n">
+        <v>370000</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="59" t="n">
+        <v>36</v>
+      </c>
+      <c r="B39" s="59" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C39" s="59" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D39" s="60" t="inlineStr">
+        <is>
+          <t>인터넷 100M + 지니TV 에센스</t>
+        </is>
+      </c>
+      <c r="E39" s="61" t="n">
+        <v>370000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="59" t="n">
+        <v>37</v>
+      </c>
+      <c r="B40" s="59" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C40" s="59" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D40" s="60" t="inlineStr">
+        <is>
+          <t>인터넷 100M + 지니TV 모든G</t>
+        </is>
+      </c>
+      <c r="E40" s="61" t="n">
+        <v>370000</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="59" t="n">
+        <v>38</v>
+      </c>
+      <c r="B41" s="59" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C41" s="59" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D41" s="60" t="inlineStr">
+        <is>
+          <t>인터넷 100M + 지니TV 디즈니+모든G</t>
+        </is>
+      </c>
+      <c r="E41" s="61" t="n">
+        <v>370000</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="59" t="n">
+        <v>39</v>
+      </c>
+      <c r="B42" s="59" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C42" s="59" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D42" s="60" t="inlineStr">
+        <is>
+          <t>인터넷 500M + 지니TV 베이직</t>
+        </is>
+      </c>
+      <c r="E42" s="61" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="59" t="n">
+        <v>40</v>
+      </c>
+      <c r="B43" s="59" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C43" s="59" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D43" s="60" t="inlineStr">
+        <is>
+          <t>인터넷 500M + 지니TV 라이트</t>
+        </is>
+      </c>
+      <c r="E43" s="61" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="59" t="n">
+        <v>41</v>
+      </c>
+      <c r="B44" s="59" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C44" s="59" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D44" s="60" t="inlineStr">
+        <is>
+          <t>인터넷 500M + 지니TV 에센스</t>
+        </is>
+      </c>
+      <c r="E44" s="61" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="59" t="n">
+        <v>42</v>
+      </c>
+      <c r="B45" s="59" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C45" s="59" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D45" s="60" t="inlineStr">
+        <is>
+          <t>인터넷 500M + 지니TV 모든G</t>
+        </is>
+      </c>
+      <c r="E45" s="61" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="59" t="n">
+        <v>43</v>
+      </c>
+      <c r="B46" s="59" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C46" s="59" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D46" s="60" t="inlineStr">
+        <is>
+          <t>인터넷 500M + 지니TV 디즈니+모든G</t>
+        </is>
+      </c>
+      <c r="E46" s="61" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="59" t="n">
+        <v>44</v>
+      </c>
+      <c r="B47" s="59" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C47" s="59" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D47" s="60" t="inlineStr">
+        <is>
+          <t>인터넷 1G + 지니TV 베이직</t>
+        </is>
+      </c>
+      <c r="E47" s="61" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="59" t="n">
+        <v>45</v>
+      </c>
+      <c r="B48" s="59" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C48" s="59" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D48" s="60" t="inlineStr">
+        <is>
+          <t>인터넷 1G + 지니TV 라이트</t>
+        </is>
+      </c>
+      <c r="E48" s="61" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="59" t="n">
+        <v>46</v>
+      </c>
+      <c r="B49" s="59" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C49" s="59" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D49" s="60" t="inlineStr">
+        <is>
+          <t>인터넷 1G + 지니TV 에센스</t>
+        </is>
+      </c>
+      <c r="E49" s="61" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="59" t="n">
+        <v>47</v>
+      </c>
+      <c r="B50" s="59" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C50" s="59" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D50" s="60" t="inlineStr">
+        <is>
+          <t>인터넷 1G + 지니TV 모든G</t>
+        </is>
+      </c>
+      <c r="E50" s="61" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="59" t="n">
+        <v>48</v>
+      </c>
+      <c r="B51" s="59" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C51" s="59" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D51" s="60" t="inlineStr">
+        <is>
+          <t>인터넷 1G + 지니TV 디즈니+모든G</t>
+        </is>
+      </c>
+      <c r="E51" s="61" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="62" t="n">
+        <v>49</v>
+      </c>
+      <c r="B52" s="62" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C52" s="62" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="D52" s="63" t="inlineStr">
+        <is>
+          <t>인터넷 100M</t>
+        </is>
+      </c>
+      <c r="E52" s="64" t="n">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="62" t="n">
+        <v>50</v>
+      </c>
+      <c r="B53" s="62" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C53" s="62" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="D53" s="63" t="inlineStr">
+        <is>
+          <t>인터넷 500M</t>
+        </is>
+      </c>
+      <c r="E53" s="64" t="n">
+        <v>230000</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="62" t="n">
+        <v>51</v>
+      </c>
+      <c r="B54" s="62" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C54" s="62" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="D54" s="63" t="inlineStr">
+        <is>
+          <t>인터넷 1G</t>
+        </is>
+      </c>
+      <c r="E54" s="64" t="n">
+        <v>230000</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="62" t="n">
+        <v>52</v>
+      </c>
+      <c r="B55" s="62" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C55" s="62" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D55" s="63" t="inlineStr">
+        <is>
+          <t>인터넷 100M + U+tv 실속형</t>
+        </is>
+      </c>
+      <c r="E55" s="64" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="62" t="n">
+        <v>53</v>
+      </c>
+      <c r="B56" s="62" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C56" s="62" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D56" s="63" t="inlineStr">
+        <is>
+          <t>인터넷 100M + U+tv 기본형</t>
+        </is>
+      </c>
+      <c r="E56" s="64" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="62" t="n">
+        <v>54</v>
+      </c>
+      <c r="B57" s="62" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C57" s="62" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D57" s="63" t="inlineStr">
+        <is>
+          <t>인터넷 100M + U+tv 프리미엄</t>
+        </is>
+      </c>
+      <c r="E57" s="64" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="62" t="n">
+        <v>55</v>
+      </c>
+      <c r="B58" s="62" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C58" s="62" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D58" s="63" t="inlineStr">
+        <is>
+          <t>인터넷 100M + U+tv 프리미엄 VOD</t>
+        </is>
+      </c>
+      <c r="E58" s="64" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="62" t="n">
+        <v>56</v>
+      </c>
+      <c r="B59" s="62" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C59" s="62" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D59" s="63" t="inlineStr">
+        <is>
+          <t>인터넷 500M + U+tv 실속형</t>
+        </is>
+      </c>
+      <c r="E59" s="64" t="n">
+        <v>470000</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="62" t="n">
+        <v>57</v>
+      </c>
+      <c r="B60" s="62" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C60" s="62" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D60" s="63" t="inlineStr">
+        <is>
+          <t>인터넷 500M + U+tv 기본형</t>
+        </is>
+      </c>
+      <c r="E60" s="64" t="n">
+        <v>470000</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="62" t="n">
+        <v>58</v>
+      </c>
+      <c r="B61" s="62" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C61" s="62" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D61" s="63" t="inlineStr">
+        <is>
+          <t>인터넷 500M + U+tv 프리미엄</t>
+        </is>
+      </c>
+      <c r="E61" s="64" t="n">
+        <v>470000</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="62" t="n">
+        <v>59</v>
+      </c>
+      <c r="B62" s="62" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C62" s="62" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D62" s="63" t="inlineStr">
+        <is>
+          <t>인터넷 500M + U+tv 프리미엄 VOD</t>
+        </is>
+      </c>
+      <c r="E62" s="64" t="n">
+        <v>470000</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="62" t="n">
+        <v>60</v>
+      </c>
+      <c r="B63" s="62" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C63" s="62" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D63" s="63" t="inlineStr">
+        <is>
+          <t>인터넷 1G + U+tv 실속형</t>
+        </is>
+      </c>
+      <c r="E63" s="64" t="n">
+        <v>470000</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B64" s="62" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C64" s="62" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D64" s="63" t="inlineStr">
+        <is>
+          <t>인터넷 1G + U+tv 기본형</t>
+        </is>
+      </c>
+      <c r="E64" s="64" t="n">
+        <v>470000</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="62" t="n">
+        <v>62</v>
+      </c>
+      <c r="B65" s="62" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C65" s="62" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D65" s="63" t="inlineStr">
+        <is>
+          <t>인터넷 1G + U+tv 프리미엄</t>
+        </is>
+      </c>
+      <c r="E65" s="64" t="n">
+        <v>470000</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="62" t="n">
+        <v>63</v>
+      </c>
+      <c r="B66" s="62" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C66" s="62" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D66" s="63" t="inlineStr">
+        <is>
+          <t>인터넷 1G + U+tv 프리미엄 VOD</t>
+        </is>
+      </c>
+      <c r="E66" s="64" t="n">
+        <v>470000</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/bongi-calculator-data.xlsx
+++ b/docs/bongi-calculator-data.xlsx
@@ -27,7 +27,6 @@
     <sheet name="15_LGU_Together" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="20_Schema" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="30_Formula" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="07_Gift_Catalog" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1493,177 +1492,1503 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>🎁 사은품</t>
+      <c r="A1" s="54" t="inlineStr">
+        <is>
+          <t>🎁 사은품 (총 63개 상품)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="55" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="55" t="inlineStr">
         <is>
           <t>통신사</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="C3" s="55" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>100M</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>500M</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>1G</t>
+      <c r="D3" s="55" t="inlineStr">
+        <is>
+          <t>상품 구성</t>
+        </is>
+      </c>
+      <c r="E3" s="55" t="inlineStr">
+        <is>
+          <t>사은품(원)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="56" t="inlineStr">
         <is>
           <t>SKT</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>solo</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="56" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="D4" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 100M</t>
+        </is>
+      </c>
+      <c r="E4" s="58" t="n">
         <v>110000</v>
       </c>
-      <c r="D4" s="5" t="n">
+    </row>
+    <row r="5">
+      <c r="A5" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C5" s="56" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="D5" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 500M</t>
+        </is>
+      </c>
+      <c r="E5" s="58" t="n">
         <v>170000</v>
       </c>
-      <c r="E4" s="5" t="n">
+    </row>
+    <row r="6">
+      <c r="A6" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C6" s="56" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="D6" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 1G</t>
+        </is>
+      </c>
+      <c r="E6" s="58" t="n">
         <v>170000</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="56" t="inlineStr">
         <is>
           <t>SKT</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>combo</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n">
+      <c r="C7" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D7" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 100M + B tv 이코노미</t>
+        </is>
+      </c>
+      <c r="E7" s="58" t="n">
         <v>400000</v>
       </c>
-      <c r="D5" s="5" t="n">
+    </row>
+    <row r="8">
+      <c r="A8" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C8" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D8" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 100M + B tv 스탠다드</t>
+        </is>
+      </c>
+      <c r="E8" s="58" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="56" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C9" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D9" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 100M + B tv 올</t>
+        </is>
+      </c>
+      <c r="E9" s="58" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="56" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C10" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D10" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 100M + B tv 스탠다드 플러스</t>
+        </is>
+      </c>
+      <c r="E10" s="58" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="56" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C11" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D11" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 100M + B tv 올 플러스</t>
+        </is>
+      </c>
+      <c r="E11" s="58" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="56" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C12" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D12" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 100M + B tv 스탠다드 넷플릭스</t>
+        </is>
+      </c>
+      <c r="E12" s="58" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="56" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C13" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D13" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 100M + B tv 올 넷플릭스</t>
+        </is>
+      </c>
+      <c r="E13" s="58" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="56" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C14" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D14" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 100M + B tv 스탠다드 넷플릭스 프리미엄</t>
+        </is>
+      </c>
+      <c r="E14" s="58" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="56" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C15" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D15" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 100M + B tv 올 넷플릭스 프리미엄</t>
+        </is>
+      </c>
+      <c r="E15" s="58" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="56" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C16" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D16" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 500M + B tv 이코노미</t>
+        </is>
+      </c>
+      <c r="E16" s="58" t="n">
         <v>430000</v>
       </c>
-      <c r="E5" s="5" t="n">
+    </row>
+    <row r="17">
+      <c r="A17" s="56" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C17" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D17" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 500M + B tv 스탠다드</t>
+        </is>
+      </c>
+      <c r="E17" s="58" t="n">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="56" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C18" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D18" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 500M + B tv 올</t>
+        </is>
+      </c>
+      <c r="E18" s="58" t="n">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="56" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C19" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D19" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 500M + B tv 스탠다드 플러스</t>
+        </is>
+      </c>
+      <c r="E19" s="58" t="n">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="56" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C20" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D20" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 500M + B tv 올 플러스</t>
+        </is>
+      </c>
+      <c r="E20" s="58" t="n">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="56" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C21" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D21" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 500M + B tv 스탠다드 넷플릭스</t>
+        </is>
+      </c>
+      <c r="E21" s="58" t="n">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="56" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C22" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D22" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 500M + B tv 올 넷플릭스</t>
+        </is>
+      </c>
+      <c r="E22" s="58" t="n">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="56" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C23" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D23" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 500M + B tv 스탠다드 넷플릭스 프리미엄</t>
+        </is>
+      </c>
+      <c r="E23" s="58" t="n">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="56" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C24" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D24" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 500M + B tv 올 넷플릭스 프리미엄</t>
+        </is>
+      </c>
+      <c r="E24" s="58" t="n">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="56" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C25" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D25" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 1G + B tv 이코노미</t>
+        </is>
+      </c>
+      <c r="E25" s="58" t="n">
         <v>490000</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="56" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C26" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D26" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 1G + B tv 스탠다드</t>
+        </is>
+      </c>
+      <c r="E26" s="58" t="n">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="56" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C27" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D27" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 1G + B tv 올</t>
+        </is>
+      </c>
+      <c r="E27" s="58" t="n">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="56" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C28" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D28" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 1G + B tv 스탠다드 플러스</t>
+        </is>
+      </c>
+      <c r="E28" s="58" t="n">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="56" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C29" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D29" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 1G + B tv 올 플러스</t>
+        </is>
+      </c>
+      <c r="E29" s="58" t="n">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="56" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C30" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D30" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 1G + B tv 스탠다드 넷플릭스</t>
+        </is>
+      </c>
+      <c r="E30" s="58" t="n">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="56" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C31" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D31" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 1G + B tv 올 넷플릭스</t>
+        </is>
+      </c>
+      <c r="E31" s="58" t="n">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="56" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C32" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D32" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 1G + B tv 스탠다드 넷플릭스 프리미엄</t>
+        </is>
+      </c>
+      <c r="E32" s="58" t="n">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="56" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="56" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C33" s="56" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D33" s="57" t="inlineStr">
+        <is>
+          <t>인터넷 1G + B tv 올 넷플릭스 프리미엄</t>
+        </is>
+      </c>
+      <c r="E33" s="58" t="n">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="59" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" s="59" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>solo</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n">
+      <c r="C34" s="59" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="D34" s="60" t="inlineStr">
+        <is>
+          <t>인터넷 100M</t>
+        </is>
+      </c>
+      <c r="E34" s="61" t="n">
         <v>90000</v>
       </c>
-      <c r="D6" s="5" t="n">
+    </row>
+    <row r="35">
+      <c r="A35" s="59" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" s="59" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C35" s="59" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="D35" s="60" t="inlineStr">
+        <is>
+          <t>인터넷 500M</t>
+        </is>
+      </c>
+      <c r="E35" s="61" t="n">
         <v>140000</v>
       </c>
-      <c r="E6" s="5" t="n">
+    </row>
+    <row r="36">
+      <c r="A36" s="59" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" s="59" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C36" s="59" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="D36" s="60" t="inlineStr">
+        <is>
+          <t>인터넷 1G</t>
+        </is>
+      </c>
+      <c r="E36" s="61" t="n">
         <v>140000</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="59" t="n">
+        <v>34</v>
+      </c>
+      <c r="B37" s="59" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>combo</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
+      <c r="C37" s="59" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D37" s="60" t="inlineStr">
+        <is>
+          <t>인터넷 100M + 지니TV 베이직</t>
+        </is>
+      </c>
+      <c r="E37" s="61" t="n">
         <v>370000</v>
       </c>
-      <c r="D7" s="5" t="n">
+    </row>
+    <row r="38">
+      <c r="A38" s="59" t="n">
+        <v>35</v>
+      </c>
+      <c r="B38" s="59" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C38" s="59" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D38" s="60" t="inlineStr">
+        <is>
+          <t>인터넷 100M + 지니TV 라이트</t>
+        </is>
+      </c>
+      <c r="E38" s="61" t="n">
+        <v>370000</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="59" t="n">
+        <v>36</v>
+      </c>
+      <c r="B39" s="59" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C39" s="59" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D39" s="60" t="inlineStr">
+        <is>
+          <t>인터넷 100M + 지니TV 에센스</t>
+        </is>
+      </c>
+      <c r="E39" s="61" t="n">
+        <v>370000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="59" t="n">
+        <v>37</v>
+      </c>
+      <c r="B40" s="59" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C40" s="59" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D40" s="60" t="inlineStr">
+        <is>
+          <t>인터넷 100M + 지니TV 모든G</t>
+        </is>
+      </c>
+      <c r="E40" s="61" t="n">
+        <v>370000</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="59" t="n">
+        <v>38</v>
+      </c>
+      <c r="B41" s="59" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C41" s="59" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D41" s="60" t="inlineStr">
+        <is>
+          <t>인터넷 100M + 지니TV 디즈니+모든G</t>
+        </is>
+      </c>
+      <c r="E41" s="61" t="n">
+        <v>370000</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="59" t="n">
+        <v>39</v>
+      </c>
+      <c r="B42" s="59" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C42" s="59" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D42" s="60" t="inlineStr">
+        <is>
+          <t>인터넷 500M + 지니TV 베이직</t>
+        </is>
+      </c>
+      <c r="E42" s="61" t="n">
         <v>450000</v>
       </c>
-      <c r="E7" s="5" t="n">
+    </row>
+    <row r="43">
+      <c r="A43" s="59" t="n">
+        <v>40</v>
+      </c>
+      <c r="B43" s="59" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C43" s="59" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D43" s="60" t="inlineStr">
+        <is>
+          <t>인터넷 500M + 지니TV 라이트</t>
+        </is>
+      </c>
+      <c r="E43" s="61" t="n">
         <v>450000</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="59" t="n">
+        <v>41</v>
+      </c>
+      <c r="B44" s="59" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C44" s="59" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D44" s="60" t="inlineStr">
+        <is>
+          <t>인터넷 500M + 지니TV 에센스</t>
+        </is>
+      </c>
+      <c r="E44" s="61" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="59" t="n">
+        <v>42</v>
+      </c>
+      <c r="B45" s="59" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C45" s="59" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D45" s="60" t="inlineStr">
+        <is>
+          <t>인터넷 500M + 지니TV 모든G</t>
+        </is>
+      </c>
+      <c r="E45" s="61" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="59" t="n">
+        <v>43</v>
+      </c>
+      <c r="B46" s="59" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C46" s="59" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D46" s="60" t="inlineStr">
+        <is>
+          <t>인터넷 500M + 지니TV 디즈니+모든G</t>
+        </is>
+      </c>
+      <c r="E46" s="61" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="59" t="n">
+        <v>44</v>
+      </c>
+      <c r="B47" s="59" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C47" s="59" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D47" s="60" t="inlineStr">
+        <is>
+          <t>인터넷 1G + 지니TV 베이직</t>
+        </is>
+      </c>
+      <c r="E47" s="61" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="59" t="n">
+        <v>45</v>
+      </c>
+      <c r="B48" s="59" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C48" s="59" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D48" s="60" t="inlineStr">
+        <is>
+          <t>인터넷 1G + 지니TV 라이트</t>
+        </is>
+      </c>
+      <c r="E48" s="61" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="59" t="n">
+        <v>46</v>
+      </c>
+      <c r="B49" s="59" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C49" s="59" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D49" s="60" t="inlineStr">
+        <is>
+          <t>인터넷 1G + 지니TV 에센스</t>
+        </is>
+      </c>
+      <c r="E49" s="61" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="59" t="n">
+        <v>47</v>
+      </c>
+      <c r="B50" s="59" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C50" s="59" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D50" s="60" t="inlineStr">
+        <is>
+          <t>인터넷 1G + 지니TV 모든G</t>
+        </is>
+      </c>
+      <c r="E50" s="61" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="59" t="n">
+        <v>48</v>
+      </c>
+      <c r="B51" s="59" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C51" s="59" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D51" s="60" t="inlineStr">
+        <is>
+          <t>인터넷 1G + 지니TV 디즈니+모든G</t>
+        </is>
+      </c>
+      <c r="E51" s="61" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="62" t="n">
+        <v>49</v>
+      </c>
+      <c r="B52" s="62" t="inlineStr">
         <is>
           <t>LG U+</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>solo</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="n">
+      <c r="C52" s="62" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="D52" s="63" t="inlineStr">
+        <is>
+          <t>인터넷 100M</t>
+        </is>
+      </c>
+      <c r="E52" s="64" t="n">
         <v>200000</v>
       </c>
-      <c r="D8" s="5" t="n">
+    </row>
+    <row r="53">
+      <c r="A53" s="62" t="n">
+        <v>50</v>
+      </c>
+      <c r="B53" s="62" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C53" s="62" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="D53" s="63" t="inlineStr">
+        <is>
+          <t>인터넷 500M</t>
+        </is>
+      </c>
+      <c r="E53" s="64" t="n">
         <v>230000</v>
       </c>
-      <c r="E8" s="5" t="n">
+    </row>
+    <row r="54">
+      <c r="A54" s="62" t="n">
+        <v>51</v>
+      </c>
+      <c r="B54" s="62" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C54" s="62" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="D54" s="63" t="inlineStr">
+        <is>
+          <t>인터넷 1G</t>
+        </is>
+      </c>
+      <c r="E54" s="64" t="n">
         <v>230000</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="62" t="n">
+        <v>52</v>
+      </c>
+      <c r="B55" s="62" t="inlineStr">
         <is>
           <t>LG U+</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>combo</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n">
+      <c r="C55" s="62" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D55" s="63" t="inlineStr">
+        <is>
+          <t>인터넷 100M + U+tv 실속형</t>
+        </is>
+      </c>
+      <c r="E55" s="64" t="n">
         <v>400000</v>
       </c>
-      <c r="D9" s="5" t="n">
+    </row>
+    <row r="56">
+      <c r="A56" s="62" t="n">
+        <v>53</v>
+      </c>
+      <c r="B56" s="62" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C56" s="62" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D56" s="63" t="inlineStr">
+        <is>
+          <t>인터넷 100M + U+tv 기본형</t>
+        </is>
+      </c>
+      <c r="E56" s="64" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="62" t="n">
+        <v>54</v>
+      </c>
+      <c r="B57" s="62" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C57" s="62" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D57" s="63" t="inlineStr">
+        <is>
+          <t>인터넷 100M + U+tv 프리미엄</t>
+        </is>
+      </c>
+      <c r="E57" s="64" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="62" t="n">
+        <v>55</v>
+      </c>
+      <c r="B58" s="62" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C58" s="62" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D58" s="63" t="inlineStr">
+        <is>
+          <t>인터넷 100M + U+tv 프리미엄 VOD</t>
+        </is>
+      </c>
+      <c r="E58" s="64" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="62" t="n">
+        <v>56</v>
+      </c>
+      <c r="B59" s="62" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C59" s="62" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D59" s="63" t="inlineStr">
+        <is>
+          <t>인터넷 500M + U+tv 실속형</t>
+        </is>
+      </c>
+      <c r="E59" s="64" t="n">
         <v>470000</v>
       </c>
-      <c r="E9" s="5" t="n">
+    </row>
+    <row r="60">
+      <c r="A60" s="62" t="n">
+        <v>57</v>
+      </c>
+      <c r="B60" s="62" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C60" s="62" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D60" s="63" t="inlineStr">
+        <is>
+          <t>인터넷 500M + U+tv 기본형</t>
+        </is>
+      </c>
+      <c r="E60" s="64" t="n">
         <v>470000</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="62" t="n">
+        <v>58</v>
+      </c>
+      <c r="B61" s="62" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C61" s="62" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D61" s="63" t="inlineStr">
+        <is>
+          <t>인터넷 500M + U+tv 프리미엄</t>
+        </is>
+      </c>
+      <c r="E61" s="64" t="n">
+        <v>470000</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="62" t="n">
+        <v>59</v>
+      </c>
+      <c r="B62" s="62" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C62" s="62" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D62" s="63" t="inlineStr">
+        <is>
+          <t>인터넷 500M + U+tv 프리미엄 VOD</t>
+        </is>
+      </c>
+      <c r="E62" s="64" t="n">
+        <v>470000</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="62" t="n">
+        <v>60</v>
+      </c>
+      <c r="B63" s="62" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C63" s="62" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D63" s="63" t="inlineStr">
+        <is>
+          <t>인터넷 1G + U+tv 실속형</t>
+        </is>
+      </c>
+      <c r="E63" s="64" t="n">
+        <v>470000</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B64" s="62" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C64" s="62" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D64" s="63" t="inlineStr">
+        <is>
+          <t>인터넷 1G + U+tv 기본형</t>
+        </is>
+      </c>
+      <c r="E64" s="64" t="n">
+        <v>470000</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="62" t="n">
+        <v>62</v>
+      </c>
+      <c r="B65" s="62" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C65" s="62" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D65" s="63" t="inlineStr">
+        <is>
+          <t>인터넷 1G + U+tv 프리미엄</t>
+        </is>
+      </c>
+      <c r="E65" s="64" t="n">
+        <v>470000</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="62" t="n">
+        <v>63</v>
+      </c>
+      <c r="B66" s="62" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C66" s="62" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D66" s="63" t="inlineStr">
+        <is>
+          <t>인터넷 1G + U+tv 프리미엄 VOD</t>
+        </is>
+      </c>
+      <c r="E66" s="64" t="n">
+        <v>470000</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6871,1513 +8196,6 @@
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A6:B6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E66"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="54" t="inlineStr">
-        <is>
-          <t>🎁 봉이 사은품 정책 카탈로그 (총 63개 상품)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="55" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B3" s="55" t="inlineStr">
-        <is>
-          <t>통신사</t>
-        </is>
-      </c>
-      <c r="C3" s="55" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="D3" s="55" t="inlineStr">
-        <is>
-          <t>상품 구성</t>
-        </is>
-      </c>
-      <c r="E3" s="55" t="inlineStr">
-        <is>
-          <t>사은품(원)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="56" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="C4" s="56" t="inlineStr">
-        <is>
-          <t>단독</t>
-        </is>
-      </c>
-      <c r="D4" s="57" t="inlineStr">
-        <is>
-          <t>인터넷 100M</t>
-        </is>
-      </c>
-      <c r="E4" s="58" t="n">
-        <v>110000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="56" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="56" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="C5" s="56" t="inlineStr">
-        <is>
-          <t>단독</t>
-        </is>
-      </c>
-      <c r="D5" s="57" t="inlineStr">
-        <is>
-          <t>인터넷 500M</t>
-        </is>
-      </c>
-      <c r="E5" s="58" t="n">
-        <v>170000</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="56" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="56" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="C6" s="56" t="inlineStr">
-        <is>
-          <t>단독</t>
-        </is>
-      </c>
-      <c r="D6" s="57" t="inlineStr">
-        <is>
-          <t>인터넷 1G</t>
-        </is>
-      </c>
-      <c r="E6" s="58" t="n">
-        <v>170000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="56" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="56" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="C7" s="56" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D7" s="57" t="inlineStr">
-        <is>
-          <t>인터넷 100M + B tv 이코노미</t>
-        </is>
-      </c>
-      <c r="E7" s="58" t="n">
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="56" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="56" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="C8" s="56" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D8" s="57" t="inlineStr">
-        <is>
-          <t>인터넷 100M + B tv 스탠다드</t>
-        </is>
-      </c>
-      <c r="E8" s="58" t="n">
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="56" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="56" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="C9" s="56" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D9" s="57" t="inlineStr">
-        <is>
-          <t>인터넷 100M + B tv 올</t>
-        </is>
-      </c>
-      <c r="E9" s="58" t="n">
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="56" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="56" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="C10" s="56" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D10" s="57" t="inlineStr">
-        <is>
-          <t>인터넷 100M + B tv 스탠다드 플러스</t>
-        </is>
-      </c>
-      <c r="E10" s="58" t="n">
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="56" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="56" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="C11" s="56" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D11" s="57" t="inlineStr">
-        <is>
-          <t>인터넷 100M + B tv 올 플러스</t>
-        </is>
-      </c>
-      <c r="E11" s="58" t="n">
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="56" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="56" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="C12" s="56" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D12" s="57" t="inlineStr">
-        <is>
-          <t>인터넷 100M + B tv 스탠다드 넷플릭스</t>
-        </is>
-      </c>
-      <c r="E12" s="58" t="n">
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="56" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="56" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="C13" s="56" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D13" s="57" t="inlineStr">
-        <is>
-          <t>인터넷 100M + B tv 올 넷플릭스</t>
-        </is>
-      </c>
-      <c r="E13" s="58" t="n">
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="56" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="56" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="C14" s="56" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D14" s="57" t="inlineStr">
-        <is>
-          <t>인터넷 100M + B tv 스탠다드 넷플릭스 프리미엄</t>
-        </is>
-      </c>
-      <c r="E14" s="58" t="n">
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="56" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="56" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="C15" s="56" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D15" s="57" t="inlineStr">
-        <is>
-          <t>인터넷 100M + B tv 올 넷플릭스 프리미엄</t>
-        </is>
-      </c>
-      <c r="E15" s="58" t="n">
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="56" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="56" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="C16" s="56" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D16" s="57" t="inlineStr">
-        <is>
-          <t>인터넷 500M + B tv 이코노미</t>
-        </is>
-      </c>
-      <c r="E16" s="58" t="n">
-        <v>430000</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="56" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="56" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="C17" s="56" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D17" s="57" t="inlineStr">
-        <is>
-          <t>인터넷 500M + B tv 스탠다드</t>
-        </is>
-      </c>
-      <c r="E17" s="58" t="n">
-        <v>430000</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="56" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="56" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="C18" s="56" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D18" s="57" t="inlineStr">
-        <is>
-          <t>인터넷 500M + B tv 올</t>
-        </is>
-      </c>
-      <c r="E18" s="58" t="n">
-        <v>430000</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="56" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="56" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="C19" s="56" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D19" s="57" t="inlineStr">
-        <is>
-          <t>인터넷 500M + B tv 스탠다드 플러스</t>
-        </is>
-      </c>
-      <c r="E19" s="58" t="n">
-        <v>430000</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="56" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="56" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="C20" s="56" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D20" s="57" t="inlineStr">
-        <is>
-          <t>인터넷 500M + B tv 올 플러스</t>
-        </is>
-      </c>
-      <c r="E20" s="58" t="n">
-        <v>430000</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="56" t="n">
-        <v>18</v>
-      </c>
-      <c r="B21" s="56" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="C21" s="56" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D21" s="57" t="inlineStr">
-        <is>
-          <t>인터넷 500M + B tv 스탠다드 넷플릭스</t>
-        </is>
-      </c>
-      <c r="E21" s="58" t="n">
-        <v>430000</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="56" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" s="56" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="C22" s="56" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D22" s="57" t="inlineStr">
-        <is>
-          <t>인터넷 500M + B tv 올 넷플릭스</t>
-        </is>
-      </c>
-      <c r="E22" s="58" t="n">
-        <v>430000</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="56" t="n">
-        <v>20</v>
-      </c>
-      <c r="B23" s="56" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="C23" s="56" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D23" s="57" t="inlineStr">
-        <is>
-          <t>인터넷 500M + B tv 스탠다드 넷플릭스 프리미엄</t>
-        </is>
-      </c>
-      <c r="E23" s="58" t="n">
-        <v>430000</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="56" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" s="56" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="C24" s="56" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D24" s="57" t="inlineStr">
-        <is>
-          <t>인터넷 500M + B tv 올 넷플릭스 프리미엄</t>
-        </is>
-      </c>
-      <c r="E24" s="58" t="n">
-        <v>430000</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="56" t="n">
-        <v>22</v>
-      </c>
-      <c r="B25" s="56" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="C25" s="56" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D25" s="57" t="inlineStr">
-        <is>
-          <t>인터넷 1G + B tv 이코노미</t>
-        </is>
-      </c>
-      <c r="E25" s="58" t="n">
-        <v>490000</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="56" t="n">
-        <v>23</v>
-      </c>
-      <c r="B26" s="56" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="C26" s="56" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D26" s="57" t="inlineStr">
-        <is>
-          <t>인터넷 1G + B tv 스탠다드</t>
-        </is>
-      </c>
-      <c r="E26" s="58" t="n">
-        <v>490000</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="56" t="n">
-        <v>24</v>
-      </c>
-      <c r="B27" s="56" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="C27" s="56" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D27" s="57" t="inlineStr">
-        <is>
-          <t>인터넷 1G + B tv 올</t>
-        </is>
-      </c>
-      <c r="E27" s="58" t="n">
-        <v>490000</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="56" t="n">
-        <v>25</v>
-      </c>
-      <c r="B28" s="56" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="C28" s="56" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D28" s="57" t="inlineStr">
-        <is>
-          <t>인터넷 1G + B tv 스탠다드 플러스</t>
-        </is>
-      </c>
-      <c r="E28" s="58" t="n">
-        <v>490000</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="56" t="n">
-        <v>26</v>
-      </c>
-      <c r="B29" s="56" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="C29" s="56" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D29" s="57" t="inlineStr">
-        <is>
-          <t>인터넷 1G + B tv 올 플러스</t>
-        </is>
-      </c>
-      <c r="E29" s="58" t="n">
-        <v>490000</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="56" t="n">
-        <v>27</v>
-      </c>
-      <c r="B30" s="56" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="C30" s="56" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D30" s="57" t="inlineStr">
-        <is>
-          <t>인터넷 1G + B tv 스탠다드 넷플릭스</t>
-        </is>
-      </c>
-      <c r="E30" s="58" t="n">
-        <v>490000</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="56" t="n">
-        <v>28</v>
-      </c>
-      <c r="B31" s="56" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="C31" s="56" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D31" s="57" t="inlineStr">
-        <is>
-          <t>인터넷 1G + B tv 올 넷플릭스</t>
-        </is>
-      </c>
-      <c r="E31" s="58" t="n">
-        <v>490000</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="56" t="n">
-        <v>29</v>
-      </c>
-      <c r="B32" s="56" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="C32" s="56" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D32" s="57" t="inlineStr">
-        <is>
-          <t>인터넷 1G + B tv 스탠다드 넷플릭스 프리미엄</t>
-        </is>
-      </c>
-      <c r="E32" s="58" t="n">
-        <v>490000</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="56" t="n">
-        <v>30</v>
-      </c>
-      <c r="B33" s="56" t="inlineStr">
-        <is>
-          <t>SKT</t>
-        </is>
-      </c>
-      <c r="C33" s="56" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D33" s="57" t="inlineStr">
-        <is>
-          <t>인터넷 1G + B tv 올 넷플릭스 프리미엄</t>
-        </is>
-      </c>
-      <c r="E33" s="58" t="n">
-        <v>490000</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="59" t="n">
-        <v>31</v>
-      </c>
-      <c r="B34" s="59" t="inlineStr">
-        <is>
-          <t>KT</t>
-        </is>
-      </c>
-      <c r="C34" s="59" t="inlineStr">
-        <is>
-          <t>단독</t>
-        </is>
-      </c>
-      <c r="D34" s="60" t="inlineStr">
-        <is>
-          <t>인터넷 100M</t>
-        </is>
-      </c>
-      <c r="E34" s="61" t="n">
-        <v>90000</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="59" t="n">
-        <v>32</v>
-      </c>
-      <c r="B35" s="59" t="inlineStr">
-        <is>
-          <t>KT</t>
-        </is>
-      </c>
-      <c r="C35" s="59" t="inlineStr">
-        <is>
-          <t>단독</t>
-        </is>
-      </c>
-      <c r="D35" s="60" t="inlineStr">
-        <is>
-          <t>인터넷 500M</t>
-        </is>
-      </c>
-      <c r="E35" s="61" t="n">
-        <v>140000</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="59" t="n">
-        <v>33</v>
-      </c>
-      <c r="B36" s="59" t="inlineStr">
-        <is>
-          <t>KT</t>
-        </is>
-      </c>
-      <c r="C36" s="59" t="inlineStr">
-        <is>
-          <t>단독</t>
-        </is>
-      </c>
-      <c r="D36" s="60" t="inlineStr">
-        <is>
-          <t>인터넷 1G</t>
-        </is>
-      </c>
-      <c r="E36" s="61" t="n">
-        <v>140000</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="59" t="n">
-        <v>34</v>
-      </c>
-      <c r="B37" s="59" t="inlineStr">
-        <is>
-          <t>KT</t>
-        </is>
-      </c>
-      <c r="C37" s="59" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D37" s="60" t="inlineStr">
-        <is>
-          <t>인터넷 100M + 지니TV 베이직</t>
-        </is>
-      </c>
-      <c r="E37" s="61" t="n">
-        <v>370000</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="59" t="n">
-        <v>35</v>
-      </c>
-      <c r="B38" s="59" t="inlineStr">
-        <is>
-          <t>KT</t>
-        </is>
-      </c>
-      <c r="C38" s="59" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D38" s="60" t="inlineStr">
-        <is>
-          <t>인터넷 100M + 지니TV 라이트</t>
-        </is>
-      </c>
-      <c r="E38" s="61" t="n">
-        <v>370000</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="59" t="n">
-        <v>36</v>
-      </c>
-      <c r="B39" s="59" t="inlineStr">
-        <is>
-          <t>KT</t>
-        </is>
-      </c>
-      <c r="C39" s="59" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D39" s="60" t="inlineStr">
-        <is>
-          <t>인터넷 100M + 지니TV 에센스</t>
-        </is>
-      </c>
-      <c r="E39" s="61" t="n">
-        <v>370000</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="59" t="n">
-        <v>37</v>
-      </c>
-      <c r="B40" s="59" t="inlineStr">
-        <is>
-          <t>KT</t>
-        </is>
-      </c>
-      <c r="C40" s="59" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D40" s="60" t="inlineStr">
-        <is>
-          <t>인터넷 100M + 지니TV 모든G</t>
-        </is>
-      </c>
-      <c r="E40" s="61" t="n">
-        <v>370000</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="59" t="n">
-        <v>38</v>
-      </c>
-      <c r="B41" s="59" t="inlineStr">
-        <is>
-          <t>KT</t>
-        </is>
-      </c>
-      <c r="C41" s="59" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D41" s="60" t="inlineStr">
-        <is>
-          <t>인터넷 100M + 지니TV 디즈니+모든G</t>
-        </is>
-      </c>
-      <c r="E41" s="61" t="n">
-        <v>370000</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="59" t="n">
-        <v>39</v>
-      </c>
-      <c r="B42" s="59" t="inlineStr">
-        <is>
-          <t>KT</t>
-        </is>
-      </c>
-      <c r="C42" s="59" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D42" s="60" t="inlineStr">
-        <is>
-          <t>인터넷 500M + 지니TV 베이직</t>
-        </is>
-      </c>
-      <c r="E42" s="61" t="n">
-        <v>450000</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="59" t="n">
-        <v>40</v>
-      </c>
-      <c r="B43" s="59" t="inlineStr">
-        <is>
-          <t>KT</t>
-        </is>
-      </c>
-      <c r="C43" s="59" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D43" s="60" t="inlineStr">
-        <is>
-          <t>인터넷 500M + 지니TV 라이트</t>
-        </is>
-      </c>
-      <c r="E43" s="61" t="n">
-        <v>450000</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="59" t="n">
-        <v>41</v>
-      </c>
-      <c r="B44" s="59" t="inlineStr">
-        <is>
-          <t>KT</t>
-        </is>
-      </c>
-      <c r="C44" s="59" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D44" s="60" t="inlineStr">
-        <is>
-          <t>인터넷 500M + 지니TV 에센스</t>
-        </is>
-      </c>
-      <c r="E44" s="61" t="n">
-        <v>450000</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="59" t="n">
-        <v>42</v>
-      </c>
-      <c r="B45" s="59" t="inlineStr">
-        <is>
-          <t>KT</t>
-        </is>
-      </c>
-      <c r="C45" s="59" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D45" s="60" t="inlineStr">
-        <is>
-          <t>인터넷 500M + 지니TV 모든G</t>
-        </is>
-      </c>
-      <c r="E45" s="61" t="n">
-        <v>450000</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="59" t="n">
-        <v>43</v>
-      </c>
-      <c r="B46" s="59" t="inlineStr">
-        <is>
-          <t>KT</t>
-        </is>
-      </c>
-      <c r="C46" s="59" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D46" s="60" t="inlineStr">
-        <is>
-          <t>인터넷 500M + 지니TV 디즈니+모든G</t>
-        </is>
-      </c>
-      <c r="E46" s="61" t="n">
-        <v>450000</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="59" t="n">
-        <v>44</v>
-      </c>
-      <c r="B47" s="59" t="inlineStr">
-        <is>
-          <t>KT</t>
-        </is>
-      </c>
-      <c r="C47" s="59" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D47" s="60" t="inlineStr">
-        <is>
-          <t>인터넷 1G + 지니TV 베이직</t>
-        </is>
-      </c>
-      <c r="E47" s="61" t="n">
-        <v>450000</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="59" t="n">
-        <v>45</v>
-      </c>
-      <c r="B48" s="59" t="inlineStr">
-        <is>
-          <t>KT</t>
-        </is>
-      </c>
-      <c r="C48" s="59" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D48" s="60" t="inlineStr">
-        <is>
-          <t>인터넷 1G + 지니TV 라이트</t>
-        </is>
-      </c>
-      <c r="E48" s="61" t="n">
-        <v>450000</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="59" t="n">
-        <v>46</v>
-      </c>
-      <c r="B49" s="59" t="inlineStr">
-        <is>
-          <t>KT</t>
-        </is>
-      </c>
-      <c r="C49" s="59" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D49" s="60" t="inlineStr">
-        <is>
-          <t>인터넷 1G + 지니TV 에센스</t>
-        </is>
-      </c>
-      <c r="E49" s="61" t="n">
-        <v>450000</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="59" t="n">
-        <v>47</v>
-      </c>
-      <c r="B50" s="59" t="inlineStr">
-        <is>
-          <t>KT</t>
-        </is>
-      </c>
-      <c r="C50" s="59" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D50" s="60" t="inlineStr">
-        <is>
-          <t>인터넷 1G + 지니TV 모든G</t>
-        </is>
-      </c>
-      <c r="E50" s="61" t="n">
-        <v>450000</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="59" t="n">
-        <v>48</v>
-      </c>
-      <c r="B51" s="59" t="inlineStr">
-        <is>
-          <t>KT</t>
-        </is>
-      </c>
-      <c r="C51" s="59" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D51" s="60" t="inlineStr">
-        <is>
-          <t>인터넷 1G + 지니TV 디즈니+모든G</t>
-        </is>
-      </c>
-      <c r="E51" s="61" t="n">
-        <v>450000</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="62" t="n">
-        <v>49</v>
-      </c>
-      <c r="B52" s="62" t="inlineStr">
-        <is>
-          <t>LG U+</t>
-        </is>
-      </c>
-      <c r="C52" s="62" t="inlineStr">
-        <is>
-          <t>단독</t>
-        </is>
-      </c>
-      <c r="D52" s="63" t="inlineStr">
-        <is>
-          <t>인터넷 100M</t>
-        </is>
-      </c>
-      <c r="E52" s="64" t="n">
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="62" t="n">
-        <v>50</v>
-      </c>
-      <c r="B53" s="62" t="inlineStr">
-        <is>
-          <t>LG U+</t>
-        </is>
-      </c>
-      <c r="C53" s="62" t="inlineStr">
-        <is>
-          <t>단독</t>
-        </is>
-      </c>
-      <c r="D53" s="63" t="inlineStr">
-        <is>
-          <t>인터넷 500M</t>
-        </is>
-      </c>
-      <c r="E53" s="64" t="n">
-        <v>230000</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="62" t="n">
-        <v>51</v>
-      </c>
-      <c r="B54" s="62" t="inlineStr">
-        <is>
-          <t>LG U+</t>
-        </is>
-      </c>
-      <c r="C54" s="62" t="inlineStr">
-        <is>
-          <t>단독</t>
-        </is>
-      </c>
-      <c r="D54" s="63" t="inlineStr">
-        <is>
-          <t>인터넷 1G</t>
-        </is>
-      </c>
-      <c r="E54" s="64" t="n">
-        <v>230000</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="62" t="n">
-        <v>52</v>
-      </c>
-      <c r="B55" s="62" t="inlineStr">
-        <is>
-          <t>LG U+</t>
-        </is>
-      </c>
-      <c r="C55" s="62" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D55" s="63" t="inlineStr">
-        <is>
-          <t>인터넷 100M + U+tv 실속형</t>
-        </is>
-      </c>
-      <c r="E55" s="64" t="n">
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="62" t="n">
-        <v>53</v>
-      </c>
-      <c r="B56" s="62" t="inlineStr">
-        <is>
-          <t>LG U+</t>
-        </is>
-      </c>
-      <c r="C56" s="62" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D56" s="63" t="inlineStr">
-        <is>
-          <t>인터넷 100M + U+tv 기본형</t>
-        </is>
-      </c>
-      <c r="E56" s="64" t="n">
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="62" t="n">
-        <v>54</v>
-      </c>
-      <c r="B57" s="62" t="inlineStr">
-        <is>
-          <t>LG U+</t>
-        </is>
-      </c>
-      <c r="C57" s="62" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D57" s="63" t="inlineStr">
-        <is>
-          <t>인터넷 100M + U+tv 프리미엄</t>
-        </is>
-      </c>
-      <c r="E57" s="64" t="n">
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="62" t="n">
-        <v>55</v>
-      </c>
-      <c r="B58" s="62" t="inlineStr">
-        <is>
-          <t>LG U+</t>
-        </is>
-      </c>
-      <c r="C58" s="62" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D58" s="63" t="inlineStr">
-        <is>
-          <t>인터넷 100M + U+tv 프리미엄 VOD</t>
-        </is>
-      </c>
-      <c r="E58" s="64" t="n">
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="62" t="n">
-        <v>56</v>
-      </c>
-      <c r="B59" s="62" t="inlineStr">
-        <is>
-          <t>LG U+</t>
-        </is>
-      </c>
-      <c r="C59" s="62" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D59" s="63" t="inlineStr">
-        <is>
-          <t>인터넷 500M + U+tv 실속형</t>
-        </is>
-      </c>
-      <c r="E59" s="64" t="n">
-        <v>470000</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="62" t="n">
-        <v>57</v>
-      </c>
-      <c r="B60" s="62" t="inlineStr">
-        <is>
-          <t>LG U+</t>
-        </is>
-      </c>
-      <c r="C60" s="62" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D60" s="63" t="inlineStr">
-        <is>
-          <t>인터넷 500M + U+tv 기본형</t>
-        </is>
-      </c>
-      <c r="E60" s="64" t="n">
-        <v>470000</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="62" t="n">
-        <v>58</v>
-      </c>
-      <c r="B61" s="62" t="inlineStr">
-        <is>
-          <t>LG U+</t>
-        </is>
-      </c>
-      <c r="C61" s="62" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D61" s="63" t="inlineStr">
-        <is>
-          <t>인터넷 500M + U+tv 프리미엄</t>
-        </is>
-      </c>
-      <c r="E61" s="64" t="n">
-        <v>470000</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="62" t="n">
-        <v>59</v>
-      </c>
-      <c r="B62" s="62" t="inlineStr">
-        <is>
-          <t>LG U+</t>
-        </is>
-      </c>
-      <c r="C62" s="62" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D62" s="63" t="inlineStr">
-        <is>
-          <t>인터넷 500M + U+tv 프리미엄 VOD</t>
-        </is>
-      </c>
-      <c r="E62" s="64" t="n">
-        <v>470000</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="62" t="n">
-        <v>60</v>
-      </c>
-      <c r="B63" s="62" t="inlineStr">
-        <is>
-          <t>LG U+</t>
-        </is>
-      </c>
-      <c r="C63" s="62" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D63" s="63" t="inlineStr">
-        <is>
-          <t>인터넷 1G + U+tv 실속형</t>
-        </is>
-      </c>
-      <c r="E63" s="64" t="n">
-        <v>470000</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="62" t="n">
-        <v>61</v>
-      </c>
-      <c r="B64" s="62" t="inlineStr">
-        <is>
-          <t>LG U+</t>
-        </is>
-      </c>
-      <c r="C64" s="62" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D64" s="63" t="inlineStr">
-        <is>
-          <t>인터넷 1G + U+tv 기본형</t>
-        </is>
-      </c>
-      <c r="E64" s="64" t="n">
-        <v>470000</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="62" t="n">
-        <v>62</v>
-      </c>
-      <c r="B65" s="62" t="inlineStr">
-        <is>
-          <t>LG U+</t>
-        </is>
-      </c>
-      <c r="C65" s="62" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D65" s="63" t="inlineStr">
-        <is>
-          <t>인터넷 1G + U+tv 프리미엄</t>
-        </is>
-      </c>
-      <c r="E65" s="64" t="n">
-        <v>470000</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="62" t="n">
-        <v>63</v>
-      </c>
-      <c r="B66" s="62" t="inlineStr">
-        <is>
-          <t>LG U+</t>
-        </is>
-      </c>
-      <c r="C66" s="62" t="inlineStr">
-        <is>
-          <t>결합</t>
-        </is>
-      </c>
-      <c r="D66" s="63" t="inlineStr">
-        <is>
-          <t>인터넷 1G + U+tv 프리미엄 VOD</t>
-        </is>
-      </c>
-      <c r="E66" s="64" t="n">
-        <v>470000</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/bongi-calculator-data.xlsx
+++ b/docs/bongi-calculator-data.xlsx
@@ -38,7 +38,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0&quot;원&quot;"/>
   </numFmts>
-  <fonts count="41">
+  <fonts count="42">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -277,8 +277,13 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00888888"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -355,6 +360,11 @@
         <fgColor rgb="00FCE7F3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF7DB"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -382,7 +392,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -504,6 +514,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
